--- a/FFT on froth/data_test_augm_Pb.xlsx
+++ b/FFT on froth/data_test_augm_Pb.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Relavage 4" sheetId="1" r:id="rId1"/>
+    <sheet name="Relavage Pb" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
   <si>
     <t>points</t>
   </si>
@@ -31,6 +31,198 @@
     <t>Zn (%)</t>
   </si>
   <si>
+    <t>rl3_pb2-4-0.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-1.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-10.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-11.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-12.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-13.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-14.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-15.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-16.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-17.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-18.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-19.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-2.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-20.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-21.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-22.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-23.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-24.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-25.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-26.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-27.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-28.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-29.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-3.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-30.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-31.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-32.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-33.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-34.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-35.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-36.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-37.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-38.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-39.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-4.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-40.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-41.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-42.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-43.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-44.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-45.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-46.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-47.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-48.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-49.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-5.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-50.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-51.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-52.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-53.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-54.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-55.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-56.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-57.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-58.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-59.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-6.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-60.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-61.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-62.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-63.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-7.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-8.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb2-4-9.jpg</t>
+  </si>
+  <si>
     <t>rl4_pb12-4-0.jpg</t>
   </si>
   <si>
@@ -254,6 +446,573 @@
   </si>
   <si>
     <t>rl4_pb12-4-9.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-0.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-1.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-10.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-11.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-12.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-13.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-14.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-15.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-16.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-17.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-18.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-19.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-2.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-20.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-21.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-22.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-23.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-24.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-25.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-26.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-27.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-28.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-29.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-3.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-30.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-31.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-32.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-33.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-34.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-35.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-36.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-37.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-38.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-39.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-4.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-40.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-41.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-42.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-43.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-44.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-45.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-46.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-47.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-48.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-49.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-5.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-50.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-51.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-52.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-53.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-54.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-55.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-56.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-57.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-58.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-59.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-6.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-60.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-61.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-62.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-63.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-7.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-8.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb16-4-9.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-0.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-1.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-10.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-11.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-12.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-13.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-14.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-15.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-16.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-17.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-18.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-19.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-2.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-20.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-21.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-22.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-23.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-24.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-25.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-26.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-27.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-28.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-29.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-3.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-30.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-31.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-32.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-33.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-34.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-35.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-36.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-37.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-38.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-39.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-4.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-40.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-41.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-42.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-43.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-44.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-45.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-46.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-47.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-48.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-49.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-5.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-50.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-51.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-52.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-53.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-54.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-55.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-56.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-57.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-58.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-59.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-6.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-60.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-61.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-62.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-7.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-8.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb23-4-9.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-0.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-1.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-10.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-11.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-12.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-13.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-14.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-15.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-16.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-17.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-18.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-19.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-2.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-20.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-21.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-22.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-23.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-24.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-25.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-26.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-27.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-28.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-29.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-3.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-30.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-31.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-32.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-33.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-34.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-35.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-36.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-37.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-38.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-39.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-4.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-40.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-41.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-42.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-43.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-44.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-45.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-46.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-47.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-48.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-49.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-5.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-50.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-51.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-52.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-53.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-54.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-55.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-56.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-57.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-58.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-59.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-6.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-60.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-61.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-7.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-8.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb9-5-9.jpg</t>
   </si>
   <si>
     <t>rl4_pb30-6-0.jpg</t>
@@ -797,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -822,16 +1581,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.132585676652327</v>
+        <v>0.6910966134186318</v>
       </c>
       <c r="C2">
-        <v>11.76431545126247</v>
+        <v>4.763870993431865</v>
       </c>
       <c r="D2">
-        <v>50.10946397784583</v>
+        <v>24.71402233831731</v>
       </c>
       <c r="E2">
-        <v>5.306501078726107</v>
+        <v>1.193366995979883</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -839,16 +1598,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>2.537339332333758</v>
+        <v>1.104979739624584</v>
       </c>
       <c r="C3">
-        <v>10.97602567842005</v>
+        <v>4.082668719150224</v>
       </c>
       <c r="D3">
-        <v>49.9082909476232</v>
+        <v>24.5407481229082</v>
       </c>
       <c r="E3">
-        <v>5.683570285094261</v>
+        <v>1.361255019236155</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -856,16 +1615,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.706077622948325</v>
+        <v>1.721927733928604</v>
       </c>
       <c r="C4">
-        <v>11.42365779796356</v>
+        <v>5.150938793662542</v>
       </c>
       <c r="D4">
-        <v>50.02716110515678</v>
+        <v>24.92795112365341</v>
       </c>
       <c r="E4">
-        <v>5.252945947754871</v>
+        <v>1.687410237436302</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -873,16 +1632,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2.126001514171041</v>
+        <v>0.9293306657125603</v>
       </c>
       <c r="C5">
-        <v>11.56777848375481</v>
+        <v>5.007910372575521</v>
       </c>
       <c r="D5">
-        <v>50.32357312001836</v>
+        <v>24.45156815949694</v>
       </c>
       <c r="E5">
-        <v>5.664200573615976</v>
+        <v>1.090950324418502</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -890,16 +1649,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.878491648032573</v>
+        <v>0.9374805606937416</v>
       </c>
       <c r="C6">
-        <v>11.30107071094802</v>
+        <v>4.387008522830512</v>
       </c>
       <c r="D6">
-        <v>50.34279808634346</v>
+        <v>24.5679834427914</v>
       </c>
       <c r="E6">
-        <v>5.413640522321058</v>
+        <v>2.10660524702416</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -907,16 +1666,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.8916253650592</v>
+        <v>1.628372987314375</v>
       </c>
       <c r="C7">
-        <v>11.18415625313449</v>
+        <v>3.959778592832005</v>
       </c>
       <c r="D7">
-        <v>50.14023280945884</v>
+        <v>24.89211146805589</v>
       </c>
       <c r="E7">
-        <v>5.86870907299561</v>
+        <v>2.558178649468103</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -924,16 +1683,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2.389271909543953</v>
+        <v>1.031401121290753</v>
       </c>
       <c r="C8">
-        <v>11.08217990593586</v>
+        <v>5.169823338451035</v>
       </c>
       <c r="D8">
-        <v>49.64142635079404</v>
+        <v>24.79400714792904</v>
       </c>
       <c r="E8">
-        <v>5.387852647468136</v>
+        <v>1.55026622152836</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -941,16 +1700,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>2.118963312883683</v>
+        <v>2.010555273166861</v>
       </c>
       <c r="C9">
-        <v>11.46602699187608</v>
+        <v>4.124190316475047</v>
       </c>
       <c r="D9">
-        <v>50.24654961423926</v>
+        <v>24.89856441338384</v>
       </c>
       <c r="E9">
-        <v>6.172057032076245</v>
+        <v>1.59260373816383</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -958,16 +1717,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>1.786391399257569</v>
+        <v>1.332431709470527</v>
       </c>
       <c r="C10">
-        <v>11.55513643776378</v>
+        <v>4.397204174295663</v>
       </c>
       <c r="D10">
-        <v>50.01946277108547</v>
+        <v>24.576909749901</v>
       </c>
       <c r="E10">
-        <v>5.955693992996324</v>
+        <v>2.411740143339842</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -975,16 +1734,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>2.317868412578835</v>
+        <v>0.3692651077586361</v>
       </c>
       <c r="C11">
-        <v>11.17076376154797</v>
+        <v>4.27020602818319</v>
       </c>
       <c r="D11">
-        <v>50.06721044573246</v>
+        <v>24.55215566941268</v>
       </c>
       <c r="E11">
-        <v>5.237271594571062</v>
+        <v>2.587360183142512</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -992,16 +1751,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2.612256621412159</v>
+        <v>0.5181674850118507</v>
       </c>
       <c r="C12">
-        <v>11.88220861141427</v>
+        <v>4.676824996280468</v>
       </c>
       <c r="D12">
-        <v>49.66844431745321</v>
+        <v>24.90101560844964</v>
       </c>
       <c r="E12">
-        <v>5.210390749628695</v>
+        <v>2.449821048401386</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1009,16 +1768,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.910502042424648</v>
+        <v>1.511014559094012</v>
       </c>
       <c r="C13">
-        <v>11.36155375093345</v>
+        <v>5.266064449728558</v>
       </c>
       <c r="D13">
-        <v>49.81679806578877</v>
+        <v>24.49964202350787</v>
       </c>
       <c r="E13">
-        <v>5.98012328383958</v>
+        <v>1.438335285185045</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1026,16 +1785,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>2.45867377583341</v>
+        <v>0.8412492599364403</v>
       </c>
       <c r="C14">
-        <v>11.5335717586864</v>
+        <v>5.089566214267114</v>
       </c>
       <c r="D14">
-        <v>50.04193710607617</v>
+        <v>24.61841934159922</v>
       </c>
       <c r="E14">
-        <v>5.764718495682209</v>
+        <v>2.129933819444214</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1043,16 +1802,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>2.501649569462633</v>
+        <v>1.538789623332457</v>
       </c>
       <c r="C15">
-        <v>11.0545724977955</v>
+        <v>5.134735813985144</v>
       </c>
       <c r="D15">
-        <v>49.5200692643355</v>
+        <v>24.89745480054356</v>
       </c>
       <c r="E15">
-        <v>6.01329277312242</v>
+        <v>2.455268078297859</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1060,16 +1819,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>2.482973938219971</v>
+        <v>1.750678322373583</v>
       </c>
       <c r="C16">
-        <v>11.72198719790803</v>
+        <v>4.266623616391734</v>
       </c>
       <c r="D16">
-        <v>50.49267733047383</v>
+        <v>24.80729906132298</v>
       </c>
       <c r="E16">
-        <v>5.758214414978617</v>
+        <v>1.301377265077181</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1077,16 +1836,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>2.413518891186111</v>
+        <v>1.671810369723121</v>
       </c>
       <c r="C17">
-        <v>11.63279309068057</v>
+        <v>4.331354633010342</v>
       </c>
       <c r="D17">
-        <v>49.99411647359847</v>
+        <v>24.62628560549368</v>
       </c>
       <c r="E17">
-        <v>5.855283255381878</v>
+        <v>2.215511137439132</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1094,16 +1853,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>2.143997337624151</v>
+        <v>0.8727202738254839</v>
       </c>
       <c r="C18">
-        <v>11.52773494541039</v>
+        <v>4.343240483332907</v>
       </c>
       <c r="D18">
-        <v>50.09964282366742</v>
+        <v>24.57197047688942</v>
       </c>
       <c r="E18">
-        <v>5.646762671137998</v>
+        <v>1.403024754025719</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1111,16 +1870,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>2.213158118950629</v>
+        <v>0.3428818752563895</v>
       </c>
       <c r="C19">
-        <v>11.08107290443111</v>
+        <v>4.32503938098959</v>
       </c>
       <c r="D19">
-        <v>50.47503644829307</v>
+        <v>24.61732089249733</v>
       </c>
       <c r="E19">
-        <v>6.002567533748007</v>
+        <v>2.43689932788002</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1128,16 +1887,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>2.213618526524777</v>
+        <v>1.008702317277945</v>
       </c>
       <c r="C20">
-        <v>11.90457076961049</v>
+        <v>4.05257230289557</v>
       </c>
       <c r="D20">
-        <v>49.99583843428885</v>
+        <v>24.88568590035424</v>
       </c>
       <c r="E20">
-        <v>5.554632017167833</v>
+        <v>2.668769873015056</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1145,16 +1904,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>2.238873015436042</v>
+        <v>1.706171565140283</v>
       </c>
       <c r="C21">
-        <v>11.68488595893285</v>
+        <v>4.917089784631064</v>
       </c>
       <c r="D21">
-        <v>49.6336271828832</v>
+        <v>24.9034069827223</v>
       </c>
       <c r="E21">
-        <v>5.208704808748985</v>
+        <v>1.194710118054415</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1162,16 +1921,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>2.408771086737818</v>
+        <v>1.54508263833148</v>
       </c>
       <c r="C22">
-        <v>11.83969277004275</v>
+        <v>4.287172023999306</v>
       </c>
       <c r="D22">
-        <v>49.86210462223313</v>
+        <v>24.7845518297938</v>
       </c>
       <c r="E22">
-        <v>5.263861198868478</v>
+        <v>1.516855656661004</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1179,16 +1938,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.715254416920019</v>
+        <v>1.349754753445421</v>
       </c>
       <c r="C23">
-        <v>11.26408542949547</v>
+        <v>4.956969938475142</v>
       </c>
       <c r="D23">
-        <v>49.81202437515596</v>
+        <v>24.61985177730347</v>
       </c>
       <c r="E23">
-        <v>5.845391265342553</v>
+        <v>1.469531864959494</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1196,16 +1955,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>1.99661635411237</v>
+        <v>1.774273879180982</v>
       </c>
       <c r="C24">
-        <v>11.76684829527675</v>
+        <v>4.916737862004853</v>
       </c>
       <c r="D24">
-        <v>50.39735894003307</v>
+        <v>24.72025875286399</v>
       </c>
       <c r="E24">
-        <v>6.152436643560765</v>
+        <v>1.914731329099999</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1213,16 +1972,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>2.140266000708194</v>
+        <v>0.9972965262010457</v>
       </c>
       <c r="C25">
-        <v>11.53903145122204</v>
+        <v>4.377753477749047</v>
       </c>
       <c r="D25">
-        <v>49.97336343114149</v>
+        <v>24.60706857539778</v>
       </c>
       <c r="E25">
-        <v>5.685929891089899</v>
+        <v>1.288844018094579</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1230,16 +1989,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>1.687686268914589</v>
+        <v>1.129042703324198</v>
       </c>
       <c r="C26">
-        <v>11.78312884517083</v>
+        <v>4.393518186518029</v>
       </c>
       <c r="D26">
-        <v>50.41146698221426</v>
+        <v>24.87908755017461</v>
       </c>
       <c r="E26">
-        <v>5.627086287231153</v>
+        <v>2.255402186833322</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1247,16 +2006,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>1.717009430432478</v>
+        <v>1.636320042479295</v>
       </c>
       <c r="C27">
-        <v>11.89265423446957</v>
+        <v>4.666153770073512</v>
       </c>
       <c r="D27">
-        <v>50.12452539634671</v>
+        <v>24.57911097887377</v>
       </c>
       <c r="E27">
-        <v>5.374623069690885</v>
+        <v>2.396603154029276</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1264,16 +2023,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>1.920098905739848</v>
+        <v>1.462677086121733</v>
       </c>
       <c r="C28">
-        <v>11.92499088437951</v>
+        <v>4.222406253899354</v>
       </c>
       <c r="D28">
-        <v>50.31224073139992</v>
+        <v>24.87017367432803</v>
       </c>
       <c r="E28">
-        <v>5.203833305018706</v>
+        <v>2.202654364424656</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1281,16 +2040,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>1.834047846488266</v>
+        <v>1.528407209140802</v>
       </c>
       <c r="C29">
-        <v>11.69978608791926</v>
+        <v>4.829692554449262</v>
       </c>
       <c r="D29">
-        <v>49.99508249635911</v>
+        <v>24.60988400578105</v>
       </c>
       <c r="E29">
-        <v>5.584412575169705</v>
+        <v>2.374206694282609</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1298,16 +2057,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>1.646894337455495</v>
+        <v>0.6567221074512464</v>
       </c>
       <c r="C30">
-        <v>11.45209370074566</v>
+        <v>4.878983373735569</v>
       </c>
       <c r="D30">
-        <v>49.73576514315756</v>
+        <v>24.77427529463407</v>
       </c>
       <c r="E30">
-        <v>5.611641038958341</v>
+        <v>1.9761437402977</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1315,16 +2074,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>2.039660588870633</v>
+        <v>1.70421656609394</v>
       </c>
       <c r="C31">
-        <v>11.3267346374152</v>
+        <v>4.866330280881623</v>
       </c>
       <c r="D31">
-        <v>49.56068053669804</v>
+        <v>24.47355114970464</v>
       </c>
       <c r="E31">
-        <v>6.051218050745781</v>
+        <v>2.001810828866813</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1332,16 +2091,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>2.545171952214045</v>
+        <v>1.354366817006748</v>
       </c>
       <c r="C32">
-        <v>11.33646915075672</v>
+        <v>5.369483720583534</v>
       </c>
       <c r="D32">
-        <v>49.73876357689925</v>
+        <v>24.56045281338513</v>
       </c>
       <c r="E32">
-        <v>5.855679360428841</v>
+        <v>2.34754653147617</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1349,16 +2108,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>2.350424131251002</v>
+        <v>1.611559561083123</v>
       </c>
       <c r="C33">
-        <v>11.39881982874414</v>
+        <v>5.449393991681716</v>
       </c>
       <c r="D33">
-        <v>49.73081557993795</v>
+        <v>24.92712005881549</v>
       </c>
       <c r="E33">
-        <v>5.823379431863728</v>
+        <v>2.270912296313252</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1366,16 +2125,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>2.263125292830063</v>
+        <v>0.6791611273457736</v>
       </c>
       <c r="C34">
-        <v>11.93146466511886</v>
+        <v>4.21100061133381</v>
       </c>
       <c r="D34">
-        <v>50.40494751276539</v>
+        <v>24.64606588741807</v>
       </c>
       <c r="E34">
-        <v>5.980257492660819</v>
+        <v>2.352485784192018</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1383,16 +2142,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>2.460608090783373</v>
+        <v>1.790289018891147</v>
       </c>
       <c r="C35">
-        <v>11.10968481698959</v>
+        <v>5.194118384230896</v>
       </c>
       <c r="D35">
-        <v>49.77869258391987</v>
+        <v>24.57280144481465</v>
       </c>
       <c r="E35">
-        <v>5.442186652924671</v>
+        <v>1.127502646021972</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1400,16 +2159,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>2.336760613357922</v>
+        <v>1.266639258747727</v>
       </c>
       <c r="C36">
-        <v>11.26461892057107</v>
+        <v>4.833246499400562</v>
       </c>
       <c r="D36">
-        <v>49.69135310877743</v>
+        <v>24.60152892858927</v>
       </c>
       <c r="E36">
-        <v>5.760744681801745</v>
+        <v>1.844744753525284</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1417,16 +2176,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>1.647077300315451</v>
+        <v>0.5570584329689932</v>
       </c>
       <c r="C37">
-        <v>11.36936490124326</v>
+        <v>4.364221302270364</v>
       </c>
       <c r="D37">
-        <v>49.6588631131716</v>
+        <v>24.54401167711294</v>
       </c>
       <c r="E37">
-        <v>6.107119178083192</v>
+        <v>2.539426459076867</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1434,16 +2193,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>2.402708271195912</v>
+        <v>0.7063276772635055</v>
       </c>
       <c r="C38">
-        <v>11.12666566585081</v>
+        <v>4.710270415871769</v>
       </c>
       <c r="D38">
-        <v>50.15953605071209</v>
+        <v>24.61714554397031</v>
       </c>
       <c r="E38">
-        <v>5.87566528423826</v>
+        <v>1.863544700359375</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1451,16 +2210,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>2.089294101020809</v>
+        <v>1.193968656658302</v>
       </c>
       <c r="C39">
-        <v>11.67844228440602</v>
+        <v>4.443603631192993</v>
       </c>
       <c r="D39">
-        <v>49.79820867573422</v>
+        <v>24.64810824743509</v>
       </c>
       <c r="E39">
-        <v>5.545832092570683</v>
+        <v>1.194935776900566</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1468,16 +2227,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>1.628805027167867</v>
+        <v>1.781438284758948</v>
       </c>
       <c r="C40">
-        <v>10.97404548909339</v>
+        <v>4.116506740081084</v>
       </c>
       <c r="D40">
-        <v>50.32228100873782</v>
+        <v>24.88661762671732</v>
       </c>
       <c r="E40">
-        <v>5.451334211265965</v>
+        <v>1.411610702432331</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1485,16 +2244,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>2.165150721302085</v>
+        <v>0.7747187185652642</v>
       </c>
       <c r="C41">
-        <v>11.26612736201534</v>
+        <v>5.131997071301438</v>
       </c>
       <c r="D41">
-        <v>50.06445239123947</v>
+        <v>24.78927980000115</v>
       </c>
       <c r="E41">
-        <v>6.164871266694394</v>
+        <v>2.013982799429992</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1502,16 +2261,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>1.788601828886556</v>
+        <v>0.3343589070839098</v>
       </c>
       <c r="C42">
-        <v>11.35909475381928</v>
+        <v>4.501353794571963</v>
       </c>
       <c r="D42">
-        <v>50.05151030861459</v>
+        <v>24.85554953828396</v>
       </c>
       <c r="E42">
-        <v>5.786735084842745</v>
+        <v>1.14847878962531</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1519,16 +2278,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>2.353153605001327</v>
+        <v>0.2628425463214364</v>
       </c>
       <c r="C43">
-        <v>10.97012811489252</v>
+        <v>4.733335773006358</v>
       </c>
       <c r="D43">
-        <v>49.62259055547361</v>
+        <v>24.44786237305382</v>
       </c>
       <c r="E43">
-        <v>5.648963747008399</v>
+        <v>1.185432122384236</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1536,16 +2295,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>2.357442191493831</v>
+        <v>1.947837002776387</v>
       </c>
       <c r="C44">
-        <v>11.34011707371044</v>
+        <v>4.096887999988252</v>
       </c>
       <c r="D44">
-        <v>49.59329487907554</v>
+        <v>24.83550654535689</v>
       </c>
       <c r="E44">
-        <v>5.403779348486061</v>
+        <v>2.635941314731275</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1553,16 +2312,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>2.550602236906782</v>
+        <v>1.038663171261939</v>
       </c>
       <c r="C45">
-        <v>11.17411190483719</v>
+        <v>4.285959602647086</v>
       </c>
       <c r="D45">
-        <v>50.02482152719909</v>
+        <v>24.47927000155376</v>
       </c>
       <c r="E45">
-        <v>5.766374135753863</v>
+        <v>1.776329210013105</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1570,16 +2329,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>2.179535621692559</v>
+        <v>1.006736750186905</v>
       </c>
       <c r="C46">
-        <v>11.90962219306224</v>
+        <v>5.170623132308693</v>
       </c>
       <c r="D46">
-        <v>50.25562848368888</v>
+        <v>24.45742772428565</v>
       </c>
       <c r="E46">
-        <v>5.430791870144284</v>
+        <v>1.608650305848594</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1587,16 +2346,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>2.554266572178664</v>
+        <v>0.5736426360737537</v>
       </c>
       <c r="C47">
-        <v>11.02413712033878</v>
+        <v>5.137038378862544</v>
       </c>
       <c r="D47">
-        <v>50.34937027583666</v>
+        <v>24.92855104010394</v>
       </c>
       <c r="E47">
-        <v>5.612836131275853</v>
+        <v>1.65829736447498</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1604,16 +2363,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>2.165403498064767</v>
+        <v>1.973128126710523</v>
       </c>
       <c r="C48">
-        <v>11.71807220987292</v>
+        <v>4.232797092687666</v>
       </c>
       <c r="D48">
-        <v>50.07065489223314</v>
+        <v>24.89097697138016</v>
       </c>
       <c r="E48">
-        <v>5.802471789051193</v>
+        <v>2.161031794196581</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1621,16 +2380,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>2.58766945180715</v>
+        <v>0.4063699626647419</v>
       </c>
       <c r="C49">
-        <v>11.69745782588626</v>
+        <v>5.459428499545693</v>
       </c>
       <c r="D49">
-        <v>50.21479535835657</v>
+        <v>24.77368398658214</v>
       </c>
       <c r="E49">
-        <v>5.943964630690899</v>
+        <v>1.577676533067385</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1638,16 +2397,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>2.44691392916281</v>
+        <v>0.9393575605667503</v>
       </c>
       <c r="C50">
-        <v>10.98913113862418</v>
+        <v>5.085110006883422</v>
       </c>
       <c r="D50">
-        <v>49.6932575061026</v>
+        <v>24.8411061828776</v>
       </c>
       <c r="E50">
-        <v>5.850502509532658</v>
+        <v>1.269544677855869</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1655,16 +2414,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>2.072210030678422</v>
+        <v>0.5964808315819488</v>
       </c>
       <c r="C51">
-        <v>11.71745449123732</v>
+        <v>5.311299799594016</v>
       </c>
       <c r="D51">
-        <v>49.91491375934132</v>
+        <v>24.50633423491992</v>
       </c>
       <c r="E51">
-        <v>5.204460663635482</v>
+        <v>1.278527722212901</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1672,16 +2431,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>2.589648494674323</v>
+        <v>0.9649125807257501</v>
       </c>
       <c r="C52">
-        <v>11.53071340652984</v>
+        <v>4.887438411767857</v>
       </c>
       <c r="D52">
-        <v>49.89805798391951</v>
+        <v>24.70223085198221</v>
       </c>
       <c r="E52">
-        <v>5.236846844883545</v>
+        <v>2.157163313792588</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1689,16 +2448,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>2.338300210023107</v>
+        <v>1.32851123896407</v>
       </c>
       <c r="C53">
-        <v>11.35912514605941</v>
+        <v>4.471055976639986</v>
       </c>
       <c r="D53">
-        <v>50.05514474585288</v>
+        <v>24.59778622076938</v>
       </c>
       <c r="E53">
-        <v>5.823748703927118</v>
+        <v>1.29865139036978</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1706,16 +2465,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>1.907036088545245</v>
+        <v>1.158278302869968</v>
       </c>
       <c r="C54">
-        <v>11.2000298416147</v>
+        <v>5.079290515334051</v>
       </c>
       <c r="D54">
-        <v>49.65936583510108</v>
+        <v>24.50957505668304</v>
       </c>
       <c r="E54">
-        <v>5.488342193904719</v>
+        <v>1.649261671855332</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1723,16 +2482,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>2.290466180833102</v>
+        <v>0.8989236976271903</v>
       </c>
       <c r="C55">
-        <v>11.89784021666368</v>
+        <v>5.35187984339414</v>
       </c>
       <c r="D55">
-        <v>50.50292121970568</v>
+        <v>24.48488525023961</v>
       </c>
       <c r="E55">
-        <v>5.349192997120544</v>
+        <v>2.024125100605625</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1740,16 +2499,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>2.308508912094092</v>
+        <v>1.837888813166072</v>
       </c>
       <c r="C56">
-        <v>11.53055952097616</v>
+        <v>4.123055674412982</v>
       </c>
       <c r="D56">
-        <v>49.78470791179842</v>
+        <v>24.77321859200997</v>
       </c>
       <c r="E56">
-        <v>5.259608968797219</v>
+        <v>1.479111011796064</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1757,16 +2516,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>2.439147337493739</v>
+        <v>1.766911556568217</v>
       </c>
       <c r="C57">
-        <v>11.15059068933556</v>
+        <v>4.27687520356365</v>
       </c>
       <c r="D57">
-        <v>50.20767510526257</v>
+        <v>24.56163021769649</v>
       </c>
       <c r="E57">
-        <v>6.068800103336187</v>
+        <v>2.631158200750463</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1774,16 +2533,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>1.748843367203323</v>
+        <v>0.3535698420245916</v>
       </c>
       <c r="C58">
-        <v>11.91770844433264</v>
+        <v>4.189589189161594</v>
       </c>
       <c r="D58">
-        <v>49.75725082716347</v>
+        <v>24.72258615365367</v>
       </c>
       <c r="E58">
-        <v>5.20545343232201</v>
+        <v>1.435272894365171</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1791,16 +2550,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>2.446102405274213</v>
+        <v>1.480776437633489</v>
       </c>
       <c r="C59">
-        <v>11.12788447284222</v>
+        <v>4.029003888990555</v>
       </c>
       <c r="D59">
-        <v>49.57147622914436</v>
+        <v>24.62978231702373</v>
       </c>
       <c r="E59">
-        <v>5.639536455591458</v>
+        <v>2.213343364686652</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1808,16 +2567,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>2.406649023411231</v>
+        <v>1.947386217102828</v>
       </c>
       <c r="C60">
-        <v>10.96564808969469</v>
+        <v>4.529411628765335</v>
       </c>
       <c r="D60">
-        <v>49.68618763723985</v>
+        <v>24.46147406557821</v>
       </c>
       <c r="E60">
-        <v>5.180738164473119</v>
+        <v>1.719137771258849</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1825,16 +2584,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>1.834883319215476</v>
+        <v>2.006649303818615</v>
       </c>
       <c r="C61">
-        <v>11.24887489217896</v>
+        <v>4.145307465081962</v>
       </c>
       <c r="D61">
-        <v>49.52260687985892</v>
+        <v>24.8227367049869</v>
       </c>
       <c r="E61">
-        <v>5.834446914615796</v>
+        <v>2.080468447806259</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1842,16 +2601,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>1.822824185730578</v>
+        <v>1.957093756049902</v>
       </c>
       <c r="C62">
-        <v>11.41113635924901</v>
+        <v>4.209553312424677</v>
       </c>
       <c r="D62">
-        <v>50.43045159748677</v>
+        <v>24.88271096193889</v>
       </c>
       <c r="E62">
-        <v>5.754865048754031</v>
+        <v>2.485092536771508</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1859,16 +2618,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>2.087661623277477</v>
+        <v>1.167590442095932</v>
       </c>
       <c r="C63">
-        <v>11.72921895991449</v>
+        <v>5.285159983248686</v>
       </c>
       <c r="D63">
-        <v>49.53208558580166</v>
+        <v>24.93361033441284</v>
       </c>
       <c r="E63">
-        <v>5.596005579065952</v>
+        <v>1.703112779041338</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1876,16 +2635,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>1.904480900849947</v>
+        <v>1.93480171148224</v>
       </c>
       <c r="C64">
-        <v>11.323509047814</v>
+        <v>5.295009324394579</v>
       </c>
       <c r="D64">
-        <v>49.97735780803752</v>
+        <v>24.7429057353087</v>
       </c>
       <c r="E64">
-        <v>5.46142795030922</v>
+        <v>1.770197504499456</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1893,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>2.361788240945652</v>
+        <v>1.239036316111097</v>
       </c>
       <c r="C65">
-        <v>11.02126987222707</v>
+        <v>5.426058007712303</v>
       </c>
       <c r="D65">
-        <v>50.32285604129652</v>
+        <v>24.63834128138473</v>
       </c>
       <c r="E65">
-        <v>5.596309668232536</v>
+        <v>2.350983820326359</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1910,16 +2669,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>2.023800260376194</v>
+        <v>1.758673923454924</v>
       </c>
       <c r="C66">
-        <v>11.39009370143402</v>
+        <v>11.00972346039145</v>
       </c>
       <c r="D66">
-        <v>50.00131606827245</v>
+        <v>49.61538788080363</v>
       </c>
       <c r="E66">
-        <v>6.054599106870247</v>
+        <v>6.751973255628856</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1927,16 +2686,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>2.084243096236656</v>
+        <v>2.172989518046351</v>
       </c>
       <c r="C67">
-        <v>11.80877719935788</v>
+        <v>11.25670052324619</v>
       </c>
       <c r="D67">
-        <v>49.89184661687126</v>
+        <v>49.96410856795394</v>
       </c>
       <c r="E67">
-        <v>5.387991898717066</v>
+        <v>5.420683403212961</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1944,16 +2703,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>2.276304181286844</v>
+        <v>2.075889746337803</v>
       </c>
       <c r="C68">
-        <v>11.23379920803337</v>
+        <v>11.6083317405028</v>
       </c>
       <c r="D68">
-        <v>50.18877962344038</v>
+        <v>49.85941721425816</v>
       </c>
       <c r="E68">
-        <v>5.523568848774308</v>
+        <v>5.987785457489232</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1961,16 +2720,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>2.298964680692454</v>
+        <v>3.265932330259516</v>
       </c>
       <c r="C69">
-        <v>11.61953411123825</v>
+        <v>11.18799689108145</v>
       </c>
       <c r="D69">
-        <v>49.8685672286839</v>
+        <v>49.96085534575136</v>
       </c>
       <c r="E69">
-        <v>6.036305403325263</v>
+        <v>6.435311140130429</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1978,16 +2737,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>2.419404778685588</v>
+        <v>2.191800710906444</v>
       </c>
       <c r="C70">
-        <v>11.6938481668164</v>
+        <v>11.92841546570467</v>
       </c>
       <c r="D70">
-        <v>50.30632317974714</v>
+        <v>49.84030807529466</v>
       </c>
       <c r="E70">
-        <v>5.569497265703237</v>
+        <v>5.778549625323959</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1995,16 +2754,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>2.409378329588209</v>
+        <v>2.509449872450655</v>
       </c>
       <c r="C71">
-        <v>11.52327271371293</v>
+        <v>10.98113615089236</v>
       </c>
       <c r="D71">
-        <v>49.74102337562216</v>
+        <v>49.92244481146446</v>
       </c>
       <c r="E71">
-        <v>5.59655522475679</v>
+        <v>6.498836291743562</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2012,16 +2771,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>2.391500638690468</v>
+        <v>3.095966478172514</v>
       </c>
       <c r="C72">
-        <v>11.1144715689948</v>
+        <v>11.35854764890733</v>
       </c>
       <c r="D72">
-        <v>49.9210644858486</v>
+        <v>49.68083781933206</v>
       </c>
       <c r="E72">
-        <v>5.493361962412835</v>
+        <v>6.248959039533091</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2029,16 +2788,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>2.479441596017134</v>
+        <v>2.946384464437393</v>
       </c>
       <c r="C73">
-        <v>11.39261871145522</v>
+        <v>11.21456510004627</v>
       </c>
       <c r="D73">
-        <v>49.70762534017669</v>
+        <v>49.54556631329744</v>
       </c>
       <c r="E73">
-        <v>5.850395878283528</v>
+        <v>5.623000376831431</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2046,16 +2805,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>2.534851134074033</v>
+        <v>3.322363046190645</v>
       </c>
       <c r="C74">
-        <v>11.80173435638885</v>
+        <v>12.52648395035401</v>
       </c>
       <c r="D74">
-        <v>49.97242184421949</v>
+        <v>49.53241924168568</v>
       </c>
       <c r="E74">
-        <v>5.785325778953128</v>
+        <v>5.413501212149159</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2063,16 +2822,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>1.677839475748251</v>
+        <v>3.134172266010751</v>
       </c>
       <c r="C75">
-        <v>11.19453959878423</v>
+        <v>11.84812566937862</v>
       </c>
       <c r="D75">
-        <v>50.50133305821568</v>
+        <v>49.6584585367291</v>
       </c>
       <c r="E75">
-        <v>5.227752530438709</v>
+        <v>5.942606361124795</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2080,16 +2839,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>2.047483292897565</v>
+        <v>2.841698652309104</v>
       </c>
       <c r="C76">
-        <v>11.41975558597168</v>
+        <v>12.47925242860893</v>
       </c>
       <c r="D76">
-        <v>50.03778368515636</v>
+        <v>49.90979874728364</v>
       </c>
       <c r="E76">
-        <v>5.381718753973117</v>
+        <v>5.604173035891455</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2097,16 +2856,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>2.188437854818983</v>
+        <v>3.060236327656927</v>
       </c>
       <c r="C77">
-        <v>6.43372332116757</v>
+        <v>11.22875203182766</v>
       </c>
       <c r="D77">
-        <v>58.28567405427071</v>
+        <v>49.62093158802119</v>
       </c>
       <c r="E77">
-        <v>1.934505244048848</v>
+        <v>5.924074855249756</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2114,16 +2873,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>1.937265484221866</v>
+        <v>2.005306938573189</v>
       </c>
       <c r="C78">
-        <v>6.411395523411409</v>
+        <v>11.33924130361846</v>
       </c>
       <c r="D78">
-        <v>57.83852899548053</v>
+        <v>49.61657293732835</v>
       </c>
       <c r="E78">
-        <v>1.836398958968576</v>
+        <v>5.589998770379611</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2131,16 +2890,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>2.118910531786271</v>
+        <v>1.736620656273004</v>
       </c>
       <c r="C79">
-        <v>6.080770496079655</v>
+        <v>11.73943337125379</v>
       </c>
       <c r="D79">
-        <v>58.66467895689368</v>
+        <v>49.92877948523923</v>
       </c>
       <c r="E79">
-        <v>1.607213907169858</v>
+        <v>6.348993851752897</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2148,16 +2907,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>2.079728125894555</v>
+        <v>2.495136594749015</v>
       </c>
       <c r="C80">
-        <v>6.543213442743996</v>
+        <v>12.39546927603237</v>
       </c>
       <c r="D80">
-        <v>58.47026719979538</v>
+        <v>49.61471492413204</v>
       </c>
       <c r="E80">
-        <v>1.543855557444437</v>
+        <v>5.766254174257029</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2165,16 +2924,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>2.075054986658444</v>
+        <v>3.081521294562178</v>
       </c>
       <c r="C81">
-        <v>6.140124152215026</v>
+        <v>11.05554083336246</v>
       </c>
       <c r="D81">
-        <v>58.5577897642794</v>
+        <v>49.71246833493442</v>
       </c>
       <c r="E81">
-        <v>2.113279963543858</v>
+        <v>5.374583901014138</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2182,16 +2941,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>2.730830436007648</v>
+        <v>1.762274926035553</v>
       </c>
       <c r="C82">
-        <v>6.535834922019722</v>
+        <v>11.72824156545743</v>
       </c>
       <c r="D82">
-        <v>58.07155437747829</v>
+        <v>49.79250960923417</v>
       </c>
       <c r="E82">
-        <v>1.758734984931957</v>
+        <v>6.73696505011784</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2199,16 +2958,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>2.713489245053678</v>
+        <v>1.654442811901103</v>
       </c>
       <c r="C83">
-        <v>6.819384289569141</v>
+        <v>11.11112319910926</v>
       </c>
       <c r="D83">
-        <v>58.52853653122266</v>
+        <v>49.85673518966585</v>
       </c>
       <c r="E83">
-        <v>1.69407317920719</v>
+        <v>5.479626792600229</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2216,16 +2975,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>2.063972372063259</v>
+        <v>2.587396324619689</v>
       </c>
       <c r="C84">
-        <v>6.555217232163035</v>
+        <v>10.98969981643416</v>
       </c>
       <c r="D84">
-        <v>58.26847023870804</v>
+        <v>49.91243335786594</v>
       </c>
       <c r="E84">
-        <v>1.826643729965951</v>
+        <v>6.461287885079238</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2233,16 +2992,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>2.736439744310417</v>
+        <v>3.218172076130322</v>
       </c>
       <c r="C85">
-        <v>6.725872329324926</v>
+        <v>11.50253720243339</v>
       </c>
       <c r="D85">
-        <v>57.92982883894955</v>
+        <v>49.75125033085737</v>
       </c>
       <c r="E85">
-        <v>2.166178302369934</v>
+        <v>5.249861279069092</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2250,16 +3009,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>1.897641568458767</v>
+        <v>2.882534681852165</v>
       </c>
       <c r="C86">
-        <v>5.989262997609286</v>
+        <v>11.80315390805036</v>
       </c>
       <c r="D86">
-        <v>58.39666653828818</v>
+        <v>49.71617332155319</v>
       </c>
       <c r="E86">
-        <v>1.878293751828943</v>
+        <v>5.417580065678095</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2267,16 +3026,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>1.801690761416662</v>
+        <v>3.204505489670303</v>
       </c>
       <c r="C87">
-        <v>6.381512688420292</v>
+        <v>12.2191534776144</v>
       </c>
       <c r="D87">
-        <v>58.26848635992619</v>
+        <v>49.9162572445829</v>
       </c>
       <c r="E87">
-        <v>1.609849410300025</v>
+        <v>6.199760901495151</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2284,16 +3043,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>2.186357394047313</v>
+        <v>2.952669093576499</v>
       </c>
       <c r="C88">
-        <v>6.341307322339748</v>
+        <v>11.41521207689273</v>
       </c>
       <c r="D88">
-        <v>58.25627942423382</v>
+        <v>49.67050183659281</v>
       </c>
       <c r="E88">
-        <v>1.475773928166081</v>
+        <v>5.435590199114602</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2301,16 +3060,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>2.332349362995538</v>
+        <v>2.508464385221374</v>
       </c>
       <c r="C89">
-        <v>6.466614815910667</v>
+        <v>11.36468084935463</v>
       </c>
       <c r="D89">
-        <v>57.78477368261928</v>
+        <v>49.63246728943543</v>
       </c>
       <c r="E89">
-        <v>1.63967143006212</v>
+        <v>5.826909310185523</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2318,16 +3077,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>2.359299444476808</v>
+        <v>2.630147211310119</v>
       </c>
       <c r="C90">
-        <v>5.940013761859865</v>
+        <v>11.02555381952847</v>
       </c>
       <c r="D90">
-        <v>58.16044828972429</v>
+        <v>49.76072712990697</v>
       </c>
       <c r="E90">
-        <v>1.313470496942738</v>
+        <v>5.215155904204023</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2335,16 +3094,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>2.065714072972674</v>
+        <v>1.864106803059773</v>
       </c>
       <c r="C91">
-        <v>6.026484467701012</v>
+        <v>12.01917815384592</v>
       </c>
       <c r="D91">
-        <v>58.14637670460739</v>
+        <v>49.58270956815955</v>
       </c>
       <c r="E91">
-        <v>1.388268145623842</v>
+        <v>6.710352151571093</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2352,16 +3111,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>2.333478884319693</v>
+        <v>2.251515556997563</v>
       </c>
       <c r="C92">
-        <v>6.173704332360755</v>
+        <v>12.31798767697917</v>
       </c>
       <c r="D92">
-        <v>58.11525116463682</v>
+        <v>49.86845595160038</v>
       </c>
       <c r="E92">
-        <v>1.511514763828793</v>
+        <v>6.323432888085616</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2369,16 +3128,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>2.530628946292211</v>
+        <v>2.409610040205911</v>
       </c>
       <c r="C93">
-        <v>6.040758827225046</v>
+        <v>11.33796186621688</v>
       </c>
       <c r="D93">
-        <v>57.82272285925489</v>
+        <v>49.69180804428018</v>
       </c>
       <c r="E93">
-        <v>2.058656908080644</v>
+        <v>5.978637220900217</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2386,16 +3145,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>1.841898052396026</v>
+        <v>3.378269216239991</v>
       </c>
       <c r="C94">
-        <v>6.391094272715305</v>
+        <v>11.80967089793802</v>
       </c>
       <c r="D94">
-        <v>58.21703577297269</v>
+        <v>49.95765589150324</v>
       </c>
       <c r="E94">
-        <v>1.382423833144337</v>
+        <v>6.312871019688477</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2403,16 +3162,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>2.420393977942213</v>
+        <v>2.702576162997715</v>
       </c>
       <c r="C95">
-        <v>6.63536200924553</v>
+        <v>12.43439581894743</v>
       </c>
       <c r="D95">
-        <v>57.97697973120376</v>
+        <v>49.92956699345293</v>
       </c>
       <c r="E95">
-        <v>1.564606481983848</v>
+        <v>5.609249604706758</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2420,16 +3179,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>2.152870312097507</v>
+        <v>2.256359985870479</v>
       </c>
       <c r="C96">
-        <v>5.974900922041064</v>
+        <v>11.4163406465007</v>
       </c>
       <c r="D96">
-        <v>57.86519888086509</v>
+        <v>50.01511198258392</v>
       </c>
       <c r="E96">
-        <v>1.724429787575862</v>
+        <v>5.252388847110002</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2437,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>2.246917338635977</v>
+        <v>2.704932468303032</v>
       </c>
       <c r="C97">
-        <v>6.85747667235725</v>
+        <v>10.99153767626337</v>
       </c>
       <c r="D97">
-        <v>58.05167382594554</v>
+        <v>49.64539121923733</v>
       </c>
       <c r="E97">
-        <v>1.447127795820892</v>
+        <v>6.37798610766925</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2454,16 +3213,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>1.967337415904437</v>
+        <v>2.178820440746949</v>
       </c>
       <c r="C98">
-        <v>6.094244061081596</v>
+        <v>12.42346037873812</v>
       </c>
       <c r="D98">
-        <v>58.66239205375774</v>
+        <v>49.63401409441549</v>
       </c>
       <c r="E98">
-        <v>1.326814861536144</v>
+        <v>6.083586466238842</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2471,16 +3230,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>2.618992094539791</v>
+        <v>1.825588798756315</v>
       </c>
       <c r="C99">
-        <v>6.450891677794551</v>
+        <v>10.98895906765944</v>
       </c>
       <c r="D99">
-        <v>57.95514427073004</v>
+        <v>49.91443247734595</v>
       </c>
       <c r="E99">
-        <v>1.883827482764261</v>
+        <v>6.495896876845761</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2488,16 +3247,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>2.315425960950801</v>
+        <v>2.062167340003145</v>
       </c>
       <c r="C100">
-        <v>6.377797431595619</v>
+        <v>11.9318966920568</v>
       </c>
       <c r="D100">
-        <v>58.28879687689553</v>
+        <v>49.52348897865348</v>
       </c>
       <c r="E100">
-        <v>2.006935454835229</v>
+        <v>5.417293865851526</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2505,16 +3264,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>2.616149561521791</v>
+        <v>2.744835210391791</v>
       </c>
       <c r="C101">
-        <v>6.270813017670968</v>
+        <v>11.6605696177611</v>
       </c>
       <c r="D101">
-        <v>57.98715092149898</v>
+        <v>49.66710978819374</v>
       </c>
       <c r="E101">
-        <v>1.895624573706583</v>
+        <v>6.439877557419877</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2522,16 +3281,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>2.134497605409225</v>
+        <v>2.668179059250964</v>
       </c>
       <c r="C102">
-        <v>6.840650472916998</v>
+        <v>12.44182198314578</v>
       </c>
       <c r="D102">
-        <v>58.42447426204892</v>
+        <v>49.972877934713</v>
       </c>
       <c r="E102">
-        <v>1.264757308936744</v>
+        <v>6.378399002788143</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2539,16 +3298,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>2.706674441687877</v>
+        <v>3.121183175321729</v>
       </c>
       <c r="C103">
-        <v>6.671541110037988</v>
+        <v>11.68803121979877</v>
       </c>
       <c r="D103">
-        <v>58.43714913500077</v>
+        <v>49.94339214727419</v>
       </c>
       <c r="E103">
-        <v>2.082044401324414</v>
+        <v>5.661682919992861</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2556,16 +3315,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>2.368735082405919</v>
+        <v>2.011263373796566</v>
       </c>
       <c r="C104">
-        <v>5.982350635473425</v>
+        <v>12.00482059315108</v>
       </c>
       <c r="D104">
-        <v>58.66264063620014</v>
+        <v>49.71061348873186</v>
       </c>
       <c r="E104">
-        <v>2.176368939373292</v>
+        <v>5.962932376707165</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2573,16 +3332,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>1.865315039359951</v>
+        <v>1.796966693259302</v>
       </c>
       <c r="C105">
-        <v>6.723476170738772</v>
+        <v>12.30400053175172</v>
       </c>
       <c r="D105">
-        <v>58.55870607906998</v>
+        <v>49.61744837392659</v>
       </c>
       <c r="E105">
-        <v>1.287821532826102</v>
+        <v>6.260096024880204</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2590,16 +3349,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>1.835168003584824</v>
+        <v>1.72944370172914</v>
       </c>
       <c r="C106">
-        <v>5.98844158092017</v>
+        <v>12.0116090039796</v>
       </c>
       <c r="D106">
-        <v>57.93304080405034</v>
+        <v>49.71159617486887</v>
       </c>
       <c r="E106">
-        <v>1.290029484632856</v>
+        <v>6.593776662374715</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2607,16 +3366,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>1.806734628885449</v>
+        <v>2.394576988860174</v>
       </c>
       <c r="C107">
-        <v>6.744218542000234</v>
+        <v>11.15666027013388</v>
       </c>
       <c r="D107">
-        <v>57.86439730365385</v>
+        <v>49.63578051279014</v>
       </c>
       <c r="E107">
-        <v>2.062889616633658</v>
+        <v>5.654773346352575</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2624,16 +3383,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>2.269009739154742</v>
+        <v>1.930772591479929</v>
       </c>
       <c r="C108">
-        <v>6.207935263752752</v>
+        <v>10.95499391238927</v>
       </c>
       <c r="D108">
-        <v>57.92672803483514</v>
+        <v>49.88824967620943</v>
       </c>
       <c r="E108">
-        <v>2.230247178105152</v>
+        <v>6.344004427126598</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2641,16 +3400,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>2.08908976926132</v>
+        <v>3.231608750374234</v>
       </c>
       <c r="C109">
-        <v>5.977109370422077</v>
+        <v>12.00198181940126</v>
       </c>
       <c r="D109">
-        <v>58.54465599037785</v>
+        <v>49.70010403528211</v>
       </c>
       <c r="E109">
-        <v>1.88270727713549</v>
+        <v>6.537304923097709</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2658,16 +3417,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>1.79869794414204</v>
+        <v>2.269360468506855</v>
       </c>
       <c r="C110">
-        <v>6.315169775623509</v>
+        <v>11.71043036524099</v>
       </c>
       <c r="D110">
-        <v>58.32769090902396</v>
+        <v>50.00264047576028</v>
       </c>
       <c r="E110">
-        <v>1.647240019782376</v>
+        <v>5.840997308102284</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2675,16 +3434,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>1.956446178469014</v>
+        <v>3.304470330064798</v>
       </c>
       <c r="C111">
-        <v>6.828869182723283</v>
+        <v>11.61354007575827</v>
       </c>
       <c r="D111">
-        <v>58.10148254202564</v>
+        <v>49.52064125937432</v>
       </c>
       <c r="E111">
-        <v>1.701982243960605</v>
+        <v>6.230828806007919</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2692,16 +3451,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>1.788227750318649</v>
+        <v>2.012583649075368</v>
       </c>
       <c r="C112">
-        <v>6.729232560001302</v>
+        <v>12.15232526268625</v>
       </c>
       <c r="D112">
-        <v>58.19719438436656</v>
+        <v>49.82356097372138</v>
       </c>
       <c r="E112">
-        <v>1.913874589275491</v>
+        <v>6.758309244936363</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2709,16 +3468,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>2.503634133149952</v>
+        <v>2.527101910709775</v>
       </c>
       <c r="C113">
-        <v>6.653507786224035</v>
+        <v>12.46167411287121</v>
       </c>
       <c r="D113">
-        <v>58.62842186124754</v>
+        <v>49.72689314506541</v>
       </c>
       <c r="E113">
-        <v>1.840957998419836</v>
+        <v>5.342553654547321</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2726,16 +3485,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>2.470137577383678</v>
+        <v>1.974364929343246</v>
       </c>
       <c r="C114">
-        <v>6.141597647998183</v>
+        <v>11.73700367826151</v>
       </c>
       <c r="D114">
-        <v>58.47531280866521</v>
+        <v>50.00000698752546</v>
       </c>
       <c r="E114">
-        <v>1.638046096511096</v>
+        <v>5.798305834647715</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2743,16 +3502,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>2.128394647553976</v>
+        <v>1.890821094382233</v>
       </c>
       <c r="C115">
-        <v>6.779074139509236</v>
+        <v>11.57499350216571</v>
       </c>
       <c r="D115">
-        <v>58.61524989611426</v>
+        <v>49.58298053433006</v>
       </c>
       <c r="E115">
-        <v>1.774088959625817</v>
+        <v>5.882637841230932</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2760,16 +3519,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>1.820229121452178</v>
+        <v>2.569098836476686</v>
       </c>
       <c r="C116">
-        <v>5.953897312211624</v>
+        <v>11.33090374067098</v>
       </c>
       <c r="D116">
-        <v>58.73970214238442</v>
+        <v>49.8552756077009</v>
       </c>
       <c r="E116">
-        <v>1.45879935148826</v>
+        <v>5.808754163862197</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2777,16 +3536,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>1.821694253199538</v>
+        <v>2.562614609329867</v>
       </c>
       <c r="C117">
-        <v>6.484972314099949</v>
+        <v>12.24779141143398</v>
       </c>
       <c r="D117">
-        <v>57.92107774108187</v>
+        <v>49.85236891113179</v>
       </c>
       <c r="E117">
-        <v>1.474541140630652</v>
+        <v>6.586124323568763</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2794,16 +3553,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>2.18368256568086</v>
+        <v>2.893351167096012</v>
       </c>
       <c r="C118">
-        <v>6.157285891474455</v>
+        <v>10.96566172001431</v>
       </c>
       <c r="D118">
-        <v>58.67661936800566</v>
+        <v>49.60858454568619</v>
       </c>
       <c r="E118">
-        <v>2.120537627057808</v>
+        <v>6.767942961289603</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2811,16 +3570,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>2.573949268783696</v>
+        <v>3.05568212381206</v>
       </c>
       <c r="C119">
-        <v>6.716759583722655</v>
+        <v>12.01387362136073</v>
       </c>
       <c r="D119">
-        <v>58.73664594738536</v>
+        <v>49.91506708970081</v>
       </c>
       <c r="E119">
-        <v>2.0895610979413</v>
+        <v>6.139556907529436</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2828,16 +3587,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>2.16765989565417</v>
+        <v>1.943216546231971</v>
       </c>
       <c r="C120">
-        <v>6.105226561360054</v>
+        <v>10.99451574966663</v>
       </c>
       <c r="D120">
-        <v>58.07343126398364</v>
+        <v>49.74096677865718</v>
       </c>
       <c r="E120">
-        <v>1.464076761392544</v>
+        <v>5.252146062320888</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2845,16 +3604,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>2.19273300646966</v>
+        <v>2.958267771115754</v>
       </c>
       <c r="C121">
-        <v>6.017604124190254</v>
+        <v>11.96803227398549</v>
       </c>
       <c r="D121">
-        <v>58.60265731042617</v>
+        <v>49.71206037750419</v>
       </c>
       <c r="E121">
-        <v>1.994887949286994</v>
+        <v>6.723227524558613</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2862,16 +3621,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>1.988609587802487</v>
+        <v>3.112866817320568</v>
       </c>
       <c r="C122">
-        <v>6.519099429508313</v>
+        <v>11.06594953730875</v>
       </c>
       <c r="D122">
-        <v>58.70849221123782</v>
+        <v>49.7870738785269</v>
       </c>
       <c r="E122">
-        <v>1.337470802644146</v>
+        <v>6.536591737459584</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2879,16 +3638,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>2.331626600292686</v>
+        <v>2.666082794029839</v>
       </c>
       <c r="C123">
-        <v>6.370940356957885</v>
+        <v>11.40071494372539</v>
       </c>
       <c r="D123">
-        <v>57.82948511343176</v>
+        <v>49.52536836446313</v>
       </c>
       <c r="E123">
-        <v>1.420352224452168</v>
+        <v>5.345720852929809</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2896,16 +3655,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>2.476221575194816</v>
+        <v>2.303544380145841</v>
       </c>
       <c r="C124">
-        <v>6.46167255652868</v>
+        <v>12.36762481389716</v>
       </c>
       <c r="D124">
-        <v>58.35693834416141</v>
+        <v>49.59996210911695</v>
       </c>
       <c r="E124">
-        <v>1.324999633283022</v>
+        <v>6.217325070634687</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2913,16 +3672,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>2.390264876418442</v>
+        <v>2.337602651790638</v>
       </c>
       <c r="C125">
-        <v>6.001744136171586</v>
+        <v>11.48672562528166</v>
       </c>
       <c r="D125">
-        <v>58.24345816467299</v>
+        <v>49.52290828710395</v>
       </c>
       <c r="E125">
-        <v>1.587262152282344</v>
+        <v>6.03989142831464</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2930,16 +3689,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>2.599766070417758</v>
+        <v>2.876811835105506</v>
       </c>
       <c r="C126">
-        <v>6.850551084068264</v>
+        <v>11.20389660651462</v>
       </c>
       <c r="D126">
-        <v>57.87706998235861</v>
+        <v>49.85246608913797</v>
       </c>
       <c r="E126">
-        <v>2.072531586612362</v>
+        <v>5.183556471181972</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2947,16 +3706,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>2.079067764576321</v>
+        <v>2.78514871761542</v>
       </c>
       <c r="C127">
-        <v>6.393158894501126</v>
+        <v>11.67423893057189</v>
       </c>
       <c r="D127">
-        <v>58.00244464235023</v>
+        <v>49.70418518397964</v>
       </c>
       <c r="E127">
-        <v>2.118003623857415</v>
+        <v>5.505221285570581</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2964,16 +3723,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>2.268509486614305</v>
+        <v>2.252866594541075</v>
       </c>
       <c r="C128">
-        <v>6.11624186239199</v>
+        <v>12.11463776498482</v>
       </c>
       <c r="D128">
-        <v>58.02680468003737</v>
+        <v>49.95932372653513</v>
       </c>
       <c r="E128">
-        <v>1.504804136818714</v>
+        <v>5.512843270323266</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2981,16 +3740,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>2.407054864451454</v>
+        <v>2.920475635746648</v>
       </c>
       <c r="C129">
-        <v>6.151710577814762</v>
+        <v>12.19230643036422</v>
       </c>
       <c r="D129">
-        <v>58.66895501199483</v>
+        <v>49.69420967531891</v>
       </c>
       <c r="E129">
-        <v>1.328482189151187</v>
+        <v>5.49495477606496</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2998,16 +3757,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>2.614736930181554</v>
+        <v>2.184327609675141</v>
       </c>
       <c r="C130">
-        <v>6.065350264279437</v>
+        <v>12.16854720326707</v>
       </c>
       <c r="D130">
-        <v>58.6799120370415</v>
+        <v>49.87104948292875</v>
       </c>
       <c r="E130">
-        <v>1.887654709272717</v>
+        <v>6.621389012593198</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3015,16 +3774,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>2.023428440312228</v>
+        <v>3.070560288560597</v>
       </c>
       <c r="C131">
-        <v>6.174807651409558</v>
+        <v>11.5829660579672</v>
       </c>
       <c r="D131">
-        <v>58.70169511542573</v>
+        <v>49.60783299288185</v>
       </c>
       <c r="E131">
-        <v>1.39632395756456</v>
+        <v>5.30905135328976</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3032,16 +3791,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>2.385924652794894</v>
+        <v>2.936954651546636</v>
       </c>
       <c r="C132">
-        <v>5.980020446789928</v>
+        <v>10.96876726280565</v>
       </c>
       <c r="D132">
-        <v>58.69819952336466</v>
+        <v>49.61122529596916</v>
       </c>
       <c r="E132">
-        <v>2.21548794692009</v>
+        <v>6.178152727702106</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3049,16 +3808,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>2.109859973881207</v>
+        <v>3.361473526535861</v>
       </c>
       <c r="C133">
-        <v>6.100073566134963</v>
+        <v>12.25345929691733</v>
       </c>
       <c r="D133">
-        <v>58.32836198556691</v>
+        <v>49.8616519857209</v>
       </c>
       <c r="E133">
-        <v>1.41254322712046</v>
+        <v>5.423727915833932</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3066,16 +3825,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>2.717827016454173</v>
+        <v>2.385702275061901</v>
       </c>
       <c r="C134">
-        <v>6.663965027251369</v>
+        <v>12.37413092109668</v>
       </c>
       <c r="D134">
-        <v>58.16307122007034</v>
+        <v>50.00574239508806</v>
       </c>
       <c r="E134">
-        <v>1.578673455618509</v>
+        <v>5.621044722265347</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3083,16 +3842,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>2.394946126330673</v>
+        <v>2.775979919246327</v>
       </c>
       <c r="C135">
-        <v>6.19926683386976</v>
+        <v>10.95444505969403</v>
       </c>
       <c r="D135">
-        <v>58.34041501982858</v>
+        <v>49.9995325859105</v>
       </c>
       <c r="E135">
-        <v>1.401061001369104</v>
+        <v>5.409577000766483</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3100,16 +3859,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>2.397697198731986</v>
+        <v>3.241745461616517</v>
       </c>
       <c r="C136">
-        <v>6.450839972033359</v>
+        <v>11.70229092686278</v>
       </c>
       <c r="D136">
-        <v>58.3970997309811</v>
+        <v>49.92020610523126</v>
       </c>
       <c r="E136">
-        <v>1.378827425611982</v>
+        <v>6.247906141414904</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3117,16 +3876,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>2.084259816807917</v>
+        <v>1.71917365851092</v>
       </c>
       <c r="C137">
-        <v>6.384199288009591</v>
+        <v>11.82080630857218</v>
       </c>
       <c r="D137">
-        <v>58.11723861551194</v>
+        <v>49.63762683409208</v>
       </c>
       <c r="E137">
-        <v>2.061398138657708</v>
+        <v>5.841882006610105</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3134,16 +3893,4317 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>2.771015028714437</v>
+        <v>2.324216863202198</v>
       </c>
       <c r="C138">
-        <v>6.542435947865839</v>
+        <v>11.72617861517919</v>
       </c>
       <c r="D138">
-        <v>58.52541377258344</v>
+        <v>49.6981362489805</v>
       </c>
       <c r="E138">
-        <v>1.649395197881069</v>
+        <v>6.42792553048096</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139">
+        <v>2.545686032748241</v>
+      </c>
+      <c r="C139">
+        <v>11.55429878985532</v>
+      </c>
+      <c r="D139">
+        <v>49.8524245344809</v>
+      </c>
+      <c r="E139">
+        <v>5.838760956346185</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140">
+        <v>3.170877347154075</v>
+      </c>
+      <c r="C140">
+        <v>11.12763025492151</v>
+      </c>
+      <c r="D140">
+        <v>49.77864264663074</v>
+      </c>
+      <c r="E140">
+        <v>6.721183547278813</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141">
+        <v>4.377652841018962</v>
+      </c>
+      <c r="C141">
+        <v>18.26887947869091</v>
+      </c>
+      <c r="D141">
+        <v>23.79283259565546</v>
+      </c>
+      <c r="E141">
+        <v>7.600985817971908</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142">
+        <v>3.751122532857558</v>
+      </c>
+      <c r="C142">
+        <v>18.41954046982333</v>
+      </c>
+      <c r="D142">
+        <v>23.47542351392672</v>
+      </c>
+      <c r="E142">
+        <v>7.660142927933089</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143">
+        <v>4.354800733059468</v>
+      </c>
+      <c r="C143">
+        <v>17.50172258228503</v>
+      </c>
+      <c r="D143">
+        <v>23.5531063622984</v>
+      </c>
+      <c r="E143">
+        <v>7.633334496960284</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144">
+        <v>4.732374803842726</v>
+      </c>
+      <c r="C144">
+        <v>18.08086489653769</v>
+      </c>
+      <c r="D144">
+        <v>23.64658214532216</v>
+      </c>
+      <c r="E144">
+        <v>7.785034736586051</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145">
+        <v>3.189758196167511</v>
+      </c>
+      <c r="C145">
+        <v>16.94452952173991</v>
+      </c>
+      <c r="D145">
+        <v>23.83781115382009</v>
+      </c>
+      <c r="E145">
+        <v>7.457630357775336</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146">
+        <v>3.006396646596667</v>
+      </c>
+      <c r="C146">
+        <v>17.38971586688543</v>
+      </c>
+      <c r="D146">
+        <v>23.46715406441969</v>
+      </c>
+      <c r="E146">
+        <v>6.701309956528932</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147">
+        <v>4.565980204850846</v>
+      </c>
+      <c r="C147">
+        <v>18.19807087398815</v>
+      </c>
+      <c r="D147">
+        <v>23.68636533774857</v>
+      </c>
+      <c r="E147">
+        <v>6.761196843906624</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148">
+        <v>4.694482496939849</v>
+      </c>
+      <c r="C148">
+        <v>17.86093825825774</v>
+      </c>
+      <c r="D148">
+        <v>23.73869484084042</v>
+      </c>
+      <c r="E148">
+        <v>7.069652139972762</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149">
+        <v>3.914268680211344</v>
+      </c>
+      <c r="C149">
+        <v>17.42516022227188</v>
+      </c>
+      <c r="D149">
+        <v>23.56983733977083</v>
+      </c>
+      <c r="E149">
+        <v>6.94938848439408</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150">
+        <v>4.169778972301858</v>
+      </c>
+      <c r="C150">
+        <v>17.41973100719951</v>
+      </c>
+      <c r="D150">
+        <v>23.51766573346331</v>
+      </c>
+      <c r="E150">
+        <v>7.368392623712647</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151">
+        <v>4.387590584288226</v>
+      </c>
+      <c r="C151">
+        <v>18.36588501754505</v>
+      </c>
+      <c r="D151">
+        <v>23.53529595298188</v>
+      </c>
+      <c r="E151">
+        <v>7.005711518245795</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152">
+        <v>3.057106451349773</v>
+      </c>
+      <c r="C152">
+        <v>17.27640578412299</v>
+      </c>
+      <c r="D152">
+        <v>23.61818769427441</v>
+      </c>
+      <c r="E152">
+        <v>7.168293782902802</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153">
+        <v>3.76956522748721</v>
+      </c>
+      <c r="C153">
+        <v>17.29368080929436</v>
+      </c>
+      <c r="D153">
+        <v>23.47626868791793</v>
+      </c>
+      <c r="E153">
+        <v>7.336044142025813</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154">
+        <v>3.842028640615065</v>
+      </c>
+      <c r="C154">
+        <v>17.54452787697338</v>
+      </c>
+      <c r="D154">
+        <v>23.75622840693863</v>
+      </c>
+      <c r="E154">
+        <v>7.745655683915223</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155">
+        <v>4.434831819530427</v>
+      </c>
+      <c r="C155">
+        <v>18.17325173501407</v>
+      </c>
+      <c r="D155">
+        <v>23.44054572860734</v>
+      </c>
+      <c r="E155">
+        <v>7.395909992028701</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156">
+        <v>4.052137206199892</v>
+      </c>
+      <c r="C156">
+        <v>17.9762076270389</v>
+      </c>
+      <c r="D156">
+        <v>23.92546661628327</v>
+      </c>
+      <c r="E156">
+        <v>7.218375924573863</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157">
+        <v>4.19273609806242</v>
+      </c>
+      <c r="C157">
+        <v>18.26688856315625</v>
+      </c>
+      <c r="D157">
+        <v>23.91403600834082</v>
+      </c>
+      <c r="E157">
+        <v>7.508049809476669</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158">
+        <v>3.964835859025783</v>
+      </c>
+      <c r="C158">
+        <v>17.67277111555176</v>
+      </c>
+      <c r="D158">
+        <v>23.63858955352264</v>
+      </c>
+      <c r="E158">
+        <v>7.908715804003084</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159">
+        <v>3.252643656672613</v>
+      </c>
+      <c r="C159">
+        <v>18.15302064147889</v>
+      </c>
+      <c r="D159">
+        <v>23.77814042105793</v>
+      </c>
+      <c r="E159">
+        <v>6.518763505964468</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160">
+        <v>4.523088605934557</v>
+      </c>
+      <c r="C160">
+        <v>18.48206923653811</v>
+      </c>
+      <c r="D160">
+        <v>23.44657164368691</v>
+      </c>
+      <c r="E160">
+        <v>6.584711272507279</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161">
+        <v>4.066473705283189</v>
+      </c>
+      <c r="C161">
+        <v>17.90392539623828</v>
+      </c>
+      <c r="D161">
+        <v>23.7107930792403</v>
+      </c>
+      <c r="E161">
+        <v>6.867810018854883</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162">
+        <v>3.590387027558573</v>
+      </c>
+      <c r="C162">
+        <v>17.43068085734292</v>
+      </c>
+      <c r="D162">
+        <v>23.79129601956421</v>
+      </c>
+      <c r="E162">
+        <v>7.405731288683684</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163">
+        <v>3.829920278681839</v>
+      </c>
+      <c r="C163">
+        <v>18.40175610045977</v>
+      </c>
+      <c r="D163">
+        <v>23.89917914510223</v>
+      </c>
+      <c r="E163">
+        <v>7.112753991430721</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164">
+        <v>3.1099044810482</v>
+      </c>
+      <c r="C164">
+        <v>17.84277649178843</v>
+      </c>
+      <c r="D164">
+        <v>23.88612719961638</v>
+      </c>
+      <c r="E164">
+        <v>6.439044515842268</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165">
+        <v>3.242322447419357</v>
+      </c>
+      <c r="C165">
+        <v>17.84534807982145</v>
+      </c>
+      <c r="D165">
+        <v>23.81391896240969</v>
+      </c>
+      <c r="E165">
+        <v>7.644237553986335</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166">
+        <v>4.539559506678073</v>
+      </c>
+      <c r="C166">
+        <v>17.10023157683098</v>
+      </c>
+      <c r="D166">
+        <v>23.64231465328724</v>
+      </c>
+      <c r="E166">
+        <v>6.75925646164414</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167">
+        <v>3.407025513197467</v>
+      </c>
+      <c r="C167">
+        <v>17.43555938805596</v>
+      </c>
+      <c r="D167">
+        <v>23.93116737408932</v>
+      </c>
+      <c r="E167">
+        <v>7.723347294229656</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>171</v>
+      </c>
+      <c r="B168">
+        <v>3.42856324145401</v>
+      </c>
+      <c r="C168">
+        <v>18.07257368693355</v>
+      </c>
+      <c r="D168">
+        <v>23.6079570810706</v>
+      </c>
+      <c r="E168">
+        <v>7.122809591807317</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169">
+        <v>4.440583044481941</v>
+      </c>
+      <c r="C169">
+        <v>17.96360479262244</v>
+      </c>
+      <c r="D169">
+        <v>23.81350310189018</v>
+      </c>
+      <c r="E169">
+        <v>6.912105245993445</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170">
+        <v>3.806087223387766</v>
+      </c>
+      <c r="C170">
+        <v>17.22106135112722</v>
+      </c>
+      <c r="D170">
+        <v>23.58817582300789</v>
+      </c>
+      <c r="E170">
+        <v>7.755051631305657</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>174</v>
+      </c>
+      <c r="B171">
+        <v>4.353659685766376</v>
+      </c>
+      <c r="C171">
+        <v>17.60542909592583</v>
+      </c>
+      <c r="D171">
+        <v>23.69788208191783</v>
+      </c>
+      <c r="E171">
+        <v>7.238620662273868</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>175</v>
+      </c>
+      <c r="B172">
+        <v>3.972191474581773</v>
+      </c>
+      <c r="C172">
+        <v>18.46102652772591</v>
+      </c>
+      <c r="D172">
+        <v>23.80582217746879</v>
+      </c>
+      <c r="E172">
+        <v>7.802882444275044</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173">
+        <v>3.411981164257338</v>
+      </c>
+      <c r="C173">
+        <v>18.293005726503</v>
+      </c>
+      <c r="D173">
+        <v>23.45947566960574</v>
+      </c>
+      <c r="E173">
+        <v>7.001668198626308</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174">
+        <v>3.732774849408338</v>
+      </c>
+      <c r="C174">
+        <v>17.55740295645926</v>
+      </c>
+      <c r="D174">
+        <v>23.58807687352032</v>
+      </c>
+      <c r="E174">
+        <v>6.618691658392317</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175">
+        <v>4.363694781657053</v>
+      </c>
+      <c r="C175">
+        <v>18.31220236124374</v>
+      </c>
+      <c r="D175">
+        <v>23.73496643644443</v>
+      </c>
+      <c r="E175">
+        <v>7.900860089561876</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176">
+        <v>4.698885638680419</v>
+      </c>
+      <c r="C176">
+        <v>17.50123372213474</v>
+      </c>
+      <c r="D176">
+        <v>23.81653097651503</v>
+      </c>
+      <c r="E176">
+        <v>7.087350009180145</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177">
+        <v>4.245980762332068</v>
+      </c>
+      <c r="C177">
+        <v>17.90692793063756</v>
+      </c>
+      <c r="D177">
+        <v>23.5877863340177</v>
+      </c>
+      <c r="E177">
+        <v>7.098438794729733</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178">
+        <v>4.144173607796599</v>
+      </c>
+      <c r="C178">
+        <v>17.97954115277498</v>
+      </c>
+      <c r="D178">
+        <v>23.70226225748015</v>
+      </c>
+      <c r="E178">
+        <v>7.739477201690983</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179">
+        <v>3.369795359978895</v>
+      </c>
+      <c r="C179">
+        <v>18.04515979724961</v>
+      </c>
+      <c r="D179">
+        <v>23.51721718961589</v>
+      </c>
+      <c r="E179">
+        <v>7.986344889131811</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180">
+        <v>4.656831985100816</v>
+      </c>
+      <c r="C180">
+        <v>17.73970170102801</v>
+      </c>
+      <c r="D180">
+        <v>23.78258242779803</v>
+      </c>
+      <c r="E180">
+        <v>6.733741863256244</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181">
+        <v>3.53356497897608</v>
+      </c>
+      <c r="C181">
+        <v>18.00721176742564</v>
+      </c>
+      <c r="D181">
+        <v>23.74168626022214</v>
+      </c>
+      <c r="E181">
+        <v>7.023071450638191</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182">
+        <v>3.058902634834436</v>
+      </c>
+      <c r="C182">
+        <v>17.74151507659632</v>
+      </c>
+      <c r="D182">
+        <v>23.6928908939038</v>
+      </c>
+      <c r="E182">
+        <v>7.31605301274292</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183">
+        <v>3.410875060100345</v>
+      </c>
+      <c r="C183">
+        <v>18.23846980997403</v>
+      </c>
+      <c r="D183">
+        <v>23.86825210706607</v>
+      </c>
+      <c r="E183">
+        <v>6.647692244270369</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184">
+        <v>4.391064664433277</v>
+      </c>
+      <c r="C184">
+        <v>16.92711292178909</v>
+      </c>
+      <c r="D184">
+        <v>23.47709746079108</v>
+      </c>
+      <c r="E184">
+        <v>6.93702839021591</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185">
+        <v>4.403121724650537</v>
+      </c>
+      <c r="C185">
+        <v>17.73464920977859</v>
+      </c>
+      <c r="D185">
+        <v>23.75624997625746</v>
+      </c>
+      <c r="E185">
+        <v>6.925443581738358</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186">
+        <v>3.342702390243291</v>
+      </c>
+      <c r="C186">
+        <v>17.45178111870829</v>
+      </c>
+      <c r="D186">
+        <v>23.51136155051091</v>
+      </c>
+      <c r="E186">
+        <v>6.765246863680064</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187">
+        <v>3.461622607273681</v>
+      </c>
+      <c r="C187">
+        <v>18.48377895539269</v>
+      </c>
+      <c r="D187">
+        <v>23.66940953581387</v>
+      </c>
+      <c r="E187">
+        <v>6.521682099302605</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188">
+        <v>4.16001359598607</v>
+      </c>
+      <c r="C188">
+        <v>17.59682576033814</v>
+      </c>
+      <c r="D188">
+        <v>23.5321670503092</v>
+      </c>
+      <c r="E188">
+        <v>7.283670689376361</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189">
+        <v>3.008230648008333</v>
+      </c>
+      <c r="C189">
+        <v>17.09043133987292</v>
+      </c>
+      <c r="D189">
+        <v>23.62990550912239</v>
+      </c>
+      <c r="E189">
+        <v>7.907729931278984</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190">
+        <v>3.997077098320472</v>
+      </c>
+      <c r="C190">
+        <v>17.66935070394986</v>
+      </c>
+      <c r="D190">
+        <v>23.49008546735277</v>
+      </c>
+      <c r="E190">
+        <v>7.748900808211784</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191">
+        <v>3.373274238314696</v>
+      </c>
+      <c r="C191">
+        <v>17.65777698749624</v>
+      </c>
+      <c r="D191">
+        <v>23.84169447771986</v>
+      </c>
+      <c r="E191">
+        <v>7.944086616053124</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192">
+        <v>3.04092928953758</v>
+      </c>
+      <c r="C192">
+        <v>18.48124569020109</v>
+      </c>
+      <c r="D192">
+        <v>23.71873221909481</v>
+      </c>
+      <c r="E192">
+        <v>7.820886968086758</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193">
+        <v>3.34683489690467</v>
+      </c>
+      <c r="C193">
+        <v>17.39639470986943</v>
+      </c>
+      <c r="D193">
+        <v>23.58055881206243</v>
+      </c>
+      <c r="E193">
+        <v>6.925012298455299</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194">
+        <v>4.438605430040315</v>
+      </c>
+      <c r="C194">
+        <v>18.12538830008846</v>
+      </c>
+      <c r="D194">
+        <v>23.44342796485034</v>
+      </c>
+      <c r="E194">
+        <v>6.775670668642177</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195">
+        <v>4.026256367395209</v>
+      </c>
+      <c r="C195">
+        <v>17.45131532611913</v>
+      </c>
+      <c r="D195">
+        <v>23.55613134455696</v>
+      </c>
+      <c r="E195">
+        <v>6.806396507654956</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196">
+        <v>4.561692530782261</v>
+      </c>
+      <c r="C196">
+        <v>17.9015617430416</v>
+      </c>
+      <c r="D196">
+        <v>23.86741257113269</v>
+      </c>
+      <c r="E196">
+        <v>7.737637064305169</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197">
+        <v>4.661453639488254</v>
+      </c>
+      <c r="C197">
+        <v>17.92641210161021</v>
+      </c>
+      <c r="D197">
+        <v>23.85524378330496</v>
+      </c>
+      <c r="E197">
+        <v>7.472352631696522</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198">
+        <v>3.019613928389112</v>
+      </c>
+      <c r="C198">
+        <v>18.18735386810522</v>
+      </c>
+      <c r="D198">
+        <v>23.74310442907687</v>
+      </c>
+      <c r="E198">
+        <v>7.080184627918939</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199">
+        <v>3.489264097379257</v>
+      </c>
+      <c r="C199">
+        <v>17.64537586062592</v>
+      </c>
+      <c r="D199">
+        <v>23.54459523904617</v>
+      </c>
+      <c r="E199">
+        <v>7.4156729105278</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200">
+        <v>3.952992195661878</v>
+      </c>
+      <c r="C200">
+        <v>17.56909508155593</v>
+      </c>
+      <c r="D200">
+        <v>23.77295981262907</v>
+      </c>
+      <c r="E200">
+        <v>6.886952454451096</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201">
+        <v>4.268556357344448</v>
+      </c>
+      <c r="C201">
+        <v>17.62889011960076</v>
+      </c>
+      <c r="D201">
+        <v>23.53517949444412</v>
+      </c>
+      <c r="E201">
+        <v>6.509032602512975</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202">
+        <v>3.783673530732244</v>
+      </c>
+      <c r="C202">
+        <v>18.28858370298701</v>
+      </c>
+      <c r="D202">
+        <v>23.54381528150741</v>
+      </c>
+      <c r="E202">
+        <v>6.955191202272887</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203">
+        <v>4.579183983764986</v>
+      </c>
+      <c r="C203">
+        <v>18.43398242016013</v>
+      </c>
+      <c r="D203">
+        <v>23.54565172299911</v>
+      </c>
+      <c r="E203">
+        <v>7.819243157151826</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204">
+        <v>4.063094258480891</v>
+      </c>
+      <c r="C204">
+        <v>17.85081905684646</v>
+      </c>
+      <c r="D204">
+        <v>23.86839413096561</v>
+      </c>
+      <c r="E204">
+        <v>6.596865874551709</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205">
+        <v>3.638198329044076</v>
+      </c>
+      <c r="C205">
+        <v>19.43413877188917</v>
+      </c>
+      <c r="D205">
+        <v>33.29804920415484</v>
+      </c>
+      <c r="E205">
+        <v>7.183056514648426</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206">
+        <v>3.819824696075475</v>
+      </c>
+      <c r="C206">
+        <v>20.42303370632577</v>
+      </c>
+      <c r="D206">
+        <v>33.55797792006655</v>
+      </c>
+      <c r="E206">
+        <v>6.154182845184558</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207">
+        <v>4.28312562846664</v>
+      </c>
+      <c r="C207">
+        <v>20.17252316660336</v>
+      </c>
+      <c r="D207">
+        <v>33.36292614433354</v>
+      </c>
+      <c r="E207">
+        <v>6.176729632095933</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208">
+        <v>4.370124522758583</v>
+      </c>
+      <c r="C208">
+        <v>19.48952261545295</v>
+      </c>
+      <c r="D208">
+        <v>33.32020358835456</v>
+      </c>
+      <c r="E208">
+        <v>6.946230534433273</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209">
+        <v>4.086888226267723</v>
+      </c>
+      <c r="C209">
+        <v>19.8025429000634</v>
+      </c>
+      <c r="D209">
+        <v>33.35621917579137</v>
+      </c>
+      <c r="E209">
+        <v>6.636691198419874</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210">
+        <v>4.34376510559182</v>
+      </c>
+      <c r="C210">
+        <v>20.18212702934084</v>
+      </c>
+      <c r="D210">
+        <v>33.28103781336439</v>
+      </c>
+      <c r="E210">
+        <v>6.395449227242284</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211">
+        <v>3.802188518684479</v>
+      </c>
+      <c r="C211">
+        <v>19.56787861154418</v>
+      </c>
+      <c r="D211">
+        <v>33.57205350280117</v>
+      </c>
+      <c r="E211">
+        <v>7.373875981264309</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212">
+        <v>4.208848460127825</v>
+      </c>
+      <c r="C212">
+        <v>19.30546119267554</v>
+      </c>
+      <c r="D212">
+        <v>33.69548010631539</v>
+      </c>
+      <c r="E212">
+        <v>6.928012738985805</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213">
+        <v>3.526943204647782</v>
+      </c>
+      <c r="C213">
+        <v>20.15609204641799</v>
+      </c>
+      <c r="D213">
+        <v>33.61705447144612</v>
+      </c>
+      <c r="E213">
+        <v>7.136332781284426</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214">
+        <v>3.47497682192885</v>
+      </c>
+      <c r="C214">
+        <v>20.8110121280981</v>
+      </c>
+      <c r="D214">
+        <v>33.4070361946284</v>
+      </c>
+      <c r="E214">
+        <v>6.186812368862087</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215">
+        <v>3.719851678546858</v>
+      </c>
+      <c r="C215">
+        <v>20.80832335433084</v>
+      </c>
+      <c r="D215">
+        <v>33.56458423123473</v>
+      </c>
+      <c r="E215">
+        <v>6.852779536409387</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216">
+        <v>4.062193242305399</v>
+      </c>
+      <c r="C216">
+        <v>19.9683260955903</v>
+      </c>
+      <c r="D216">
+        <v>33.67962357730676</v>
+      </c>
+      <c r="E216">
+        <v>6.373535306102434</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217">
+        <v>3.51696535124313</v>
+      </c>
+      <c r="C217">
+        <v>20.13758957186434</v>
+      </c>
+      <c r="D217">
+        <v>33.22382716744322</v>
+      </c>
+      <c r="E217">
+        <v>6.859994393758672</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218">
+        <v>3.830665808738036</v>
+      </c>
+      <c r="C218">
+        <v>20.64268562434301</v>
+      </c>
+      <c r="D218">
+        <v>33.67384780744056</v>
+      </c>
+      <c r="E218">
+        <v>6.748537417580039</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219">
+        <v>3.186841337383527</v>
+      </c>
+      <c r="C219">
+        <v>20.75465023037295</v>
+      </c>
+      <c r="D219">
+        <v>33.520298485765</v>
+      </c>
+      <c r="E219">
+        <v>6.779514114607633</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220">
+        <v>3.386157188763903</v>
+      </c>
+      <c r="C220">
+        <v>20.58916574327436</v>
+      </c>
+      <c r="D220">
+        <v>33.21667315862507</v>
+      </c>
+      <c r="E220">
+        <v>6.229227330497539</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221">
+        <v>3.510746857255537</v>
+      </c>
+      <c r="C221">
+        <v>20.00687280434313</v>
+      </c>
+      <c r="D221">
+        <v>33.33718799284536</v>
+      </c>
+      <c r="E221">
+        <v>6.860624555232098</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222">
+        <v>2.887129369501283</v>
+      </c>
+      <c r="C222">
+        <v>20.64473119672211</v>
+      </c>
+      <c r="D222">
+        <v>33.577032732712</v>
+      </c>
+      <c r="E222">
+        <v>7.464184280379359</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223">
+        <v>3.290385615252006</v>
+      </c>
+      <c r="C223">
+        <v>19.93653636301151</v>
+      </c>
+      <c r="D223">
+        <v>33.44445856900626</v>
+      </c>
+      <c r="E223">
+        <v>7.679220126931565</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224">
+        <v>3.288632187507173</v>
+      </c>
+      <c r="C224">
+        <v>20.61388676338851</v>
+      </c>
+      <c r="D224">
+        <v>33.27395444085501</v>
+      </c>
+      <c r="E224">
+        <v>6.602532217107443</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225">
+        <v>4.177411584151451</v>
+      </c>
+      <c r="C225">
+        <v>20.40259082906963</v>
+      </c>
+      <c r="D225">
+        <v>33.5137632274667</v>
+      </c>
+      <c r="E225">
+        <v>6.615176934294867</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226">
+        <v>4.480482087442621</v>
+      </c>
+      <c r="C226">
+        <v>20.03996755972844</v>
+      </c>
+      <c r="D226">
+        <v>33.28438640624657</v>
+      </c>
+      <c r="E226">
+        <v>6.306516225916151</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227">
+        <v>2.946355654584537</v>
+      </c>
+      <c r="C227">
+        <v>20.0829285117071</v>
+      </c>
+      <c r="D227">
+        <v>33.32932753229021</v>
+      </c>
+      <c r="E227">
+        <v>7.101904688110372</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228">
+        <v>3.585981740031138</v>
+      </c>
+      <c r="C228">
+        <v>20.35083639542752</v>
+      </c>
+      <c r="D228">
+        <v>33.40343342209208</v>
+      </c>
+      <c r="E228">
+        <v>6.247264296926714</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="s">
+        <v>232</v>
+      </c>
+      <c r="B229">
+        <v>4.020949246780653</v>
+      </c>
+      <c r="C229">
+        <v>19.98742275105666</v>
+      </c>
+      <c r="D229">
+        <v>33.24364553195505</v>
+      </c>
+      <c r="E229">
+        <v>7.477876114699527</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="s">
+        <v>233</v>
+      </c>
+      <c r="B230">
+        <v>4.47315433492605</v>
+      </c>
+      <c r="C230">
+        <v>20.00743373448768</v>
+      </c>
+      <c r="D230">
+        <v>33.23078847119869</v>
+      </c>
+      <c r="E230">
+        <v>6.42286580345313</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="s">
+        <v>234</v>
+      </c>
+      <c r="B231">
+        <v>2.898798833622815</v>
+      </c>
+      <c r="C231">
+        <v>19.77210456914539</v>
+      </c>
+      <c r="D231">
+        <v>33.4519714706645</v>
+      </c>
+      <c r="E231">
+        <v>6.572460926765368</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="s">
+        <v>235</v>
+      </c>
+      <c r="B232">
+        <v>4.097101835225651</v>
+      </c>
+      <c r="C232">
+        <v>20.01449720349418</v>
+      </c>
+      <c r="D232">
+        <v>33.63426120290856</v>
+      </c>
+      <c r="E232">
+        <v>7.208482383163741</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="s">
+        <v>236</v>
+      </c>
+      <c r="B233">
+        <v>3.469158156033368</v>
+      </c>
+      <c r="C233">
+        <v>19.88424612884533</v>
+      </c>
+      <c r="D233">
+        <v>33.59192127322304</v>
+      </c>
+      <c r="E233">
+        <v>7.164608286794524</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="s">
+        <v>237</v>
+      </c>
+      <c r="B234">
+        <v>3.511404356970085</v>
+      </c>
+      <c r="C234">
+        <v>20.49707202732929</v>
+      </c>
+      <c r="D234">
+        <v>33.54236382896624</v>
+      </c>
+      <c r="E234">
+        <v>7.43851706809262</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="s">
+        <v>238</v>
+      </c>
+      <c r="B235">
+        <v>4.16151709086488</v>
+      </c>
+      <c r="C235">
+        <v>19.45155940534881</v>
+      </c>
+      <c r="D235">
+        <v>33.55768913918886</v>
+      </c>
+      <c r="E235">
+        <v>6.654872366674048</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="s">
+        <v>239</v>
+      </c>
+      <c r="B236">
+        <v>3.232564788649302</v>
+      </c>
+      <c r="C236">
+        <v>19.9571714594963</v>
+      </c>
+      <c r="D236">
+        <v>33.38569945485992</v>
+      </c>
+      <c r="E236">
+        <v>6.362992061851767</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="s">
+        <v>240</v>
+      </c>
+      <c r="B237">
+        <v>3.487308554874436</v>
+      </c>
+      <c r="C237">
+        <v>19.53737908103775</v>
+      </c>
+      <c r="D237">
+        <v>33.66980284905369</v>
+      </c>
+      <c r="E237">
+        <v>7.397556172502091</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="s">
+        <v>241</v>
+      </c>
+      <c r="B238">
+        <v>4.089775641680263</v>
+      </c>
+      <c r="C238">
+        <v>20.50867945989327</v>
+      </c>
+      <c r="D238">
+        <v>33.65221437944947</v>
+      </c>
+      <c r="E238">
+        <v>7.362545746588334</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239">
+        <v>3.309945851055148</v>
+      </c>
+      <c r="C239">
+        <v>19.86153767346439</v>
+      </c>
+      <c r="D239">
+        <v>33.39485169929022</v>
+      </c>
+      <c r="E239">
+        <v>6.417510061882395</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="s">
+        <v>243</v>
+      </c>
+      <c r="B240">
+        <v>3.97334101559781</v>
+      </c>
+      <c r="C240">
+        <v>20.32600140074697</v>
+      </c>
+      <c r="D240">
+        <v>33.2642552019927</v>
+      </c>
+      <c r="E240">
+        <v>6.809270541583662</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="s">
+        <v>244</v>
+      </c>
+      <c r="B241">
+        <v>3.731084784734866</v>
+      </c>
+      <c r="C241">
+        <v>20.06725557886262</v>
+      </c>
+      <c r="D241">
+        <v>33.50017235387163</v>
+      </c>
+      <c r="E241">
+        <v>7.370725863138803</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="s">
+        <v>245</v>
+      </c>
+      <c r="B242">
+        <v>4.033595742200234</v>
+      </c>
+      <c r="C242">
+        <v>20.70052156349461</v>
+      </c>
+      <c r="D242">
+        <v>33.40124031996077</v>
+      </c>
+      <c r="E242">
+        <v>7.595171007734342</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="s">
+        <v>246</v>
+      </c>
+      <c r="B243">
+        <v>4.318476815708634</v>
+      </c>
+      <c r="C243">
+        <v>20.328763257632</v>
+      </c>
+      <c r="D243">
+        <v>33.58621814633956</v>
+      </c>
+      <c r="E243">
+        <v>6.206903671473747</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>247</v>
+      </c>
+      <c r="B244">
+        <v>3.082838938293948</v>
+      </c>
+      <c r="C244">
+        <v>19.9850521700962</v>
+      </c>
+      <c r="D244">
+        <v>33.57655673970604</v>
+      </c>
+      <c r="E244">
+        <v>7.36883438059014</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>248</v>
+      </c>
+      <c r="B245">
+        <v>4.082281084277936</v>
+      </c>
+      <c r="C245">
+        <v>19.6997123720772</v>
+      </c>
+      <c r="D245">
+        <v>33.58511015283281</v>
+      </c>
+      <c r="E245">
+        <v>6.635475300765808</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>249</v>
+      </c>
+      <c r="B246">
+        <v>3.090475952762719</v>
+      </c>
+      <c r="C246">
+        <v>20.7273570477357</v>
+      </c>
+      <c r="D246">
+        <v>33.30992644139273</v>
+      </c>
+      <c r="E246">
+        <v>7.424008231047599</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>250</v>
+      </c>
+      <c r="B247">
+        <v>4.215897547505712</v>
+      </c>
+      <c r="C247">
+        <v>20.51270597032166</v>
+      </c>
+      <c r="D247">
+        <v>33.41925222871456</v>
+      </c>
+      <c r="E247">
+        <v>6.546897519876919</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="s">
+        <v>251</v>
+      </c>
+      <c r="B248">
+        <v>4.008549292640279</v>
+      </c>
+      <c r="C248">
+        <v>19.88246114131893</v>
+      </c>
+      <c r="D248">
+        <v>33.48464203589172</v>
+      </c>
+      <c r="E248">
+        <v>7.357107497293772</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="s">
+        <v>252</v>
+      </c>
+      <c r="B249">
+        <v>3.51094624210401</v>
+      </c>
+      <c r="C249">
+        <v>20.07430191423622</v>
+      </c>
+      <c r="D249">
+        <v>33.40294110467234</v>
+      </c>
+      <c r="E249">
+        <v>7.515014338332311</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="s">
+        <v>253</v>
+      </c>
+      <c r="B250">
+        <v>3.251531876866013</v>
+      </c>
+      <c r="C250">
+        <v>19.72348135058771</v>
+      </c>
+      <c r="D250">
+        <v>33.26781392768818</v>
+      </c>
+      <c r="E250">
+        <v>6.921032717769013</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="s">
+        <v>254</v>
+      </c>
+      <c r="B251">
+        <v>3.737381236079702</v>
+      </c>
+      <c r="C251">
+        <v>19.71807672045899</v>
+      </c>
+      <c r="D251">
+        <v>33.2430823833207</v>
+      </c>
+      <c r="E251">
+        <v>6.820039509775537</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" t="s">
+        <v>255</v>
+      </c>
+      <c r="B252">
+        <v>2.832003931511977</v>
+      </c>
+      <c r="C252">
+        <v>20.32750501889222</v>
+      </c>
+      <c r="D252">
+        <v>33.62444719544282</v>
+      </c>
+      <c r="E252">
+        <v>6.736540673344294</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" t="s">
+        <v>256</v>
+      </c>
+      <c r="B253">
+        <v>4.229892482261006</v>
+      </c>
+      <c r="C253">
+        <v>19.63489690550887</v>
+      </c>
+      <c r="D253">
+        <v>33.60195969890569</v>
+      </c>
+      <c r="E253">
+        <v>6.444573187639008</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" t="s">
+        <v>257</v>
+      </c>
+      <c r="B254">
+        <v>2.968116384592632</v>
+      </c>
+      <c r="C254">
+        <v>20.00965452415539</v>
+      </c>
+      <c r="D254">
+        <v>33.38725443720042</v>
+      </c>
+      <c r="E254">
+        <v>7.11168441486878</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" t="s">
+        <v>258</v>
+      </c>
+      <c r="B255">
+        <v>4.180473815889891</v>
+      </c>
+      <c r="C255">
+        <v>20.28680541160186</v>
+      </c>
+      <c r="D255">
+        <v>33.43145325715642</v>
+      </c>
+      <c r="E255">
+        <v>7.041964850631955</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256">
+        <v>4.245440139935329</v>
+      </c>
+      <c r="C256">
+        <v>19.7918022792085</v>
+      </c>
+      <c r="D256">
+        <v>33.65209752631242</v>
+      </c>
+      <c r="E256">
+        <v>6.834938433057111</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" t="s">
+        <v>260</v>
+      </c>
+      <c r="B257">
+        <v>3.257623276937541</v>
+      </c>
+      <c r="C257">
+        <v>20.42661887756342</v>
+      </c>
+      <c r="D257">
+        <v>33.50421839274266</v>
+      </c>
+      <c r="E257">
+        <v>6.178319035484941</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" t="s">
+        <v>261</v>
+      </c>
+      <c r="B258">
+        <v>3.940444173353773</v>
+      </c>
+      <c r="C258">
+        <v>19.23891801901467</v>
+      </c>
+      <c r="D258">
+        <v>33.67909005369017</v>
+      </c>
+      <c r="E258">
+        <v>7.245727379860597</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" t="s">
+        <v>262</v>
+      </c>
+      <c r="B259">
+        <v>2.850488064975552</v>
+      </c>
+      <c r="C259">
+        <v>19.24602306036698</v>
+      </c>
+      <c r="D259">
+        <v>33.46425698124318</v>
+      </c>
+      <c r="E259">
+        <v>7.012840243930055</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="s">
+        <v>263</v>
+      </c>
+      <c r="B260">
+        <v>2.889846334793635</v>
+      </c>
+      <c r="C260">
+        <v>20.10725093301949</v>
+      </c>
+      <c r="D260">
+        <v>33.44556477027082</v>
+      </c>
+      <c r="E260">
+        <v>7.085643040282362</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
+        <v>264</v>
+      </c>
+      <c r="B261">
+        <v>3.155673347162797</v>
+      </c>
+      <c r="C261">
+        <v>19.9052464933525</v>
+      </c>
+      <c r="D261">
+        <v>33.59244261400591</v>
+      </c>
+      <c r="E261">
+        <v>6.253529363452976</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" t="s">
+        <v>265</v>
+      </c>
+      <c r="B262">
+        <v>4.157296122681879</v>
+      </c>
+      <c r="C262">
+        <v>20.43262349630123</v>
+      </c>
+      <c r="D262">
+        <v>33.38774045053801</v>
+      </c>
+      <c r="E262">
+        <v>6.695607651458028</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" t="s">
+        <v>266</v>
+      </c>
+      <c r="B263">
+        <v>2.770100441860005</v>
+      </c>
+      <c r="C263">
+        <v>20.46214067194112</v>
+      </c>
+      <c r="D263">
+        <v>33.69014159833436</v>
+      </c>
+      <c r="E263">
+        <v>6.404540467501576</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" t="s">
+        <v>267</v>
+      </c>
+      <c r="B264">
+        <v>4.043026269880583</v>
+      </c>
+      <c r="C264">
+        <v>19.8867000777717</v>
+      </c>
+      <c r="D264">
+        <v>33.26460948459681</v>
+      </c>
+      <c r="E264">
+        <v>6.847349618610349</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" t="s">
+        <v>268</v>
+      </c>
+      <c r="B265">
+        <v>3.67155571605057</v>
+      </c>
+      <c r="C265">
+        <v>20.45272227693395</v>
+      </c>
+      <c r="D265">
+        <v>33.41764978064071</v>
+      </c>
+      <c r="E265">
+        <v>7.47907570146421</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" t="s">
+        <v>269</v>
+      </c>
+      <c r="B266">
+        <v>3.786040156027282</v>
+      </c>
+      <c r="C266">
+        <v>19.36450785162003</v>
+      </c>
+      <c r="D266">
+        <v>33.58350440255412</v>
+      </c>
+      <c r="E266">
+        <v>6.60889651757174</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" t="s">
+        <v>270</v>
+      </c>
+      <c r="B267">
+        <v>2.89406278917419</v>
+      </c>
+      <c r="C267">
+        <v>20.14065162874738</v>
+      </c>
+      <c r="D267">
+        <v>33.608110185895</v>
+      </c>
+      <c r="E267">
+        <v>6.238233615479743</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" t="s">
+        <v>271</v>
+      </c>
+      <c r="B268">
+        <v>6.8429575373812</v>
+      </c>
+      <c r="C268">
+        <v>19.14394804611547</v>
+      </c>
+      <c r="D268">
+        <v>28.21445790858716</v>
+      </c>
+      <c r="E268">
+        <v>7.846987172938016</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" t="s">
+        <v>272</v>
+      </c>
+      <c r="B269">
+        <v>6.391156941011847</v>
+      </c>
+      <c r="C269">
+        <v>18.76242740841722</v>
+      </c>
+      <c r="D269">
+        <v>28.55803111007726</v>
+      </c>
+      <c r="E269">
+        <v>6.88139318115832</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" t="s">
+        <v>273</v>
+      </c>
+      <c r="B270">
+        <v>6.298167080333296</v>
+      </c>
+      <c r="C270">
+        <v>18.1137025568752</v>
+      </c>
+      <c r="D270">
+        <v>28.50838117578119</v>
+      </c>
+      <c r="E270">
+        <v>8.081806976347057</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
+        <v>274</v>
+      </c>
+      <c r="B271">
+        <v>6.470583271540448</v>
+      </c>
+      <c r="C271">
+        <v>18.80478814385375</v>
+      </c>
+      <c r="D271">
+        <v>28.2231786770335</v>
+      </c>
+      <c r="E271">
+        <v>7.35509555768971</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272">
+        <v>6.895333319532275</v>
+      </c>
+      <c r="C272">
+        <v>18.27090245863318</v>
+      </c>
+      <c r="D272">
+        <v>28.46258901121361</v>
+      </c>
+      <c r="E272">
+        <v>7.366365682475712</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273">
+        <v>6.834533975799513</v>
+      </c>
+      <c r="C273">
+        <v>19.37811006939979</v>
+      </c>
+      <c r="D273">
+        <v>28.45907384137534</v>
+      </c>
+      <c r="E273">
+        <v>7.303934873465945</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274">
+        <v>6.561108446180961</v>
+      </c>
+      <c r="C274">
+        <v>19.04492869670953</v>
+      </c>
+      <c r="D274">
+        <v>28.61305540734913</v>
+      </c>
+      <c r="E274">
+        <v>6.908683114795904</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275">
+        <v>6.830406015088839</v>
+      </c>
+      <c r="C275">
+        <v>18.33825273105459</v>
+      </c>
+      <c r="D275">
+        <v>28.62188674813314</v>
+      </c>
+      <c r="E275">
+        <v>7.305033596737323</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276">
+        <v>5.782284500511738</v>
+      </c>
+      <c r="C276">
+        <v>19.51660452254531</v>
+      </c>
+      <c r="D276">
+        <v>28.24442378498468</v>
+      </c>
+      <c r="E276">
+        <v>6.636457043610767</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277">
+        <v>6.608957082082606</v>
+      </c>
+      <c r="C277">
+        <v>19.23446452032865</v>
+      </c>
+      <c r="D277">
+        <v>28.45137854533379</v>
+      </c>
+      <c r="E277">
+        <v>7.70962198855028</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278">
+        <v>5.675445685130129</v>
+      </c>
+      <c r="C278">
+        <v>19.07762616035254</v>
+      </c>
+      <c r="D278">
+        <v>28.5056047734821</v>
+      </c>
+      <c r="E278">
+        <v>8.066714319563008</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279">
+        <v>5.810756979654357</v>
+      </c>
+      <c r="C279">
+        <v>19.57484944020696</v>
+      </c>
+      <c r="D279">
+        <v>28.64116689949666</v>
+      </c>
+      <c r="E279">
+        <v>7.104632462895005</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280">
+        <v>5.895056830403765</v>
+      </c>
+      <c r="C280">
+        <v>18.64402113007887</v>
+      </c>
+      <c r="D280">
+        <v>28.37645566938615</v>
+      </c>
+      <c r="E280">
+        <v>7.543366462844682</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281">
+        <v>6.856962182067252</v>
+      </c>
+      <c r="C281">
+        <v>18.5851685207014</v>
+      </c>
+      <c r="D281">
+        <v>28.53783604364919</v>
+      </c>
+      <c r="E281">
+        <v>6.598217727184357</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282">
+        <v>5.944124763820565</v>
+      </c>
+      <c r="C282">
+        <v>19.14604278630542</v>
+      </c>
+      <c r="D282">
+        <v>28.44831806677363</v>
+      </c>
+      <c r="E282">
+        <v>7.66762689084934</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" t="s">
+        <v>286</v>
+      </c>
+      <c r="B283">
+        <v>5.982995110457103</v>
+      </c>
+      <c r="C283">
+        <v>19.61643512158053</v>
+      </c>
+      <c r="D283">
+        <v>28.42968475195954</v>
+      </c>
+      <c r="E283">
+        <v>7.650023695053951</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>287</v>
+      </c>
+      <c r="B284">
+        <v>6.615939736375506</v>
+      </c>
+      <c r="C284">
+        <v>18.45065692033062</v>
+      </c>
+      <c r="D284">
+        <v>28.61970728942392</v>
+      </c>
+      <c r="E284">
+        <v>7.614796259016475</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" t="s">
+        <v>288</v>
+      </c>
+      <c r="B285">
+        <v>5.334045046095387</v>
+      </c>
+      <c r="C285">
+        <v>19.59325838465868</v>
+      </c>
+      <c r="D285">
+        <v>28.51781207798154</v>
+      </c>
+      <c r="E285">
+        <v>6.691948558209114</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" t="s">
+        <v>289</v>
+      </c>
+      <c r="B286">
+        <v>6.154625106271158</v>
+      </c>
+      <c r="C286">
+        <v>19.41052220571262</v>
+      </c>
+      <c r="D286">
+        <v>28.47353216154252</v>
+      </c>
+      <c r="E286">
+        <v>7.927369459428999</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287">
+        <v>5.279469271769961</v>
+      </c>
+      <c r="C287">
+        <v>19.39963266314408</v>
+      </c>
+      <c r="D287">
+        <v>28.41617484665338</v>
+      </c>
+      <c r="E287">
+        <v>7.825799422394138</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" t="s">
+        <v>291</v>
+      </c>
+      <c r="B288">
+        <v>6.378887571518282</v>
+      </c>
+      <c r="C288">
+        <v>19.18368305836634</v>
+      </c>
+      <c r="D288">
+        <v>28.34381828865514</v>
+      </c>
+      <c r="E288">
+        <v>7.614669622681568</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" t="s">
+        <v>292</v>
+      </c>
+      <c r="B289">
+        <v>5.767534534223589</v>
+      </c>
+      <c r="C289">
+        <v>18.20060110511882</v>
+      </c>
+      <c r="D289">
+        <v>28.31126795863614</v>
+      </c>
+      <c r="E289">
+        <v>6.725865923122424</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" t="s">
+        <v>293</v>
+      </c>
+      <c r="B290">
+        <v>6.073681162572681</v>
+      </c>
+      <c r="C290">
+        <v>18.30099768767331</v>
+      </c>
+      <c r="D290">
+        <v>28.34843704809116</v>
+      </c>
+      <c r="E290">
+        <v>7.017633389772577</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" t="s">
+        <v>294</v>
+      </c>
+      <c r="B291">
+        <v>6.25154597809192</v>
+      </c>
+      <c r="C291">
+        <v>18.80412379806327</v>
+      </c>
+      <c r="D291">
+        <v>28.26373078771014</v>
+      </c>
+      <c r="E291">
+        <v>7.954285767908631</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" t="s">
+        <v>295</v>
+      </c>
+      <c r="B292">
+        <v>6.489324042999144</v>
+      </c>
+      <c r="C292">
+        <v>18.39590600650261</v>
+      </c>
+      <c r="D292">
+        <v>28.27134912504051</v>
+      </c>
+      <c r="E292">
+        <v>7.007415593350822</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" t="s">
+        <v>296</v>
+      </c>
+      <c r="B293">
+        <v>6.288582831584683</v>
+      </c>
+      <c r="C293">
+        <v>18.41141474202515</v>
+      </c>
+      <c r="D293">
+        <v>28.32442476464693</v>
+      </c>
+      <c r="E293">
+        <v>7.98768310481014</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" t="s">
+        <v>297</v>
+      </c>
+      <c r="B294">
+        <v>6.544942143090276</v>
+      </c>
+      <c r="C294">
+        <v>19.39816438637145</v>
+      </c>
+      <c r="D294">
+        <v>28.18724794901466</v>
+      </c>
+      <c r="E294">
+        <v>7.012959116732769</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" t="s">
+        <v>298</v>
+      </c>
+      <c r="B295">
+        <v>6.216219285022786</v>
+      </c>
+      <c r="C295">
+        <v>18.55025418526871</v>
+      </c>
+      <c r="D295">
+        <v>28.45247392173311</v>
+      </c>
+      <c r="E295">
+        <v>7.973929921357035</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" t="s">
+        <v>299</v>
+      </c>
+      <c r="B296">
+        <v>5.415321948877735</v>
+      </c>
+      <c r="C296">
+        <v>18.30801147636031</v>
+      </c>
+      <c r="D296">
+        <v>28.42120977030895</v>
+      </c>
+      <c r="E296">
+        <v>7.420270025896448</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" t="s">
+        <v>300</v>
+      </c>
+      <c r="B297">
+        <v>6.415000241649459</v>
+      </c>
+      <c r="C297">
+        <v>18.47991627046141</v>
+      </c>
+      <c r="D297">
+        <v>28.32149473376737</v>
+      </c>
+      <c r="E297">
+        <v>6.793795680283193</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" t="s">
+        <v>301</v>
+      </c>
+      <c r="B298">
+        <v>6.057201602220662</v>
+      </c>
+      <c r="C298">
+        <v>19.58041911993555</v>
+      </c>
+      <c r="D298">
+        <v>28.47868243842119</v>
+      </c>
+      <c r="E298">
+        <v>7.853562668345678</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" t="s">
+        <v>302</v>
+      </c>
+      <c r="B299">
+        <v>6.284591818617772</v>
+      </c>
+      <c r="C299">
+        <v>18.84510953200376</v>
+      </c>
+      <c r="D299">
+        <v>28.4092425330415</v>
+      </c>
+      <c r="E299">
+        <v>7.525901668680218</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" t="s">
+        <v>303</v>
+      </c>
+      <c r="B300">
+        <v>6.769216139016928</v>
+      </c>
+      <c r="C300">
+        <v>18.8292502029602</v>
+      </c>
+      <c r="D300">
+        <v>28.37608140734342</v>
+      </c>
+      <c r="E300">
+        <v>8.053548104325184</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" t="s">
+        <v>304</v>
+      </c>
+      <c r="B301">
+        <v>6.338291240921563</v>
+      </c>
+      <c r="C301">
+        <v>18.57226627891907</v>
+      </c>
+      <c r="D301">
+        <v>28.6153790724362</v>
+      </c>
+      <c r="E301">
+        <v>7.850717664590386</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" t="s">
+        <v>305</v>
+      </c>
+      <c r="B302">
+        <v>6.784167474370165</v>
+      </c>
+      <c r="C302">
+        <v>18.71126784256851</v>
+      </c>
+      <c r="D302">
+        <v>28.3264383701223</v>
+      </c>
+      <c r="E302">
+        <v>7.970770439048037</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" t="s">
+        <v>306</v>
+      </c>
+      <c r="B303">
+        <v>5.16846099673401</v>
+      </c>
+      <c r="C303">
+        <v>18.6614481605526</v>
+      </c>
+      <c r="D303">
+        <v>28.50588988444066</v>
+      </c>
+      <c r="E303">
+        <v>6.927167980470927</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" t="s">
+        <v>307</v>
+      </c>
+      <c r="B304">
+        <v>6.855142305825838</v>
+      </c>
+      <c r="C304">
+        <v>19.08737931132488</v>
+      </c>
+      <c r="D304">
+        <v>28.48142547577253</v>
+      </c>
+      <c r="E304">
+        <v>7.335202619702812</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" t="s">
+        <v>308</v>
+      </c>
+      <c r="B305">
+        <v>6.641403038392433</v>
+      </c>
+      <c r="C305">
+        <v>18.94356322665855</v>
+      </c>
+      <c r="D305">
+        <v>28.41802215089355</v>
+      </c>
+      <c r="E305">
+        <v>7.807826329600124</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" t="s">
+        <v>309</v>
+      </c>
+      <c r="B306">
+        <v>5.292053263434374</v>
+      </c>
+      <c r="C306">
+        <v>18.9434613335389</v>
+      </c>
+      <c r="D306">
+        <v>28.18728673584967</v>
+      </c>
+      <c r="E306">
+        <v>7.060504558254265</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" t="s">
+        <v>310</v>
+      </c>
+      <c r="B307">
+        <v>6.034187752691111</v>
+      </c>
+      <c r="C307">
+        <v>19.33222696020646</v>
+      </c>
+      <c r="D307">
+        <v>28.52936198345478</v>
+      </c>
+      <c r="E307">
+        <v>7.622147297415616</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" t="s">
+        <v>311</v>
+      </c>
+      <c r="B308">
+        <v>6.298232581620576</v>
+      </c>
+      <c r="C308">
+        <v>19.28345638019039</v>
+      </c>
+      <c r="D308">
+        <v>28.35732623238816</v>
+      </c>
+      <c r="E308">
+        <v>7.07788344743564</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" t="s">
+        <v>312</v>
+      </c>
+      <c r="B309">
+        <v>5.721672428727174</v>
+      </c>
+      <c r="C309">
+        <v>18.4590815773384</v>
+      </c>
+      <c r="D309">
+        <v>28.46445823890138</v>
+      </c>
+      <c r="E309">
+        <v>7.832619356925321</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" t="s">
+        <v>313</v>
+      </c>
+      <c r="B310">
+        <v>6.080070380664585</v>
+      </c>
+      <c r="C310">
+        <v>19.06296577570368</v>
+      </c>
+      <c r="D310">
+        <v>28.37306689604017</v>
+      </c>
+      <c r="E310">
+        <v>7.800134931565848</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" t="s">
+        <v>314</v>
+      </c>
+      <c r="B311">
+        <v>5.579218978226068</v>
+      </c>
+      <c r="C311">
+        <v>19.4723221450399</v>
+      </c>
+      <c r="D311">
+        <v>28.63167379127901</v>
+      </c>
+      <c r="E311">
+        <v>7.062160835949741</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" t="s">
+        <v>315</v>
+      </c>
+      <c r="B312">
+        <v>5.908200513163845</v>
+      </c>
+      <c r="C312">
+        <v>19.36814295411907</v>
+      </c>
+      <c r="D312">
+        <v>28.57570902485471</v>
+      </c>
+      <c r="E312">
+        <v>6.750079538912445</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" t="s">
+        <v>316</v>
+      </c>
+      <c r="B313">
+        <v>5.738650199617929</v>
+      </c>
+      <c r="C313">
+        <v>18.30887093016885</v>
+      </c>
+      <c r="D313">
+        <v>28.55959922251639</v>
+      </c>
+      <c r="E313">
+        <v>7.206861334710208</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" t="s">
+        <v>317</v>
+      </c>
+      <c r="B314">
+        <v>5.26686658643623</v>
+      </c>
+      <c r="C314">
+        <v>18.97257413187095</v>
+      </c>
+      <c r="D314">
+        <v>28.41639702086014</v>
+      </c>
+      <c r="E314">
+        <v>7.285167578461549</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" t="s">
+        <v>318</v>
+      </c>
+      <c r="B315">
+        <v>6.573083942590506</v>
+      </c>
+      <c r="C315">
+        <v>19.14027426013924</v>
+      </c>
+      <c r="D315">
+        <v>28.52348505241057</v>
+      </c>
+      <c r="E315">
+        <v>7.854107049943202</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" t="s">
+        <v>319</v>
+      </c>
+      <c r="B316">
+        <v>6.356619031365975</v>
+      </c>
+      <c r="C316">
+        <v>19.27567557613764</v>
+      </c>
+      <c r="D316">
+        <v>28.67250985323345</v>
+      </c>
+      <c r="E316">
+        <v>6.577224931905993</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" t="s">
+        <v>320</v>
+      </c>
+      <c r="B317">
+        <v>5.84808365835034</v>
+      </c>
+      <c r="C317">
+        <v>18.67486375715947</v>
+      </c>
+      <c r="D317">
+        <v>28.57138912136468</v>
+      </c>
+      <c r="E317">
+        <v>6.584100769219256</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" t="s">
+        <v>321</v>
+      </c>
+      <c r="B318">
+        <v>6.320356863110217</v>
+      </c>
+      <c r="C318">
+        <v>18.43755692454038</v>
+      </c>
+      <c r="D318">
+        <v>28.50520515029757</v>
+      </c>
+      <c r="E318">
+        <v>7.810133134230052</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" t="s">
+        <v>322</v>
+      </c>
+      <c r="B319">
+        <v>6.552938681436178</v>
+      </c>
+      <c r="C319">
+        <v>18.82758088745131</v>
+      </c>
+      <c r="D319">
+        <v>28.40572019513425</v>
+      </c>
+      <c r="E319">
+        <v>7.782982723600472</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" t="s">
+        <v>323</v>
+      </c>
+      <c r="B320">
+        <v>5.755728789114848</v>
+      </c>
+      <c r="C320">
+        <v>18.92155572473591</v>
+      </c>
+      <c r="D320">
+        <v>28.67553737349844</v>
+      </c>
+      <c r="E320">
+        <v>6.808629300970966</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" t="s">
+        <v>324</v>
+      </c>
+      <c r="B321">
+        <v>5.129685181277577</v>
+      </c>
+      <c r="C321">
+        <v>19.34559497086653</v>
+      </c>
+      <c r="D321">
+        <v>28.52625600158551</v>
+      </c>
+      <c r="E321">
+        <v>7.885393031423465</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" t="s">
+        <v>325</v>
+      </c>
+      <c r="B322">
+        <v>5.737650344204541</v>
+      </c>
+      <c r="C322">
+        <v>19.08430799228555</v>
+      </c>
+      <c r="D322">
+        <v>28.49508629593273</v>
+      </c>
+      <c r="E322">
+        <v>7.506842921714255</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" t="s">
+        <v>326</v>
+      </c>
+      <c r="B323">
+        <v>6.260847505370865</v>
+      </c>
+      <c r="C323">
+        <v>19.26075838956957</v>
+      </c>
+      <c r="D323">
+        <v>28.5610051542547</v>
+      </c>
+      <c r="E323">
+        <v>6.921318569857543</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" t="s">
+        <v>327</v>
+      </c>
+      <c r="B324">
+        <v>6.806695452841196</v>
+      </c>
+      <c r="C324">
+        <v>18.63661870779102</v>
+      </c>
+      <c r="D324">
+        <v>28.39436181179413</v>
+      </c>
+      <c r="E324">
+        <v>6.753605763541247</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" t="s">
+        <v>328</v>
+      </c>
+      <c r="B325">
+        <v>6.132491950279179</v>
+      </c>
+      <c r="C325">
+        <v>19.60139076439607</v>
+      </c>
+      <c r="D325">
+        <v>28.37910013953379</v>
+      </c>
+      <c r="E325">
+        <v>8.071819406209015</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" t="s">
+        <v>329</v>
+      </c>
+      <c r="B326">
+        <v>5.706915041885232</v>
+      </c>
+      <c r="C326">
+        <v>18.37643682668667</v>
+      </c>
+      <c r="D326">
+        <v>28.28641540857603</v>
+      </c>
+      <c r="E326">
+        <v>6.860139923557321</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" t="s">
+        <v>330</v>
+      </c>
+      <c r="B327">
+        <v>6.12343224202843</v>
+      </c>
+      <c r="C327">
+        <v>19.36574802409532</v>
+      </c>
+      <c r="D327">
+        <v>28.57121318086109</v>
+      </c>
+      <c r="E327">
+        <v>6.67986580274988</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" t="s">
+        <v>331</v>
+      </c>
+      <c r="B328">
+        <v>6.203219271019888</v>
+      </c>
+      <c r="C328">
+        <v>19.37955073634196</v>
+      </c>
+      <c r="D328">
+        <v>28.25517168661486</v>
+      </c>
+      <c r="E328">
+        <v>7.70290450260406</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" t="s">
+        <v>332</v>
+      </c>
+      <c r="B329">
+        <v>5.527290232709345</v>
+      </c>
+      <c r="C329">
+        <v>19.41421361043518</v>
+      </c>
+      <c r="D329">
+        <v>28.46282543589081</v>
+      </c>
+      <c r="E329">
+        <v>6.86058035610621</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" t="s">
+        <v>333</v>
+      </c>
+      <c r="B330">
+        <v>3.175629603150818</v>
+      </c>
+      <c r="C330">
+        <v>7.216298200412728</v>
+      </c>
+      <c r="D330">
+        <v>57.99733794422777</v>
+      </c>
+      <c r="E330">
+        <v>1.811374840674428</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" t="s">
+        <v>334</v>
+      </c>
+      <c r="B331">
+        <v>2.643949734216563</v>
+      </c>
+      <c r="C331">
+        <v>6.691571252671482</v>
+      </c>
+      <c r="D331">
+        <v>58.24051947607289</v>
+      </c>
+      <c r="E331">
+        <v>1.597555559100905</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" t="s">
+        <v>335</v>
+      </c>
+      <c r="B332">
+        <v>2.244394947642849</v>
+      </c>
+      <c r="C332">
+        <v>7.355936936400889</v>
+      </c>
+      <c r="D332">
+        <v>57.87452588384427</v>
+      </c>
+      <c r="E332">
+        <v>1.289833423939174</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333">
+        <v>2.531580477995731</v>
+      </c>
+      <c r="C333">
+        <v>6.496654045041068</v>
+      </c>
+      <c r="D333">
+        <v>57.86614864963545</v>
+      </c>
+      <c r="E333">
+        <v>2.692196003471712</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" t="s">
+        <v>337</v>
+      </c>
+      <c r="B334">
+        <v>2.291636847993273</v>
+      </c>
+      <c r="C334">
+        <v>6.553058265007375</v>
+      </c>
+      <c r="D334">
+        <v>57.79618507354044</v>
+      </c>
+      <c r="E334">
+        <v>2.46352037443858</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" t="s">
+        <v>338</v>
+      </c>
+      <c r="B335">
+        <v>2.062709333569394</v>
+      </c>
+      <c r="C335">
+        <v>7.222347930789424</v>
+      </c>
+      <c r="D335">
+        <v>58.04710195029547</v>
+      </c>
+      <c r="E335">
+        <v>2.081482051929509</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" t="s">
+        <v>339</v>
+      </c>
+      <c r="B336">
+        <v>2.438019428582049</v>
+      </c>
+      <c r="C336">
+        <v>6.399912575789114</v>
+      </c>
+      <c r="D336">
+        <v>58.03870822042632</v>
+      </c>
+      <c r="E336">
+        <v>2.384945615828868</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" t="s">
+        <v>340</v>
+      </c>
+      <c r="B337">
+        <v>3.093410271630642</v>
+      </c>
+      <c r="C337">
+        <v>6.693585242339689</v>
+      </c>
+      <c r="D337">
+        <v>57.956073885728</v>
+      </c>
+      <c r="E337">
+        <v>1.866960746220065</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" t="s">
+        <v>341</v>
+      </c>
+      <c r="B338">
+        <v>1.808770786918878</v>
+      </c>
+      <c r="C338">
+        <v>7.032699177740839</v>
+      </c>
+      <c r="D338">
+        <v>58.21348153076951</v>
+      </c>
+      <c r="E338">
+        <v>1.614469550038643</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" t="s">
+        <v>342</v>
+      </c>
+      <c r="B339">
+        <v>1.971609034677386</v>
+      </c>
+      <c r="C339">
+        <v>6.364394194064847</v>
+      </c>
+      <c r="D339">
+        <v>57.8529406006938</v>
+      </c>
+      <c r="E339">
+        <v>1.457474465900623</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" t="s">
+        <v>343</v>
+      </c>
+      <c r="B340">
+        <v>2.170426907739422</v>
+      </c>
+      <c r="C340">
+        <v>7.027586858881016</v>
+      </c>
+      <c r="D340">
+        <v>58.05955430438826</v>
+      </c>
+      <c r="E340">
+        <v>2.819940938326673</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" t="s">
+        <v>344</v>
+      </c>
+      <c r="B341">
+        <v>3.309267292226621</v>
+      </c>
+      <c r="C341">
+        <v>7.253486085720202</v>
+      </c>
+      <c r="D341">
+        <v>57.89737886392487</v>
+      </c>
+      <c r="E341">
+        <v>2.238824524907231</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" t="s">
+        <v>345</v>
+      </c>
+      <c r="B342">
+        <v>2.137563923759596</v>
+      </c>
+      <c r="C342">
+        <v>6.564277719602032</v>
+      </c>
+      <c r="D342">
+        <v>58.05702964488516</v>
+      </c>
+      <c r="E342">
+        <v>2.67651314234905</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" t="s">
+        <v>346</v>
+      </c>
+      <c r="B343">
+        <v>2.383514950642182</v>
+      </c>
+      <c r="C343">
+        <v>7.310075013958031</v>
+      </c>
+      <c r="D343">
+        <v>57.80850793908457</v>
+      </c>
+      <c r="E343">
+        <v>1.814947313099168</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" t="s">
+        <v>347</v>
+      </c>
+      <c r="B344">
+        <v>2.087909317393904</v>
+      </c>
+      <c r="C344">
+        <v>7.167251960960897</v>
+      </c>
+      <c r="D344">
+        <v>58.08175249729743</v>
+      </c>
+      <c r="E344">
+        <v>1.760599718507034</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" t="s">
+        <v>348</v>
+      </c>
+      <c r="B345">
+        <v>3.133750453360928</v>
+      </c>
+      <c r="C345">
+        <v>7.444390762966114</v>
+      </c>
+      <c r="D345">
+        <v>57.96943738565763</v>
+      </c>
+      <c r="E345">
+        <v>1.591350148399004</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" t="s">
+        <v>349</v>
+      </c>
+      <c r="B346">
+        <v>2.843686035822912</v>
+      </c>
+      <c r="C346">
+        <v>7.159819018589926</v>
+      </c>
+      <c r="D346">
+        <v>57.95723043202766</v>
+      </c>
+      <c r="E346">
+        <v>2.303593874284365</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" t="s">
+        <v>350</v>
+      </c>
+      <c r="B347">
+        <v>1.798212246144874</v>
+      </c>
+      <c r="C347">
+        <v>6.022611556219353</v>
+      </c>
+      <c r="D347">
+        <v>58.15468363861891</v>
+      </c>
+      <c r="E347">
+        <v>1.576279733422374</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" t="s">
+        <v>351</v>
+      </c>
+      <c r="B348">
+        <v>1.997245298529642</v>
+      </c>
+      <c r="C348">
+        <v>7.277238117925479</v>
+      </c>
+      <c r="D348">
+        <v>57.81239030432798</v>
+      </c>
+      <c r="E348">
+        <v>1.686387245859633</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" t="s">
+        <v>352</v>
+      </c>
+      <c r="B349">
+        <v>2.240876440262315</v>
+      </c>
+      <c r="C349">
+        <v>6.810904117791901</v>
+      </c>
+      <c r="D349">
+        <v>57.94226900433443</v>
+      </c>
+      <c r="E349">
+        <v>1.557890060089896</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" t="s">
+        <v>353</v>
+      </c>
+      <c r="B350">
+        <v>3.324549543198978</v>
+      </c>
+      <c r="C350">
+        <v>6.05794698073654</v>
+      </c>
+      <c r="D350">
+        <v>58.15884031266823</v>
+      </c>
+      <c r="E350">
+        <v>1.822062444586201</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" t="s">
+        <v>354</v>
+      </c>
+      <c r="B351">
+        <v>2.025221627042841</v>
+      </c>
+      <c r="C351">
+        <v>5.986008099472251</v>
+      </c>
+      <c r="D351">
+        <v>58.08184591637649</v>
+      </c>
+      <c r="E351">
+        <v>2.088674081869384</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" t="s">
+        <v>355</v>
+      </c>
+      <c r="B352">
+        <v>2.619713686292113</v>
+      </c>
+      <c r="C352">
+        <v>6.859594516149325</v>
+      </c>
+      <c r="D352">
+        <v>58.23544597306012</v>
+      </c>
+      <c r="E352">
+        <v>1.671100407006711</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" t="s">
+        <v>356</v>
+      </c>
+      <c r="B353">
+        <v>2.538021483114351</v>
+      </c>
+      <c r="C353">
+        <v>7.348435657304966</v>
+      </c>
+      <c r="D353">
+        <v>58.13829889420257</v>
+      </c>
+      <c r="E353">
+        <v>2.178254337196504</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" t="s">
+        <v>357</v>
+      </c>
+      <c r="B354">
+        <v>2.240511241561642</v>
+      </c>
+      <c r="C354">
+        <v>6.24840001028508</v>
+      </c>
+      <c r="D354">
+        <v>57.98974317298552</v>
+      </c>
+      <c r="E354">
+        <v>2.286522002634129</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" t="s">
+        <v>358</v>
+      </c>
+      <c r="B355">
+        <v>3.508745942897887</v>
+      </c>
+      <c r="C355">
+        <v>6.271883718860069</v>
+      </c>
+      <c r="D355">
+        <v>58.05573733910694</v>
+      </c>
+      <c r="E355">
+        <v>1.715650951336404</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" t="s">
+        <v>359</v>
+      </c>
+      <c r="B356">
+        <v>3.370008219402643</v>
+      </c>
+      <c r="C356">
+        <v>6.852402702761774</v>
+      </c>
+      <c r="D356">
+        <v>58.1648870191609</v>
+      </c>
+      <c r="E356">
+        <v>1.25491512709876</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" t="s">
+        <v>360</v>
+      </c>
+      <c r="B357">
+        <v>2.475020372907663</v>
+      </c>
+      <c r="C357">
+        <v>6.84641989462678</v>
+      </c>
+      <c r="D357">
+        <v>58.00241743223393</v>
+      </c>
+      <c r="E357">
+        <v>1.633664460941541</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" t="s">
+        <v>361</v>
+      </c>
+      <c r="B358">
+        <v>2.729605118579086</v>
+      </c>
+      <c r="C358">
+        <v>6.215192994407703</v>
+      </c>
+      <c r="D358">
+        <v>58.1349311816167</v>
+      </c>
+      <c r="E358">
+        <v>2.83500874523905</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" t="s">
+        <v>362</v>
+      </c>
+      <c r="B359">
+        <v>3.131668732631494</v>
+      </c>
+      <c r="C359">
+        <v>6.624846021151988</v>
+      </c>
+      <c r="D359">
+        <v>57.98043349348313</v>
+      </c>
+      <c r="E359">
+        <v>2.431838144917262</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" t="s">
+        <v>363</v>
+      </c>
+      <c r="B360">
+        <v>3.222115061932337</v>
+      </c>
+      <c r="C360">
+        <v>7.198234432166065</v>
+      </c>
+      <c r="D360">
+        <v>58.16750570519093</v>
+      </c>
+      <c r="E360">
+        <v>1.470579657176042</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" t="s">
+        <v>364</v>
+      </c>
+      <c r="B361">
+        <v>3.191688664554958</v>
+      </c>
+      <c r="C361">
+        <v>6.273068183638883</v>
+      </c>
+      <c r="D361">
+        <v>57.81577448987745</v>
+      </c>
+      <c r="E361">
+        <v>2.731291534423581</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" t="s">
+        <v>365</v>
+      </c>
+      <c r="B362">
+        <v>3.030390392963836</v>
+      </c>
+      <c r="C362">
+        <v>6.770678989287601</v>
+      </c>
+      <c r="D362">
+        <v>57.8424566404118</v>
+      </c>
+      <c r="E362">
+        <v>1.813842145005164</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" t="s">
+        <v>366</v>
+      </c>
+      <c r="B363">
+        <v>3.11540171312433</v>
+      </c>
+      <c r="C363">
+        <v>6.740884795125512</v>
+      </c>
+      <c r="D363">
+        <v>57.7970490755503</v>
+      </c>
+      <c r="E363">
+        <v>1.721854573479334</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" t="s">
+        <v>367</v>
+      </c>
+      <c r="B364">
+        <v>2.862955684375605</v>
+      </c>
+      <c r="C364">
+        <v>6.577455344807224</v>
+      </c>
+      <c r="D364">
+        <v>57.86807990460403</v>
+      </c>
+      <c r="E364">
+        <v>2.160706946126175</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" t="s">
+        <v>368</v>
+      </c>
+      <c r="B365">
+        <v>2.722461897684343</v>
+      </c>
+      <c r="C365">
+        <v>6.067554952026713</v>
+      </c>
+      <c r="D365">
+        <v>58.06306678935828</v>
+      </c>
+      <c r="E365">
+        <v>2.595934678489623</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" t="s">
+        <v>369</v>
+      </c>
+      <c r="B366">
+        <v>3.549049540964826</v>
+      </c>
+      <c r="C366">
+        <v>7.313089075694975</v>
+      </c>
+      <c r="D366">
+        <v>58.22577051998514</v>
+      </c>
+      <c r="E366">
+        <v>2.10954439309506</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" t="s">
+        <v>370</v>
+      </c>
+      <c r="B367">
+        <v>2.481894183701861</v>
+      </c>
+      <c r="C367">
+        <v>6.976411704059888</v>
+      </c>
+      <c r="D367">
+        <v>58.26596822759268</v>
+      </c>
+      <c r="E367">
+        <v>2.205274287886875</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" t="s">
+        <v>371</v>
+      </c>
+      <c r="B368">
+        <v>2.495717581318642</v>
+      </c>
+      <c r="C368">
+        <v>6.581553961084427</v>
+      </c>
+      <c r="D368">
+        <v>57.9071932299134</v>
+      </c>
+      <c r="E368">
+        <v>1.385576047094437</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" t="s">
+        <v>372</v>
+      </c>
+      <c r="B369">
+        <v>3.459065854214042</v>
+      </c>
+      <c r="C369">
+        <v>6.311969902575079</v>
+      </c>
+      <c r="D369">
+        <v>57.84104489157471</v>
+      </c>
+      <c r="E369">
+        <v>2.783708844496997</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" t="s">
+        <v>373</v>
+      </c>
+      <c r="B370">
+        <v>2.390569408638884</v>
+      </c>
+      <c r="C370">
+        <v>7.339399237813036</v>
+      </c>
+      <c r="D370">
+        <v>57.80073732181103</v>
+      </c>
+      <c r="E370">
+        <v>1.448995901294903</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" t="s">
+        <v>374</v>
+      </c>
+      <c r="B371">
+        <v>2.816850496203848</v>
+      </c>
+      <c r="C371">
+        <v>6.834051844359731</v>
+      </c>
+      <c r="D371">
+        <v>58.10999866853987</v>
+      </c>
+      <c r="E371">
+        <v>1.723113386006388</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" t="s">
+        <v>375</v>
+      </c>
+      <c r="B372">
+        <v>3.422447959600952</v>
+      </c>
+      <c r="C372">
+        <v>6.07061297735486</v>
+      </c>
+      <c r="D372">
+        <v>57.95059478602263</v>
+      </c>
+      <c r="E372">
+        <v>2.631075695458359</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" t="s">
+        <v>376</v>
+      </c>
+      <c r="B373">
+        <v>2.561068163276611</v>
+      </c>
+      <c r="C373">
+        <v>6.269778229183489</v>
+      </c>
+      <c r="D373">
+        <v>57.85603746633622</v>
+      </c>
+      <c r="E373">
+        <v>1.275092610741673</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" t="s">
+        <v>377</v>
+      </c>
+      <c r="B374">
+        <v>2.201021986541132</v>
+      </c>
+      <c r="C374">
+        <v>6.579606828562607</v>
+      </c>
+      <c r="D374">
+        <v>57.94310896306769</v>
+      </c>
+      <c r="E374">
+        <v>2.376670657273277</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" t="s">
+        <v>378</v>
+      </c>
+      <c r="B375">
+        <v>2.992338281648099</v>
+      </c>
+      <c r="C375">
+        <v>6.522779058771009</v>
+      </c>
+      <c r="D375">
+        <v>58.01717639802649</v>
+      </c>
+      <c r="E375">
+        <v>1.996332075154462</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" t="s">
+        <v>379</v>
+      </c>
+      <c r="B376">
+        <v>2.656204421828584</v>
+      </c>
+      <c r="C376">
+        <v>6.858901024716684</v>
+      </c>
+      <c r="D376">
+        <v>57.88629586614683</v>
+      </c>
+      <c r="E376">
+        <v>1.477855248681895</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" t="s">
+        <v>380</v>
+      </c>
+      <c r="B377">
+        <v>1.96532669585334</v>
+      </c>
+      <c r="C377">
+        <v>6.97103483671334</v>
+      </c>
+      <c r="D377">
+        <v>58.17113529140006</v>
+      </c>
+      <c r="E377">
+        <v>2.39322339812652</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" t="s">
+        <v>381</v>
+      </c>
+      <c r="B378">
+        <v>3.039071917419577</v>
+      </c>
+      <c r="C378">
+        <v>6.989027609231356</v>
+      </c>
+      <c r="D378">
+        <v>57.90555351722581</v>
+      </c>
+      <c r="E378">
+        <v>2.027119652279216</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" t="s">
+        <v>382</v>
+      </c>
+      <c r="B379">
+        <v>2.029524584002819</v>
+      </c>
+      <c r="C379">
+        <v>6.890936568350174</v>
+      </c>
+      <c r="D379">
+        <v>58.04258107135102</v>
+      </c>
+      <c r="E379">
+        <v>2.575929715675908</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" t="s">
+        <v>383</v>
+      </c>
+      <c r="B380">
+        <v>2.248710802608307</v>
+      </c>
+      <c r="C380">
+        <v>7.425439327347561</v>
+      </c>
+      <c r="D380">
+        <v>58.13105535915305</v>
+      </c>
+      <c r="E380">
+        <v>2.122882565976161</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" t="s">
+        <v>384</v>
+      </c>
+      <c r="B381">
+        <v>2.708444565339558</v>
+      </c>
+      <c r="C381">
+        <v>7.228662158625488</v>
+      </c>
+      <c r="D381">
+        <v>58.02406959478535</v>
+      </c>
+      <c r="E381">
+        <v>1.718785527903745</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" t="s">
+        <v>385</v>
+      </c>
+      <c r="B382">
+        <v>3.115999675066044</v>
+      </c>
+      <c r="C382">
+        <v>7.403298090900111</v>
+      </c>
+      <c r="D382">
+        <v>58.091805288731</v>
+      </c>
+      <c r="E382">
+        <v>2.006212513369521</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" t="s">
+        <v>386</v>
+      </c>
+      <c r="B383">
+        <v>3.139888719087781</v>
+      </c>
+      <c r="C383">
+        <v>6.816433257184478</v>
+      </c>
+      <c r="D383">
+        <v>58.14044785115126</v>
+      </c>
+      <c r="E383">
+        <v>2.1285892887219</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" t="s">
+        <v>387</v>
+      </c>
+      <c r="B384">
+        <v>2.007670032271099</v>
+      </c>
+      <c r="C384">
+        <v>7.057830672353711</v>
+      </c>
+      <c r="D384">
+        <v>58.12899514387767</v>
+      </c>
+      <c r="E384">
+        <v>2.738905839650213</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" t="s">
+        <v>388</v>
+      </c>
+      <c r="B385">
+        <v>3.092319305361133</v>
+      </c>
+      <c r="C385">
+        <v>5.990472674639599</v>
+      </c>
+      <c r="D385">
+        <v>58.21830972963564</v>
+      </c>
+      <c r="E385">
+        <v>2.465250296429513</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" t="s">
+        <v>389</v>
+      </c>
+      <c r="B386">
+        <v>3.196286870267768</v>
+      </c>
+      <c r="C386">
+        <v>6.678683896765358</v>
+      </c>
+      <c r="D386">
+        <v>58.08407121416866</v>
+      </c>
+      <c r="E386">
+        <v>2.404287468197624</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" t="s">
+        <v>390</v>
+      </c>
+      <c r="B387">
+        <v>1.938038437085108</v>
+      </c>
+      <c r="C387">
+        <v>6.41105525548823</v>
+      </c>
+      <c r="D387">
+        <v>57.78410632880715</v>
+      </c>
+      <c r="E387">
+        <v>1.481791864508295</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" t="s">
+        <v>391</v>
+      </c>
+      <c r="B388">
+        <v>2.881358766068935</v>
+      </c>
+      <c r="C388">
+        <v>6.188017548835234</v>
+      </c>
+      <c r="D388">
+        <v>58.04213309191462</v>
+      </c>
+      <c r="E388">
+        <v>2.228519218478778</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" t="s">
+        <v>392</v>
+      </c>
+      <c r="B389">
+        <v>3.429472336363275</v>
+      </c>
+      <c r="C389">
+        <v>7.462515005189264</v>
+      </c>
+      <c r="D389">
+        <v>58.09330949209291</v>
+      </c>
+      <c r="E389">
+        <v>1.559724878301673</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" t="s">
+        <v>393</v>
+      </c>
+      <c r="B390">
+        <v>3.500612143733543</v>
+      </c>
+      <c r="C390">
+        <v>7.19050930600247</v>
+      </c>
+      <c r="D390">
+        <v>58.20764673581339</v>
+      </c>
+      <c r="E390">
+        <v>2.81379182726522</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" t="s">
+        <v>394</v>
+      </c>
+      <c r="B391">
+        <v>2.284949577184614</v>
+      </c>
+      <c r="C391">
+        <v>5.893234451614115</v>
+      </c>
+      <c r="D391">
+        <v>57.83270699167944</v>
+      </c>
+      <c r="E391">
+        <v>2.517818550916674</v>
       </c>
     </row>
   </sheetData>

--- a/FFT on froth/data_test_augm_Pb.xlsx
+++ b/FFT on froth/data_test_augm_Pb.xlsx
@@ -1581,16 +1581,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.6910966134186318</v>
+        <v>0.9555667088996663</v>
       </c>
       <c r="C2">
-        <v>4.763870993431865</v>
+        <v>4.364903999701304</v>
       </c>
       <c r="D2">
-        <v>24.71402233831731</v>
+        <v>24.56180507422911</v>
       </c>
       <c r="E2">
-        <v>1.193366995979883</v>
+        <v>1.55598026434504</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1598,16 +1598,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.104979739624584</v>
+        <v>0.8080282092230482</v>
       </c>
       <c r="C3">
-        <v>4.082668719150224</v>
+        <v>5.158964252651785</v>
       </c>
       <c r="D3">
-        <v>24.5407481229082</v>
+        <v>24.65766490004864</v>
       </c>
       <c r="E3">
-        <v>1.361255019236155</v>
+        <v>2.548098053577777</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1615,16 +1615,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.721927733928604</v>
+        <v>0.4920040734632759</v>
       </c>
       <c r="C4">
-        <v>5.150938793662542</v>
+        <v>5.50189814091298</v>
       </c>
       <c r="D4">
-        <v>24.92795112365341</v>
+        <v>24.47797460162434</v>
       </c>
       <c r="E4">
-        <v>1.687410237436302</v>
+        <v>1.090312776926774</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1632,16 +1632,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.9293306657125603</v>
+        <v>1.156482616002067</v>
       </c>
       <c r="C5">
-        <v>5.007910372575521</v>
+        <v>5.456590753404928</v>
       </c>
       <c r="D5">
-        <v>24.45156815949694</v>
+        <v>24.83575194355496</v>
       </c>
       <c r="E5">
-        <v>1.090950324418502</v>
+        <v>2.335295986386509</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1649,16 +1649,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.9374805606937416</v>
+        <v>0.3089879346057939</v>
       </c>
       <c r="C6">
-        <v>4.387008522830512</v>
+        <v>4.538734575025399</v>
       </c>
       <c r="D6">
-        <v>24.5679834427914</v>
+        <v>24.80110308330329</v>
       </c>
       <c r="E6">
-        <v>2.10660524702416</v>
+        <v>1.234858862192039</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1666,16 +1666,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.628372987314375</v>
+        <v>1.819121150691276</v>
       </c>
       <c r="C7">
-        <v>3.959778592832005</v>
+        <v>4.399118435659346</v>
       </c>
       <c r="D7">
-        <v>24.89211146805589</v>
+        <v>24.6637257540357</v>
       </c>
       <c r="E7">
-        <v>2.558178649468103</v>
+        <v>1.188459868480736</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1683,16 +1683,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1.031401121290753</v>
+        <v>1.075716846255165</v>
       </c>
       <c r="C8">
-        <v>5.169823338451035</v>
+        <v>4.758999646026719</v>
       </c>
       <c r="D8">
-        <v>24.79400714792904</v>
+        <v>24.59996082825779</v>
       </c>
       <c r="E8">
-        <v>1.55026622152836</v>
+        <v>1.626390725466464</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1700,16 +1700,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>2.010555273166861</v>
+        <v>1.129395173607574</v>
       </c>
       <c r="C9">
-        <v>4.124190316475047</v>
+        <v>4.212956206659545</v>
       </c>
       <c r="D9">
-        <v>24.89856441338384</v>
+        <v>24.88999975101926</v>
       </c>
       <c r="E9">
-        <v>1.59260373816383</v>
+        <v>1.318192727387592</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1717,16 +1717,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>1.332431709470527</v>
+        <v>1.545389477947994</v>
       </c>
       <c r="C10">
-        <v>4.397204174295663</v>
+        <v>4.574206104975183</v>
       </c>
       <c r="D10">
-        <v>24.576909749901</v>
+        <v>24.49747429864211</v>
       </c>
       <c r="E10">
-        <v>2.411740143339842</v>
+        <v>1.771424260683905</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1734,16 +1734,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.3692651077586361</v>
+        <v>1.944912600943915</v>
       </c>
       <c r="C11">
-        <v>4.27020602818319</v>
+        <v>5.506783757626465</v>
       </c>
       <c r="D11">
-        <v>24.55215566941268</v>
+        <v>24.87337797048334</v>
       </c>
       <c r="E11">
-        <v>2.587360183142512</v>
+        <v>2.413127057854254</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1751,16 +1751,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.5181674850118507</v>
+        <v>1.396543269829813</v>
       </c>
       <c r="C12">
-        <v>4.676824996280468</v>
+        <v>4.2894754380728</v>
       </c>
       <c r="D12">
-        <v>24.90101560844964</v>
+        <v>24.78719021943286</v>
       </c>
       <c r="E12">
-        <v>2.449821048401386</v>
+        <v>1.556103463553439</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1768,16 +1768,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>1.511014559094012</v>
+        <v>0.6727961262700493</v>
       </c>
       <c r="C13">
-        <v>5.266064449728558</v>
+        <v>4.912929710218657</v>
       </c>
       <c r="D13">
-        <v>24.49964202350787</v>
+        <v>24.46108691237233</v>
       </c>
       <c r="E13">
-        <v>1.438335285185045</v>
+        <v>2.28960959242826</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1785,16 +1785,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.8412492599364403</v>
+        <v>1.648287099503863</v>
       </c>
       <c r="C14">
-        <v>5.089566214267114</v>
+        <v>5.383559524988656</v>
       </c>
       <c r="D14">
-        <v>24.61841934159922</v>
+        <v>24.64476758288256</v>
       </c>
       <c r="E14">
-        <v>2.129933819444214</v>
+        <v>2.448275475119757</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1802,16 +1802,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1.538789623332457</v>
+        <v>2.00177994646992</v>
       </c>
       <c r="C15">
-        <v>5.134735813985144</v>
+        <v>5.274599788025585</v>
       </c>
       <c r="D15">
-        <v>24.89745480054356</v>
+        <v>24.59005777760901</v>
       </c>
       <c r="E15">
-        <v>2.455268078297859</v>
+        <v>1.447055028815551</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1819,16 +1819,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>1.750678322373583</v>
+        <v>1.66039806291069</v>
       </c>
       <c r="C16">
-        <v>4.266623616391734</v>
+        <v>5.061792981895898</v>
       </c>
       <c r="D16">
-        <v>24.80729906132298</v>
+        <v>24.51326877203281</v>
       </c>
       <c r="E16">
-        <v>1.301377265077181</v>
+        <v>2.561109476559743</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1836,16 +1836,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.671810369723121</v>
+        <v>0.4228083880623049</v>
       </c>
       <c r="C17">
-        <v>4.331354633010342</v>
+        <v>4.013390444520812</v>
       </c>
       <c r="D17">
-        <v>24.62628560549368</v>
+        <v>24.46992191695369</v>
       </c>
       <c r="E17">
-        <v>2.215511137439132</v>
+        <v>1.557006020186011</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1853,16 +1853,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.8727202738254839</v>
+        <v>1.522396082772647</v>
       </c>
       <c r="C18">
-        <v>4.343240483332907</v>
+        <v>5.396959319497238</v>
       </c>
       <c r="D18">
-        <v>24.57197047688942</v>
+        <v>24.58140701352641</v>
       </c>
       <c r="E18">
-        <v>1.403024754025719</v>
+        <v>2.221246540562557</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1870,16 +1870,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.3428818752563895</v>
+        <v>1.66453304599699</v>
       </c>
       <c r="C19">
-        <v>4.32503938098959</v>
+        <v>5.131167842681558</v>
       </c>
       <c r="D19">
-        <v>24.61732089249733</v>
+        <v>24.75185829786818</v>
       </c>
       <c r="E19">
-        <v>2.43689932788002</v>
+        <v>2.337893927603198</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1887,16 +1887,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1.008702317277945</v>
+        <v>0.7756576488220717</v>
       </c>
       <c r="C20">
-        <v>4.05257230289557</v>
+        <v>4.105581514423673</v>
       </c>
       <c r="D20">
-        <v>24.88568590035424</v>
+        <v>24.47998686101991</v>
       </c>
       <c r="E20">
-        <v>2.668769873015056</v>
+        <v>2.128615489016429</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1904,16 +1904,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>1.706171565140283</v>
+        <v>0.2431158929194354</v>
       </c>
       <c r="C21">
-        <v>4.917089784631064</v>
+        <v>4.347570875623862</v>
       </c>
       <c r="D21">
-        <v>24.9034069827223</v>
+        <v>24.57267826428366</v>
       </c>
       <c r="E21">
-        <v>1.194710118054415</v>
+        <v>2.145939827910002</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1921,16 +1921,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>1.54508263833148</v>
+        <v>0.9527512247947825</v>
       </c>
       <c r="C22">
-        <v>4.287172023999306</v>
+        <v>4.675901249531073</v>
       </c>
       <c r="D22">
-        <v>24.7845518297938</v>
+        <v>24.66074681276168</v>
       </c>
       <c r="E22">
-        <v>1.516855656661004</v>
+        <v>2.123016274824416</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1938,16 +1938,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.349754753445421</v>
+        <v>1.123561323260033</v>
       </c>
       <c r="C23">
-        <v>4.956969938475142</v>
+        <v>4.524225415873076</v>
       </c>
       <c r="D23">
-        <v>24.61985177730347</v>
+        <v>24.87137818092765</v>
       </c>
       <c r="E23">
-        <v>1.469531864959494</v>
+        <v>1.555099183133885</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1955,16 +1955,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>1.774273879180982</v>
+        <v>1.505781761560082</v>
       </c>
       <c r="C24">
-        <v>4.916737862004853</v>
+        <v>4.568337928429746</v>
       </c>
       <c r="D24">
-        <v>24.72025875286399</v>
+        <v>24.58232310565377</v>
       </c>
       <c r="E24">
-        <v>1.914731329099999</v>
+        <v>1.919110642040513</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1972,16 +1972,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>0.9972965262010457</v>
+        <v>0.8129453429647987</v>
       </c>
       <c r="C25">
-        <v>4.377753477749047</v>
+        <v>4.018054802238123</v>
       </c>
       <c r="D25">
-        <v>24.60706857539778</v>
+        <v>24.68019015848621</v>
       </c>
       <c r="E25">
-        <v>1.288844018094579</v>
+        <v>1.653198099069156</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1989,16 +1989,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>1.129042703324198</v>
+        <v>1.870564465481604</v>
       </c>
       <c r="C26">
-        <v>4.393518186518029</v>
+        <v>4.59373428739941</v>
       </c>
       <c r="D26">
-        <v>24.87908755017461</v>
+        <v>24.77632888872651</v>
       </c>
       <c r="E26">
-        <v>2.255402186833322</v>
+        <v>1.985334952862015</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2006,16 +2006,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>1.636320042479295</v>
+        <v>1.444092245723115</v>
       </c>
       <c r="C27">
-        <v>4.666153770073512</v>
+        <v>4.92559754402891</v>
       </c>
       <c r="D27">
-        <v>24.57911097887377</v>
+        <v>24.72240025418588</v>
       </c>
       <c r="E27">
-        <v>2.396603154029276</v>
+        <v>1.424840198073308</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2023,16 +2023,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>1.462677086121733</v>
+        <v>1.444977852419282</v>
       </c>
       <c r="C28">
-        <v>4.222406253899354</v>
+        <v>4.584718259970344</v>
       </c>
       <c r="D28">
-        <v>24.87017367432803</v>
+        <v>24.72795640328489</v>
       </c>
       <c r="E28">
-        <v>2.202654364424656</v>
+        <v>1.363413225626976</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2040,16 +2040,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>1.528407209140802</v>
+        <v>0.6998073460927383</v>
       </c>
       <c r="C29">
-        <v>4.829692554449262</v>
+        <v>5.203428688656933</v>
       </c>
       <c r="D29">
-        <v>24.60988400578105</v>
+        <v>24.8003545416795</v>
       </c>
       <c r="E29">
-        <v>2.374206694282609</v>
+        <v>2.000438127983425</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2057,16 +2057,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>0.6567221074512464</v>
+        <v>0.4631532775921544</v>
       </c>
       <c r="C30">
-        <v>4.878983373735569</v>
+        <v>4.226676109794047</v>
       </c>
       <c r="D30">
-        <v>24.77427529463407</v>
+        <v>24.78843680319482</v>
       </c>
       <c r="E30">
-        <v>1.9761437402977</v>
+        <v>2.114142450110528</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2074,16 +2074,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>1.70421656609394</v>
+        <v>1.634661763458791</v>
       </c>
       <c r="C31">
-        <v>4.866330280881623</v>
+        <v>5.212353669266903</v>
       </c>
       <c r="D31">
-        <v>24.47355114970464</v>
+        <v>24.62005969824211</v>
       </c>
       <c r="E31">
-        <v>2.001810828866813</v>
+        <v>1.762437146444966</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2091,16 +2091,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>1.354366817006748</v>
+        <v>0.2588112408472616</v>
       </c>
       <c r="C32">
-        <v>5.369483720583534</v>
+        <v>5.397596724506902</v>
       </c>
       <c r="D32">
-        <v>24.56045281338513</v>
+        <v>24.85902493320587</v>
       </c>
       <c r="E32">
-        <v>2.34754653147617</v>
+        <v>1.105745916982189</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2108,16 +2108,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>1.611559561083123</v>
+        <v>1.51833355960633</v>
       </c>
       <c r="C33">
-        <v>5.449393991681716</v>
+        <v>4.813412636238001</v>
       </c>
       <c r="D33">
-        <v>24.92712005881549</v>
+        <v>24.93226620609397</v>
       </c>
       <c r="E33">
-        <v>2.270912296313252</v>
+        <v>2.042658429417801</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2125,16 +2125,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>0.6791611273457736</v>
+        <v>0.9783280315871379</v>
       </c>
       <c r="C34">
-        <v>4.21100061133381</v>
+        <v>5.358225697343489</v>
       </c>
       <c r="D34">
-        <v>24.64606588741807</v>
+        <v>24.52082475735386</v>
       </c>
       <c r="E34">
-        <v>2.352485784192018</v>
+        <v>1.190400369138359</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2142,16 +2142,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>1.790289018891147</v>
+        <v>0.764724094304098</v>
       </c>
       <c r="C35">
-        <v>5.194118384230896</v>
+        <v>4.526028795962061</v>
       </c>
       <c r="D35">
-        <v>24.57280144481465</v>
+        <v>24.72012646333247</v>
       </c>
       <c r="E35">
-        <v>1.127502646021972</v>
+        <v>1.142399604356264</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2159,16 +2159,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>1.266639258747727</v>
+        <v>1.304109639653208</v>
       </c>
       <c r="C36">
-        <v>4.833246499400562</v>
+        <v>4.164135590493556</v>
       </c>
       <c r="D36">
-        <v>24.60152892858927</v>
+        <v>24.77240132135953</v>
       </c>
       <c r="E36">
-        <v>1.844744753525284</v>
+        <v>1.833115689984975</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2176,16 +2176,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>0.5570584329689932</v>
+        <v>1.511686502548258</v>
       </c>
       <c r="C37">
-        <v>4.364221302270364</v>
+        <v>4.746783830564675</v>
       </c>
       <c r="D37">
-        <v>24.54401167711294</v>
+        <v>24.53865558077281</v>
       </c>
       <c r="E37">
-        <v>2.539426459076867</v>
+        <v>2.535112977486456</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2193,16 +2193,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>0.7063276772635055</v>
+        <v>2.026421220691496</v>
       </c>
       <c r="C38">
-        <v>4.710270415871769</v>
+        <v>4.659540310622146</v>
       </c>
       <c r="D38">
-        <v>24.61714554397031</v>
+        <v>24.53941184992679</v>
       </c>
       <c r="E38">
-        <v>1.863544700359375</v>
+        <v>2.282621526724388</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2210,16 +2210,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>1.193968656658302</v>
+        <v>1.992833282970305</v>
       </c>
       <c r="C39">
-        <v>4.443603631192993</v>
+        <v>4.270216590659826</v>
       </c>
       <c r="D39">
-        <v>24.64810824743509</v>
+        <v>24.81392245925781</v>
       </c>
       <c r="E39">
-        <v>1.194935776900566</v>
+        <v>1.130494715950539</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2227,16 +2227,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>1.781438284758948</v>
+        <v>0.8008098992023523</v>
       </c>
       <c r="C40">
-        <v>4.116506740081084</v>
+        <v>3.963916068568902</v>
       </c>
       <c r="D40">
-        <v>24.88661762671732</v>
+        <v>24.63397094332831</v>
       </c>
       <c r="E40">
-        <v>1.411610702432331</v>
+        <v>2.453994335538701</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2244,16 +2244,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>0.7747187185652642</v>
+        <v>1.55283823320112</v>
       </c>
       <c r="C41">
-        <v>5.131997071301438</v>
+        <v>4.35159927191861</v>
       </c>
       <c r="D41">
-        <v>24.78927980000115</v>
+        <v>24.71539807278468</v>
       </c>
       <c r="E41">
-        <v>2.013982799429992</v>
+        <v>1.11986062584991</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2261,16 +2261,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>0.3343589070839098</v>
+        <v>1.339573624378898</v>
       </c>
       <c r="C42">
-        <v>4.501353794571963</v>
+        <v>4.898947944205732</v>
       </c>
       <c r="D42">
-        <v>24.85554953828396</v>
+        <v>24.855658198775</v>
       </c>
       <c r="E42">
-        <v>1.14847878962531</v>
+        <v>1.667260751750022</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2278,16 +2278,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>0.2628425463214364</v>
+        <v>1.549354608160784</v>
       </c>
       <c r="C43">
-        <v>4.733335773006358</v>
+        <v>5.172390447111688</v>
       </c>
       <c r="D43">
-        <v>24.44786237305382</v>
+        <v>24.54200406931979</v>
       </c>
       <c r="E43">
-        <v>1.185432122384236</v>
+        <v>1.962118600494538</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2295,16 +2295,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>1.947837002776387</v>
+        <v>0.3857436415993758</v>
       </c>
       <c r="C44">
-        <v>4.096887999988252</v>
+        <v>4.698363440402244</v>
       </c>
       <c r="D44">
-        <v>24.83550654535689</v>
+        <v>24.66566975062199</v>
       </c>
       <c r="E44">
-        <v>2.635941314731275</v>
+        <v>2.076981858464305</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2312,16 +2312,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>1.038663171261939</v>
+        <v>1.523477033396664</v>
       </c>
       <c r="C45">
-        <v>4.285959602647086</v>
+        <v>4.559315664250001</v>
       </c>
       <c r="D45">
-        <v>24.47927000155376</v>
+        <v>24.51673654212346</v>
       </c>
       <c r="E45">
-        <v>1.776329210013105</v>
+        <v>1.333072747790572</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2329,16 +2329,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>1.006736750186905</v>
+        <v>1.801478229538373</v>
       </c>
       <c r="C46">
-        <v>5.170623132308693</v>
+        <v>5.324122331234</v>
       </c>
       <c r="D46">
-        <v>24.45742772428565</v>
+        <v>24.48969699146863</v>
       </c>
       <c r="E46">
-        <v>1.608650305848594</v>
+        <v>2.611989873320507</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2346,16 +2346,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>0.5736426360737537</v>
+        <v>1.191890914055417</v>
       </c>
       <c r="C47">
-        <v>5.137038378862544</v>
+        <v>5.308849828005341</v>
       </c>
       <c r="D47">
-        <v>24.92855104010394</v>
+        <v>24.7768215915374</v>
       </c>
       <c r="E47">
-        <v>1.65829736447498</v>
+        <v>2.202911273850801</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2363,16 +2363,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>1.973128126710523</v>
+        <v>2.012638065648866</v>
       </c>
       <c r="C48">
-        <v>4.232797092687666</v>
+        <v>4.172442050619764</v>
       </c>
       <c r="D48">
-        <v>24.89097697138016</v>
+        <v>24.74685280165546</v>
       </c>
       <c r="E48">
-        <v>2.161031794196581</v>
+        <v>1.596514393402087</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2380,16 +2380,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>0.4063699626647419</v>
+        <v>1.708197423301432</v>
       </c>
       <c r="C49">
-        <v>5.459428499545693</v>
+        <v>4.26925821374074</v>
       </c>
       <c r="D49">
-        <v>24.77368398658214</v>
+        <v>24.73606951073208</v>
       </c>
       <c r="E49">
-        <v>1.577676533067385</v>
+        <v>2.190374127142412</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2397,16 +2397,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>0.9393575605667503</v>
+        <v>0.5978557454401694</v>
       </c>
       <c r="C50">
-        <v>5.085110006883422</v>
+        <v>5.277515834087021</v>
       </c>
       <c r="D50">
-        <v>24.8411061828776</v>
+        <v>24.66779617707913</v>
       </c>
       <c r="E50">
-        <v>1.269544677855869</v>
+        <v>2.121986049465684</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2414,16 +2414,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>0.5964808315819488</v>
+        <v>0.7295395736800678</v>
       </c>
       <c r="C51">
-        <v>5.311299799594016</v>
+        <v>4.443080565070345</v>
       </c>
       <c r="D51">
-        <v>24.50633423491992</v>
+        <v>24.67921845536601</v>
       </c>
       <c r="E51">
-        <v>1.278527722212901</v>
+        <v>2.133300101261431</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2431,16 +2431,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>0.9649125807257501</v>
+        <v>1.737833563135487</v>
       </c>
       <c r="C52">
-        <v>4.887438411767857</v>
+        <v>4.054536933575871</v>
       </c>
       <c r="D52">
-        <v>24.70223085198221</v>
+        <v>24.52371420158364</v>
       </c>
       <c r="E52">
-        <v>2.157163313792588</v>
+        <v>2.633415319440835</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2448,16 +2448,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>1.32851123896407</v>
+        <v>1.260826776410075</v>
       </c>
       <c r="C53">
-        <v>4.471055976639986</v>
+        <v>5.497070845006358</v>
       </c>
       <c r="D53">
-        <v>24.59778622076938</v>
+        <v>24.49527060908468</v>
       </c>
       <c r="E53">
-        <v>1.29865139036978</v>
+        <v>2.24629768939751</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2465,16 +2465,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>1.158278302869968</v>
+        <v>0.6814466445410761</v>
       </c>
       <c r="C54">
-        <v>5.079290515334051</v>
+        <v>4.940290276213283</v>
       </c>
       <c r="D54">
-        <v>24.50957505668304</v>
+        <v>24.6716571330317</v>
       </c>
       <c r="E54">
-        <v>1.649261671855332</v>
+        <v>1.53813989333979</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2482,16 +2482,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>0.8989236976271903</v>
+        <v>1.34663357265804</v>
       </c>
       <c r="C55">
-        <v>5.35187984339414</v>
+        <v>4.083621531161793</v>
       </c>
       <c r="D55">
-        <v>24.48488525023961</v>
+        <v>24.87423492503024</v>
       </c>
       <c r="E55">
-        <v>2.024125100605625</v>
+        <v>1.71925069130928</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2499,16 +2499,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>1.837888813166072</v>
+        <v>1.497598518085351</v>
       </c>
       <c r="C56">
-        <v>4.123055674412982</v>
+        <v>5.005425688363625</v>
       </c>
       <c r="D56">
-        <v>24.77321859200997</v>
+        <v>24.45583479586761</v>
       </c>
       <c r="E56">
-        <v>1.479111011796064</v>
+        <v>1.136941532347282</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2516,16 +2516,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>1.766911556568217</v>
+        <v>0.3226921791736903</v>
       </c>
       <c r="C57">
-        <v>4.27687520356365</v>
+        <v>3.98764003214158</v>
       </c>
       <c r="D57">
-        <v>24.56163021769649</v>
+        <v>24.82829226483059</v>
       </c>
       <c r="E57">
-        <v>2.631158200750463</v>
+        <v>2.12337354856637</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2533,16 +2533,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>0.3535698420245916</v>
+        <v>1.122900015152961</v>
       </c>
       <c r="C58">
-        <v>4.189589189161594</v>
+        <v>4.078204121901044</v>
       </c>
       <c r="D58">
-        <v>24.72258615365367</v>
+        <v>24.44016258051151</v>
       </c>
       <c r="E58">
-        <v>1.435272894365171</v>
+        <v>1.58396369275754</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2550,16 +2550,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>1.480776437633489</v>
+        <v>1.082819832211841</v>
       </c>
       <c r="C59">
-        <v>4.029003888990555</v>
+        <v>4.513977611864374</v>
       </c>
       <c r="D59">
-        <v>24.62978231702373</v>
+        <v>24.72356599435389</v>
       </c>
       <c r="E59">
-        <v>2.213343364686652</v>
+        <v>1.802560465700983</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2567,16 +2567,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>1.947386217102828</v>
+        <v>1.531045662914803</v>
       </c>
       <c r="C60">
-        <v>4.529411628765335</v>
+        <v>4.032498304667114</v>
       </c>
       <c r="D60">
-        <v>24.46147406557821</v>
+        <v>24.9044065236653</v>
       </c>
       <c r="E60">
-        <v>1.719137771258849</v>
+        <v>1.387067527347596</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2584,16 +2584,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>2.006649303818615</v>
+        <v>1.589802209134636</v>
       </c>
       <c r="C61">
-        <v>4.145307465081962</v>
+        <v>4.318036572419882</v>
       </c>
       <c r="D61">
-        <v>24.8227367049869</v>
+        <v>24.81079320683206</v>
       </c>
       <c r="E61">
-        <v>2.080468447806259</v>
+        <v>2.230183502023245</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2601,16 +2601,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>1.957093756049902</v>
+        <v>1.303348740050686</v>
       </c>
       <c r="C62">
-        <v>4.209553312424677</v>
+        <v>4.295200767759716</v>
       </c>
       <c r="D62">
-        <v>24.88271096193889</v>
+        <v>24.60330968709728</v>
       </c>
       <c r="E62">
-        <v>2.485092536771508</v>
+        <v>2.005446914935391</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2618,16 +2618,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>1.167590442095932</v>
+        <v>1.518451839426841</v>
       </c>
       <c r="C63">
-        <v>5.285159983248686</v>
+        <v>4.020559273617608</v>
       </c>
       <c r="D63">
-        <v>24.93361033441284</v>
+        <v>24.85938005673085</v>
       </c>
       <c r="E63">
-        <v>1.703112779041338</v>
+        <v>2.642424505773939</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2635,16 +2635,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>1.93480171148224</v>
+        <v>1.207757477416461</v>
       </c>
       <c r="C64">
-        <v>5.295009324394579</v>
+        <v>4.630579468023841</v>
       </c>
       <c r="D64">
-        <v>24.7429057353087</v>
+        <v>24.62031958623629</v>
       </c>
       <c r="E64">
-        <v>1.770197504499456</v>
+        <v>2.243276906470946</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>1.239036316111097</v>
+        <v>1.230387585976694</v>
       </c>
       <c r="C65">
-        <v>5.426058007712303</v>
+        <v>4.623436658150086</v>
       </c>
       <c r="D65">
-        <v>24.63834128138473</v>
+        <v>24.5396562885795</v>
       </c>
       <c r="E65">
-        <v>2.350983820326359</v>
+        <v>1.305443750918934</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2669,16 +2669,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>1.758673923454924</v>
+        <v>3.355568417325071</v>
       </c>
       <c r="C66">
-        <v>11.00972346039145</v>
+        <v>12.12701301198723</v>
       </c>
       <c r="D66">
-        <v>49.61538788080363</v>
+        <v>49.61876927702531</v>
       </c>
       <c r="E66">
-        <v>6.751973255628856</v>
+        <v>5.285314507897851</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2686,16 +2686,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>2.172989518046351</v>
+        <v>3.322032961645851</v>
       </c>
       <c r="C67">
-        <v>11.25670052324619</v>
+        <v>11.79086606694883</v>
       </c>
       <c r="D67">
-        <v>49.96410856795394</v>
+        <v>49.72841275139797</v>
       </c>
       <c r="E67">
-        <v>5.420683403212961</v>
+        <v>5.431058532327112</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2703,16 +2703,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>2.075889746337803</v>
+        <v>3.120082118662423</v>
       </c>
       <c r="C68">
-        <v>11.6083317405028</v>
+        <v>11.71217079729706</v>
       </c>
       <c r="D68">
-        <v>49.85941721425816</v>
+        <v>49.86362257550075</v>
       </c>
       <c r="E68">
-        <v>5.987785457489232</v>
+        <v>6.215859302618915</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2720,16 +2720,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>3.265932330259516</v>
+        <v>2.036398400809234</v>
       </c>
       <c r="C69">
-        <v>11.18799689108145</v>
+        <v>10.96118655966529</v>
       </c>
       <c r="D69">
-        <v>49.96085534575136</v>
+        <v>49.94125573477441</v>
       </c>
       <c r="E69">
-        <v>6.435311140130429</v>
+        <v>5.736809696766611</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2737,16 +2737,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>2.191800710906444</v>
+        <v>2.11793046600087</v>
       </c>
       <c r="C70">
-        <v>11.92841546570467</v>
+        <v>12.26780641916457</v>
       </c>
       <c r="D70">
-        <v>49.84030807529466</v>
+        <v>49.8067567896083</v>
       </c>
       <c r="E70">
-        <v>5.778549625323959</v>
+        <v>5.509683841032852</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2754,16 +2754,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>2.509449872450655</v>
+        <v>1.770005457310164</v>
       </c>
       <c r="C71">
-        <v>10.98113615089236</v>
+        <v>12.25395604671692</v>
       </c>
       <c r="D71">
-        <v>49.92244481146446</v>
+        <v>49.6789018099399</v>
       </c>
       <c r="E71">
-        <v>6.498836291743562</v>
+        <v>6.53118631688015</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2771,16 +2771,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.095966478172514</v>
+        <v>3.020071363888114</v>
       </c>
       <c r="C72">
-        <v>11.35854764890733</v>
+        <v>11.91577373500315</v>
       </c>
       <c r="D72">
-        <v>49.68083781933206</v>
+        <v>49.73820136408673</v>
       </c>
       <c r="E72">
-        <v>6.248959039533091</v>
+        <v>6.018196504141361</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2788,16 +2788,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>2.946384464437393</v>
+        <v>2.667658859425841</v>
       </c>
       <c r="C73">
-        <v>11.21456510004627</v>
+        <v>12.08994436556641</v>
       </c>
       <c r="D73">
-        <v>49.54556631329744</v>
+        <v>49.58148404311077</v>
       </c>
       <c r="E73">
-        <v>5.623000376831431</v>
+        <v>5.292818834257427</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2805,16 +2805,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>3.322363046190645</v>
+        <v>2.224432460075226</v>
       </c>
       <c r="C74">
-        <v>12.52648395035401</v>
+        <v>12.29843912851419</v>
       </c>
       <c r="D74">
-        <v>49.53241924168568</v>
+        <v>49.96978471569334</v>
       </c>
       <c r="E74">
-        <v>5.413501212149159</v>
+        <v>6.471437052273131</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2822,16 +2822,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>3.134172266010751</v>
+        <v>2.788650181180617</v>
       </c>
       <c r="C75">
-        <v>11.84812566937862</v>
+        <v>10.98708090672892</v>
       </c>
       <c r="D75">
-        <v>49.6584585367291</v>
+        <v>49.80025482722289</v>
       </c>
       <c r="E75">
-        <v>5.942606361124795</v>
+        <v>6.318601827732117</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2839,16 +2839,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>2.841698652309104</v>
+        <v>3.409175373636301</v>
       </c>
       <c r="C76">
-        <v>12.47925242860893</v>
+        <v>12.4845383749401</v>
       </c>
       <c r="D76">
-        <v>49.90979874728364</v>
+        <v>50.01323507409586</v>
       </c>
       <c r="E76">
-        <v>5.604173035891455</v>
+        <v>6.128209126740988</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2856,16 +2856,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>3.060236327656927</v>
+        <v>2.333698589466655</v>
       </c>
       <c r="C77">
-        <v>11.22875203182766</v>
+        <v>11.89881406428589</v>
       </c>
       <c r="D77">
-        <v>49.62093158802119</v>
+        <v>49.56049411929813</v>
       </c>
       <c r="E77">
-        <v>5.924074855249756</v>
+        <v>5.656494846589861</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2873,16 +2873,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>2.005306938573189</v>
+        <v>2.061183889072479</v>
       </c>
       <c r="C78">
-        <v>11.33924130361846</v>
+        <v>11.14913914140924</v>
       </c>
       <c r="D78">
-        <v>49.61657293732835</v>
+        <v>49.93378141381358</v>
       </c>
       <c r="E78">
-        <v>5.589998770379611</v>
+        <v>6.657718392660486</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2890,16 +2890,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>1.736620656273004</v>
+        <v>2.26990094242532</v>
       </c>
       <c r="C79">
-        <v>11.73943337125379</v>
+        <v>12.52578124156083</v>
       </c>
       <c r="D79">
-        <v>49.92877948523923</v>
+        <v>49.65491861682379</v>
       </c>
       <c r="E79">
-        <v>6.348993851752897</v>
+        <v>6.696735174575926</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2907,16 +2907,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>2.495136594749015</v>
+        <v>2.26953509501712</v>
       </c>
       <c r="C80">
-        <v>12.39546927603237</v>
+        <v>11.26786402613301</v>
       </c>
       <c r="D80">
-        <v>49.61471492413204</v>
+        <v>49.86047360800602</v>
       </c>
       <c r="E80">
-        <v>5.766254174257029</v>
+        <v>6.634265088767204</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2924,16 +2924,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>3.081521294562178</v>
+        <v>2.796342906371165</v>
       </c>
       <c r="C81">
-        <v>11.05554083336246</v>
+        <v>11.56236021047399</v>
       </c>
       <c r="D81">
-        <v>49.71246833493442</v>
+        <v>49.56477640268047</v>
       </c>
       <c r="E81">
-        <v>5.374583901014138</v>
+        <v>5.816068905112533</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2941,16 +2941,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>1.762274926035553</v>
+        <v>3.119304068007062</v>
       </c>
       <c r="C82">
-        <v>11.72824156545743</v>
+        <v>12.27707121820607</v>
       </c>
       <c r="D82">
-        <v>49.79250960923417</v>
+        <v>49.86109989125165</v>
       </c>
       <c r="E82">
-        <v>6.73696505011784</v>
+        <v>6.665189073129625</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2958,16 +2958,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>1.654442811901103</v>
+        <v>1.789648089640747</v>
       </c>
       <c r="C83">
-        <v>11.11112319910926</v>
+        <v>12.09570861683482</v>
       </c>
       <c r="D83">
-        <v>49.85673518966585</v>
+        <v>49.52419390498924</v>
       </c>
       <c r="E83">
-        <v>5.479626792600229</v>
+        <v>5.379948780638809</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2975,16 +2975,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>2.587396324619689</v>
+        <v>3.138288340308092</v>
       </c>
       <c r="C84">
-        <v>10.98969981643416</v>
+        <v>11.8569191166517</v>
       </c>
       <c r="D84">
-        <v>49.91243335786594</v>
+        <v>49.71115424371722</v>
       </c>
       <c r="E84">
-        <v>6.461287885079238</v>
+        <v>5.712503644316084</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2992,16 +2992,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>3.218172076130322</v>
+        <v>1.620723686258709</v>
       </c>
       <c r="C85">
-        <v>11.50253720243339</v>
+        <v>11.99900121689122</v>
       </c>
       <c r="D85">
-        <v>49.75125033085737</v>
+        <v>49.73069495059775</v>
       </c>
       <c r="E85">
-        <v>5.249861279069092</v>
+        <v>6.61019719617456</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3009,16 +3009,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>2.882534681852165</v>
+        <v>3.168888392250126</v>
       </c>
       <c r="C86">
-        <v>11.80315390805036</v>
+        <v>12.26944262094447</v>
       </c>
       <c r="D86">
-        <v>49.71617332155319</v>
+        <v>49.8807699337007</v>
       </c>
       <c r="E86">
-        <v>5.417580065678095</v>
+        <v>5.268076782044046</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3026,16 +3026,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>3.204505489670303</v>
+        <v>1.628416287696114</v>
       </c>
       <c r="C87">
-        <v>12.2191534776144</v>
+        <v>11.8268426653946</v>
       </c>
       <c r="D87">
-        <v>49.9162572445829</v>
+        <v>49.62539647447456</v>
       </c>
       <c r="E87">
-        <v>6.199760901495151</v>
+        <v>6.666998276573683</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3043,16 +3043,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>2.952669093576499</v>
+        <v>3.243556189081533</v>
       </c>
       <c r="C88">
-        <v>11.41521207689273</v>
+        <v>11.60319332775817</v>
       </c>
       <c r="D88">
-        <v>49.67050183659281</v>
+        <v>49.5481164915277</v>
       </c>
       <c r="E88">
-        <v>5.435590199114602</v>
+        <v>6.529175845305257</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3060,16 +3060,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>2.508464385221374</v>
+        <v>2.631528395474913</v>
       </c>
       <c r="C89">
-        <v>11.36468084935463</v>
+        <v>12.05583439006315</v>
       </c>
       <c r="D89">
-        <v>49.63246728943543</v>
+        <v>49.78016221684098</v>
       </c>
       <c r="E89">
-        <v>5.826909310185523</v>
+        <v>6.461771876249356</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3077,16 +3077,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>2.630147211310119</v>
+        <v>2.985513164095199</v>
       </c>
       <c r="C90">
-        <v>11.02555381952847</v>
+        <v>11.66983294099791</v>
       </c>
       <c r="D90">
-        <v>49.76072712990697</v>
+        <v>50.00831397808062</v>
       </c>
       <c r="E90">
-        <v>5.215155904204023</v>
+        <v>5.186447754818101</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3094,16 +3094,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>1.864106803059773</v>
+        <v>3.200010435480746</v>
       </c>
       <c r="C91">
-        <v>12.01917815384592</v>
+        <v>11.07015218158477</v>
       </c>
       <c r="D91">
-        <v>49.58270956815955</v>
+        <v>49.79214111315556</v>
       </c>
       <c r="E91">
-        <v>6.710352151571093</v>
+        <v>5.829544364498193</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3111,16 +3111,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>2.251515556997563</v>
+        <v>1.763119731364597</v>
       </c>
       <c r="C92">
-        <v>12.31798767697917</v>
+        <v>11.10909037259095</v>
       </c>
       <c r="D92">
-        <v>49.86845595160038</v>
+        <v>49.61065273652797</v>
       </c>
       <c r="E92">
-        <v>6.323432888085616</v>
+        <v>5.810626305412312</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3128,16 +3128,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>2.409610040205911</v>
+        <v>1.786708662718198</v>
       </c>
       <c r="C93">
-        <v>11.33796186621688</v>
+        <v>12.13876906149911</v>
       </c>
       <c r="D93">
-        <v>49.69180804428018</v>
+        <v>49.75017329022712</v>
       </c>
       <c r="E93">
-        <v>5.978637220900217</v>
+        <v>6.763849593803088</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3145,16 +3145,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>3.378269216239991</v>
+        <v>2.192023097665313</v>
       </c>
       <c r="C94">
-        <v>11.80967089793802</v>
+        <v>11.14355231926362</v>
       </c>
       <c r="D94">
-        <v>49.95765589150324</v>
+        <v>49.69992206726321</v>
       </c>
       <c r="E94">
-        <v>6.312871019688477</v>
+        <v>5.213739081338763</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3162,16 +3162,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>2.702576162997715</v>
+        <v>2.098147864493232</v>
       </c>
       <c r="C95">
-        <v>12.43439581894743</v>
+        <v>11.55398390172075</v>
       </c>
       <c r="D95">
-        <v>49.92956699345293</v>
+        <v>49.92459001451419</v>
       </c>
       <c r="E95">
-        <v>5.609249604706758</v>
+        <v>5.654190552532621</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3179,16 +3179,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>2.256359985870479</v>
+        <v>3.289260067969994</v>
       </c>
       <c r="C96">
-        <v>11.4163406465007</v>
+        <v>11.42480075187355</v>
       </c>
       <c r="D96">
-        <v>50.01511198258392</v>
+        <v>49.76290191224071</v>
       </c>
       <c r="E96">
-        <v>5.252388847110002</v>
+        <v>6.549404052907769</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3196,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>2.704932468303032</v>
+        <v>1.754887585761624</v>
       </c>
       <c r="C97">
-        <v>10.99153767626337</v>
+        <v>11.20434221757824</v>
       </c>
       <c r="D97">
-        <v>49.64539121923733</v>
+        <v>49.99961571311022</v>
       </c>
       <c r="E97">
-        <v>6.37798610766925</v>
+        <v>6.650661899532292</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3213,16 +3213,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>2.178820440746949</v>
+        <v>1.78202293106997</v>
       </c>
       <c r="C98">
-        <v>12.42346037873812</v>
+        <v>12.33912589281699</v>
       </c>
       <c r="D98">
-        <v>49.63401409441549</v>
+        <v>49.67539400187962</v>
       </c>
       <c r="E98">
-        <v>6.083586466238842</v>
+        <v>5.285832101458237</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3230,16 +3230,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>1.825588798756315</v>
+        <v>2.442198079779018</v>
       </c>
       <c r="C99">
-        <v>10.98895906765944</v>
+        <v>11.77580205025932</v>
       </c>
       <c r="D99">
-        <v>49.91443247734595</v>
+        <v>49.96768776226789</v>
       </c>
       <c r="E99">
-        <v>6.495896876845761</v>
+        <v>5.537869823398873</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3247,16 +3247,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>2.062167340003145</v>
+        <v>3.020463210742745</v>
       </c>
       <c r="C100">
-        <v>11.9318966920568</v>
+        <v>11.17252051212623</v>
       </c>
       <c r="D100">
-        <v>49.52348897865348</v>
+        <v>49.53695149310622</v>
       </c>
       <c r="E100">
-        <v>5.417293865851526</v>
+        <v>5.570731980533919</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3264,16 +3264,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>2.744835210391791</v>
+        <v>3.242386064377203</v>
       </c>
       <c r="C101">
-        <v>11.6605696177611</v>
+        <v>12.13824115979401</v>
       </c>
       <c r="D101">
-        <v>49.66710978819374</v>
+        <v>49.72327558572039</v>
       </c>
       <c r="E101">
-        <v>6.439877557419877</v>
+        <v>5.550955312229116</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3281,16 +3281,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>2.668179059250964</v>
+        <v>3.196433318299909</v>
       </c>
       <c r="C102">
-        <v>12.44182198314578</v>
+        <v>11.61293254471544</v>
       </c>
       <c r="D102">
-        <v>49.972877934713</v>
+        <v>49.67785813796644</v>
       </c>
       <c r="E102">
-        <v>6.378399002788143</v>
+        <v>5.271437821998894</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3298,16 +3298,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>3.121183175321729</v>
+        <v>3.165710097510108</v>
       </c>
       <c r="C103">
-        <v>11.68803121979877</v>
+        <v>12.30149879902082</v>
       </c>
       <c r="D103">
-        <v>49.94339214727419</v>
+        <v>49.89554816171159</v>
       </c>
       <c r="E103">
-        <v>5.661682919992861</v>
+        <v>5.841316009469105</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3315,16 +3315,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>2.011263373796566</v>
+        <v>1.692539875464695</v>
       </c>
       <c r="C104">
-        <v>12.00482059315108</v>
+        <v>11.41856034755984</v>
       </c>
       <c r="D104">
-        <v>49.71061348873186</v>
+        <v>49.88070806255269</v>
       </c>
       <c r="E104">
-        <v>5.962932376707165</v>
+        <v>5.91188101860509</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3332,16 +3332,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>1.796966693259302</v>
+        <v>3.092867811581316</v>
       </c>
       <c r="C105">
-        <v>12.30400053175172</v>
+        <v>12.35578757162434</v>
       </c>
       <c r="D105">
-        <v>49.61744837392659</v>
+        <v>49.61477159862827</v>
       </c>
       <c r="E105">
-        <v>6.260096024880204</v>
+        <v>5.551749194556145</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3349,16 +3349,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>1.72944370172914</v>
+        <v>2.498144762707891</v>
       </c>
       <c r="C106">
-        <v>12.0116090039796</v>
+        <v>11.90574817937342</v>
       </c>
       <c r="D106">
-        <v>49.71159617486887</v>
+        <v>49.68902193393316</v>
       </c>
       <c r="E106">
-        <v>6.593776662374715</v>
+        <v>6.32818567284348</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3366,16 +3366,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>2.394576988860174</v>
+        <v>2.964250753103403</v>
       </c>
       <c r="C107">
-        <v>11.15666027013388</v>
+        <v>12.44408014527484</v>
       </c>
       <c r="D107">
-        <v>49.63578051279014</v>
+        <v>49.95457161703577</v>
       </c>
       <c r="E107">
-        <v>5.654773346352575</v>
+        <v>6.400659210688707</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3383,16 +3383,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>1.930772591479929</v>
+        <v>3.371389179967412</v>
       </c>
       <c r="C108">
-        <v>10.95499391238927</v>
+        <v>12.07629492899583</v>
       </c>
       <c r="D108">
-        <v>49.88824967620943</v>
+        <v>49.6706889156191</v>
       </c>
       <c r="E108">
-        <v>6.344004427126598</v>
+        <v>6.156575557604443</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3400,16 +3400,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>3.231608750374234</v>
+        <v>2.445141434079483</v>
       </c>
       <c r="C109">
-        <v>12.00198181940126</v>
+        <v>11.97662127431641</v>
       </c>
       <c r="D109">
-        <v>49.70010403528211</v>
+        <v>49.58252454108252</v>
       </c>
       <c r="E109">
-        <v>6.537304923097709</v>
+        <v>5.996949961108376</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3417,16 +3417,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>2.269360468506855</v>
+        <v>3.275057297773007</v>
       </c>
       <c r="C110">
-        <v>11.71043036524099</v>
+        <v>12.29226256500423</v>
       </c>
       <c r="D110">
-        <v>50.00264047576028</v>
+        <v>49.86172490786355</v>
       </c>
       <c r="E110">
-        <v>5.840997308102284</v>
+        <v>5.209333308021785</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3434,16 +3434,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>3.304470330064798</v>
+        <v>2.112999327699638</v>
       </c>
       <c r="C111">
-        <v>11.61354007575827</v>
+        <v>11.96983506408338</v>
       </c>
       <c r="D111">
-        <v>49.52064125937432</v>
+        <v>49.72766817934775</v>
       </c>
       <c r="E111">
-        <v>6.230828806007919</v>
+        <v>6.236607463342947</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3451,16 +3451,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>2.012583649075368</v>
+        <v>2.158562901464358</v>
       </c>
       <c r="C112">
-        <v>12.15232526268625</v>
+        <v>11.10891254138354</v>
       </c>
       <c r="D112">
-        <v>49.82356097372138</v>
+        <v>49.88488556223425</v>
       </c>
       <c r="E112">
-        <v>6.758309244936363</v>
+        <v>6.571553181985199</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3468,16 +3468,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>2.527101910709775</v>
+        <v>1.809885672479815</v>
       </c>
       <c r="C113">
-        <v>12.46167411287121</v>
+        <v>11.00774068051991</v>
       </c>
       <c r="D113">
-        <v>49.72689314506541</v>
+        <v>49.89355218007768</v>
       </c>
       <c r="E113">
-        <v>5.342553654547321</v>
+        <v>5.738609215334939</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3485,16 +3485,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>1.974364929343246</v>
+        <v>2.465515554779792</v>
       </c>
       <c r="C114">
-        <v>11.73700367826151</v>
+        <v>11.60825936616757</v>
       </c>
       <c r="D114">
-        <v>50.00000698752546</v>
+        <v>49.60596178123609</v>
       </c>
       <c r="E114">
-        <v>5.798305834647715</v>
+        <v>6.706065197608896</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3502,16 +3502,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>1.890821094382233</v>
+        <v>1.951048663837026</v>
       </c>
       <c r="C115">
-        <v>11.57499350216571</v>
+        <v>11.10223632562148</v>
       </c>
       <c r="D115">
-        <v>49.58298053433006</v>
+        <v>49.87306031187286</v>
       </c>
       <c r="E115">
-        <v>5.882637841230932</v>
+        <v>5.490878397203107</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3519,16 +3519,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>2.569098836476686</v>
+        <v>2.969562549104762</v>
       </c>
       <c r="C116">
-        <v>11.33090374067098</v>
+        <v>12.19763779608417</v>
       </c>
       <c r="D116">
-        <v>49.8552756077009</v>
+        <v>49.6983399753385</v>
       </c>
       <c r="E116">
-        <v>5.808754163862197</v>
+        <v>5.28096458918067</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3536,16 +3536,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>2.562614609329867</v>
+        <v>3.179836986956173</v>
       </c>
       <c r="C117">
-        <v>12.24779141143398</v>
+        <v>11.80986393601927</v>
       </c>
       <c r="D117">
-        <v>49.85236891113179</v>
+        <v>49.57259340150534</v>
       </c>
       <c r="E117">
-        <v>6.586124323568763</v>
+        <v>6.454176514648598</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3553,16 +3553,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>2.893351167096012</v>
+        <v>2.870441555045302</v>
       </c>
       <c r="C118">
-        <v>10.96566172001431</v>
+        <v>11.12828039312921</v>
       </c>
       <c r="D118">
-        <v>49.60858454568619</v>
+        <v>49.57479950305677</v>
       </c>
       <c r="E118">
-        <v>6.767942961289603</v>
+        <v>5.339587776567892</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3570,16 +3570,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>3.05568212381206</v>
+        <v>3.328825190463501</v>
       </c>
       <c r="C119">
-        <v>12.01387362136073</v>
+        <v>12.50693102892161</v>
       </c>
       <c r="D119">
-        <v>49.91506708970081</v>
+        <v>49.9032094758757</v>
       </c>
       <c r="E119">
-        <v>6.139556907529436</v>
+        <v>6.163132305143383</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3587,16 +3587,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>1.943216546231971</v>
+        <v>2.308673386672441</v>
       </c>
       <c r="C120">
-        <v>10.99451574966663</v>
+        <v>11.8793634822026</v>
       </c>
       <c r="D120">
-        <v>49.74096677865718</v>
+        <v>49.64842836762317</v>
       </c>
       <c r="E120">
-        <v>5.252146062320888</v>
+        <v>6.227965714861548</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3604,16 +3604,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>2.958267771115754</v>
+        <v>2.299164139495777</v>
       </c>
       <c r="C121">
-        <v>11.96803227398549</v>
+        <v>11.13950684232008</v>
       </c>
       <c r="D121">
-        <v>49.71206037750419</v>
+        <v>49.53217307846888</v>
       </c>
       <c r="E121">
-        <v>6.723227524558613</v>
+        <v>6.038775571757308</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3621,16 +3621,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>3.112866817320568</v>
+        <v>1.906093022118147</v>
       </c>
       <c r="C122">
-        <v>11.06594953730875</v>
+        <v>11.67534730851279</v>
       </c>
       <c r="D122">
-        <v>49.7870738785269</v>
+        <v>49.91178899227103</v>
       </c>
       <c r="E122">
-        <v>6.536591737459584</v>
+        <v>5.83147351655313</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3638,16 +3638,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>2.666082794029839</v>
+        <v>2.970917543136018</v>
       </c>
       <c r="C123">
-        <v>11.40071494372539</v>
+        <v>12.18678969276513</v>
       </c>
       <c r="D123">
-        <v>49.52536836446313</v>
+        <v>49.70917944354626</v>
       </c>
       <c r="E123">
-        <v>5.345720852929809</v>
+        <v>5.48308716074204</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3655,16 +3655,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>2.303544380145841</v>
+        <v>3.217751854837742</v>
       </c>
       <c r="C124">
-        <v>12.36762481389716</v>
+        <v>12.34669618096538</v>
       </c>
       <c r="D124">
-        <v>49.59996210911695</v>
+        <v>49.88274069166953</v>
       </c>
       <c r="E124">
-        <v>6.217325070634687</v>
+        <v>5.564686791855624</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3672,16 +3672,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>2.337602651790638</v>
+        <v>2.492829581404647</v>
       </c>
       <c r="C125">
-        <v>11.48672562528166</v>
+        <v>11.87013890752023</v>
       </c>
       <c r="D125">
-        <v>49.52290828710395</v>
+        <v>49.52424017195132</v>
       </c>
       <c r="E125">
-        <v>6.03989142831464</v>
+        <v>5.89973776522416</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3689,16 +3689,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>2.876811835105506</v>
+        <v>2.731394362290692</v>
       </c>
       <c r="C126">
-        <v>11.20389660651462</v>
+        <v>11.74946256291022</v>
       </c>
       <c r="D126">
-        <v>49.85246608913797</v>
+        <v>49.77207368387959</v>
       </c>
       <c r="E126">
-        <v>5.183556471181972</v>
+        <v>5.879619467782203</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3706,16 +3706,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>2.78514871761542</v>
+        <v>2.734466776949702</v>
       </c>
       <c r="C127">
-        <v>11.67423893057189</v>
+        <v>11.14551964259243</v>
       </c>
       <c r="D127">
-        <v>49.70418518397964</v>
+        <v>49.74199874338084</v>
       </c>
       <c r="E127">
-        <v>5.505221285570581</v>
+        <v>6.079118293609106</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3723,16 +3723,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>2.252866594541075</v>
+        <v>2.841701535856843</v>
       </c>
       <c r="C128">
-        <v>12.11463776498482</v>
+        <v>12.09452213085121</v>
       </c>
       <c r="D128">
-        <v>49.95932372653513</v>
+        <v>49.78976559514398</v>
       </c>
       <c r="E128">
-        <v>5.512843270323266</v>
+        <v>5.709163923238599</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3740,16 +3740,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>2.920475635746648</v>
+        <v>1.645973477311834</v>
       </c>
       <c r="C129">
-        <v>12.19230643036422</v>
+        <v>11.57647864658438</v>
       </c>
       <c r="D129">
-        <v>49.69420967531891</v>
+        <v>49.86968614508576</v>
       </c>
       <c r="E129">
-        <v>5.49495477606496</v>
+        <v>6.753487658129677</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3757,16 +3757,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>2.184327609675141</v>
+        <v>3.16718983040511</v>
       </c>
       <c r="C130">
-        <v>12.16854720326707</v>
+        <v>12.04285732226536</v>
       </c>
       <c r="D130">
-        <v>49.87104948292875</v>
+        <v>49.77399221286657</v>
       </c>
       <c r="E130">
-        <v>6.621389012593198</v>
+        <v>5.492409364599826</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3774,16 +3774,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>3.070560288560597</v>
+        <v>2.92181829411818</v>
       </c>
       <c r="C131">
-        <v>11.5829660579672</v>
+        <v>12.0348004964192</v>
       </c>
       <c r="D131">
-        <v>49.60783299288185</v>
+        <v>49.86282062544395</v>
       </c>
       <c r="E131">
-        <v>5.30905135328976</v>
+        <v>6.523090938265374</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3791,16 +3791,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>2.936954651546636</v>
+        <v>3.198300496875293</v>
       </c>
       <c r="C132">
-        <v>10.96876726280565</v>
+        <v>12.11675258397446</v>
       </c>
       <c r="D132">
-        <v>49.61122529596916</v>
+        <v>49.75300803160832</v>
       </c>
       <c r="E132">
-        <v>6.178152727702106</v>
+        <v>6.354975754647235</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3808,16 +3808,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>3.361473526535861</v>
+        <v>3.316447604892993</v>
       </c>
       <c r="C133">
-        <v>12.25345929691733</v>
+        <v>11.40846695456345</v>
       </c>
       <c r="D133">
-        <v>49.8616519857209</v>
+        <v>49.6340718845134</v>
       </c>
       <c r="E133">
-        <v>5.423727915833932</v>
+        <v>6.486445914081573</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3825,16 +3825,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>2.385702275061901</v>
+        <v>3.26980150056059</v>
       </c>
       <c r="C134">
-        <v>12.37413092109668</v>
+        <v>11.17844639042259</v>
       </c>
       <c r="D134">
-        <v>50.00574239508806</v>
+        <v>49.58242225451199</v>
       </c>
       <c r="E134">
-        <v>5.621044722265347</v>
+        <v>5.920265855870613</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3842,16 +3842,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>2.775979919246327</v>
+        <v>2.755742996679501</v>
       </c>
       <c r="C135">
-        <v>10.95444505969403</v>
+        <v>12.31902587186197</v>
       </c>
       <c r="D135">
-        <v>49.9995325859105</v>
+        <v>49.95659002801535</v>
       </c>
       <c r="E135">
-        <v>5.409577000766483</v>
+        <v>5.253165675809858</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3859,16 +3859,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>3.241745461616517</v>
+        <v>2.407357893391212</v>
       </c>
       <c r="C136">
-        <v>11.70229092686278</v>
+        <v>11.2045286448714</v>
       </c>
       <c r="D136">
-        <v>49.92020610523126</v>
+        <v>49.82088506737452</v>
       </c>
       <c r="E136">
-        <v>6.247906141414904</v>
+        <v>5.772343785470753</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3876,16 +3876,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>1.71917365851092</v>
+        <v>2.692025416348085</v>
       </c>
       <c r="C137">
-        <v>11.82080630857218</v>
+        <v>12.1973738759916</v>
       </c>
       <c r="D137">
-        <v>49.63762683409208</v>
+        <v>49.98380140742064</v>
       </c>
       <c r="E137">
-        <v>5.841882006610105</v>
+        <v>5.566949616096894</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3893,16 +3893,16 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>2.324216863202198</v>
+        <v>2.380479960460417</v>
       </c>
       <c r="C138">
-        <v>11.72617861517919</v>
+        <v>11.4543886421089</v>
       </c>
       <c r="D138">
-        <v>49.6981362489805</v>
+        <v>49.80246214926569</v>
       </c>
       <c r="E138">
-        <v>6.42792553048096</v>
+        <v>5.513401078371307</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3910,16 +3910,16 @@
         <v>142</v>
       </c>
       <c r="B139">
-        <v>2.545686032748241</v>
+        <v>2.496686447058165</v>
       </c>
       <c r="C139">
-        <v>11.55429878985532</v>
+        <v>12.47228322037424</v>
       </c>
       <c r="D139">
-        <v>49.8524245344809</v>
+        <v>49.61123298412058</v>
       </c>
       <c r="E139">
-        <v>5.838760956346185</v>
+        <v>5.258845490051332</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3927,16 +3927,16 @@
         <v>143</v>
       </c>
       <c r="B140">
-        <v>3.170877347154075</v>
+        <v>3.37460511336473</v>
       </c>
       <c r="C140">
-        <v>11.12763025492151</v>
+        <v>11.77652531970716</v>
       </c>
       <c r="D140">
-        <v>49.77864264663074</v>
+        <v>49.66845778724957</v>
       </c>
       <c r="E140">
-        <v>6.721183547278813</v>
+        <v>5.425567488117285</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3944,16 +3944,16 @@
         <v>144</v>
       </c>
       <c r="B141">
-        <v>4.377652841018962</v>
+        <v>4.196448877785261</v>
       </c>
       <c r="C141">
-        <v>18.26887947869091</v>
+        <v>18.08248713384027</v>
       </c>
       <c r="D141">
-        <v>23.79283259565546</v>
+        <v>23.75937449910269</v>
       </c>
       <c r="E141">
-        <v>7.600985817971908</v>
+        <v>6.534782281038478</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3961,16 +3961,16 @@
         <v>145</v>
       </c>
       <c r="B142">
-        <v>3.751122532857558</v>
+        <v>3.681013834007544</v>
       </c>
       <c r="C142">
-        <v>18.41954046982333</v>
+        <v>17.5877731484603</v>
       </c>
       <c r="D142">
-        <v>23.47542351392672</v>
+        <v>23.88603319664164</v>
       </c>
       <c r="E142">
-        <v>7.660142927933089</v>
+        <v>6.454616330778007</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3978,16 +3978,16 @@
         <v>146</v>
       </c>
       <c r="B143">
-        <v>4.354800733059468</v>
+        <v>3.035027464817137</v>
       </c>
       <c r="C143">
-        <v>17.50172258228503</v>
+        <v>17.0984240090871</v>
       </c>
       <c r="D143">
-        <v>23.5531063622984</v>
+        <v>23.8321491224078</v>
       </c>
       <c r="E143">
-        <v>7.633334496960284</v>
+        <v>7.953939660224417</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3995,16 +3995,16 @@
         <v>147</v>
       </c>
       <c r="B144">
-        <v>4.732374803842726</v>
+        <v>3.413190097990686</v>
       </c>
       <c r="C144">
-        <v>18.08086489653769</v>
+        <v>17.6550774244723</v>
       </c>
       <c r="D144">
-        <v>23.64658214532216</v>
+        <v>23.811376817187</v>
       </c>
       <c r="E144">
-        <v>7.785034736586051</v>
+        <v>7.831180099607001</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4012,16 +4012,16 @@
         <v>148</v>
       </c>
       <c r="B145">
-        <v>3.189758196167511</v>
+        <v>4.459869079261578</v>
       </c>
       <c r="C145">
-        <v>16.94452952173991</v>
+        <v>17.23342776917606</v>
       </c>
       <c r="D145">
-        <v>23.83781115382009</v>
+        <v>23.67503706413896</v>
       </c>
       <c r="E145">
-        <v>7.457630357775336</v>
+        <v>7.91636151047042</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4029,16 +4029,16 @@
         <v>149</v>
       </c>
       <c r="B146">
-        <v>3.006396646596667</v>
+        <v>4.107589640430134</v>
       </c>
       <c r="C146">
-        <v>17.38971586688543</v>
+        <v>18.22859778469376</v>
       </c>
       <c r="D146">
-        <v>23.46715406441969</v>
+        <v>23.63819005209044</v>
       </c>
       <c r="E146">
-        <v>6.701309956528932</v>
+        <v>6.473408403158841</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4046,16 +4046,16 @@
         <v>150</v>
       </c>
       <c r="B147">
-        <v>4.565980204850846</v>
+        <v>4.656883788879658</v>
       </c>
       <c r="C147">
-        <v>18.19807087398815</v>
+        <v>17.2477274335513</v>
       </c>
       <c r="D147">
-        <v>23.68636533774857</v>
+        <v>23.77090694673004</v>
       </c>
       <c r="E147">
-        <v>6.761196843906624</v>
+        <v>6.962962865256336</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4063,16 +4063,16 @@
         <v>151</v>
       </c>
       <c r="B148">
-        <v>4.694482496939849</v>
+        <v>3.502631609327193</v>
       </c>
       <c r="C148">
-        <v>17.86093825825774</v>
+        <v>17.1353988710672</v>
       </c>
       <c r="D148">
-        <v>23.73869484084042</v>
+        <v>23.81668197402255</v>
       </c>
       <c r="E148">
-        <v>7.069652139972762</v>
+        <v>6.764143004280208</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4080,16 +4080,16 @@
         <v>152</v>
       </c>
       <c r="B149">
-        <v>3.914268680211344</v>
+        <v>4.375409961841946</v>
       </c>
       <c r="C149">
-        <v>17.42516022227188</v>
+        <v>17.82431407715656</v>
       </c>
       <c r="D149">
-        <v>23.56983733977083</v>
+        <v>23.515992900615</v>
       </c>
       <c r="E149">
-        <v>6.94938848439408</v>
+        <v>7.99402216629491</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4097,16 +4097,16 @@
         <v>153</v>
       </c>
       <c r="B150">
-        <v>4.169778972301858</v>
+        <v>4.001393460658708</v>
       </c>
       <c r="C150">
-        <v>17.41973100719951</v>
+        <v>17.85982396522055</v>
       </c>
       <c r="D150">
-        <v>23.51766573346331</v>
+        <v>23.71216216508926</v>
       </c>
       <c r="E150">
-        <v>7.368392623712647</v>
+        <v>7.46631533600176</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4114,16 +4114,16 @@
         <v>154</v>
       </c>
       <c r="B151">
-        <v>4.387590584288226</v>
+        <v>3.579446851061465</v>
       </c>
       <c r="C151">
-        <v>18.36588501754505</v>
+        <v>17.66611598900338</v>
       </c>
       <c r="D151">
-        <v>23.53529595298188</v>
+        <v>23.84581983694318</v>
       </c>
       <c r="E151">
-        <v>7.005711518245795</v>
+        <v>7.852894516521912</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4131,16 +4131,16 @@
         <v>155</v>
       </c>
       <c r="B152">
-        <v>3.057106451349773</v>
+        <v>4.392356767081955</v>
       </c>
       <c r="C152">
-        <v>17.27640578412299</v>
+        <v>17.96838346773329</v>
       </c>
       <c r="D152">
-        <v>23.61818769427441</v>
+        <v>23.77490593002992</v>
       </c>
       <c r="E152">
-        <v>7.168293782902802</v>
+        <v>7.103013457393104</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4148,16 +4148,16 @@
         <v>156</v>
       </c>
       <c r="B153">
-        <v>3.76956522748721</v>
+        <v>4.659698005981737</v>
       </c>
       <c r="C153">
-        <v>17.29368080929436</v>
+        <v>17.56787294606571</v>
       </c>
       <c r="D153">
-        <v>23.47626868791793</v>
+        <v>23.46359371243408</v>
       </c>
       <c r="E153">
-        <v>7.336044142025813</v>
+        <v>7.488305680024089</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4165,16 +4165,16 @@
         <v>157</v>
       </c>
       <c r="B154">
-        <v>3.842028640615065</v>
+        <v>3.441900447606162</v>
       </c>
       <c r="C154">
-        <v>17.54452787697338</v>
+        <v>17.71582909450349</v>
       </c>
       <c r="D154">
-        <v>23.75622840693863</v>
+        <v>23.67630474926088</v>
       </c>
       <c r="E154">
-        <v>7.745655683915223</v>
+        <v>7.323874733996479</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4182,16 +4182,16 @@
         <v>158</v>
       </c>
       <c r="B155">
-        <v>4.434831819530427</v>
+        <v>4.122132455386428</v>
       </c>
       <c r="C155">
-        <v>18.17325173501407</v>
+        <v>17.93739271525715</v>
       </c>
       <c r="D155">
-        <v>23.44054572860734</v>
+        <v>23.91606183965653</v>
       </c>
       <c r="E155">
-        <v>7.395909992028701</v>
+        <v>7.24008198817878</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4199,16 +4199,16 @@
         <v>159</v>
       </c>
       <c r="B156">
-        <v>4.052137206199892</v>
+        <v>3.298525308144291</v>
       </c>
       <c r="C156">
-        <v>17.9762076270389</v>
+        <v>16.90196596649304</v>
       </c>
       <c r="D156">
-        <v>23.92546661628327</v>
+        <v>23.78276706504013</v>
       </c>
       <c r="E156">
-        <v>7.218375924573863</v>
+        <v>6.854263712769642</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4216,16 +4216,16 @@
         <v>160</v>
       </c>
       <c r="B157">
-        <v>4.19273609806242</v>
+        <v>4.534932071771039</v>
       </c>
       <c r="C157">
-        <v>18.26688856315625</v>
+        <v>17.04590155717228</v>
       </c>
       <c r="D157">
-        <v>23.91403600834082</v>
+        <v>23.53741226019574</v>
       </c>
       <c r="E157">
-        <v>7.508049809476669</v>
+        <v>7.260599639669572</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4233,16 +4233,16 @@
         <v>161</v>
       </c>
       <c r="B158">
-        <v>3.964835859025783</v>
+        <v>3.636026429988279</v>
       </c>
       <c r="C158">
-        <v>17.67277111555176</v>
+        <v>18.39042926726703</v>
       </c>
       <c r="D158">
-        <v>23.63858955352264</v>
+        <v>23.65604159179861</v>
       </c>
       <c r="E158">
-        <v>7.908715804003084</v>
+        <v>7.764895733771052</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4250,16 +4250,16 @@
         <v>162</v>
       </c>
       <c r="B159">
-        <v>3.252643656672613</v>
+        <v>3.161001793819688</v>
       </c>
       <c r="C159">
-        <v>18.15302064147889</v>
+        <v>17.2278281166157</v>
       </c>
       <c r="D159">
-        <v>23.77814042105793</v>
+        <v>23.9345254410016</v>
       </c>
       <c r="E159">
-        <v>6.518763505964468</v>
+        <v>6.798649988701484</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4267,16 +4267,16 @@
         <v>163</v>
       </c>
       <c r="B160">
-        <v>4.523088605934557</v>
+        <v>3.77711710097788</v>
       </c>
       <c r="C160">
-        <v>18.48206923653811</v>
+        <v>18.24135050540388</v>
       </c>
       <c r="D160">
-        <v>23.44657164368691</v>
+        <v>23.47626305137612</v>
       </c>
       <c r="E160">
-        <v>6.584711272507279</v>
+        <v>6.580182991390443</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4284,16 +4284,16 @@
         <v>164</v>
       </c>
       <c r="B161">
-        <v>4.066473705283189</v>
+        <v>4.381619339185611</v>
       </c>
       <c r="C161">
-        <v>17.90392539623828</v>
+        <v>17.05054648059055</v>
       </c>
       <c r="D161">
-        <v>23.7107930792403</v>
+        <v>23.90200429112734</v>
       </c>
       <c r="E161">
-        <v>6.867810018854883</v>
+        <v>7.593897293643177</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4301,16 +4301,16 @@
         <v>165</v>
       </c>
       <c r="B162">
-        <v>3.590387027558573</v>
+        <v>4.599468533005468</v>
       </c>
       <c r="C162">
-        <v>17.43068085734292</v>
+        <v>17.49838835968773</v>
       </c>
       <c r="D162">
-        <v>23.79129601956421</v>
+        <v>23.60271257067016</v>
       </c>
       <c r="E162">
-        <v>7.405731288683684</v>
+        <v>7.665292937446132</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4318,16 +4318,16 @@
         <v>166</v>
       </c>
       <c r="B163">
-        <v>3.829920278681839</v>
+        <v>3.100552723175753</v>
       </c>
       <c r="C163">
-        <v>18.40175610045977</v>
+        <v>17.45410794564849</v>
       </c>
       <c r="D163">
-        <v>23.89917914510223</v>
+        <v>23.70711736008942</v>
       </c>
       <c r="E163">
-        <v>7.112753991430721</v>
+        <v>7.138535706556908</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4335,16 +4335,16 @@
         <v>167</v>
       </c>
       <c r="B164">
-        <v>3.1099044810482</v>
+        <v>3.153434758022896</v>
       </c>
       <c r="C164">
-        <v>17.84277649178843</v>
+        <v>18.10091689871634</v>
       </c>
       <c r="D164">
-        <v>23.88612719961638</v>
+        <v>23.933776265994</v>
       </c>
       <c r="E164">
-        <v>6.439044515842268</v>
+        <v>7.224666379244471</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4352,16 +4352,16 @@
         <v>168</v>
       </c>
       <c r="B165">
-        <v>3.242322447419357</v>
+        <v>3.947844208893964</v>
       </c>
       <c r="C165">
-        <v>17.84534807982145</v>
+        <v>18.32295670604699</v>
       </c>
       <c r="D165">
-        <v>23.81391896240969</v>
+        <v>23.70873625248845</v>
       </c>
       <c r="E165">
-        <v>7.644237553986335</v>
+        <v>7.587485371894373</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4369,16 +4369,16 @@
         <v>169</v>
       </c>
       <c r="B166">
-        <v>4.539559506678073</v>
+        <v>4.470628077864255</v>
       </c>
       <c r="C166">
-        <v>17.10023157683098</v>
+        <v>18.15848434505649</v>
       </c>
       <c r="D166">
-        <v>23.64231465328724</v>
+        <v>23.89326559552585</v>
       </c>
       <c r="E166">
-        <v>6.75925646164414</v>
+        <v>6.471711749461018</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4386,16 +4386,16 @@
         <v>170</v>
       </c>
       <c r="B167">
-        <v>3.407025513197467</v>
+        <v>4.235879340883391</v>
       </c>
       <c r="C167">
-        <v>17.43555938805596</v>
+        <v>16.93952536447033</v>
       </c>
       <c r="D167">
-        <v>23.93116737408932</v>
+        <v>23.7653342280589</v>
       </c>
       <c r="E167">
-        <v>7.723347294229656</v>
+        <v>7.784885378448971</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4403,16 +4403,16 @@
         <v>171</v>
       </c>
       <c r="B168">
-        <v>3.42856324145401</v>
+        <v>3.958552195774206</v>
       </c>
       <c r="C168">
-        <v>18.07257368693355</v>
+        <v>17.64473654609817</v>
       </c>
       <c r="D168">
-        <v>23.6079570810706</v>
+        <v>23.82105739752085</v>
       </c>
       <c r="E168">
-        <v>7.122809591807317</v>
+        <v>6.886878004374304</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4420,16 +4420,16 @@
         <v>172</v>
       </c>
       <c r="B169">
-        <v>4.440583044481941</v>
+        <v>2.967204550343916</v>
       </c>
       <c r="C169">
-        <v>17.96360479262244</v>
+        <v>17.23329918794368</v>
       </c>
       <c r="D169">
-        <v>23.81350310189018</v>
+        <v>23.53879938709209</v>
       </c>
       <c r="E169">
-        <v>6.912105245993445</v>
+        <v>7.46353101314452</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4437,16 +4437,16 @@
         <v>173</v>
       </c>
       <c r="B170">
-        <v>3.806087223387766</v>
+        <v>3.982656855281842</v>
       </c>
       <c r="C170">
-        <v>17.22106135112722</v>
+        <v>17.30753644897969</v>
       </c>
       <c r="D170">
-        <v>23.58817582300789</v>
+        <v>23.72163693206098</v>
       </c>
       <c r="E170">
-        <v>7.755051631305657</v>
+        <v>6.682539829080565</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4454,16 +4454,16 @@
         <v>174</v>
       </c>
       <c r="B171">
-        <v>4.353659685766376</v>
+        <v>3.408787258090665</v>
       </c>
       <c r="C171">
-        <v>17.60542909592583</v>
+        <v>18.12009313182273</v>
       </c>
       <c r="D171">
-        <v>23.69788208191783</v>
+        <v>23.80848871917452</v>
       </c>
       <c r="E171">
-        <v>7.238620662273868</v>
+        <v>6.486636200578125</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4471,16 +4471,16 @@
         <v>175</v>
       </c>
       <c r="B172">
-        <v>3.972191474581773</v>
+        <v>3.950678242608555</v>
       </c>
       <c r="C172">
-        <v>18.46102652772591</v>
+        <v>17.46916177640074</v>
       </c>
       <c r="D172">
-        <v>23.80582217746879</v>
+        <v>23.7889923966025</v>
       </c>
       <c r="E172">
-        <v>7.802882444275044</v>
+        <v>7.074134868772754</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4488,16 +4488,16 @@
         <v>176</v>
       </c>
       <c r="B173">
-        <v>3.411981164257338</v>
+        <v>3.089034314779219</v>
       </c>
       <c r="C173">
-        <v>18.293005726503</v>
+        <v>16.94426656130766</v>
       </c>
       <c r="D173">
-        <v>23.45947566960574</v>
+        <v>23.90553724636804</v>
       </c>
       <c r="E173">
-        <v>7.001668198626308</v>
+        <v>7.515602510374771</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4505,16 +4505,16 @@
         <v>177</v>
       </c>
       <c r="B174">
-        <v>3.732774849408338</v>
+        <v>3.429887585373742</v>
       </c>
       <c r="C174">
-        <v>17.55740295645926</v>
+        <v>18.37918616067902</v>
       </c>
       <c r="D174">
-        <v>23.58807687352032</v>
+        <v>23.82953875658128</v>
       </c>
       <c r="E174">
-        <v>6.618691658392317</v>
+        <v>7.47919423160384</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4522,16 +4522,16 @@
         <v>178</v>
       </c>
       <c r="B175">
-        <v>4.363694781657053</v>
+        <v>3.855159583148806</v>
       </c>
       <c r="C175">
-        <v>18.31220236124374</v>
+        <v>17.24881375107583</v>
       </c>
       <c r="D175">
-        <v>23.73496643644443</v>
+        <v>23.74941455871054</v>
       </c>
       <c r="E175">
-        <v>7.900860089561876</v>
+        <v>6.666961657686651</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4539,16 +4539,16 @@
         <v>179</v>
       </c>
       <c r="B176">
-        <v>4.698885638680419</v>
+        <v>4.334812931646108</v>
       </c>
       <c r="C176">
-        <v>17.50123372213474</v>
+        <v>17.89382887912809</v>
       </c>
       <c r="D176">
-        <v>23.81653097651503</v>
+        <v>23.54501815232187</v>
       </c>
       <c r="E176">
-        <v>7.087350009180145</v>
+        <v>7.066584836415462</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4556,16 +4556,16 @@
         <v>180</v>
       </c>
       <c r="B177">
-        <v>4.245980762332068</v>
+        <v>4.743619715740889</v>
       </c>
       <c r="C177">
-        <v>17.90692793063756</v>
+        <v>18.25141720238327</v>
       </c>
       <c r="D177">
-        <v>23.5877863340177</v>
+        <v>23.79174942430758</v>
       </c>
       <c r="E177">
-        <v>7.098438794729733</v>
+        <v>7.494218373500918</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4573,16 +4573,16 @@
         <v>181</v>
       </c>
       <c r="B178">
-        <v>4.144173607796599</v>
+        <v>4.413916988099578</v>
       </c>
       <c r="C178">
-        <v>17.97954115277498</v>
+        <v>17.03567207753653</v>
       </c>
       <c r="D178">
-        <v>23.70226225748015</v>
+        <v>23.79183584097355</v>
       </c>
       <c r="E178">
-        <v>7.739477201690983</v>
+        <v>7.14258665651704</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4590,16 +4590,16 @@
         <v>182</v>
       </c>
       <c r="B179">
-        <v>3.369795359978895</v>
+        <v>4.263829683329838</v>
       </c>
       <c r="C179">
-        <v>18.04515979724961</v>
+        <v>18.47023581774042</v>
       </c>
       <c r="D179">
-        <v>23.51721718961589</v>
+        <v>23.71870539683456</v>
       </c>
       <c r="E179">
-        <v>7.986344889131811</v>
+        <v>7.02151903596766</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4607,16 +4607,16 @@
         <v>183</v>
       </c>
       <c r="B180">
-        <v>4.656831985100816</v>
+        <v>4.517439037118672</v>
       </c>
       <c r="C180">
-        <v>17.73970170102801</v>
+        <v>17.18329902366412</v>
       </c>
       <c r="D180">
-        <v>23.78258242779803</v>
+        <v>23.89210951349442</v>
       </c>
       <c r="E180">
-        <v>6.733741863256244</v>
+        <v>6.428654677410531</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4624,16 +4624,16 @@
         <v>184</v>
       </c>
       <c r="B181">
-        <v>3.53356497897608</v>
+        <v>3.083436552243605</v>
       </c>
       <c r="C181">
-        <v>18.00721176742564</v>
+        <v>17.42508504272335</v>
       </c>
       <c r="D181">
-        <v>23.74168626022214</v>
+        <v>23.6037116171378</v>
       </c>
       <c r="E181">
-        <v>7.023071450638191</v>
+        <v>6.410425864031783</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4641,16 +4641,16 @@
         <v>185</v>
       </c>
       <c r="B182">
-        <v>3.058902634834436</v>
+        <v>3.660863358880221</v>
       </c>
       <c r="C182">
-        <v>17.74151507659632</v>
+        <v>17.37692893268176</v>
       </c>
       <c r="D182">
-        <v>23.6928908939038</v>
+        <v>23.65378214912322</v>
       </c>
       <c r="E182">
-        <v>7.31605301274292</v>
+        <v>6.566540002688678</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4658,16 +4658,16 @@
         <v>186</v>
       </c>
       <c r="B183">
-        <v>3.410875060100345</v>
+        <v>4.281556867888659</v>
       </c>
       <c r="C183">
-        <v>18.23846980997403</v>
+        <v>17.50504665579077</v>
       </c>
       <c r="D183">
-        <v>23.86825210706607</v>
+        <v>23.83871978209769</v>
       </c>
       <c r="E183">
-        <v>6.647692244270369</v>
+        <v>7.406404669446228</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4675,16 +4675,16 @@
         <v>187</v>
       </c>
       <c r="B184">
-        <v>4.391064664433277</v>
+        <v>3.558747355031552</v>
       </c>
       <c r="C184">
-        <v>16.92711292178909</v>
+        <v>17.94985021956472</v>
       </c>
       <c r="D184">
-        <v>23.47709746079108</v>
+        <v>23.62538984737752</v>
       </c>
       <c r="E184">
-        <v>6.93702839021591</v>
+        <v>7.202791880496149</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4692,16 +4692,16 @@
         <v>188</v>
       </c>
       <c r="B185">
-        <v>4.403121724650537</v>
+        <v>3.216275133217127</v>
       </c>
       <c r="C185">
-        <v>17.73464920977859</v>
+        <v>17.55027279209382</v>
       </c>
       <c r="D185">
-        <v>23.75624997625746</v>
+        <v>23.88004616688881</v>
       </c>
       <c r="E185">
-        <v>6.925443581738358</v>
+        <v>6.903076378150798</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4709,16 +4709,16 @@
         <v>189</v>
       </c>
       <c r="B186">
-        <v>3.342702390243291</v>
+        <v>3.798573055709732</v>
       </c>
       <c r="C186">
-        <v>17.45178111870829</v>
+        <v>18.18400184681976</v>
       </c>
       <c r="D186">
-        <v>23.51136155051091</v>
+        <v>23.72208052782359</v>
       </c>
       <c r="E186">
-        <v>6.765246863680064</v>
+        <v>7.417965975175849</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4726,16 +4726,16 @@
         <v>190</v>
       </c>
       <c r="B187">
-        <v>3.461622607273681</v>
+        <v>4.599091295366566</v>
       </c>
       <c r="C187">
-        <v>18.48377895539269</v>
+        <v>17.88734918695186</v>
       </c>
       <c r="D187">
-        <v>23.66940953581387</v>
+        <v>23.53819182146288</v>
       </c>
       <c r="E187">
-        <v>6.521682099302605</v>
+        <v>6.989247129974102</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4743,16 +4743,16 @@
         <v>191</v>
       </c>
       <c r="B188">
-        <v>4.16001359598607</v>
+        <v>3.852308150814886</v>
       </c>
       <c r="C188">
-        <v>17.59682576033814</v>
+        <v>17.59935287858773</v>
       </c>
       <c r="D188">
-        <v>23.5321670503092</v>
+        <v>23.7707658774887</v>
       </c>
       <c r="E188">
-        <v>7.283670689376361</v>
+        <v>6.726779393661442</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4760,16 +4760,16 @@
         <v>192</v>
       </c>
       <c r="B189">
-        <v>3.008230648008333</v>
+        <v>4.096195527635102</v>
       </c>
       <c r="C189">
-        <v>17.09043133987292</v>
+        <v>17.58931933432976</v>
       </c>
       <c r="D189">
-        <v>23.62990550912239</v>
+        <v>23.68020892311249</v>
       </c>
       <c r="E189">
-        <v>7.907729931278984</v>
+        <v>7.609056696716916</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4777,16 +4777,16 @@
         <v>193</v>
       </c>
       <c r="B190">
-        <v>3.997077098320472</v>
+        <v>3.305987395202974</v>
       </c>
       <c r="C190">
-        <v>17.66935070394986</v>
+        <v>18.31582956762627</v>
       </c>
       <c r="D190">
-        <v>23.49008546735277</v>
+        <v>23.72624268855163</v>
       </c>
       <c r="E190">
-        <v>7.748900808211784</v>
+        <v>7.37346202652701</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4794,16 +4794,16 @@
         <v>194</v>
       </c>
       <c r="B191">
-        <v>3.373274238314696</v>
+        <v>3.27743908321283</v>
       </c>
       <c r="C191">
-        <v>17.65777698749624</v>
+        <v>17.44761441863773</v>
       </c>
       <c r="D191">
-        <v>23.84169447771986</v>
+        <v>23.48121198932288</v>
       </c>
       <c r="E191">
-        <v>7.944086616053124</v>
+        <v>6.425075199812945</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4811,16 +4811,16 @@
         <v>195</v>
       </c>
       <c r="B192">
-        <v>3.04092928953758</v>
+        <v>4.142899669443487</v>
       </c>
       <c r="C192">
-        <v>18.48124569020109</v>
+        <v>18.23563707769497</v>
       </c>
       <c r="D192">
-        <v>23.71873221909481</v>
+        <v>23.64708390714748</v>
       </c>
       <c r="E192">
-        <v>7.820886968086758</v>
+        <v>6.852579238567636</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4828,16 +4828,16 @@
         <v>196</v>
       </c>
       <c r="B193">
-        <v>3.34683489690467</v>
+        <v>4.426097309413751</v>
       </c>
       <c r="C193">
-        <v>17.39639470986943</v>
+        <v>17.868049782177</v>
       </c>
       <c r="D193">
-        <v>23.58055881206243</v>
+        <v>23.48136247937474</v>
       </c>
       <c r="E193">
-        <v>6.925012298455299</v>
+        <v>7.962847883715488</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4845,16 +4845,16 @@
         <v>197</v>
       </c>
       <c r="B194">
-        <v>4.438605430040315</v>
+        <v>3.804556058356902</v>
       </c>
       <c r="C194">
-        <v>18.12538830008846</v>
+        <v>17.62168372506041</v>
       </c>
       <c r="D194">
-        <v>23.44342796485034</v>
+        <v>23.53976548027436</v>
       </c>
       <c r="E194">
-        <v>6.775670668642177</v>
+        <v>6.934621433960982</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4862,16 +4862,16 @@
         <v>198</v>
       </c>
       <c r="B195">
-        <v>4.026256367395209</v>
+        <v>3.199282450273693</v>
       </c>
       <c r="C195">
-        <v>17.45131532611913</v>
+        <v>18.0554570348204</v>
       </c>
       <c r="D195">
-        <v>23.55613134455696</v>
+        <v>23.88105833831601</v>
       </c>
       <c r="E195">
-        <v>6.806396507654956</v>
+        <v>7.566769372019865</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4879,16 +4879,16 @@
         <v>199</v>
       </c>
       <c r="B196">
-        <v>4.561692530782261</v>
+        <v>4.631148187238857</v>
       </c>
       <c r="C196">
-        <v>17.9015617430416</v>
+        <v>18.47306788580882</v>
       </c>
       <c r="D196">
-        <v>23.86741257113269</v>
+        <v>23.78072113159539</v>
       </c>
       <c r="E196">
-        <v>7.737637064305169</v>
+        <v>7.938592697023285</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4896,16 +4896,16 @@
         <v>200</v>
       </c>
       <c r="B197">
-        <v>4.661453639488254</v>
+        <v>4.409447132992703</v>
       </c>
       <c r="C197">
-        <v>17.92641210161021</v>
+        <v>17.37081824479195</v>
       </c>
       <c r="D197">
-        <v>23.85524378330496</v>
+        <v>23.90033230194053</v>
       </c>
       <c r="E197">
-        <v>7.472352631696522</v>
+        <v>7.808957872753979</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4913,16 +4913,16 @@
         <v>201</v>
       </c>
       <c r="B198">
-        <v>3.019613928389112</v>
+        <v>3.113606039364987</v>
       </c>
       <c r="C198">
-        <v>18.18735386810522</v>
+        <v>18.01500802743731</v>
       </c>
       <c r="D198">
-        <v>23.74310442907687</v>
+        <v>23.54963576867264</v>
       </c>
       <c r="E198">
-        <v>7.080184627918939</v>
+        <v>7.916973015012162</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4930,16 +4930,16 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>3.489264097379257</v>
+        <v>3.3609431795908</v>
       </c>
       <c r="C199">
-        <v>17.64537586062592</v>
+        <v>17.27511188147777</v>
       </c>
       <c r="D199">
-        <v>23.54459523904617</v>
+        <v>23.89499844068041</v>
       </c>
       <c r="E199">
-        <v>7.4156729105278</v>
+        <v>7.61685190767543</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4947,16 +4947,16 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>3.952992195661878</v>
+        <v>4.047040045073597</v>
       </c>
       <c r="C200">
-        <v>17.56909508155593</v>
+        <v>17.10740218396582</v>
       </c>
       <c r="D200">
-        <v>23.77295981262907</v>
+        <v>23.85038986818605</v>
       </c>
       <c r="E200">
-        <v>6.886952454451096</v>
+        <v>6.804213228750902</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4964,16 +4964,16 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>4.268556357344448</v>
+        <v>3.495917509978445</v>
       </c>
       <c r="C201">
-        <v>17.62889011960076</v>
+        <v>16.94744935388776</v>
       </c>
       <c r="D201">
-        <v>23.53517949444412</v>
+        <v>23.89717621962914</v>
       </c>
       <c r="E201">
-        <v>6.509032602512975</v>
+        <v>7.887669896337728</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4981,16 +4981,16 @@
         <v>205</v>
       </c>
       <c r="B202">
-        <v>3.783673530732244</v>
+        <v>4.092193931458784</v>
       </c>
       <c r="C202">
-        <v>18.28858370298701</v>
+        <v>17.86401813466475</v>
       </c>
       <c r="D202">
-        <v>23.54381528150741</v>
+        <v>23.87176761956986</v>
       </c>
       <c r="E202">
-        <v>6.955191202272887</v>
+        <v>7.851780904958281</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4998,16 +4998,16 @@
         <v>206</v>
       </c>
       <c r="B203">
-        <v>4.579183983764986</v>
+        <v>4.607834006754556</v>
       </c>
       <c r="C203">
-        <v>18.43398242016013</v>
+        <v>18.42597403249749</v>
       </c>
       <c r="D203">
-        <v>23.54565172299911</v>
+        <v>23.81565034561439</v>
       </c>
       <c r="E203">
-        <v>7.819243157151826</v>
+        <v>7.947768177482553</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -5015,16 +5015,16 @@
         <v>207</v>
       </c>
       <c r="B204">
-        <v>4.063094258480891</v>
+        <v>4.106719198114006</v>
       </c>
       <c r="C204">
-        <v>17.85081905684646</v>
+        <v>17.64818924918517</v>
       </c>
       <c r="D204">
-        <v>23.86839413096561</v>
+        <v>23.79358451643965</v>
       </c>
       <c r="E204">
-        <v>6.596865874551709</v>
+        <v>7.849943339586534</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -5032,16 +5032,16 @@
         <v>208</v>
       </c>
       <c r="B205">
-        <v>3.638198329044076</v>
+        <v>3.337688578579503</v>
       </c>
       <c r="C205">
-        <v>19.43413877188917</v>
+        <v>19.92928403845589</v>
       </c>
       <c r="D205">
-        <v>33.29804920415484</v>
+        <v>33.25880108209555</v>
       </c>
       <c r="E205">
-        <v>7.183056514648426</v>
+        <v>7.323285167709029</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -5049,16 +5049,16 @@
         <v>209</v>
       </c>
       <c r="B206">
-        <v>3.819824696075475</v>
+        <v>3.436154276366449</v>
       </c>
       <c r="C206">
-        <v>20.42303370632577</v>
+        <v>20.05349659689786</v>
       </c>
       <c r="D206">
-        <v>33.55797792006655</v>
+        <v>33.60705738270167</v>
       </c>
       <c r="E206">
-        <v>6.154182845184558</v>
+        <v>7.056849486389332</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -5066,16 +5066,16 @@
         <v>210</v>
       </c>
       <c r="B207">
-        <v>4.28312562846664</v>
+        <v>3.499634823797096</v>
       </c>
       <c r="C207">
-        <v>20.17252316660336</v>
+        <v>19.89521551596869</v>
       </c>
       <c r="D207">
-        <v>33.36292614433354</v>
+        <v>33.67066904419818</v>
       </c>
       <c r="E207">
-        <v>6.176729632095933</v>
+        <v>7.044151984126541</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -5083,16 +5083,16 @@
         <v>211</v>
       </c>
       <c r="B208">
-        <v>4.370124522758583</v>
+        <v>3.219057672536892</v>
       </c>
       <c r="C208">
-        <v>19.48952261545295</v>
+        <v>20.03740575893542</v>
       </c>
       <c r="D208">
-        <v>33.32020358835456</v>
+        <v>33.29935450539281</v>
       </c>
       <c r="E208">
-        <v>6.946230534433273</v>
+        <v>6.780523182935712</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -5100,16 +5100,16 @@
         <v>212</v>
       </c>
       <c r="B209">
-        <v>4.086888226267723</v>
+        <v>3.221268518877322</v>
       </c>
       <c r="C209">
-        <v>19.8025429000634</v>
+        <v>19.9419215830504</v>
       </c>
       <c r="D209">
-        <v>33.35621917579137</v>
+        <v>33.21584511169247</v>
       </c>
       <c r="E209">
-        <v>6.636691198419874</v>
+        <v>6.709210877567638</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -5117,16 +5117,16 @@
         <v>213</v>
       </c>
       <c r="B210">
-        <v>4.34376510559182</v>
+        <v>3.778784969866681</v>
       </c>
       <c r="C210">
-        <v>20.18212702934084</v>
+        <v>20.09740180332098</v>
       </c>
       <c r="D210">
-        <v>33.28103781336439</v>
+        <v>33.31282516576623</v>
       </c>
       <c r="E210">
-        <v>6.395449227242284</v>
+        <v>6.179258813174315</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5134,16 +5134,16 @@
         <v>214</v>
       </c>
       <c r="B211">
-        <v>3.802188518684479</v>
+        <v>3.180813094182523</v>
       </c>
       <c r="C211">
-        <v>19.56787861154418</v>
+        <v>19.78249240669672</v>
       </c>
       <c r="D211">
-        <v>33.57205350280117</v>
+        <v>33.64567710529575</v>
       </c>
       <c r="E211">
-        <v>7.373875981264309</v>
+        <v>6.289599444378529</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5151,16 +5151,16 @@
         <v>215</v>
       </c>
       <c r="B212">
-        <v>4.208848460127825</v>
+        <v>3.201660250035644</v>
       </c>
       <c r="C212">
-        <v>19.30546119267554</v>
+        <v>19.54700201941396</v>
       </c>
       <c r="D212">
-        <v>33.69548010631539</v>
+        <v>33.28003000783377</v>
       </c>
       <c r="E212">
-        <v>6.928012738985805</v>
+        <v>6.757909539671068</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5168,16 +5168,16 @@
         <v>216</v>
       </c>
       <c r="B213">
-        <v>3.526943204647782</v>
+        <v>4.424591897908156</v>
       </c>
       <c r="C213">
-        <v>20.15609204641799</v>
+        <v>19.41280665515262</v>
       </c>
       <c r="D213">
-        <v>33.61705447144612</v>
+        <v>33.69117588651034</v>
       </c>
       <c r="E213">
-        <v>7.136332781284426</v>
+        <v>7.084101024371912</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5185,16 +5185,16 @@
         <v>217</v>
       </c>
       <c r="B214">
-        <v>3.47497682192885</v>
+        <v>3.396087537422151</v>
       </c>
       <c r="C214">
-        <v>20.8110121280981</v>
+        <v>20.38247259597255</v>
       </c>
       <c r="D214">
-        <v>33.4070361946284</v>
+        <v>33.49494404893014</v>
       </c>
       <c r="E214">
-        <v>6.186812368862087</v>
+        <v>7.139311743218582</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5202,16 +5202,16 @@
         <v>218</v>
       </c>
       <c r="B215">
-        <v>3.719851678546858</v>
+        <v>2.887892397679679</v>
       </c>
       <c r="C215">
-        <v>20.80832335433084</v>
+        <v>19.63280824940757</v>
       </c>
       <c r="D215">
-        <v>33.56458423123473</v>
+        <v>33.27084481800247</v>
       </c>
       <c r="E215">
-        <v>6.852779536409387</v>
+        <v>6.607859102390024</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5219,16 +5219,16 @@
         <v>219</v>
       </c>
       <c r="B216">
-        <v>4.062193242305399</v>
+        <v>3.173895450805871</v>
       </c>
       <c r="C216">
-        <v>19.9683260955903</v>
+        <v>19.32290260625743</v>
       </c>
       <c r="D216">
-        <v>33.67962357730676</v>
+        <v>33.67495920070184</v>
       </c>
       <c r="E216">
-        <v>6.373535306102434</v>
+        <v>6.66660656038031</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5236,16 +5236,16 @@
         <v>220</v>
       </c>
       <c r="B217">
-        <v>3.51696535124313</v>
+        <v>4.246564646397712</v>
       </c>
       <c r="C217">
-        <v>20.13758957186434</v>
+        <v>19.7395539758359</v>
       </c>
       <c r="D217">
-        <v>33.22382716744322</v>
+        <v>33.33084574575149</v>
       </c>
       <c r="E217">
-        <v>6.859994393758672</v>
+        <v>7.565608851232746</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -5253,16 +5253,16 @@
         <v>221</v>
       </c>
       <c r="B218">
-        <v>3.830665808738036</v>
+        <v>4.173439787090679</v>
       </c>
       <c r="C218">
-        <v>20.64268562434301</v>
+        <v>19.25423293908741</v>
       </c>
       <c r="D218">
-        <v>33.67384780744056</v>
+        <v>33.66143816673923</v>
       </c>
       <c r="E218">
-        <v>6.748537417580039</v>
+        <v>7.16979911679373</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5270,16 +5270,16 @@
         <v>222</v>
       </c>
       <c r="B219">
-        <v>3.186841337383527</v>
+        <v>4.093435918980199</v>
       </c>
       <c r="C219">
-        <v>20.75465023037295</v>
+        <v>19.42813541509838</v>
       </c>
       <c r="D219">
-        <v>33.520298485765</v>
+        <v>33.32191556337587</v>
       </c>
       <c r="E219">
-        <v>6.779514114607633</v>
+        <v>7.186690992093028</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -5287,16 +5287,16 @@
         <v>223</v>
       </c>
       <c r="B220">
-        <v>3.386157188763903</v>
+        <v>3.635938623098726</v>
       </c>
       <c r="C220">
-        <v>20.58916574327436</v>
+        <v>19.59277313271253</v>
       </c>
       <c r="D220">
-        <v>33.21667315862507</v>
+        <v>33.58174356846813</v>
       </c>
       <c r="E220">
-        <v>6.229227330497539</v>
+        <v>7.612100865210415</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5304,16 +5304,16 @@
         <v>224</v>
       </c>
       <c r="B221">
-        <v>3.510746857255537</v>
+        <v>3.906446960601051</v>
       </c>
       <c r="C221">
-        <v>20.00687280434313</v>
+        <v>20.19750754193428</v>
       </c>
       <c r="D221">
-        <v>33.33718799284536</v>
+        <v>33.36903985959599</v>
       </c>
       <c r="E221">
-        <v>6.860624555232098</v>
+        <v>6.628939990253649</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5321,16 +5321,16 @@
         <v>225</v>
       </c>
       <c r="B222">
-        <v>2.887129369501283</v>
+        <v>3.780495521386866</v>
       </c>
       <c r="C222">
-        <v>20.64473119672211</v>
+        <v>19.63849058988292</v>
       </c>
       <c r="D222">
-        <v>33.577032732712</v>
+        <v>33.45228376346248</v>
       </c>
       <c r="E222">
-        <v>7.464184280379359</v>
+        <v>7.454932963209798</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5338,16 +5338,16 @@
         <v>226</v>
       </c>
       <c r="B223">
-        <v>3.290385615252006</v>
+        <v>3.512089368456476</v>
       </c>
       <c r="C223">
-        <v>19.93653636301151</v>
+        <v>20.77115155870317</v>
       </c>
       <c r="D223">
-        <v>33.44445856900626</v>
+        <v>33.43658445361741</v>
       </c>
       <c r="E223">
-        <v>7.679220126931565</v>
+        <v>7.404066797242993</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5355,16 +5355,16 @@
         <v>227</v>
       </c>
       <c r="B224">
-        <v>3.288632187507173</v>
+        <v>3.075617878410116</v>
       </c>
       <c r="C224">
-        <v>20.61388676338851</v>
+        <v>19.28236019436685</v>
       </c>
       <c r="D224">
-        <v>33.27395444085501</v>
+        <v>33.26883608025538</v>
       </c>
       <c r="E224">
-        <v>6.602532217107443</v>
+        <v>7.577676211040925</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5372,16 +5372,16 @@
         <v>228</v>
       </c>
       <c r="B225">
-        <v>4.177411584151451</v>
+        <v>4.11742453463553</v>
       </c>
       <c r="C225">
-        <v>20.40259082906963</v>
+        <v>19.60057238950103</v>
       </c>
       <c r="D225">
-        <v>33.5137632274667</v>
+        <v>33.46041465076914</v>
       </c>
       <c r="E225">
-        <v>6.615176934294867</v>
+        <v>7.033309987191201</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5389,16 +5389,16 @@
         <v>229</v>
       </c>
       <c r="B226">
-        <v>4.480482087442621</v>
+        <v>2.847732269498557</v>
       </c>
       <c r="C226">
-        <v>20.03996755972844</v>
+        <v>20.22433459543003</v>
       </c>
       <c r="D226">
-        <v>33.28438640624657</v>
+        <v>33.65528623278751</v>
       </c>
       <c r="E226">
-        <v>6.306516225916151</v>
+        <v>7.543127201961342</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5406,16 +5406,16 @@
         <v>230</v>
       </c>
       <c r="B227">
-        <v>2.946355654584537</v>
+        <v>3.900796608461039</v>
       </c>
       <c r="C227">
-        <v>20.0829285117071</v>
+        <v>20.60229557984994</v>
       </c>
       <c r="D227">
-        <v>33.32932753229021</v>
+        <v>33.34039357659276</v>
       </c>
       <c r="E227">
-        <v>7.101904688110372</v>
+        <v>7.526512879202732</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5423,16 +5423,16 @@
         <v>231</v>
       </c>
       <c r="B228">
-        <v>3.585981740031138</v>
+        <v>2.763546247806913</v>
       </c>
       <c r="C228">
-        <v>20.35083639542752</v>
+        <v>20.01525551394823</v>
       </c>
       <c r="D228">
-        <v>33.40343342209208</v>
+        <v>33.36222483876203</v>
       </c>
       <c r="E228">
-        <v>6.247264296926714</v>
+        <v>7.111985545831614</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5440,16 +5440,16 @@
         <v>232</v>
       </c>
       <c r="B229">
-        <v>4.020949246780653</v>
+        <v>4.170024634329817</v>
       </c>
       <c r="C229">
-        <v>19.98742275105666</v>
+        <v>20.33908165741813</v>
       </c>
       <c r="D229">
-        <v>33.24364553195505</v>
+        <v>33.42365831760505</v>
       </c>
       <c r="E229">
-        <v>7.477876114699527</v>
+        <v>6.661499781133415</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5457,16 +5457,16 @@
         <v>233</v>
       </c>
       <c r="B230">
-        <v>4.47315433492605</v>
+        <v>4.362934511568275</v>
       </c>
       <c r="C230">
-        <v>20.00743373448768</v>
+        <v>20.12528413546227</v>
       </c>
       <c r="D230">
-        <v>33.23078847119869</v>
+        <v>33.32762801856892</v>
       </c>
       <c r="E230">
-        <v>6.42286580345313</v>
+        <v>7.383946083050779</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5474,16 +5474,16 @@
         <v>234</v>
       </c>
       <c r="B231">
-        <v>2.898798833622815</v>
+        <v>3.422837456809703</v>
       </c>
       <c r="C231">
-        <v>19.77210456914539</v>
+        <v>19.25503593052468</v>
       </c>
       <c r="D231">
-        <v>33.4519714706645</v>
+        <v>33.31374767729914</v>
       </c>
       <c r="E231">
-        <v>6.572460926765368</v>
+        <v>6.298778049225688</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5491,16 +5491,16 @@
         <v>235</v>
       </c>
       <c r="B232">
-        <v>4.097101835225651</v>
+        <v>3.582004951010748</v>
       </c>
       <c r="C232">
-        <v>20.01449720349418</v>
+        <v>20.33351442808043</v>
       </c>
       <c r="D232">
-        <v>33.63426120290856</v>
+        <v>33.33608064870441</v>
       </c>
       <c r="E232">
-        <v>7.208482383163741</v>
+        <v>6.736319041332564</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5508,16 +5508,16 @@
         <v>236</v>
       </c>
       <c r="B233">
-        <v>3.469158156033368</v>
+        <v>3.042940179702065</v>
       </c>
       <c r="C233">
-        <v>19.88424612884533</v>
+        <v>20.49553589694575</v>
       </c>
       <c r="D233">
-        <v>33.59192127322304</v>
+        <v>33.51974150691186</v>
       </c>
       <c r="E233">
-        <v>7.164608286794524</v>
+        <v>6.351591599322208</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5525,16 +5525,16 @@
         <v>237</v>
       </c>
       <c r="B234">
-        <v>3.511404356970085</v>
+        <v>4.270364227118048</v>
       </c>
       <c r="C234">
-        <v>20.49707202732929</v>
+        <v>19.94259414623797</v>
       </c>
       <c r="D234">
-        <v>33.54236382896624</v>
+        <v>33.49564237542841</v>
       </c>
       <c r="E234">
-        <v>7.43851706809262</v>
+        <v>6.164799117768528</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5542,16 +5542,16 @@
         <v>238</v>
       </c>
       <c r="B235">
-        <v>4.16151709086488</v>
+        <v>2.876206083452212</v>
       </c>
       <c r="C235">
-        <v>19.45155940534881</v>
+        <v>19.91494955014065</v>
       </c>
       <c r="D235">
-        <v>33.55768913918886</v>
+        <v>33.25663132645017</v>
       </c>
       <c r="E235">
-        <v>6.654872366674048</v>
+        <v>6.348608171380407</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5559,16 +5559,16 @@
         <v>239</v>
       </c>
       <c r="B236">
-        <v>3.232564788649302</v>
+        <v>3.316694656127055</v>
       </c>
       <c r="C236">
-        <v>19.9571714594963</v>
+        <v>20.32467693031093</v>
       </c>
       <c r="D236">
-        <v>33.38569945485992</v>
+        <v>33.42878709726868</v>
       </c>
       <c r="E236">
-        <v>6.362992061851767</v>
+        <v>7.095416714560822</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5576,16 +5576,16 @@
         <v>240</v>
       </c>
       <c r="B237">
-        <v>3.487308554874436</v>
+        <v>4.451766727900886</v>
       </c>
       <c r="C237">
-        <v>19.53737908103775</v>
+        <v>20.45037360670728</v>
       </c>
       <c r="D237">
-        <v>33.66980284905369</v>
+        <v>33.22365246901393</v>
       </c>
       <c r="E237">
-        <v>7.397556172502091</v>
+        <v>7.246538503004209</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5593,16 +5593,16 @@
         <v>241</v>
       </c>
       <c r="B238">
-        <v>4.089775641680263</v>
+        <v>3.289379402928978</v>
       </c>
       <c r="C238">
-        <v>20.50867945989327</v>
+        <v>19.893971689259</v>
       </c>
       <c r="D238">
-        <v>33.65221437944947</v>
+        <v>33.32353609161041</v>
       </c>
       <c r="E238">
-        <v>7.362545746588334</v>
+        <v>6.56904433863186</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5610,16 +5610,16 @@
         <v>242</v>
       </c>
       <c r="B239">
-        <v>3.309945851055148</v>
+        <v>3.044825189304054</v>
       </c>
       <c r="C239">
-        <v>19.86153767346439</v>
+        <v>20.35287358888349</v>
       </c>
       <c r="D239">
-        <v>33.39485169929022</v>
+        <v>33.38342302005221</v>
       </c>
       <c r="E239">
-        <v>6.417510061882395</v>
+        <v>6.323897660593221</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5627,16 +5627,16 @@
         <v>243</v>
       </c>
       <c r="B240">
-        <v>3.97334101559781</v>
+        <v>3.382362094502832</v>
       </c>
       <c r="C240">
-        <v>20.32600140074697</v>
+        <v>19.45294486557911</v>
       </c>
       <c r="D240">
-        <v>33.2642552019927</v>
+        <v>33.43375464326535</v>
       </c>
       <c r="E240">
-        <v>6.809270541583662</v>
+        <v>6.568248043197649</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5644,16 +5644,16 @@
         <v>244</v>
       </c>
       <c r="B241">
-        <v>3.731084784734866</v>
+        <v>4.161824239485101</v>
       </c>
       <c r="C241">
-        <v>20.06725557886262</v>
+        <v>19.80946356189641</v>
       </c>
       <c r="D241">
-        <v>33.50017235387163</v>
+        <v>33.29322757383349</v>
       </c>
       <c r="E241">
-        <v>7.370725863138803</v>
+        <v>6.638359796395527</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5661,16 +5661,16 @@
         <v>245</v>
       </c>
       <c r="B242">
-        <v>4.033595742200234</v>
+        <v>4.080502541754981</v>
       </c>
       <c r="C242">
-        <v>20.70052156349461</v>
+        <v>20.27012937697372</v>
       </c>
       <c r="D242">
-        <v>33.40124031996077</v>
+        <v>33.52317544845175</v>
       </c>
       <c r="E242">
-        <v>7.595171007734342</v>
+        <v>7.38282291985432</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5678,16 +5678,16 @@
         <v>246</v>
       </c>
       <c r="B243">
-        <v>4.318476815708634</v>
+        <v>2.880578562661486</v>
       </c>
       <c r="C243">
-        <v>20.328763257632</v>
+        <v>20.6929468141939</v>
       </c>
       <c r="D243">
-        <v>33.58621814633956</v>
+        <v>33.27186947620014</v>
       </c>
       <c r="E243">
-        <v>6.206903671473747</v>
+        <v>7.584290349883172</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5695,16 +5695,16 @@
         <v>247</v>
       </c>
       <c r="B244">
-        <v>3.082838938293948</v>
+        <v>4.064136562594404</v>
       </c>
       <c r="C244">
-        <v>19.9850521700962</v>
+        <v>20.36160906894821</v>
       </c>
       <c r="D244">
-        <v>33.57655673970604</v>
+        <v>33.42580963573901</v>
       </c>
       <c r="E244">
-        <v>7.36883438059014</v>
+        <v>6.863033766677225</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5712,16 +5712,16 @@
         <v>248</v>
       </c>
       <c r="B245">
-        <v>4.082281084277936</v>
+        <v>3.955614150317899</v>
       </c>
       <c r="C245">
-        <v>19.6997123720772</v>
+        <v>19.61061797146595</v>
       </c>
       <c r="D245">
-        <v>33.58511015283281</v>
+        <v>33.65751424433827</v>
       </c>
       <c r="E245">
-        <v>6.635475300765808</v>
+        <v>6.547986145796653</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5729,16 +5729,16 @@
         <v>249</v>
       </c>
       <c r="B246">
-        <v>3.090475952762719</v>
+        <v>4.366175530969887</v>
       </c>
       <c r="C246">
-        <v>20.7273570477357</v>
+        <v>20.33375908900756</v>
       </c>
       <c r="D246">
-        <v>33.30992644139273</v>
+        <v>33.27025540012726</v>
       </c>
       <c r="E246">
-        <v>7.424008231047599</v>
+        <v>7.605162094209088</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5746,16 +5746,16 @@
         <v>250</v>
       </c>
       <c r="B247">
-        <v>4.215897547505712</v>
+        <v>3.346600943401787</v>
       </c>
       <c r="C247">
-        <v>20.51270597032166</v>
+        <v>20.76708720789549</v>
       </c>
       <c r="D247">
-        <v>33.41925222871456</v>
+        <v>33.24993238767695</v>
       </c>
       <c r="E247">
-        <v>6.546897519876919</v>
+        <v>6.88565582741332</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5763,16 +5763,16 @@
         <v>251</v>
       </c>
       <c r="B248">
-        <v>4.008549292640279</v>
+        <v>4.108082247814642</v>
       </c>
       <c r="C248">
-        <v>19.88246114131893</v>
+        <v>19.4483543036773</v>
       </c>
       <c r="D248">
-        <v>33.48464203589172</v>
+        <v>33.60722564121792</v>
       </c>
       <c r="E248">
-        <v>7.357107497293772</v>
+        <v>7.194915099877006</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5780,16 +5780,16 @@
         <v>252</v>
       </c>
       <c r="B249">
-        <v>3.51094624210401</v>
+        <v>4.089861528086401</v>
       </c>
       <c r="C249">
-        <v>20.07430191423622</v>
+        <v>20.63642507117568</v>
       </c>
       <c r="D249">
-        <v>33.40294110467234</v>
+        <v>33.25658482038623</v>
       </c>
       <c r="E249">
-        <v>7.515014338332311</v>
+        <v>7.506183275738715</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5797,16 +5797,16 @@
         <v>253</v>
       </c>
       <c r="B250">
-        <v>3.251531876866013</v>
+        <v>2.959191513645527</v>
       </c>
       <c r="C250">
-        <v>19.72348135058771</v>
+        <v>19.30496340298251</v>
       </c>
       <c r="D250">
-        <v>33.26781392768818</v>
+        <v>33.61479132861515</v>
       </c>
       <c r="E250">
-        <v>6.921032717769013</v>
+        <v>6.373594256524355</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5814,16 +5814,16 @@
         <v>254</v>
       </c>
       <c r="B251">
-        <v>3.737381236079702</v>
+        <v>3.449729039648354</v>
       </c>
       <c r="C251">
-        <v>19.71807672045899</v>
+        <v>20.43375206780894</v>
       </c>
       <c r="D251">
-        <v>33.2430823833207</v>
+        <v>33.63974899474408</v>
       </c>
       <c r="E251">
-        <v>6.820039509775537</v>
+        <v>6.428458832872066</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5831,16 +5831,16 @@
         <v>255</v>
       </c>
       <c r="B252">
-        <v>2.832003931511977</v>
+        <v>4.50038698029272</v>
       </c>
       <c r="C252">
-        <v>20.32750501889222</v>
+        <v>19.68138847156246</v>
       </c>
       <c r="D252">
-        <v>33.62444719544282</v>
+        <v>33.27866697362224</v>
       </c>
       <c r="E252">
-        <v>6.736540673344294</v>
+        <v>7.250401048550675</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5848,16 +5848,16 @@
         <v>256</v>
       </c>
       <c r="B253">
-        <v>4.229892482261006</v>
+        <v>4.040765692165442</v>
       </c>
       <c r="C253">
-        <v>19.63489690550887</v>
+        <v>20.17015461303878</v>
       </c>
       <c r="D253">
-        <v>33.60195969890569</v>
+        <v>33.40949115530078</v>
       </c>
       <c r="E253">
-        <v>6.444573187639008</v>
+        <v>6.770890587904582</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5865,16 +5865,16 @@
         <v>257</v>
       </c>
       <c r="B254">
-        <v>2.968116384592632</v>
+        <v>2.848963919625826</v>
       </c>
       <c r="C254">
-        <v>20.00965452415539</v>
+        <v>20.51503823935471</v>
       </c>
       <c r="D254">
-        <v>33.38725443720042</v>
+        <v>33.28883456803461</v>
       </c>
       <c r="E254">
-        <v>7.11168441486878</v>
+        <v>6.703524808865564</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5882,16 +5882,16 @@
         <v>258</v>
       </c>
       <c r="B255">
-        <v>4.180473815889891</v>
+        <v>4.442749301315725</v>
       </c>
       <c r="C255">
-        <v>20.28680541160186</v>
+        <v>20.21988082833944</v>
       </c>
       <c r="D255">
-        <v>33.43145325715642</v>
+        <v>33.39903078913244</v>
       </c>
       <c r="E255">
-        <v>7.041964850631955</v>
+        <v>6.184203235535477</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5899,16 +5899,16 @@
         <v>259</v>
       </c>
       <c r="B256">
-        <v>4.245440139935329</v>
+        <v>4.280295238483175</v>
       </c>
       <c r="C256">
-        <v>19.7918022792085</v>
+        <v>20.75838260044094</v>
       </c>
       <c r="D256">
-        <v>33.65209752631242</v>
+        <v>33.69413728482201</v>
       </c>
       <c r="E256">
-        <v>6.834938433057111</v>
+        <v>7.469321780620732</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5916,16 +5916,16 @@
         <v>260</v>
       </c>
       <c r="B257">
-        <v>3.257623276937541</v>
+        <v>4.44157015052621</v>
       </c>
       <c r="C257">
-        <v>20.42661887756342</v>
+        <v>20.29785612357837</v>
       </c>
       <c r="D257">
-        <v>33.50421839274266</v>
+        <v>33.61133822320733</v>
       </c>
       <c r="E257">
-        <v>6.178319035484941</v>
+        <v>7.564685765251701</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5933,16 +5933,16 @@
         <v>261</v>
       </c>
       <c r="B258">
-        <v>3.940444173353773</v>
+        <v>3.244722256108877</v>
       </c>
       <c r="C258">
-        <v>19.23891801901467</v>
+        <v>19.90815572425388</v>
       </c>
       <c r="D258">
-        <v>33.67909005369017</v>
+        <v>33.28209422499516</v>
       </c>
       <c r="E258">
-        <v>7.245727379860597</v>
+        <v>6.813174625524106</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5950,16 +5950,16 @@
         <v>262</v>
       </c>
       <c r="B259">
-        <v>2.850488064975552</v>
+        <v>3.478131434975172</v>
       </c>
       <c r="C259">
-        <v>19.24602306036698</v>
+        <v>19.62016423836017</v>
       </c>
       <c r="D259">
-        <v>33.46425698124318</v>
+        <v>33.21628664076419</v>
       </c>
       <c r="E259">
-        <v>7.012840243930055</v>
+        <v>6.765134777004892</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5967,16 +5967,16 @@
         <v>263</v>
       </c>
       <c r="B260">
-        <v>2.889846334793635</v>
+        <v>4.282480749646044</v>
       </c>
       <c r="C260">
-        <v>20.10725093301949</v>
+        <v>19.31450539721516</v>
       </c>
       <c r="D260">
-        <v>33.44556477027082</v>
+        <v>33.69612170543856</v>
       </c>
       <c r="E260">
-        <v>7.085643040282362</v>
+        <v>6.601756148113176</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5984,16 +5984,16 @@
         <v>264</v>
       </c>
       <c r="B261">
-        <v>3.155673347162797</v>
+        <v>4.393033159635934</v>
       </c>
       <c r="C261">
-        <v>19.9052464933525</v>
+        <v>20.54252581401158</v>
       </c>
       <c r="D261">
-        <v>33.59244261400591</v>
+        <v>33.3084667660281</v>
       </c>
       <c r="E261">
-        <v>6.253529363452976</v>
+        <v>7.524899295856067</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -6001,16 +6001,16 @@
         <v>265</v>
       </c>
       <c r="B262">
-        <v>4.157296122681879</v>
+        <v>3.476183542946905</v>
       </c>
       <c r="C262">
-        <v>20.43262349630123</v>
+        <v>19.91500576050328</v>
       </c>
       <c r="D262">
-        <v>33.38774045053801</v>
+        <v>33.45404840004295</v>
       </c>
       <c r="E262">
-        <v>6.695607651458028</v>
+        <v>6.464149929001907</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -6018,16 +6018,16 @@
         <v>266</v>
       </c>
       <c r="B263">
-        <v>2.770100441860005</v>
+        <v>3.517305372522672</v>
       </c>
       <c r="C263">
-        <v>20.46214067194112</v>
+        <v>20.4714065665953</v>
       </c>
       <c r="D263">
-        <v>33.69014159833436</v>
+        <v>33.37196769670171</v>
       </c>
       <c r="E263">
-        <v>6.404540467501576</v>
+        <v>6.699539981950738</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -6035,16 +6035,16 @@
         <v>267</v>
       </c>
       <c r="B264">
-        <v>4.043026269880583</v>
+        <v>3.758228298756349</v>
       </c>
       <c r="C264">
-        <v>19.8867000777717</v>
+        <v>19.63082024765015</v>
       </c>
       <c r="D264">
-        <v>33.26460948459681</v>
+        <v>33.3067574012292</v>
       </c>
       <c r="E264">
-        <v>6.847349618610349</v>
+        <v>7.195491020670101</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -6052,16 +6052,16 @@
         <v>268</v>
       </c>
       <c r="B265">
-        <v>3.67155571605057</v>
+        <v>4.204285147047536</v>
       </c>
       <c r="C265">
-        <v>20.45272227693395</v>
+        <v>19.51906895463944</v>
       </c>
       <c r="D265">
-        <v>33.41764978064071</v>
+        <v>33.35799509997452</v>
       </c>
       <c r="E265">
-        <v>7.47907570146421</v>
+        <v>6.607074723710265</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -6069,16 +6069,16 @@
         <v>269</v>
       </c>
       <c r="B266">
-        <v>3.786040156027282</v>
+        <v>3.70932084302511</v>
       </c>
       <c r="C266">
-        <v>19.36450785162003</v>
+        <v>19.38425144376097</v>
       </c>
       <c r="D266">
-        <v>33.58350440255412</v>
+        <v>33.26399213865013</v>
       </c>
       <c r="E266">
-        <v>6.60889651757174</v>
+        <v>6.5409413884406</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -6086,16 +6086,16 @@
         <v>270</v>
       </c>
       <c r="B267">
-        <v>2.89406278917419</v>
+        <v>3.060184903923155</v>
       </c>
       <c r="C267">
-        <v>20.14065162874738</v>
+        <v>19.79633386681543</v>
       </c>
       <c r="D267">
-        <v>33.608110185895</v>
+        <v>33.44002304235682</v>
       </c>
       <c r="E267">
-        <v>6.238233615479743</v>
+        <v>7.64804832056056</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -6103,16 +6103,16 @@
         <v>271</v>
       </c>
       <c r="B268">
-        <v>6.8429575373812</v>
+        <v>5.542733626737111</v>
       </c>
       <c r="C268">
-        <v>19.14394804611547</v>
+        <v>18.6969773478773</v>
       </c>
       <c r="D268">
-        <v>28.21445790858716</v>
+        <v>28.25299802560883</v>
       </c>
       <c r="E268">
-        <v>7.846987172938016</v>
+        <v>6.600047451939351</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -6120,16 +6120,16 @@
         <v>272</v>
       </c>
       <c r="B269">
-        <v>6.391156941011847</v>
+        <v>5.506215423821371</v>
       </c>
       <c r="C269">
-        <v>18.76242740841722</v>
+        <v>19.11453372807458</v>
       </c>
       <c r="D269">
-        <v>28.55803111007726</v>
+        <v>28.21176780722006</v>
       </c>
       <c r="E269">
-        <v>6.88139318115832</v>
+        <v>7.711359034986856</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -6137,16 +6137,16 @@
         <v>273</v>
       </c>
       <c r="B270">
-        <v>6.298167080333296</v>
+        <v>5.168802306023256</v>
       </c>
       <c r="C270">
-        <v>18.1137025568752</v>
+        <v>19.38308648286001</v>
       </c>
       <c r="D270">
-        <v>28.50838117578119</v>
+        <v>28.38299011938273</v>
       </c>
       <c r="E270">
-        <v>8.081806976347057</v>
+        <v>6.975115472138492</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -6154,16 +6154,16 @@
         <v>274</v>
       </c>
       <c r="B271">
-        <v>6.470583271540448</v>
+        <v>6.495808609785612</v>
       </c>
       <c r="C271">
-        <v>18.80478814385375</v>
+        <v>18.23869155028161</v>
       </c>
       <c r="D271">
-        <v>28.2231786770335</v>
+        <v>28.3380045466093</v>
       </c>
       <c r="E271">
-        <v>7.35509555768971</v>
+        <v>7.856079746725657</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -6171,16 +6171,16 @@
         <v>275</v>
       </c>
       <c r="B272">
-        <v>6.895333319532275</v>
+        <v>6.88292547465858</v>
       </c>
       <c r="C272">
-        <v>18.27090245863318</v>
+        <v>19.49346682560889</v>
       </c>
       <c r="D272">
-        <v>28.46258901121361</v>
+        <v>28.29186828851993</v>
       </c>
       <c r="E272">
-        <v>7.366365682475712</v>
+        <v>6.622768253151981</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -6188,16 +6188,16 @@
         <v>276</v>
       </c>
       <c r="B273">
-        <v>6.834533975799513</v>
+        <v>6.095871239329411</v>
       </c>
       <c r="C273">
-        <v>19.37811006939979</v>
+        <v>18.96003154895832</v>
       </c>
       <c r="D273">
-        <v>28.45907384137534</v>
+        <v>28.18540463104845</v>
       </c>
       <c r="E273">
-        <v>7.303934873465945</v>
+        <v>7.040603375261656</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -6205,16 +6205,16 @@
         <v>277</v>
       </c>
       <c r="B274">
-        <v>6.561108446180961</v>
+        <v>6.221443656747103</v>
       </c>
       <c r="C274">
-        <v>19.04492869670953</v>
+        <v>19.10781220995311</v>
       </c>
       <c r="D274">
-        <v>28.61305540734913</v>
+        <v>28.28390702596926</v>
       </c>
       <c r="E274">
-        <v>6.908683114795904</v>
+        <v>7.632509264893393</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -6222,16 +6222,16 @@
         <v>278</v>
       </c>
       <c r="B275">
-        <v>6.830406015088839</v>
+        <v>6.279828285198037</v>
       </c>
       <c r="C275">
-        <v>18.33825273105459</v>
+        <v>18.40058378070379</v>
       </c>
       <c r="D275">
-        <v>28.62188674813314</v>
+        <v>28.53653613493674</v>
       </c>
       <c r="E275">
-        <v>7.305033596737323</v>
+        <v>7.94025394701193</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -6239,16 +6239,16 @@
         <v>279</v>
       </c>
       <c r="B276">
-        <v>5.782284500511738</v>
+        <v>6.161043347384921</v>
       </c>
       <c r="C276">
-        <v>19.51660452254531</v>
+        <v>19.47270183767468</v>
       </c>
       <c r="D276">
-        <v>28.24442378498468</v>
+        <v>28.31753917283623</v>
       </c>
       <c r="E276">
-        <v>6.636457043610767</v>
+        <v>7.846682729282234</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -6256,16 +6256,16 @@
         <v>280</v>
       </c>
       <c r="B277">
-        <v>6.608957082082606</v>
+        <v>5.578676763752158</v>
       </c>
       <c r="C277">
-        <v>19.23446452032865</v>
+        <v>19.46496781806241</v>
       </c>
       <c r="D277">
-        <v>28.45137854533379</v>
+        <v>28.3267724621984</v>
       </c>
       <c r="E277">
-        <v>7.70962198855028</v>
+        <v>7.409134439556762</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -6273,16 +6273,16 @@
         <v>281</v>
       </c>
       <c r="B278">
-        <v>5.675445685130129</v>
+        <v>5.83376598933293</v>
       </c>
       <c r="C278">
-        <v>19.07762616035254</v>
+        <v>18.2478095178372</v>
       </c>
       <c r="D278">
-        <v>28.5056047734821</v>
+        <v>28.38145930151274</v>
       </c>
       <c r="E278">
-        <v>8.066714319563008</v>
+        <v>7.496577867181589</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -6290,16 +6290,16 @@
         <v>282</v>
       </c>
       <c r="B279">
-        <v>5.810756979654357</v>
+        <v>6.578102804122016</v>
       </c>
       <c r="C279">
-        <v>19.57484944020696</v>
+        <v>18.57275867793783</v>
       </c>
       <c r="D279">
-        <v>28.64116689949666</v>
+        <v>28.6056040481377</v>
       </c>
       <c r="E279">
-        <v>7.104632462895005</v>
+        <v>8.073274782977776</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6307,16 +6307,16 @@
         <v>283</v>
       </c>
       <c r="B280">
-        <v>5.895056830403765</v>
+        <v>6.231106856678532</v>
       </c>
       <c r="C280">
-        <v>18.64402113007887</v>
+        <v>19.68656560922348</v>
       </c>
       <c r="D280">
-        <v>28.37645566938615</v>
+        <v>28.38193156236217</v>
       </c>
       <c r="E280">
-        <v>7.543366462844682</v>
+        <v>7.959126916253993</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -6324,16 +6324,16 @@
         <v>284</v>
       </c>
       <c r="B281">
-        <v>6.856962182067252</v>
+        <v>6.825575083098437</v>
       </c>
       <c r="C281">
-        <v>18.5851685207014</v>
+        <v>18.75886426317039</v>
       </c>
       <c r="D281">
-        <v>28.53783604364919</v>
+        <v>28.29548796716182</v>
       </c>
       <c r="E281">
-        <v>6.598217727184357</v>
+        <v>7.073514142754292</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -6341,16 +6341,16 @@
         <v>285</v>
       </c>
       <c r="B282">
-        <v>5.944124763820565</v>
+        <v>5.132671324690843</v>
       </c>
       <c r="C282">
-        <v>19.14604278630542</v>
+        <v>18.10440229310876</v>
       </c>
       <c r="D282">
-        <v>28.44831806677363</v>
+        <v>28.34179103742969</v>
       </c>
       <c r="E282">
-        <v>7.66762689084934</v>
+        <v>6.680755297325326</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -6358,16 +6358,16 @@
         <v>286</v>
       </c>
       <c r="B283">
-        <v>5.982995110457103</v>
+        <v>5.159228426349548</v>
       </c>
       <c r="C283">
-        <v>19.61643512158053</v>
+        <v>18.75655635451303</v>
       </c>
       <c r="D283">
-        <v>28.42968475195954</v>
+        <v>28.36298248235084</v>
       </c>
       <c r="E283">
-        <v>7.650023695053951</v>
+        <v>7.860856884156362</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -6375,16 +6375,16 @@
         <v>287</v>
       </c>
       <c r="B284">
-        <v>6.615939736375506</v>
+        <v>5.516410409665103</v>
       </c>
       <c r="C284">
-        <v>18.45065692033062</v>
+        <v>19.02531559963077</v>
       </c>
       <c r="D284">
-        <v>28.61970728942392</v>
+        <v>28.49167090587873</v>
       </c>
       <c r="E284">
-        <v>7.614796259016475</v>
+        <v>6.996490692719737</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -6392,16 +6392,16 @@
         <v>288</v>
       </c>
       <c r="B285">
-        <v>5.334045046095387</v>
+        <v>6.385803709790486</v>
       </c>
       <c r="C285">
-        <v>19.59325838465868</v>
+        <v>19.62651558961253</v>
       </c>
       <c r="D285">
-        <v>28.51781207798154</v>
+        <v>28.57620540800451</v>
       </c>
       <c r="E285">
-        <v>6.691948558209114</v>
+        <v>7.253308730196943</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -6409,16 +6409,16 @@
         <v>289</v>
       </c>
       <c r="B286">
-        <v>6.154625106271158</v>
+        <v>6.239845472019704</v>
       </c>
       <c r="C286">
-        <v>19.41052220571262</v>
+        <v>18.3063436228856</v>
       </c>
       <c r="D286">
-        <v>28.47353216154252</v>
+        <v>28.43130216311092</v>
       </c>
       <c r="E286">
-        <v>7.927369459428999</v>
+        <v>6.666730492010361</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6426,16 +6426,16 @@
         <v>290</v>
       </c>
       <c r="B287">
-        <v>5.279469271769961</v>
+        <v>6.886642741482447</v>
       </c>
       <c r="C287">
-        <v>19.39963266314408</v>
+        <v>19.16150522895978</v>
       </c>
       <c r="D287">
-        <v>28.41617484665338</v>
+        <v>28.48882624082365</v>
       </c>
       <c r="E287">
-        <v>7.825799422394138</v>
+        <v>6.720953846319277</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -6443,16 +6443,16 @@
         <v>291</v>
       </c>
       <c r="B288">
-        <v>6.378887571518282</v>
+        <v>5.246097677759913</v>
       </c>
       <c r="C288">
-        <v>19.18368305836634</v>
+        <v>19.0836599099468</v>
       </c>
       <c r="D288">
-        <v>28.34381828865514</v>
+        <v>28.27932072859683</v>
       </c>
       <c r="E288">
-        <v>7.614669622681568</v>
+        <v>6.954790830488675</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -6460,16 +6460,16 @@
         <v>292</v>
       </c>
       <c r="B289">
-        <v>5.767534534223589</v>
+        <v>5.286295519097306</v>
       </c>
       <c r="C289">
-        <v>18.20060110511882</v>
+        <v>18.39926571971086</v>
       </c>
       <c r="D289">
-        <v>28.31126795863614</v>
+        <v>28.53637355434516</v>
       </c>
       <c r="E289">
-        <v>6.725865923122424</v>
+        <v>6.921137566433955</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -6477,16 +6477,16 @@
         <v>293</v>
       </c>
       <c r="B290">
-        <v>6.073681162572681</v>
+        <v>6.185805451046434</v>
       </c>
       <c r="C290">
-        <v>18.30099768767331</v>
+        <v>18.85888006759876</v>
       </c>
       <c r="D290">
-        <v>28.34843704809116</v>
+        <v>28.45986186808448</v>
       </c>
       <c r="E290">
-        <v>7.017633389772577</v>
+        <v>7.557110459589552</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -6494,16 +6494,16 @@
         <v>294</v>
       </c>
       <c r="B291">
-        <v>6.25154597809192</v>
+        <v>6.037526682332536</v>
       </c>
       <c r="C291">
-        <v>18.80412379806327</v>
+        <v>18.45650368826678</v>
       </c>
       <c r="D291">
-        <v>28.26373078771014</v>
+        <v>28.64096571639549</v>
       </c>
       <c r="E291">
-        <v>7.954285767908631</v>
+        <v>7.044907211711759</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -6511,16 +6511,16 @@
         <v>295</v>
       </c>
       <c r="B292">
-        <v>6.489324042999144</v>
+        <v>6.316784140600359</v>
       </c>
       <c r="C292">
-        <v>18.39590600650261</v>
+        <v>18.92666046577046</v>
       </c>
       <c r="D292">
-        <v>28.27134912504051</v>
+        <v>28.50194942847865</v>
       </c>
       <c r="E292">
-        <v>7.007415593350822</v>
+        <v>7.017465277117717</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -6528,16 +6528,16 @@
         <v>296</v>
       </c>
       <c r="B293">
-        <v>6.288582831584683</v>
+        <v>5.337859966582632</v>
       </c>
       <c r="C293">
-        <v>18.41141474202515</v>
+        <v>19.33963342209665</v>
       </c>
       <c r="D293">
-        <v>28.32442476464693</v>
+        <v>28.22836181500502</v>
       </c>
       <c r="E293">
-        <v>7.98768310481014</v>
+        <v>7.470394925343584</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -6545,16 +6545,16 @@
         <v>297</v>
       </c>
       <c r="B294">
-        <v>6.544942143090276</v>
+        <v>5.683321196556666</v>
       </c>
       <c r="C294">
-        <v>19.39816438637145</v>
+        <v>18.520552458625</v>
       </c>
       <c r="D294">
-        <v>28.18724794901466</v>
+        <v>28.3784794842277</v>
       </c>
       <c r="E294">
-        <v>7.012959116732769</v>
+        <v>6.656452660564672</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -6562,16 +6562,16 @@
         <v>298</v>
       </c>
       <c r="B295">
-        <v>6.216219285022786</v>
+        <v>6.296387772101221</v>
       </c>
       <c r="C295">
-        <v>18.55025418526871</v>
+        <v>18.35139325206421</v>
       </c>
       <c r="D295">
-        <v>28.45247392173311</v>
+        <v>28.37048238307101</v>
       </c>
       <c r="E295">
-        <v>7.973929921357035</v>
+        <v>7.0002322906592</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -6579,16 +6579,16 @@
         <v>299</v>
       </c>
       <c r="B296">
-        <v>5.415321948877735</v>
+        <v>6.054924781806807</v>
       </c>
       <c r="C296">
-        <v>18.30801147636031</v>
+        <v>19.3249708113727</v>
       </c>
       <c r="D296">
-        <v>28.42120977030895</v>
+        <v>28.56448064550423</v>
       </c>
       <c r="E296">
-        <v>7.420270025896448</v>
+        <v>7.611408069108784</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -6596,16 +6596,16 @@
         <v>300</v>
       </c>
       <c r="B297">
-        <v>6.415000241649459</v>
+        <v>6.609625932508848</v>
       </c>
       <c r="C297">
-        <v>18.47991627046141</v>
+        <v>18.49850864530034</v>
       </c>
       <c r="D297">
-        <v>28.32149473376737</v>
+        <v>28.61130988514159</v>
       </c>
       <c r="E297">
-        <v>6.793795680283193</v>
+        <v>8.092043162412915</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -6613,16 +6613,16 @@
         <v>301</v>
       </c>
       <c r="B298">
-        <v>6.057201602220662</v>
+        <v>5.583264248234356</v>
       </c>
       <c r="C298">
-        <v>19.58041911993555</v>
+        <v>19.10598598248799</v>
       </c>
       <c r="D298">
-        <v>28.47868243842119</v>
+        <v>28.56150653534035</v>
       </c>
       <c r="E298">
-        <v>7.853562668345678</v>
+        <v>7.584935650455321</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -6630,16 +6630,16 @@
         <v>302</v>
       </c>
       <c r="B299">
-        <v>6.284591818617772</v>
+        <v>6.787811373079495</v>
       </c>
       <c r="C299">
-        <v>18.84510953200376</v>
+        <v>19.23489190083724</v>
       </c>
       <c r="D299">
-        <v>28.4092425330415</v>
+        <v>28.64859285682265</v>
       </c>
       <c r="E299">
-        <v>7.525901668680218</v>
+        <v>7.628532513404781</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -6647,16 +6647,16 @@
         <v>303</v>
       </c>
       <c r="B300">
-        <v>6.769216139016928</v>
+        <v>5.960914231674408</v>
       </c>
       <c r="C300">
-        <v>18.8292502029602</v>
+        <v>19.18619777120673</v>
       </c>
       <c r="D300">
-        <v>28.37608140734342</v>
+        <v>28.63289269997727</v>
       </c>
       <c r="E300">
-        <v>8.053548104325184</v>
+        <v>6.673517139827679</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -6664,16 +6664,16 @@
         <v>304</v>
       </c>
       <c r="B301">
-        <v>6.338291240921563</v>
+        <v>5.369386154782705</v>
       </c>
       <c r="C301">
-        <v>18.57226627891907</v>
+        <v>19.14945844242789</v>
       </c>
       <c r="D301">
-        <v>28.6153790724362</v>
+        <v>28.3177590234648</v>
       </c>
       <c r="E301">
-        <v>7.850717664590386</v>
+        <v>7.752362264280141</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -6681,16 +6681,16 @@
         <v>305</v>
       </c>
       <c r="B302">
-        <v>6.784167474370165</v>
+        <v>5.262084846577031</v>
       </c>
       <c r="C302">
-        <v>18.71126784256851</v>
+        <v>18.67192712399134</v>
       </c>
       <c r="D302">
-        <v>28.3264383701223</v>
+        <v>28.42105623052227</v>
       </c>
       <c r="E302">
-        <v>7.970770439048037</v>
+        <v>7.361823027152166</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -6698,16 +6698,16 @@
         <v>306</v>
       </c>
       <c r="B303">
-        <v>5.16846099673401</v>
+        <v>5.253048923402311</v>
       </c>
       <c r="C303">
-        <v>18.6614481605526</v>
+        <v>18.11272286345916</v>
       </c>
       <c r="D303">
-        <v>28.50588988444066</v>
+        <v>28.63894329169189</v>
       </c>
       <c r="E303">
-        <v>6.927167980470927</v>
+        <v>6.566744907435417</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -6715,16 +6715,16 @@
         <v>307</v>
       </c>
       <c r="B304">
-        <v>6.855142305825838</v>
+        <v>6.016337620687828</v>
       </c>
       <c r="C304">
-        <v>19.08737931132488</v>
+        <v>18.60576022649295</v>
       </c>
       <c r="D304">
-        <v>28.48142547577253</v>
+        <v>28.24626508724235</v>
       </c>
       <c r="E304">
-        <v>7.335202619702812</v>
+        <v>7.777028672242245</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -6732,16 +6732,16 @@
         <v>308</v>
       </c>
       <c r="B305">
-        <v>6.641403038392433</v>
+        <v>6.486340756946477</v>
       </c>
       <c r="C305">
-        <v>18.94356322665855</v>
+        <v>19.46548654226419</v>
       </c>
       <c r="D305">
-        <v>28.41802215089355</v>
+        <v>28.38283580405391</v>
       </c>
       <c r="E305">
-        <v>7.807826329600124</v>
+        <v>6.618238365873006</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -6749,16 +6749,16 @@
         <v>309</v>
       </c>
       <c r="B306">
-        <v>5.292053263434374</v>
+        <v>5.842402373108475</v>
       </c>
       <c r="C306">
-        <v>18.9434613335389</v>
+        <v>18.46924026170744</v>
       </c>
       <c r="D306">
-        <v>28.18728673584967</v>
+        <v>28.48884561736527</v>
       </c>
       <c r="E306">
-        <v>7.060504558254265</v>
+        <v>7.321072544351201</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -6766,16 +6766,16 @@
         <v>310</v>
       </c>
       <c r="B307">
-        <v>6.034187752691111</v>
+        <v>6.75276432862411</v>
       </c>
       <c r="C307">
-        <v>19.33222696020646</v>
+        <v>18.44740724764925</v>
       </c>
       <c r="D307">
-        <v>28.52936198345478</v>
+        <v>28.39289330532046</v>
       </c>
       <c r="E307">
-        <v>7.622147297415616</v>
+        <v>7.481615039308116</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -6783,16 +6783,16 @@
         <v>311</v>
       </c>
       <c r="B308">
-        <v>6.298232581620576</v>
+        <v>6.883827077306542</v>
       </c>
       <c r="C308">
-        <v>19.28345638019039</v>
+        <v>19.11555710802022</v>
       </c>
       <c r="D308">
-        <v>28.35732623238816</v>
+        <v>28.18049374912476</v>
       </c>
       <c r="E308">
-        <v>7.07788344743564</v>
+        <v>6.652330560653048</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -6800,16 +6800,16 @@
         <v>312</v>
       </c>
       <c r="B309">
-        <v>5.721672428727174</v>
+        <v>5.15801100768448</v>
       </c>
       <c r="C309">
-        <v>18.4590815773384</v>
+        <v>18.51230673919949</v>
       </c>
       <c r="D309">
-        <v>28.46445823890138</v>
+        <v>28.5682577426327</v>
       </c>
       <c r="E309">
-        <v>7.832619356925321</v>
+        <v>7.427433577570913</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -6817,16 +6817,16 @@
         <v>313</v>
       </c>
       <c r="B310">
-        <v>6.080070380664585</v>
+        <v>6.216634846505078</v>
       </c>
       <c r="C310">
-        <v>19.06296577570368</v>
+        <v>18.74063879814315</v>
       </c>
       <c r="D310">
-        <v>28.37306689604017</v>
+        <v>28.57318243223585</v>
       </c>
       <c r="E310">
-        <v>7.800134931565848</v>
+        <v>7.213940938115249</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -6834,16 +6834,16 @@
         <v>314</v>
       </c>
       <c r="B311">
-        <v>5.579218978226068</v>
+        <v>5.561216665219147</v>
       </c>
       <c r="C311">
-        <v>19.4723221450399</v>
+        <v>19.34842654663246</v>
       </c>
       <c r="D311">
-        <v>28.63167379127901</v>
+        <v>28.41723438482775</v>
       </c>
       <c r="E311">
-        <v>7.062160835949741</v>
+        <v>7.803425919960302</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -6851,16 +6851,16 @@
         <v>315</v>
       </c>
       <c r="B312">
-        <v>5.908200513163845</v>
+        <v>5.269481381994282</v>
       </c>
       <c r="C312">
-        <v>19.36814295411907</v>
+        <v>18.47760114724568</v>
       </c>
       <c r="D312">
-        <v>28.57570902485471</v>
+        <v>28.38345734663984</v>
       </c>
       <c r="E312">
-        <v>6.750079538912445</v>
+        <v>6.636473207333238</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -6868,16 +6868,16 @@
         <v>316</v>
       </c>
       <c r="B313">
-        <v>5.738650199617929</v>
+        <v>6.446363565616045</v>
       </c>
       <c r="C313">
-        <v>18.30887093016885</v>
+        <v>18.92171679294643</v>
       </c>
       <c r="D313">
-        <v>28.55959922251639</v>
+        <v>28.44685479561498</v>
       </c>
       <c r="E313">
-        <v>7.206861334710208</v>
+        <v>7.758859831954037</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -6885,16 +6885,16 @@
         <v>317</v>
       </c>
       <c r="B314">
-        <v>5.26686658643623</v>
+        <v>6.834693293563322</v>
       </c>
       <c r="C314">
-        <v>18.97257413187095</v>
+        <v>18.41176215017631</v>
       </c>
       <c r="D314">
-        <v>28.41639702086014</v>
+        <v>28.56371688137525</v>
       </c>
       <c r="E314">
-        <v>7.285167578461549</v>
+        <v>7.588907340732635</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -6902,16 +6902,16 @@
         <v>318</v>
       </c>
       <c r="B315">
-        <v>6.573083942590506</v>
+        <v>5.934874385895887</v>
       </c>
       <c r="C315">
-        <v>19.14027426013924</v>
+        <v>19.45917305588965</v>
       </c>
       <c r="D315">
-        <v>28.52348505241057</v>
+        <v>28.33535599038608</v>
       </c>
       <c r="E315">
-        <v>7.854107049943202</v>
+        <v>6.849177302410776</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6919,16 +6919,16 @@
         <v>319</v>
       </c>
       <c r="B316">
-        <v>6.356619031365975</v>
+        <v>6.671471891441284</v>
       </c>
       <c r="C316">
-        <v>19.27567557613764</v>
+        <v>18.77872773168262</v>
       </c>
       <c r="D316">
-        <v>28.67250985323345</v>
+        <v>28.44830357848051</v>
       </c>
       <c r="E316">
-        <v>6.577224931905993</v>
+        <v>7.989294308776024</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -6936,16 +6936,16 @@
         <v>320</v>
       </c>
       <c r="B317">
-        <v>5.84808365835034</v>
+        <v>5.889547450485222</v>
       </c>
       <c r="C317">
-        <v>18.67486375715947</v>
+        <v>19.64306303144643</v>
       </c>
       <c r="D317">
-        <v>28.57138912136468</v>
+        <v>28.55603983141656</v>
       </c>
       <c r="E317">
-        <v>6.584100769219256</v>
+        <v>7.195064424985899</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -6953,16 +6953,16 @@
         <v>321</v>
       </c>
       <c r="B318">
-        <v>6.320356863110217</v>
+        <v>5.885548264453496</v>
       </c>
       <c r="C318">
-        <v>18.43755692454038</v>
+        <v>19.49340390744296</v>
       </c>
       <c r="D318">
-        <v>28.50520515029757</v>
+        <v>28.53327510941455</v>
       </c>
       <c r="E318">
-        <v>7.810133134230052</v>
+        <v>8.126832299801004</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -6970,16 +6970,16 @@
         <v>322</v>
       </c>
       <c r="B319">
-        <v>6.552938681436178</v>
+        <v>5.737166491174807</v>
       </c>
       <c r="C319">
-        <v>18.82758088745131</v>
+        <v>18.27897121724055</v>
       </c>
       <c r="D319">
-        <v>28.40572019513425</v>
+        <v>28.22627233621961</v>
       </c>
       <c r="E319">
-        <v>7.782982723600472</v>
+        <v>7.823284454076495</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6987,16 +6987,16 @@
         <v>323</v>
       </c>
       <c r="B320">
-        <v>5.755728789114848</v>
+        <v>6.519242847785632</v>
       </c>
       <c r="C320">
-        <v>18.92155572473591</v>
+        <v>18.38037034311565</v>
       </c>
       <c r="D320">
-        <v>28.67553737349844</v>
+        <v>28.6237068789556</v>
       </c>
       <c r="E320">
-        <v>6.808629300970966</v>
+        <v>8.110263582615735</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -7004,16 +7004,16 @@
         <v>324</v>
       </c>
       <c r="B321">
-        <v>5.129685181277577</v>
+        <v>5.402922555191099</v>
       </c>
       <c r="C321">
-        <v>19.34559497086653</v>
+        <v>19.2445677955615</v>
       </c>
       <c r="D321">
-        <v>28.52625600158551</v>
+        <v>28.57514062294054</v>
       </c>
       <c r="E321">
-        <v>7.885393031423465</v>
+        <v>7.572500152692552</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -7021,16 +7021,16 @@
         <v>325</v>
       </c>
       <c r="B322">
-        <v>5.737650344204541</v>
+        <v>6.592423893350261</v>
       </c>
       <c r="C322">
-        <v>19.08430799228555</v>
+        <v>18.18987323525844</v>
       </c>
       <c r="D322">
-        <v>28.49508629593273</v>
+        <v>28.63466592963875</v>
       </c>
       <c r="E322">
-        <v>7.506842921714255</v>
+        <v>8.075720485671644</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -7038,16 +7038,16 @@
         <v>326</v>
       </c>
       <c r="B323">
-        <v>6.260847505370865</v>
+        <v>6.256500548891822</v>
       </c>
       <c r="C323">
-        <v>19.26075838956957</v>
+        <v>18.17501376560747</v>
       </c>
       <c r="D323">
-        <v>28.5610051542547</v>
+        <v>28.1938423185012</v>
       </c>
       <c r="E323">
-        <v>6.921318569857543</v>
+        <v>7.940316639791622</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -7055,16 +7055,16 @@
         <v>327</v>
       </c>
       <c r="B324">
-        <v>6.806695452841196</v>
+        <v>6.446727965181978</v>
       </c>
       <c r="C324">
-        <v>18.63661870779102</v>
+        <v>18.12498598550416</v>
       </c>
       <c r="D324">
-        <v>28.39436181179413</v>
+        <v>28.31219684632033</v>
       </c>
       <c r="E324">
-        <v>6.753605763541247</v>
+        <v>7.029520136171021</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -7072,16 +7072,16 @@
         <v>328</v>
       </c>
       <c r="B325">
-        <v>6.132491950279179</v>
+        <v>5.67410479921272</v>
       </c>
       <c r="C325">
-        <v>19.60139076439607</v>
+        <v>19.64233150496812</v>
       </c>
       <c r="D325">
-        <v>28.37910013953379</v>
+        <v>28.35368000375519</v>
       </c>
       <c r="E325">
-        <v>8.071819406209015</v>
+        <v>7.251498990423834</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -7089,16 +7089,16 @@
         <v>329</v>
       </c>
       <c r="B326">
-        <v>5.706915041885232</v>
+        <v>5.879128210620213</v>
       </c>
       <c r="C326">
-        <v>18.37643682668667</v>
+        <v>19.4448983854217</v>
       </c>
       <c r="D326">
-        <v>28.28641540857603</v>
+        <v>28.48413796498826</v>
       </c>
       <c r="E326">
-        <v>6.860139923557321</v>
+        <v>8.050163402890364</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -7106,16 +7106,16 @@
         <v>330</v>
       </c>
       <c r="B327">
-        <v>6.12343224202843</v>
+        <v>6.542505498995856</v>
       </c>
       <c r="C327">
-        <v>19.36574802409532</v>
+        <v>19.69013216848086</v>
       </c>
       <c r="D327">
-        <v>28.57121318086109</v>
+        <v>28.61247269978954</v>
       </c>
       <c r="E327">
-        <v>6.67986580274988</v>
+        <v>6.599910052222246</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -7123,16 +7123,16 @@
         <v>331</v>
       </c>
       <c r="B328">
-        <v>6.203219271019888</v>
+        <v>6.307992740118235</v>
       </c>
       <c r="C328">
-        <v>19.37955073634196</v>
+        <v>19.48082279864087</v>
       </c>
       <c r="D328">
-        <v>28.25517168661486</v>
+        <v>28.40784417917718</v>
       </c>
       <c r="E328">
-        <v>7.70290450260406</v>
+        <v>7.520279321199107</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -7140,16 +7140,16 @@
         <v>332</v>
       </c>
       <c r="B329">
-        <v>5.527290232709345</v>
+        <v>6.50547059841349</v>
       </c>
       <c r="C329">
-        <v>19.41421361043518</v>
+        <v>18.7485651548139</v>
       </c>
       <c r="D329">
-        <v>28.46282543589081</v>
+        <v>28.53990154954938</v>
       </c>
       <c r="E329">
-        <v>6.86058035610621</v>
+        <v>8.083366629799945</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -7157,16 +7157,16 @@
         <v>333</v>
       </c>
       <c r="B330">
-        <v>3.175629603150818</v>
+        <v>2.343325322243685</v>
       </c>
       <c r="C330">
-        <v>7.216298200412728</v>
+        <v>6.96881465699109</v>
       </c>
       <c r="D330">
-        <v>57.99733794422777</v>
+        <v>58.13718672357489</v>
       </c>
       <c r="E330">
-        <v>1.811374840674428</v>
+        <v>2.071010844904865</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -7174,16 +7174,16 @@
         <v>334</v>
       </c>
       <c r="B331">
-        <v>2.643949734216563</v>
+        <v>3.470305399962826</v>
       </c>
       <c r="C331">
-        <v>6.691571252671482</v>
+        <v>5.954909987064802</v>
       </c>
       <c r="D331">
-        <v>58.24051947607289</v>
+        <v>58.19114517031176</v>
       </c>
       <c r="E331">
-        <v>1.597555559100905</v>
+        <v>2.408553026347066</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -7191,16 +7191,16 @@
         <v>335</v>
       </c>
       <c r="B332">
-        <v>2.244394947642849</v>
+        <v>1.850060104043005</v>
       </c>
       <c r="C332">
-        <v>7.355936936400889</v>
+        <v>6.10687993946776</v>
       </c>
       <c r="D332">
-        <v>57.87452588384427</v>
+        <v>58.24637701398861</v>
       </c>
       <c r="E332">
-        <v>1.289833423939174</v>
+        <v>2.532309605524716</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -7208,16 +7208,16 @@
         <v>336</v>
       </c>
       <c r="B333">
-        <v>2.531580477995731</v>
+        <v>2.202996433026629</v>
       </c>
       <c r="C333">
-        <v>6.496654045041068</v>
+        <v>6.377011110566653</v>
       </c>
       <c r="D333">
-        <v>57.86614864963545</v>
+        <v>58.12050116445409</v>
       </c>
       <c r="E333">
-        <v>2.692196003471712</v>
+        <v>2.304905037993365</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -7225,16 +7225,16 @@
         <v>337</v>
       </c>
       <c r="B334">
-        <v>2.291636847993273</v>
+        <v>2.220588858592683</v>
       </c>
       <c r="C334">
-        <v>6.553058265007375</v>
+        <v>6.660237253103874</v>
       </c>
       <c r="D334">
-        <v>57.79618507354044</v>
+        <v>57.90223097555567</v>
       </c>
       <c r="E334">
-        <v>2.46352037443858</v>
+        <v>2.737742904373149</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -7242,16 +7242,16 @@
         <v>338</v>
       </c>
       <c r="B335">
-        <v>2.062709333569394</v>
+        <v>3.388038483295766</v>
       </c>
       <c r="C335">
-        <v>7.222347930789424</v>
+        <v>6.09657921085509</v>
       </c>
       <c r="D335">
-        <v>58.04710195029547</v>
+        <v>58.10947691948299</v>
       </c>
       <c r="E335">
-        <v>2.081482051929509</v>
+        <v>2.75759967381064</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -7259,16 +7259,16 @@
         <v>339</v>
       </c>
       <c r="B336">
-        <v>2.438019428582049</v>
+        <v>2.002357541680854</v>
       </c>
       <c r="C336">
-        <v>6.399912575789114</v>
+        <v>6.698200904080614</v>
       </c>
       <c r="D336">
-        <v>58.03870822042632</v>
+        <v>57.79557147761256</v>
       </c>
       <c r="E336">
-        <v>2.384945615828868</v>
+        <v>2.1119131777268</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -7276,16 +7276,16 @@
         <v>340</v>
       </c>
       <c r="B337">
-        <v>3.093410271630642</v>
+        <v>2.686225396648948</v>
       </c>
       <c r="C337">
-        <v>6.693585242339689</v>
+        <v>7.296316360430994</v>
       </c>
       <c r="D337">
-        <v>57.956073885728</v>
+        <v>57.96084203505233</v>
       </c>
       <c r="E337">
-        <v>1.866960746220065</v>
+        <v>2.216102648580483</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -7293,16 +7293,16 @@
         <v>341</v>
       </c>
       <c r="B338">
-        <v>1.808770786918878</v>
+        <v>3.127784911635852</v>
       </c>
       <c r="C338">
-        <v>7.032699177740839</v>
+        <v>7.339301218091759</v>
       </c>
       <c r="D338">
-        <v>58.21348153076951</v>
+        <v>58.18640128816071</v>
       </c>
       <c r="E338">
-        <v>1.614469550038643</v>
+        <v>2.152448921410712</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -7310,16 +7310,16 @@
         <v>342</v>
       </c>
       <c r="B339">
-        <v>1.971609034677386</v>
+        <v>2.674522819573613</v>
       </c>
       <c r="C339">
-        <v>6.364394194064847</v>
+        <v>7.128943370068285</v>
       </c>
       <c r="D339">
-        <v>57.8529406006938</v>
+        <v>57.9001423553509</v>
       </c>
       <c r="E339">
-        <v>1.457474465900623</v>
+        <v>2.027611390262563</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -7327,16 +7327,16 @@
         <v>343</v>
       </c>
       <c r="B340">
-        <v>2.170426907739422</v>
+        <v>1.810098645518141</v>
       </c>
       <c r="C340">
-        <v>7.027586858881016</v>
+        <v>6.699796892977931</v>
       </c>
       <c r="D340">
-        <v>58.05955430438826</v>
+        <v>58.1831055579171</v>
       </c>
       <c r="E340">
-        <v>2.819940938326673</v>
+        <v>2.720653445328441</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -7344,16 +7344,16 @@
         <v>344</v>
       </c>
       <c r="B341">
-        <v>3.309267292226621</v>
+        <v>3.48027992158928</v>
       </c>
       <c r="C341">
-        <v>7.253486085720202</v>
+        <v>5.988591689308641</v>
       </c>
       <c r="D341">
-        <v>57.89737886392487</v>
+        <v>58.23655736616602</v>
       </c>
       <c r="E341">
-        <v>2.238824524907231</v>
+        <v>1.2739340302571</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -7361,16 +7361,16 @@
         <v>345</v>
       </c>
       <c r="B342">
-        <v>2.137563923759596</v>
+        <v>3.288718798974151</v>
       </c>
       <c r="C342">
-        <v>6.564277719602032</v>
+        <v>5.997328897412688</v>
       </c>
       <c r="D342">
-        <v>58.05702964488516</v>
+        <v>58.1949988343023</v>
       </c>
       <c r="E342">
-        <v>2.67651314234905</v>
+        <v>2.237321078172034</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -7378,16 +7378,16 @@
         <v>346</v>
       </c>
       <c r="B343">
-        <v>2.383514950642182</v>
+        <v>2.770279066588513</v>
       </c>
       <c r="C343">
-        <v>7.310075013958031</v>
+        <v>7.254135158157158</v>
       </c>
       <c r="D343">
-        <v>57.80850793908457</v>
+        <v>58.03811734371667</v>
       </c>
       <c r="E343">
-        <v>1.814947313099168</v>
+        <v>1.858546236038383</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -7395,16 +7395,16 @@
         <v>347</v>
       </c>
       <c r="B344">
-        <v>2.087909317393904</v>
+        <v>3.396810645040886</v>
       </c>
       <c r="C344">
-        <v>7.167251960960897</v>
+        <v>6.595390731949374</v>
       </c>
       <c r="D344">
-        <v>58.08175249729743</v>
+        <v>57.90085690509354</v>
       </c>
       <c r="E344">
-        <v>1.760599718507034</v>
+        <v>2.197265517842157</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -7412,16 +7412,16 @@
         <v>348</v>
       </c>
       <c r="B345">
-        <v>3.133750453360928</v>
+        <v>1.901696898428362</v>
       </c>
       <c r="C345">
-        <v>7.444390762966114</v>
+        <v>6.544494982979786</v>
       </c>
       <c r="D345">
-        <v>57.96943738565763</v>
+        <v>57.93099446407611</v>
       </c>
       <c r="E345">
-        <v>1.591350148399004</v>
+        <v>1.911956734931438</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -7429,16 +7429,16 @@
         <v>349</v>
       </c>
       <c r="B346">
-        <v>2.843686035822912</v>
+        <v>3.390228396845751</v>
       </c>
       <c r="C346">
-        <v>7.159819018589926</v>
+        <v>7.129809196533892</v>
       </c>
       <c r="D346">
-        <v>57.95723043202766</v>
+        <v>57.903271408651</v>
       </c>
       <c r="E346">
-        <v>2.303593874284365</v>
+        <v>1.394461641545885</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -7446,16 +7446,16 @@
         <v>350</v>
       </c>
       <c r="B347">
-        <v>1.798212246144874</v>
+        <v>2.341669845148152</v>
       </c>
       <c r="C347">
-        <v>6.022611556219353</v>
+        <v>6.095188992336217</v>
       </c>
       <c r="D347">
-        <v>58.15468363861891</v>
+        <v>58.21460540899444</v>
       </c>
       <c r="E347">
-        <v>1.576279733422374</v>
+        <v>2.761997865342707</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -7463,16 +7463,16 @@
         <v>351</v>
       </c>
       <c r="B348">
-        <v>1.997245298529642</v>
+        <v>2.9929120016221</v>
       </c>
       <c r="C348">
-        <v>7.277238117925479</v>
+        <v>6.108149521671093</v>
       </c>
       <c r="D348">
-        <v>57.81239030432798</v>
+        <v>58.0102881740326</v>
       </c>
       <c r="E348">
-        <v>1.686387245859633</v>
+        <v>2.300446993109568</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -7480,16 +7480,16 @@
         <v>352</v>
       </c>
       <c r="B349">
-        <v>2.240876440262315</v>
+        <v>2.476096930337412</v>
       </c>
       <c r="C349">
-        <v>6.810904117791901</v>
+        <v>7.068456776355251</v>
       </c>
       <c r="D349">
-        <v>57.94226900433443</v>
+        <v>58.07733859008275</v>
       </c>
       <c r="E349">
-        <v>1.557890060089896</v>
+        <v>1.526404931179601</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -7497,16 +7497,16 @@
         <v>353</v>
       </c>
       <c r="B350">
-        <v>3.324549543198978</v>
+        <v>3.543073627144441</v>
       </c>
       <c r="C350">
-        <v>6.05794698073654</v>
+        <v>6.492610414006073</v>
       </c>
       <c r="D350">
-        <v>58.15884031266823</v>
+        <v>57.84396330306958</v>
       </c>
       <c r="E350">
-        <v>1.822062444586201</v>
+        <v>1.49996107303451</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -7514,16 +7514,16 @@
         <v>354</v>
       </c>
       <c r="B351">
-        <v>2.025221627042841</v>
+        <v>1.983174296600106</v>
       </c>
       <c r="C351">
-        <v>5.986008099472251</v>
+        <v>6.70497107844289</v>
       </c>
       <c r="D351">
-        <v>58.08184591637649</v>
+        <v>58.10946555049797</v>
       </c>
       <c r="E351">
-        <v>2.088674081869384</v>
+        <v>1.64038150732678</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -7531,16 +7531,16 @@
         <v>355</v>
       </c>
       <c r="B352">
-        <v>2.619713686292113</v>
+        <v>2.737465107020927</v>
       </c>
       <c r="C352">
-        <v>6.859594516149325</v>
+        <v>5.939681651826493</v>
       </c>
       <c r="D352">
-        <v>58.23544597306012</v>
+        <v>57.83879002828157</v>
       </c>
       <c r="E352">
-        <v>1.671100407006711</v>
+        <v>2.617214379136229</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -7548,16 +7548,16 @@
         <v>356</v>
       </c>
       <c r="B353">
-        <v>2.538021483114351</v>
+        <v>2.128691713653114</v>
       </c>
       <c r="C353">
-        <v>7.348435657304966</v>
+        <v>6.040700262090636</v>
       </c>
       <c r="D353">
-        <v>58.13829889420257</v>
+        <v>57.81331972643605</v>
       </c>
       <c r="E353">
-        <v>2.178254337196504</v>
+        <v>2.786005251912078</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -7565,16 +7565,16 @@
         <v>357</v>
       </c>
       <c r="B354">
-        <v>2.240511241561642</v>
+        <v>1.987261758491428</v>
       </c>
       <c r="C354">
-        <v>6.24840001028508</v>
+        <v>6.356462274784429</v>
       </c>
       <c r="D354">
-        <v>57.98974317298552</v>
+        <v>58.26119307162146</v>
       </c>
       <c r="E354">
-        <v>2.286522002634129</v>
+        <v>2.739928230122291</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -7582,16 +7582,16 @@
         <v>358</v>
       </c>
       <c r="B355">
-        <v>3.508745942897887</v>
+        <v>2.238947788414885</v>
       </c>
       <c r="C355">
-        <v>6.271883718860069</v>
+        <v>6.412705351738104</v>
       </c>
       <c r="D355">
-        <v>58.05573733910694</v>
+        <v>58.01498061861685</v>
       </c>
       <c r="E355">
-        <v>1.715650951336404</v>
+        <v>1.403910915694736</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -7599,16 +7599,16 @@
         <v>359</v>
       </c>
       <c r="B356">
-        <v>3.370008219402643</v>
+        <v>2.068140647776926</v>
       </c>
       <c r="C356">
-        <v>6.852402702761774</v>
+        <v>7.031950665161464</v>
       </c>
       <c r="D356">
-        <v>58.1648870191609</v>
+        <v>58.0038167544206</v>
       </c>
       <c r="E356">
-        <v>1.25491512709876</v>
+        <v>1.741067759573201</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -7616,16 +7616,16 @@
         <v>360</v>
       </c>
       <c r="B357">
-        <v>2.475020372907663</v>
+        <v>2.389639205437371</v>
       </c>
       <c r="C357">
-        <v>6.84641989462678</v>
+        <v>6.428187933886387</v>
       </c>
       <c r="D357">
-        <v>58.00241743223393</v>
+        <v>58.17424176372633</v>
       </c>
       <c r="E357">
-        <v>1.633664460941541</v>
+        <v>2.609509257068564</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -7633,16 +7633,16 @@
         <v>361</v>
       </c>
       <c r="B358">
-        <v>2.729605118579086</v>
+        <v>2.407408728093169</v>
       </c>
       <c r="C358">
-        <v>6.215192994407703</v>
+        <v>7.076690505582791</v>
       </c>
       <c r="D358">
-        <v>58.1349311816167</v>
+        <v>58.0863655341683</v>
       </c>
       <c r="E358">
-        <v>2.83500874523905</v>
+        <v>1.6098825298359</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -7650,16 +7650,16 @@
         <v>362</v>
       </c>
       <c r="B359">
-        <v>3.131668732631494</v>
+        <v>2.011224599391169</v>
       </c>
       <c r="C359">
-        <v>6.624846021151988</v>
+        <v>6.066653451885794</v>
       </c>
       <c r="D359">
-        <v>57.98043349348313</v>
+        <v>57.83287790674516</v>
       </c>
       <c r="E359">
-        <v>2.431838144917262</v>
+        <v>2.672587076121449</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -7667,16 +7667,16 @@
         <v>363</v>
       </c>
       <c r="B360">
-        <v>3.222115061932337</v>
+        <v>3.102776577712884</v>
       </c>
       <c r="C360">
-        <v>7.198234432166065</v>
+        <v>7.018841209446395</v>
       </c>
       <c r="D360">
-        <v>58.16750570519093</v>
+        <v>57.94033205398348</v>
       </c>
       <c r="E360">
-        <v>1.470579657176042</v>
+        <v>1.6189531471843</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -7684,16 +7684,16 @@
         <v>364</v>
       </c>
       <c r="B361">
-        <v>3.191688664554958</v>
+        <v>1.98956356896746</v>
       </c>
       <c r="C361">
-        <v>6.273068183638883</v>
+        <v>6.984442132826088</v>
       </c>
       <c r="D361">
-        <v>57.81577448987745</v>
+        <v>58.07491261957747</v>
       </c>
       <c r="E361">
-        <v>2.731291534423581</v>
+        <v>1.910613856934994</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -7701,16 +7701,16 @@
         <v>365</v>
       </c>
       <c r="B362">
-        <v>3.030390392963836</v>
+        <v>3.465481825210373</v>
       </c>
       <c r="C362">
-        <v>6.770678989287601</v>
+        <v>6.864518494696225</v>
       </c>
       <c r="D362">
-        <v>57.8424566404118</v>
+        <v>57.96811036555017</v>
       </c>
       <c r="E362">
-        <v>1.813842145005164</v>
+        <v>2.319742591335978</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -7718,16 +7718,16 @@
         <v>366</v>
       </c>
       <c r="B363">
-        <v>3.11540171312433</v>
+        <v>1.955813486597399</v>
       </c>
       <c r="C363">
-        <v>6.740884795125512</v>
+        <v>5.952177333312663</v>
       </c>
       <c r="D363">
-        <v>57.7970490755503</v>
+        <v>58.05896011610051</v>
       </c>
       <c r="E363">
-        <v>1.721854573479334</v>
+        <v>2.728496510475883</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -7735,16 +7735,16 @@
         <v>367</v>
       </c>
       <c r="B364">
-        <v>2.862955684375605</v>
+        <v>3.168502130672663</v>
       </c>
       <c r="C364">
-        <v>6.577455344807224</v>
+        <v>6.078266083049139</v>
       </c>
       <c r="D364">
-        <v>57.86807990460403</v>
+        <v>57.92727365475018</v>
       </c>
       <c r="E364">
-        <v>2.160706946126175</v>
+        <v>2.396733675217214</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -7752,16 +7752,16 @@
         <v>368</v>
       </c>
       <c r="B365">
-        <v>2.722461897684343</v>
+        <v>2.166049287576784</v>
       </c>
       <c r="C365">
-        <v>6.067554952026713</v>
+        <v>7.350674375856366</v>
       </c>
       <c r="D365">
-        <v>58.06306678935828</v>
+        <v>58.27297056404498</v>
       </c>
       <c r="E365">
-        <v>2.595934678489623</v>
+        <v>1.894805097831195</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -7769,16 +7769,16 @@
         <v>369</v>
       </c>
       <c r="B366">
-        <v>3.549049540964826</v>
+        <v>3.259843946006528</v>
       </c>
       <c r="C366">
-        <v>7.313089075694975</v>
+        <v>7.354348035681607</v>
       </c>
       <c r="D366">
-        <v>58.22577051998514</v>
+        <v>58.08441718625371</v>
       </c>
       <c r="E366">
-        <v>2.10954439309506</v>
+        <v>2.243650406639776</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -7786,16 +7786,16 @@
         <v>370</v>
       </c>
       <c r="B367">
-        <v>2.481894183701861</v>
+        <v>3.343542272300159</v>
       </c>
       <c r="C367">
-        <v>6.976411704059888</v>
+        <v>6.978967678445544</v>
       </c>
       <c r="D367">
-        <v>58.26596822759268</v>
+        <v>58.01370294992238</v>
       </c>
       <c r="E367">
-        <v>2.205274287886875</v>
+        <v>1.761022869198678</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -7803,16 +7803,16 @@
         <v>371</v>
       </c>
       <c r="B368">
-        <v>2.495717581318642</v>
+        <v>3.178628625605569</v>
       </c>
       <c r="C368">
-        <v>6.581553961084427</v>
+        <v>6.951104099244311</v>
       </c>
       <c r="D368">
-        <v>57.9071932299134</v>
+        <v>57.99481448826121</v>
       </c>
       <c r="E368">
-        <v>1.385576047094437</v>
+        <v>1.246762083263791</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -7820,16 +7820,16 @@
         <v>372</v>
       </c>
       <c r="B369">
-        <v>3.459065854214042</v>
+        <v>3.109789158130881</v>
       </c>
       <c r="C369">
-        <v>6.311969902575079</v>
+        <v>6.367772712396107</v>
       </c>
       <c r="D369">
-        <v>57.84104489157471</v>
+        <v>58.19688557777448</v>
       </c>
       <c r="E369">
-        <v>2.783708844496997</v>
+        <v>1.672636540424344</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -7837,16 +7837,16 @@
         <v>373</v>
       </c>
       <c r="B370">
-        <v>2.390569408638884</v>
+        <v>2.536698549437127</v>
       </c>
       <c r="C370">
-        <v>7.339399237813036</v>
+        <v>7.095452298852829</v>
       </c>
       <c r="D370">
-        <v>57.80073732181103</v>
+        <v>58.24328098578555</v>
       </c>
       <c r="E370">
-        <v>1.448995901294903</v>
+        <v>2.10896278408769</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -7854,16 +7854,16 @@
         <v>374</v>
       </c>
       <c r="B371">
-        <v>2.816850496203848</v>
+        <v>2.505342590243917</v>
       </c>
       <c r="C371">
-        <v>6.834051844359731</v>
+        <v>6.473997206779689</v>
       </c>
       <c r="D371">
-        <v>58.10999866853987</v>
+        <v>58.27009708303456</v>
       </c>
       <c r="E371">
-        <v>1.723113386006388</v>
+        <v>2.217356694291221</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -7871,16 +7871,16 @@
         <v>375</v>
       </c>
       <c r="B372">
-        <v>3.422447959600952</v>
+        <v>3.563232963183729</v>
       </c>
       <c r="C372">
-        <v>6.07061297735486</v>
+        <v>6.600276915970052</v>
       </c>
       <c r="D372">
-        <v>57.95059478602263</v>
+        <v>57.98013778599235</v>
       </c>
       <c r="E372">
-        <v>2.631075695458359</v>
+        <v>1.452520808610792</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -7888,16 +7888,16 @@
         <v>376</v>
       </c>
       <c r="B373">
-        <v>2.561068163276611</v>
+        <v>2.036698736466347</v>
       </c>
       <c r="C373">
-        <v>6.269778229183489</v>
+        <v>6.870287691308622</v>
       </c>
       <c r="D373">
-        <v>57.85603746633622</v>
+        <v>58.00167395642011</v>
       </c>
       <c r="E373">
-        <v>1.275092610741673</v>
+        <v>1.467703914274658</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -7905,16 +7905,16 @@
         <v>377</v>
       </c>
       <c r="B374">
-        <v>2.201021986541132</v>
+        <v>2.397237165621834</v>
       </c>
       <c r="C374">
-        <v>6.579606828562607</v>
+        <v>5.982444953636688</v>
       </c>
       <c r="D374">
-        <v>57.94310896306769</v>
+        <v>58.12547932735964</v>
       </c>
       <c r="E374">
-        <v>2.376670657273277</v>
+        <v>2.150505145142154</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -7922,16 +7922,16 @@
         <v>378</v>
       </c>
       <c r="B375">
-        <v>2.992338281648099</v>
+        <v>2.649421614340422</v>
       </c>
       <c r="C375">
-        <v>6.522779058771009</v>
+        <v>6.588021859987575</v>
       </c>
       <c r="D375">
-        <v>58.01717639802649</v>
+        <v>58.07858061879863</v>
       </c>
       <c r="E375">
-        <v>1.996332075154462</v>
+        <v>2.496145253219095</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7939,16 +7939,16 @@
         <v>379</v>
       </c>
       <c r="B376">
-        <v>2.656204421828584</v>
+        <v>3.53575158456356</v>
       </c>
       <c r="C376">
-        <v>6.858901024716684</v>
+        <v>6.113351028208506</v>
       </c>
       <c r="D376">
-        <v>57.88629586614683</v>
+        <v>58.11867759615075</v>
       </c>
       <c r="E376">
-        <v>1.477855248681895</v>
+        <v>2.605053824434794</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -7956,16 +7956,16 @@
         <v>380</v>
       </c>
       <c r="B377">
-        <v>1.96532669585334</v>
+        <v>3.482590964295596</v>
       </c>
       <c r="C377">
-        <v>6.97103483671334</v>
+        <v>6.517627999254693</v>
       </c>
       <c r="D377">
-        <v>58.17113529140006</v>
+        <v>58.19725859636795</v>
       </c>
       <c r="E377">
-        <v>2.39322339812652</v>
+        <v>1.643491697078324</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -7973,16 +7973,16 @@
         <v>381</v>
       </c>
       <c r="B378">
-        <v>3.039071917419577</v>
+        <v>3.482797085802679</v>
       </c>
       <c r="C378">
-        <v>6.989027609231356</v>
+        <v>6.159915094637825</v>
       </c>
       <c r="D378">
-        <v>57.90555351722581</v>
+        <v>58.25817957931489</v>
       </c>
       <c r="E378">
-        <v>2.027119652279216</v>
+        <v>1.263120555864907</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7990,16 +7990,16 @@
         <v>382</v>
       </c>
       <c r="B379">
-        <v>2.029524584002819</v>
+        <v>2.184088110025487</v>
       </c>
       <c r="C379">
-        <v>6.890936568350174</v>
+        <v>7.15480187641616</v>
       </c>
       <c r="D379">
-        <v>58.04258107135102</v>
+        <v>58.11082170286671</v>
       </c>
       <c r="E379">
-        <v>2.575929715675908</v>
+        <v>1.339218550329786</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -8007,16 +8007,16 @@
         <v>383</v>
       </c>
       <c r="B380">
-        <v>2.248710802608307</v>
+        <v>2.603487623161131</v>
       </c>
       <c r="C380">
-        <v>7.425439327347561</v>
+        <v>7.13955288088765</v>
       </c>
       <c r="D380">
-        <v>58.13105535915305</v>
+        <v>58.19713612354678</v>
       </c>
       <c r="E380">
-        <v>2.122882565976161</v>
+        <v>1.418163223490505</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -8024,16 +8024,16 @@
         <v>384</v>
       </c>
       <c r="B381">
-        <v>2.708444565339558</v>
+        <v>2.387423928107646</v>
       </c>
       <c r="C381">
-        <v>7.228662158625488</v>
+        <v>6.118487767614454</v>
       </c>
       <c r="D381">
-        <v>58.02406959478535</v>
+        <v>57.90579332347016</v>
       </c>
       <c r="E381">
-        <v>1.718785527903745</v>
+        <v>2.819634264160586</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -8041,16 +8041,16 @@
         <v>385</v>
       </c>
       <c r="B382">
-        <v>3.115999675066044</v>
+        <v>1.967258698598893</v>
       </c>
       <c r="C382">
-        <v>7.403298090900111</v>
+        <v>6.977333331736995</v>
       </c>
       <c r="D382">
-        <v>58.091805288731</v>
+        <v>58.19152205810811</v>
       </c>
       <c r="E382">
-        <v>2.006212513369521</v>
+        <v>2.8164791838967</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -8058,16 +8058,16 @@
         <v>386</v>
       </c>
       <c r="B383">
-        <v>3.139888719087781</v>
+        <v>1.959111612852306</v>
       </c>
       <c r="C383">
-        <v>6.816433257184478</v>
+        <v>6.574814135362229</v>
       </c>
       <c r="D383">
-        <v>58.14044785115126</v>
+        <v>57.96011691359259</v>
       </c>
       <c r="E383">
-        <v>2.1285892887219</v>
+        <v>2.178185673320046</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -8075,16 +8075,16 @@
         <v>387</v>
       </c>
       <c r="B384">
-        <v>2.007670032271099</v>
+        <v>2.313387276342652</v>
       </c>
       <c r="C384">
-        <v>7.057830672353711</v>
+        <v>6.100648026435664</v>
       </c>
       <c r="D384">
-        <v>58.12899514387767</v>
+        <v>58.08932612099753</v>
       </c>
       <c r="E384">
-        <v>2.738905839650213</v>
+        <v>2.460918583706643</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -8092,16 +8092,16 @@
         <v>388</v>
       </c>
       <c r="B385">
-        <v>3.092319305361133</v>
+        <v>2.31342799942759</v>
       </c>
       <c r="C385">
-        <v>5.990472674639599</v>
+        <v>6.238173780437291</v>
       </c>
       <c r="D385">
-        <v>58.21830972963564</v>
+        <v>58.12671013076669</v>
       </c>
       <c r="E385">
-        <v>2.465250296429513</v>
+        <v>1.305946785316249</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -8109,16 +8109,16 @@
         <v>389</v>
       </c>
       <c r="B386">
-        <v>3.196286870267768</v>
+        <v>1.828391522406631</v>
       </c>
       <c r="C386">
-        <v>6.678683896765358</v>
+        <v>6.698236379311282</v>
       </c>
       <c r="D386">
-        <v>58.08407121416866</v>
+        <v>58.20852617525416</v>
       </c>
       <c r="E386">
-        <v>2.404287468197624</v>
+        <v>1.6962249397543</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -8126,16 +8126,16 @@
         <v>390</v>
       </c>
       <c r="B387">
-        <v>1.938038437085108</v>
+        <v>3.500197525411643</v>
       </c>
       <c r="C387">
-        <v>6.41105525548823</v>
+        <v>6.684917218249571</v>
       </c>
       <c r="D387">
-        <v>57.78410632880715</v>
+        <v>57.85564305398159</v>
       </c>
       <c r="E387">
-        <v>1.481791864508295</v>
+        <v>1.833810084369308</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -8143,16 +8143,16 @@
         <v>391</v>
       </c>
       <c r="B388">
-        <v>2.881358766068935</v>
+        <v>2.120329528679945</v>
       </c>
       <c r="C388">
-        <v>6.188017548835234</v>
+        <v>5.953919181823043</v>
       </c>
       <c r="D388">
-        <v>58.04213309191462</v>
+        <v>58.26722110249236</v>
       </c>
       <c r="E388">
-        <v>2.228519218478778</v>
+        <v>1.779773782849449</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -8160,16 +8160,16 @@
         <v>392</v>
       </c>
       <c r="B389">
-        <v>3.429472336363275</v>
+        <v>2.030106194429405</v>
       </c>
       <c r="C389">
-        <v>7.462515005189264</v>
+        <v>6.826772518899678</v>
       </c>
       <c r="D389">
-        <v>58.09330949209291</v>
+        <v>58.2190454816331</v>
       </c>
       <c r="E389">
-        <v>1.559724878301673</v>
+        <v>2.553725193716797</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -8177,16 +8177,16 @@
         <v>393</v>
       </c>
       <c r="B390">
-        <v>3.500612143733543</v>
+        <v>3.37804573283643</v>
       </c>
       <c r="C390">
-        <v>7.19050930600247</v>
+        <v>6.28031555551028</v>
       </c>
       <c r="D390">
-        <v>58.20764673581339</v>
+        <v>57.99810121862598</v>
       </c>
       <c r="E390">
-        <v>2.81379182726522</v>
+        <v>2.442782393995746</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -8194,16 +8194,16 @@
         <v>394</v>
       </c>
       <c r="B391">
-        <v>2.284949577184614</v>
+        <v>2.693658710938186</v>
       </c>
       <c r="C391">
-        <v>5.893234451614115</v>
+        <v>7.281803434613223</v>
       </c>
       <c r="D391">
-        <v>57.83270699167944</v>
+        <v>58.21770938492449</v>
       </c>
       <c r="E391">
-        <v>2.517818550916674</v>
+        <v>2.60817118868443</v>
       </c>
     </row>
   </sheetData>

--- a/FFT on froth/data_test_augm_Pb.xlsx
+++ b/FFT on froth/data_test_augm_Pb.xlsx
@@ -1581,16 +1581,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>0.9555667088996663</v>
+        <v>0.2495547501438126</v>
       </c>
       <c r="C2">
-        <v>4.364903999701304</v>
+        <v>4.37333089590267</v>
       </c>
       <c r="D2">
-        <v>24.56180507422911</v>
+        <v>25.43635718464065</v>
       </c>
       <c r="E2">
-        <v>1.55598026434504</v>
+        <v>1.222832062746549</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1598,16 +1598,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.8080282092230482</v>
+        <v>0.3471398404011262</v>
       </c>
       <c r="C3">
-        <v>5.158964252651785</v>
+        <v>4.384538413160222</v>
       </c>
       <c r="D3">
-        <v>24.65766490004864</v>
+        <v>25.8351268063388</v>
       </c>
       <c r="E3">
-        <v>2.548098053577777</v>
+        <v>1.191095817178607</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1615,16 +1615,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.4920040734632759</v>
+        <v>0.3507441920273919</v>
       </c>
       <c r="C4">
-        <v>5.50189814091298</v>
+        <v>4.295009153879299</v>
       </c>
       <c r="D4">
-        <v>24.47797460162434</v>
+        <v>25.63055546382881</v>
       </c>
       <c r="E4">
-        <v>1.090312776926774</v>
+        <v>1.164672052415605</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1632,16 +1632,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>1.156482616002067</v>
+        <v>0.3523084976935503</v>
       </c>
       <c r="C5">
-        <v>5.456590753404928</v>
+        <v>4.035774733967574</v>
       </c>
       <c r="D5">
-        <v>24.83575194355496</v>
+        <v>25.94804153926476</v>
       </c>
       <c r="E5">
-        <v>2.335295986386509</v>
+        <v>1.137445576113026</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1649,16 +1649,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.3089879346057939</v>
+        <v>0.2922881976811358</v>
       </c>
       <c r="C6">
-        <v>4.538734575025399</v>
+        <v>4.203754238751699</v>
       </c>
       <c r="D6">
-        <v>24.80110308330329</v>
+        <v>24.94795938342268</v>
       </c>
       <c r="E6">
-        <v>1.234858862192039</v>
+        <v>1.158895022032622</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1666,16 +1666,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.819121150691276</v>
+        <v>0.275614642038215</v>
       </c>
       <c r="C7">
-        <v>4.399118435659346</v>
+        <v>4.290475074990711</v>
       </c>
       <c r="D7">
-        <v>24.6637257540357</v>
+        <v>25.96994429028656</v>
       </c>
       <c r="E7">
-        <v>1.188459868480736</v>
+        <v>1.158287736866929</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1683,16 +1683,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>1.075716846255165</v>
+        <v>0.2505600862027176</v>
       </c>
       <c r="C8">
-        <v>4.758999646026719</v>
+        <v>3.952454766698358</v>
       </c>
       <c r="D8">
-        <v>24.59996082825779</v>
+        <v>24.58179261263685</v>
       </c>
       <c r="E8">
-        <v>1.626390725466464</v>
+        <v>1.110501023048291</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1700,16 +1700,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>1.129395173607574</v>
+        <v>0.2799898359846776</v>
       </c>
       <c r="C9">
-        <v>4.212956206659545</v>
+        <v>3.957533359956849</v>
       </c>
       <c r="D9">
-        <v>24.88999975101926</v>
+        <v>24.57544828133306</v>
       </c>
       <c r="E9">
-        <v>1.318192727387592</v>
+        <v>1.135760882887331</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1717,16 +1717,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>1.545389477947994</v>
+        <v>0.2764745596804528</v>
       </c>
       <c r="C10">
-        <v>4.574206104975183</v>
+        <v>4.121077566214467</v>
       </c>
       <c r="D10">
-        <v>24.49747429864211</v>
+        <v>24.55557812125284</v>
       </c>
       <c r="E10">
-        <v>1.771424260683905</v>
+        <v>1.112292647112315</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1734,16 +1734,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.944912600943915</v>
+        <v>0.3083153873331829</v>
       </c>
       <c r="C11">
-        <v>5.506783757626465</v>
+        <v>3.933830882493409</v>
       </c>
       <c r="D11">
-        <v>24.87337797048334</v>
+        <v>25.4562344756238</v>
       </c>
       <c r="E11">
-        <v>2.413127057854254</v>
+        <v>1.149858639062239</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1751,16 +1751,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1.396543269829813</v>
+        <v>0.2494500082277488</v>
       </c>
       <c r="C12">
-        <v>4.2894754380728</v>
+        <v>4.417605094093934</v>
       </c>
       <c r="D12">
-        <v>24.78719021943286</v>
+        <v>25.89948853069322</v>
       </c>
       <c r="E12">
-        <v>1.556103463553439</v>
+        <v>1.218566680240027</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1768,16 +1768,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.6727961262700493</v>
+        <v>0.2897147740929827</v>
       </c>
       <c r="C13">
-        <v>4.912929710218657</v>
+        <v>4.191242988382428</v>
       </c>
       <c r="D13">
-        <v>24.46108691237233</v>
+        <v>25.43074389833512</v>
       </c>
       <c r="E13">
-        <v>2.28960959242826</v>
+        <v>1.189034911223922</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1785,16 +1785,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>1.648287099503863</v>
+        <v>0.2426031413760374</v>
       </c>
       <c r="C14">
-        <v>5.383559524988656</v>
+        <v>4.072003339922356</v>
       </c>
       <c r="D14">
-        <v>24.64476758288256</v>
+        <v>24.99920394159043</v>
       </c>
       <c r="E14">
-        <v>2.448275475119757</v>
+        <v>1.207911448497104</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1802,16 +1802,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>2.00177994646992</v>
+        <v>0.2645641007908911</v>
       </c>
       <c r="C15">
-        <v>5.274599788025585</v>
+        <v>4.061149189629304</v>
       </c>
       <c r="D15">
-        <v>24.59005777760901</v>
+        <v>25.05942797772167</v>
       </c>
       <c r="E15">
-        <v>1.447055028815551</v>
+        <v>1.149661414667547</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1819,16 +1819,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>1.66039806291069</v>
+        <v>0.3061132072901357</v>
       </c>
       <c r="C16">
-        <v>5.061792981895898</v>
+        <v>4.099494056438137</v>
       </c>
       <c r="D16">
-        <v>24.51326877203281</v>
+        <v>25.07209708388431</v>
       </c>
       <c r="E16">
-        <v>2.561109476559743</v>
+        <v>1.231590542863453</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1836,16 +1836,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.4228083880623049</v>
+        <v>0.3534497228321453</v>
       </c>
       <c r="C17">
-        <v>4.013390444520812</v>
+        <v>4.147065061518299</v>
       </c>
       <c r="D17">
-        <v>24.46992191695369</v>
+        <v>25.25927637141934</v>
       </c>
       <c r="E17">
-        <v>1.557006020186011</v>
+        <v>1.096282007680788</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1853,16 +1853,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.522396082772647</v>
+        <v>0.3268669691928122</v>
       </c>
       <c r="C18">
-        <v>5.396959319497238</v>
+        <v>4.217436375833944</v>
       </c>
       <c r="D18">
-        <v>24.58140701352641</v>
+        <v>24.72075327010202</v>
       </c>
       <c r="E18">
-        <v>2.221246540562557</v>
+        <v>1.187217621086051</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1870,16 +1870,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>1.66453304599699</v>
+        <v>0.2779037115432709</v>
       </c>
       <c r="C19">
-        <v>5.131167842681558</v>
+        <v>4.210576256275736</v>
       </c>
       <c r="D19">
-        <v>24.75185829786818</v>
+        <v>24.80558573550377</v>
       </c>
       <c r="E19">
-        <v>2.337893927603198</v>
+        <v>1.097765789826324</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1887,16 +1887,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>0.7756576488220717</v>
+        <v>0.3003096965195747</v>
       </c>
       <c r="C20">
-        <v>4.105581514423673</v>
+        <v>4.127184106116287</v>
       </c>
       <c r="D20">
-        <v>24.47998686101991</v>
+        <v>25.5019266814613</v>
       </c>
       <c r="E20">
-        <v>2.128615489016429</v>
+        <v>1.225911714522471</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1904,16 +1904,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>0.2431158929194354</v>
+        <v>0.2926590017212303</v>
       </c>
       <c r="C21">
-        <v>4.347570875623862</v>
+        <v>4.041891695247084</v>
       </c>
       <c r="D21">
-        <v>24.57267826428366</v>
+        <v>25.23448097301131</v>
       </c>
       <c r="E21">
-        <v>2.145939827910002</v>
+        <v>1.235133871158581</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1921,16 +1921,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>0.9527512247947825</v>
+        <v>0.3327245298272377</v>
       </c>
       <c r="C22">
-        <v>4.675901249531073</v>
+        <v>4.114111956626182</v>
       </c>
       <c r="D22">
-        <v>24.66074681276168</v>
+        <v>24.49748254550588</v>
       </c>
       <c r="E22">
-        <v>2.123016274824416</v>
+        <v>1.162566009019663</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1938,16 +1938,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.123561323260033</v>
+        <v>0.3157986485265045</v>
       </c>
       <c r="C23">
-        <v>4.524225415873076</v>
+        <v>4.217019563477409</v>
       </c>
       <c r="D23">
-        <v>24.87137818092765</v>
+        <v>25.98716471685662</v>
       </c>
       <c r="E23">
-        <v>1.555099183133885</v>
+        <v>1.128714325648954</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1955,16 +1955,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>1.505781761560082</v>
+        <v>0.3254574421216516</v>
       </c>
       <c r="C24">
-        <v>4.568337928429746</v>
+        <v>4.046703785346049</v>
       </c>
       <c r="D24">
-        <v>24.58232310565377</v>
+        <v>24.4708986435164</v>
       </c>
       <c r="E24">
-        <v>1.919110642040513</v>
+        <v>1.246384720083419</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1972,16 +1972,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>0.8129453429647987</v>
+        <v>0.2402679635426381</v>
       </c>
       <c r="C25">
-        <v>4.018054802238123</v>
+        <v>4.126133908706509</v>
       </c>
       <c r="D25">
-        <v>24.68019015848621</v>
+        <v>25.22737262701919</v>
       </c>
       <c r="E25">
-        <v>1.653198099069156</v>
+        <v>1.169853780496146</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1989,16 +1989,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>1.870564465481604</v>
+        <v>0.3039893374489136</v>
       </c>
       <c r="C26">
-        <v>4.59373428739941</v>
+        <v>4.08178030177622</v>
       </c>
       <c r="D26">
-        <v>24.77632888872651</v>
+        <v>25.45196887221365</v>
       </c>
       <c r="E26">
-        <v>1.985334952862015</v>
+        <v>1.167600117736662</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2006,16 +2006,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>1.444092245723115</v>
+        <v>0.3235937543496651</v>
       </c>
       <c r="C27">
-        <v>4.92559754402891</v>
+        <v>3.987090961969848</v>
       </c>
       <c r="D27">
-        <v>24.72240025418588</v>
+        <v>25.65607670576564</v>
       </c>
       <c r="E27">
-        <v>1.424840198073308</v>
+        <v>1.203729371739323</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2023,16 +2023,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>1.444977852419282</v>
+        <v>0.2846814575326057</v>
       </c>
       <c r="C28">
-        <v>4.584718259970344</v>
+        <v>4.396733975954692</v>
       </c>
       <c r="D28">
-        <v>24.72795640328489</v>
+        <v>25.33117389477177</v>
       </c>
       <c r="E28">
-        <v>1.363413225626976</v>
+        <v>1.086008130551273</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2040,16 +2040,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>0.6998073460927383</v>
+        <v>0.3500710492865134</v>
       </c>
       <c r="C29">
-        <v>5.203428688656933</v>
+        <v>4.018206505348926</v>
       </c>
       <c r="D29">
-        <v>24.8003545416795</v>
+        <v>25.79048014310187</v>
       </c>
       <c r="E29">
-        <v>2.000438127983425</v>
+        <v>1.086083661066448</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2057,16 +2057,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>0.4631532775921544</v>
+        <v>0.2873582255517834</v>
       </c>
       <c r="C30">
-        <v>4.226676109794047</v>
+        <v>4.237399528566527</v>
       </c>
       <c r="D30">
-        <v>24.78843680319482</v>
+        <v>24.44474632225962</v>
       </c>
       <c r="E30">
-        <v>2.114142450110528</v>
+        <v>1.124634873508808</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2074,16 +2074,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>1.634661763458791</v>
+        <v>0.2861964039356246</v>
       </c>
       <c r="C31">
-        <v>5.212353669266903</v>
+        <v>4.145029592462262</v>
       </c>
       <c r="D31">
-        <v>24.62005969824211</v>
+        <v>24.76911172556816</v>
       </c>
       <c r="E31">
-        <v>1.762437146444966</v>
+        <v>1.082832666603735</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2091,16 +2091,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>0.2588112408472616</v>
+        <v>0.3073453946561421</v>
       </c>
       <c r="C32">
-        <v>5.397596724506902</v>
+        <v>4.082729570640352</v>
       </c>
       <c r="D32">
-        <v>24.85902493320587</v>
+        <v>25.75195757237625</v>
       </c>
       <c r="E32">
-        <v>1.105745916982189</v>
+        <v>1.12901253657096</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2108,16 +2108,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>1.51833355960633</v>
+        <v>0.3535977988649547</v>
       </c>
       <c r="C33">
-        <v>4.813412636238001</v>
+        <v>4.305121931539986</v>
       </c>
       <c r="D33">
-        <v>24.93226620609397</v>
+        <v>25.34510567661433</v>
       </c>
       <c r="E33">
-        <v>2.042658429417801</v>
+        <v>1.124326961659245</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2125,16 +2125,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>0.9783280315871379</v>
+        <v>0.3231114959669509</v>
       </c>
       <c r="C34">
-        <v>5.358225697343489</v>
+        <v>4.111001402900744</v>
       </c>
       <c r="D34">
-        <v>24.52082475735386</v>
+        <v>25.84034798692562</v>
       </c>
       <c r="E34">
-        <v>1.190400369138359</v>
+        <v>1.111369467335827</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2142,16 +2142,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>0.764724094304098</v>
+        <v>0.3178186011747473</v>
       </c>
       <c r="C35">
-        <v>4.526028795962061</v>
+        <v>4.270655422265981</v>
       </c>
       <c r="D35">
-        <v>24.72012646333247</v>
+        <v>25.77035267138119</v>
       </c>
       <c r="E35">
-        <v>1.142399604356264</v>
+        <v>1.106041270318726</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2159,16 +2159,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>1.304109639653208</v>
+        <v>0.2821287791427169</v>
       </c>
       <c r="C36">
-        <v>4.164135590493556</v>
+        <v>4.073721438360833</v>
       </c>
       <c r="D36">
-        <v>24.77240132135953</v>
+        <v>25.81932658679038</v>
       </c>
       <c r="E36">
-        <v>1.833115689984975</v>
+        <v>1.230130645771559</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2176,16 +2176,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>1.511686502548258</v>
+        <v>0.3085686970562985</v>
       </c>
       <c r="C37">
-        <v>4.746783830564675</v>
+        <v>4.271296091147097</v>
       </c>
       <c r="D37">
-        <v>24.53865558077281</v>
+        <v>24.92304139669268</v>
       </c>
       <c r="E37">
-        <v>2.535112977486456</v>
+        <v>1.249180297071334</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2193,16 +2193,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>2.026421220691496</v>
+        <v>0.2998984744100466</v>
       </c>
       <c r="C38">
-        <v>4.659540310622146</v>
+        <v>4.216857723232525</v>
       </c>
       <c r="D38">
-        <v>24.53941184992679</v>
+        <v>25.11650190006845</v>
       </c>
       <c r="E38">
-        <v>2.282621526724388</v>
+        <v>1.081323016203321</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2210,16 +2210,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>1.992833282970305</v>
+        <v>0.3262462972313564</v>
       </c>
       <c r="C39">
-        <v>4.270216590659826</v>
+        <v>4.288784698724584</v>
       </c>
       <c r="D39">
-        <v>24.81392245925781</v>
+        <v>25.08490616230124</v>
       </c>
       <c r="E39">
-        <v>1.130494715950539</v>
+        <v>1.084511256583801</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2227,16 +2227,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>0.8008098992023523</v>
+        <v>0.287669470775014</v>
       </c>
       <c r="C40">
-        <v>3.963916068568902</v>
+        <v>3.938661748598286</v>
       </c>
       <c r="D40">
-        <v>24.63397094332831</v>
+        <v>24.75707484141736</v>
       </c>
       <c r="E40">
-        <v>2.453994335538701</v>
+        <v>1.130403676260237</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2244,16 +2244,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>1.55283823320112</v>
+        <v>0.2818341328326268</v>
       </c>
       <c r="C41">
-        <v>4.35159927191861</v>
+        <v>4.002151812012107</v>
       </c>
       <c r="D41">
-        <v>24.71539807278468</v>
+        <v>25.75691703699151</v>
       </c>
       <c r="E41">
-        <v>1.11986062584991</v>
+        <v>1.185555156629872</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2261,16 +2261,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>1.339573624378898</v>
+        <v>0.2552746237453548</v>
       </c>
       <c r="C42">
-        <v>4.898947944205732</v>
+        <v>4.113954950769583</v>
       </c>
       <c r="D42">
-        <v>24.855658198775</v>
+        <v>25.89683199901534</v>
       </c>
       <c r="E42">
-        <v>1.667260751750022</v>
+        <v>1.185058314173394</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2278,16 +2278,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>1.549354608160784</v>
+        <v>0.266700179601132</v>
       </c>
       <c r="C43">
-        <v>5.172390447111688</v>
+        <v>4.305022907837481</v>
       </c>
       <c r="D43">
-        <v>24.54200406931979</v>
+        <v>24.53766296654029</v>
       </c>
       <c r="E43">
-        <v>1.962118600494538</v>
+        <v>1.145695044210577</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2295,16 +2295,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>0.3857436415993758</v>
+        <v>0.3279186618952366</v>
       </c>
       <c r="C44">
-        <v>4.698363440402244</v>
+        <v>4.194411522581462</v>
       </c>
       <c r="D44">
-        <v>24.66566975062199</v>
+        <v>24.8452337232335</v>
       </c>
       <c r="E44">
-        <v>2.076981858464305</v>
+        <v>1.105687076439745</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2312,16 +2312,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>1.523477033396664</v>
+        <v>0.2550388069509316</v>
       </c>
       <c r="C45">
-        <v>4.559315664250001</v>
+        <v>4.081375865993471</v>
       </c>
       <c r="D45">
-        <v>24.51673654212346</v>
+        <v>24.93521387705135</v>
       </c>
       <c r="E45">
-        <v>1.333072747790572</v>
+        <v>1.088558792030496</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2329,16 +2329,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>1.801478229538373</v>
+        <v>0.3089732181265426</v>
       </c>
       <c r="C46">
-        <v>5.324122331234</v>
+        <v>4.00801960044003</v>
       </c>
       <c r="D46">
-        <v>24.48969699146863</v>
+        <v>24.99903361310155</v>
       </c>
       <c r="E46">
-        <v>2.611989873320507</v>
+        <v>1.246592934592238</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2346,16 +2346,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>1.191890914055417</v>
+        <v>0.2781682305362757</v>
       </c>
       <c r="C47">
-        <v>5.308849828005341</v>
+        <v>4.084348110183965</v>
       </c>
       <c r="D47">
-        <v>24.7768215915374</v>
+        <v>25.27911555397114</v>
       </c>
       <c r="E47">
-        <v>2.202911273850801</v>
+        <v>1.15320381528997</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2363,16 +2363,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>2.012638065648866</v>
+        <v>0.2836719014132718</v>
       </c>
       <c r="C48">
-        <v>4.172442050619764</v>
+        <v>4.112248192670875</v>
       </c>
       <c r="D48">
-        <v>24.74685280165546</v>
+        <v>24.67425692460804</v>
       </c>
       <c r="E48">
-        <v>1.596514393402087</v>
+        <v>1.083161998723989</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2380,16 +2380,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>1.708197423301432</v>
+        <v>0.3229311680403836</v>
       </c>
       <c r="C49">
-        <v>4.26925821374074</v>
+        <v>4.218504763800527</v>
       </c>
       <c r="D49">
-        <v>24.73606951073208</v>
+        <v>24.48055215589164</v>
       </c>
       <c r="E49">
-        <v>2.190374127142412</v>
+        <v>1.226017910807293</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2397,16 +2397,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>0.5978557454401694</v>
+        <v>0.2909555404902049</v>
       </c>
       <c r="C50">
-        <v>5.277515834087021</v>
+        <v>4.174527477021883</v>
       </c>
       <c r="D50">
-        <v>24.66779617707913</v>
+        <v>24.83804342267344</v>
       </c>
       <c r="E50">
-        <v>2.121986049465684</v>
+        <v>1.221034057498536</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2414,16 +2414,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>0.7295395736800678</v>
+        <v>0.3545265882145325</v>
       </c>
       <c r="C51">
-        <v>4.443080565070345</v>
+        <v>4.121081928103922</v>
       </c>
       <c r="D51">
-        <v>24.67921845536601</v>
+        <v>25.98530391090827</v>
       </c>
       <c r="E51">
-        <v>2.133300101261431</v>
+        <v>1.230349872907963</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2431,16 +2431,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>1.737833563135487</v>
+        <v>0.3235758344392339</v>
       </c>
       <c r="C52">
-        <v>4.054536933575871</v>
+        <v>4.015959823662098</v>
       </c>
       <c r="D52">
-        <v>24.52371420158364</v>
+        <v>25.73075812466734</v>
       </c>
       <c r="E52">
-        <v>2.633415319440835</v>
+        <v>1.158355071713699</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2448,16 +2448,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>1.260826776410075</v>
+        <v>0.3341637948355138</v>
       </c>
       <c r="C53">
-        <v>5.497070845006358</v>
+        <v>4.260259194623674</v>
       </c>
       <c r="D53">
-        <v>24.49527060908468</v>
+        <v>25.21075498316848</v>
       </c>
       <c r="E53">
-        <v>2.24629768939751</v>
+        <v>1.16765877870659</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2465,16 +2465,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>0.6814466445410761</v>
+        <v>0.2766155224632946</v>
       </c>
       <c r="C54">
-        <v>4.940290276213283</v>
+        <v>4.199908825046225</v>
       </c>
       <c r="D54">
-        <v>24.6716571330317</v>
+        <v>24.46381732300538</v>
       </c>
       <c r="E54">
-        <v>1.53813989333979</v>
+        <v>1.188041906170934</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2482,16 +2482,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>1.34663357265804</v>
+        <v>0.2535972857722684</v>
       </c>
       <c r="C55">
-        <v>4.083621531161793</v>
+        <v>4.008870716847372</v>
       </c>
       <c r="D55">
-        <v>24.87423492503024</v>
+        <v>25.72395421639771</v>
       </c>
       <c r="E55">
-        <v>1.71925069130928</v>
+        <v>1.134923206535354</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2499,16 +2499,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>1.497598518085351</v>
+        <v>0.2953370150646577</v>
       </c>
       <c r="C56">
-        <v>5.005425688363625</v>
+        <v>3.978016347943473</v>
       </c>
       <c r="D56">
-        <v>24.45583479586761</v>
+        <v>25.22211642662919</v>
       </c>
       <c r="E56">
-        <v>1.136941532347282</v>
+        <v>1.22036541672202</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2516,16 +2516,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>0.3226921791736903</v>
+        <v>0.3473712766656323</v>
       </c>
       <c r="C57">
-        <v>3.98764003214158</v>
+        <v>4.081845606402833</v>
       </c>
       <c r="D57">
-        <v>24.82829226483059</v>
+        <v>24.44418304783191</v>
       </c>
       <c r="E57">
-        <v>2.12337354856637</v>
+        <v>1.169548399189849</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2533,16 +2533,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>1.122900015152961</v>
+        <v>0.2726666615630549</v>
       </c>
       <c r="C58">
-        <v>4.078204121901044</v>
+        <v>4.204831615522371</v>
       </c>
       <c r="D58">
-        <v>24.44016258051151</v>
+        <v>25.92743937089303</v>
       </c>
       <c r="E58">
-        <v>1.58396369275754</v>
+        <v>1.150230738341303</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2550,16 +2550,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>1.082819832211841</v>
+        <v>0.2904680605686173</v>
       </c>
       <c r="C59">
-        <v>4.513977611864374</v>
+        <v>4.409037383613367</v>
       </c>
       <c r="D59">
-        <v>24.72356599435389</v>
+        <v>25.0554964087873</v>
       </c>
       <c r="E59">
-        <v>1.802560465700983</v>
+        <v>1.194819130745188</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2567,16 +2567,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>1.531045662914803</v>
+        <v>0.2482639250547669</v>
       </c>
       <c r="C60">
-        <v>4.032498304667114</v>
+        <v>3.985801139987903</v>
       </c>
       <c r="D60">
-        <v>24.9044065236653</v>
+        <v>25.36407525376227</v>
       </c>
       <c r="E60">
-        <v>1.387067527347596</v>
+        <v>1.227101652991436</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2584,16 +2584,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>1.589802209134636</v>
+        <v>0.254563006022095</v>
       </c>
       <c r="C61">
-        <v>4.318036572419882</v>
+        <v>4.124660890587001</v>
       </c>
       <c r="D61">
-        <v>24.81079320683206</v>
+        <v>25.55008155689616</v>
       </c>
       <c r="E61">
-        <v>2.230183502023245</v>
+        <v>1.242476426117856</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2601,16 +2601,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>1.303348740050686</v>
+        <v>0.3053993471081562</v>
       </c>
       <c r="C62">
-        <v>4.295200767759716</v>
+        <v>4.348683632800785</v>
       </c>
       <c r="D62">
-        <v>24.60330968709728</v>
+        <v>24.67591303216187</v>
       </c>
       <c r="E62">
-        <v>2.005446914935391</v>
+        <v>1.081298225897621</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2618,16 +2618,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>1.518451839426841</v>
+        <v>0.2749209439384102</v>
       </c>
       <c r="C63">
-        <v>4.020559273617608</v>
+        <v>4.186221125881464</v>
       </c>
       <c r="D63">
-        <v>24.85938005673085</v>
+        <v>25.52231947787304</v>
       </c>
       <c r="E63">
-        <v>2.642424505773939</v>
+        <v>1.242169950829388</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2635,16 +2635,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>1.207757477416461</v>
+        <v>0.3227819753535401</v>
       </c>
       <c r="C64">
-        <v>4.630579468023841</v>
+        <v>4.269488437194274</v>
       </c>
       <c r="D64">
-        <v>24.62031958623629</v>
+        <v>25.03215522000668</v>
       </c>
       <c r="E64">
-        <v>2.243276906470946</v>
+        <v>1.221628754467916</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>1.230387585976694</v>
+        <v>0.2570101492088869</v>
       </c>
       <c r="C65">
-        <v>4.623436658150086</v>
+        <v>4.179210563640755</v>
       </c>
       <c r="D65">
-        <v>24.5396562885795</v>
+        <v>25.6348053112247</v>
       </c>
       <c r="E65">
-        <v>1.305443750918934</v>
+        <v>1.206253992098215</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2669,16 +2669,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>3.355568417325071</v>
+        <v>1.72354725828537</v>
       </c>
       <c r="C66">
-        <v>12.12701301198723</v>
+        <v>11.09871707623015</v>
       </c>
       <c r="D66">
-        <v>49.61876927702531</v>
+        <v>50.94009293511492</v>
       </c>
       <c r="E66">
-        <v>5.285314507897851</v>
+        <v>5.322732387101114</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2686,16 +2686,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>3.322032961645851</v>
+        <v>1.679176443720263</v>
       </c>
       <c r="C67">
-        <v>11.79086606694883</v>
+        <v>11.02987423955224</v>
       </c>
       <c r="D67">
-        <v>49.72841275139797</v>
+        <v>50.66039279483486</v>
       </c>
       <c r="E67">
-        <v>5.431058532327112</v>
+        <v>5.220646376696457</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2703,16 +2703,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>3.120082118662423</v>
+        <v>1.699378836467967</v>
       </c>
       <c r="C68">
-        <v>11.71217079729706</v>
+        <v>11.22579871561791</v>
       </c>
       <c r="D68">
-        <v>49.86362257550075</v>
+        <v>49.84782753842919</v>
       </c>
       <c r="E68">
-        <v>6.215859302618915</v>
+        <v>5.260749203128198</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2720,16 +2720,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>2.036398400809234</v>
+        <v>1.722955004694138</v>
       </c>
       <c r="C69">
-        <v>10.96118655966529</v>
+        <v>11.40792284821794</v>
       </c>
       <c r="D69">
-        <v>49.94125573477441</v>
+        <v>50.64972147987087</v>
       </c>
       <c r="E69">
-        <v>5.736809696766611</v>
+        <v>5.28239659594839</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2737,16 +2737,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>2.11793046600087</v>
+        <v>1.63951662590562</v>
       </c>
       <c r="C70">
-        <v>12.26780641916457</v>
+        <v>11.41983968936011</v>
       </c>
       <c r="D70">
-        <v>49.8067567896083</v>
+        <v>49.79122647787705</v>
       </c>
       <c r="E70">
-        <v>5.509683841032852</v>
+        <v>5.210395544826947</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2754,16 +2754,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>1.770005457310164</v>
+        <v>1.668667738748401</v>
       </c>
       <c r="C71">
-        <v>12.25395604671692</v>
+        <v>10.99476344293926</v>
       </c>
       <c r="D71">
-        <v>49.6789018099399</v>
+        <v>50.08394358579338</v>
       </c>
       <c r="E71">
-        <v>6.53118631688015</v>
+        <v>5.213431600270459</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2771,16 +2771,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.020071363888114</v>
+        <v>1.666723891513747</v>
       </c>
       <c r="C72">
-        <v>11.91577373500315</v>
+        <v>11.14015973332813</v>
       </c>
       <c r="D72">
-        <v>49.73820136408673</v>
+        <v>50.04241296591488</v>
       </c>
       <c r="E72">
-        <v>6.018196504141361</v>
+        <v>5.209470553621694</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2788,16 +2788,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>2.667658859425841</v>
+        <v>1.670146682093189</v>
       </c>
       <c r="C73">
-        <v>12.08994436556641</v>
+        <v>11.00363798445858</v>
       </c>
       <c r="D73">
-        <v>49.58148404311077</v>
+        <v>50.16078691573902</v>
       </c>
       <c r="E73">
-        <v>5.292818834257427</v>
+        <v>5.198019502719596</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2805,16 +2805,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>2.224432460075226</v>
+        <v>1.66832830270992</v>
       </c>
       <c r="C74">
-        <v>12.29843912851419</v>
+        <v>11.38253683128739</v>
       </c>
       <c r="D74">
-        <v>49.96978471569334</v>
+        <v>49.77026374309434</v>
       </c>
       <c r="E74">
-        <v>6.471437052273131</v>
+        <v>5.195796226397221</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2822,16 +2822,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>2.788650181180617</v>
+        <v>1.7341359458332</v>
       </c>
       <c r="C75">
-        <v>10.98708090672892</v>
+        <v>11.22995936063237</v>
       </c>
       <c r="D75">
-        <v>49.80025482722289</v>
+        <v>49.84019225019998</v>
       </c>
       <c r="E75">
-        <v>6.318601827732117</v>
+        <v>5.203306781196287</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2839,16 +2839,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>3.409175373636301</v>
+        <v>1.645454462035834</v>
       </c>
       <c r="C76">
-        <v>12.4845383749401</v>
+        <v>11.31157314267937</v>
       </c>
       <c r="D76">
-        <v>50.01323507409586</v>
+        <v>50.68499530526471</v>
       </c>
       <c r="E76">
-        <v>6.128209126740988</v>
+        <v>5.304240632858062</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2856,16 +2856,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>2.333698589466655</v>
+        <v>1.649337852894506</v>
       </c>
       <c r="C77">
-        <v>11.89881406428589</v>
+        <v>11.08149980453761</v>
       </c>
       <c r="D77">
-        <v>49.56049411929813</v>
+        <v>50.98163034293713</v>
       </c>
       <c r="E77">
-        <v>5.656494846589861</v>
+        <v>5.230230628048671</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2873,16 +2873,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>2.061183889072479</v>
+        <v>1.682116233238837</v>
       </c>
       <c r="C78">
-        <v>11.14913914140924</v>
+        <v>11.15790165796695</v>
       </c>
       <c r="D78">
-        <v>49.93378141381358</v>
+        <v>49.73958371764299</v>
       </c>
       <c r="E78">
-        <v>6.657718392660486</v>
+        <v>5.273988081815779</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2890,16 +2890,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>2.26990094242532</v>
+        <v>1.622761441766974</v>
       </c>
       <c r="C79">
-        <v>12.52578124156083</v>
+        <v>11.04985633402343</v>
       </c>
       <c r="D79">
-        <v>49.65491861682379</v>
+        <v>49.94493533319013</v>
       </c>
       <c r="E79">
-        <v>6.696735174575926</v>
+        <v>5.213143203327958</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2907,16 +2907,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>2.26953509501712</v>
+        <v>1.721902133557105</v>
       </c>
       <c r="C80">
-        <v>11.26786402613301</v>
+        <v>11.17688758410655</v>
       </c>
       <c r="D80">
-        <v>49.86047360800602</v>
+        <v>50.29116923688591</v>
       </c>
       <c r="E80">
-        <v>6.634265088767204</v>
+        <v>5.230573347397047</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2924,16 +2924,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>2.796342906371165</v>
+        <v>1.715198656608024</v>
       </c>
       <c r="C81">
-        <v>11.56236021047399</v>
+        <v>11.42925663205618</v>
       </c>
       <c r="D81">
-        <v>49.56477640268047</v>
+        <v>49.74655978012122</v>
       </c>
       <c r="E81">
-        <v>5.816068905112533</v>
+        <v>5.227154269413209</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2941,16 +2941,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>3.119304068007062</v>
+        <v>1.691255150680576</v>
       </c>
       <c r="C82">
-        <v>12.27707121820607</v>
+        <v>11.2121367623755</v>
       </c>
       <c r="D82">
-        <v>49.86109989125165</v>
+        <v>50.59488734276221</v>
       </c>
       <c r="E82">
-        <v>6.665189073129625</v>
+        <v>5.286076585307553</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2958,16 +2958,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>1.789648089640747</v>
+        <v>1.669345575386963</v>
       </c>
       <c r="C83">
-        <v>12.09570861683482</v>
+        <v>11.01580643414882</v>
       </c>
       <c r="D83">
-        <v>49.52419390498924</v>
+        <v>50.78874215479536</v>
       </c>
       <c r="E83">
-        <v>5.379948780638809</v>
+        <v>5.192010162626165</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2975,16 +2975,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>3.138288340308092</v>
+        <v>1.643855257492584</v>
       </c>
       <c r="C84">
-        <v>11.8569191166517</v>
+        <v>11.0066086476763</v>
       </c>
       <c r="D84">
-        <v>49.71115424371722</v>
+        <v>50.12905277263089</v>
       </c>
       <c r="E84">
-        <v>5.712503644316084</v>
+        <v>5.264787076665048</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2992,16 +2992,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>1.620723686258709</v>
+        <v>1.640978383056718</v>
       </c>
       <c r="C85">
-        <v>11.99900121689122</v>
+        <v>11.43674481768767</v>
       </c>
       <c r="D85">
-        <v>49.73069495059775</v>
+        <v>49.65936567111721</v>
       </c>
       <c r="E85">
-        <v>6.61019719617456</v>
+        <v>5.341450598469199</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3009,16 +3009,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>3.168888392250126</v>
+        <v>1.733354460005982</v>
       </c>
       <c r="C86">
-        <v>12.26944262094447</v>
+        <v>11.35894659140654</v>
       </c>
       <c r="D86">
-        <v>49.8807699337007</v>
+        <v>50.02564566430124</v>
       </c>
       <c r="E86">
-        <v>5.268076782044046</v>
+        <v>5.276816722935942</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3026,16 +3026,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>1.628416287696114</v>
+        <v>1.634940440394842</v>
       </c>
       <c r="C87">
-        <v>11.8268426653946</v>
+        <v>11.27528590683082</v>
       </c>
       <c r="D87">
-        <v>49.62539647447456</v>
+        <v>49.57720053855096</v>
       </c>
       <c r="E87">
-        <v>6.666998276573683</v>
+        <v>5.242663752687537</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3043,16 +3043,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>3.243556189081533</v>
+        <v>1.671381660936776</v>
       </c>
       <c r="C88">
-        <v>11.60319332775817</v>
+        <v>11.43376865833454</v>
       </c>
       <c r="D88">
-        <v>49.5481164915277</v>
+        <v>49.70290617560156</v>
       </c>
       <c r="E88">
-        <v>6.529175845305257</v>
+        <v>5.304548410185575</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3060,16 +3060,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>2.631528395474913</v>
+        <v>1.723847747348643</v>
       </c>
       <c r="C89">
-        <v>12.05583439006315</v>
+        <v>11.09370365931167</v>
       </c>
       <c r="D89">
-        <v>49.78016221684098</v>
+        <v>51.06677199893265</v>
       </c>
       <c r="E89">
-        <v>6.461771876249356</v>
+        <v>5.229480319263419</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3077,16 +3077,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>2.985513164095199</v>
+        <v>1.659572799985319</v>
       </c>
       <c r="C90">
-        <v>11.66983294099791</v>
+        <v>11.29355925019839</v>
       </c>
       <c r="D90">
-        <v>50.00831397808062</v>
+        <v>50.47291979025421</v>
       </c>
       <c r="E90">
-        <v>5.186447754818101</v>
+        <v>5.248569992265734</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3094,16 +3094,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>3.200010435480746</v>
+        <v>1.671359462168265</v>
       </c>
       <c r="C91">
-        <v>11.07015218158477</v>
+        <v>11.22441921701067</v>
       </c>
       <c r="D91">
-        <v>49.79214111315556</v>
+        <v>50.74588734294331</v>
       </c>
       <c r="E91">
-        <v>5.829544364498193</v>
+        <v>5.261382237742398</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3111,16 +3111,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>1.763119731364597</v>
+        <v>1.655774678671157</v>
       </c>
       <c r="C92">
-        <v>11.10909037259095</v>
+        <v>11.31910555103719</v>
       </c>
       <c r="D92">
-        <v>49.61065273652797</v>
+        <v>50.42826169101296</v>
       </c>
       <c r="E92">
-        <v>5.810626305412312</v>
+        <v>5.282432092257781</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3128,16 +3128,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>1.786708662718198</v>
+        <v>1.651193543190716</v>
       </c>
       <c r="C93">
-        <v>12.13876906149911</v>
+        <v>11.06778501423529</v>
       </c>
       <c r="D93">
-        <v>49.75017329022712</v>
+        <v>50.27778479297926</v>
       </c>
       <c r="E93">
-        <v>6.763849593803088</v>
+        <v>5.319671361136923</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3145,16 +3145,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>2.192023097665313</v>
+        <v>1.644140809791258</v>
       </c>
       <c r="C94">
-        <v>11.14355231926362</v>
+        <v>11.20356658210362</v>
       </c>
       <c r="D94">
-        <v>49.69992206726321</v>
+        <v>50.96299465126385</v>
       </c>
       <c r="E94">
-        <v>5.213739081338763</v>
+        <v>5.257976697942172</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3162,16 +3162,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>2.098147864493232</v>
+        <v>1.726588011091476</v>
       </c>
       <c r="C95">
-        <v>11.55398390172075</v>
+        <v>11.25066697933562</v>
       </c>
       <c r="D95">
-        <v>49.92459001451419</v>
+        <v>50.96291171662087</v>
       </c>
       <c r="E95">
-        <v>5.654190552532621</v>
+        <v>5.292732399911201</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3179,16 +3179,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>3.289260067969994</v>
+        <v>1.727948680430168</v>
       </c>
       <c r="C96">
-        <v>11.42480075187355</v>
+        <v>11.00241912555406</v>
       </c>
       <c r="D96">
-        <v>49.76290191224071</v>
+        <v>50.43305072520941</v>
       </c>
       <c r="E96">
-        <v>6.549404052907769</v>
+        <v>5.271617830530528</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3196,16 +3196,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>1.754887585761624</v>
+        <v>1.684201212919918</v>
       </c>
       <c r="C97">
-        <v>11.20434221757824</v>
+        <v>10.97241789550528</v>
       </c>
       <c r="D97">
-        <v>49.99961571311022</v>
+        <v>50.084652532238</v>
       </c>
       <c r="E97">
-        <v>6.650661899532292</v>
+        <v>5.28734109877879</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3213,16 +3213,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>1.78202293106997</v>
+        <v>1.729071010521962</v>
       </c>
       <c r="C98">
-        <v>12.33912589281699</v>
+        <v>11.21696535939041</v>
       </c>
       <c r="D98">
-        <v>49.67539400187962</v>
+        <v>50.8846870469109</v>
       </c>
       <c r="E98">
-        <v>5.285832101458237</v>
+        <v>5.262459926952301</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3230,16 +3230,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>2.442198079779018</v>
+        <v>1.693559824352219</v>
       </c>
       <c r="C99">
-        <v>11.77580205025932</v>
+        <v>11.02263922785826</v>
       </c>
       <c r="D99">
-        <v>49.96768776226789</v>
+        <v>49.75766790530363</v>
       </c>
       <c r="E99">
-        <v>5.537869823398873</v>
+        <v>5.32656570202492</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3247,16 +3247,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>3.020463210742745</v>
+        <v>1.664752136699134</v>
       </c>
       <c r="C100">
-        <v>11.17252051212623</v>
+        <v>11.34365012848086</v>
       </c>
       <c r="D100">
-        <v>49.53695149310622</v>
+        <v>50.63004298063309</v>
       </c>
       <c r="E100">
-        <v>5.570731980533919</v>
+        <v>5.189808771040941</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3264,16 +3264,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>3.242386064377203</v>
+        <v>1.623506184319344</v>
       </c>
       <c r="C101">
-        <v>12.13824115979401</v>
+        <v>11.20648240244562</v>
       </c>
       <c r="D101">
-        <v>49.72327558572039</v>
+        <v>50.60389496393091</v>
       </c>
       <c r="E101">
-        <v>5.550955312229116</v>
+        <v>5.272958792889176</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3281,16 +3281,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>3.196433318299909</v>
+        <v>1.632976366772656</v>
       </c>
       <c r="C102">
-        <v>11.61293254471544</v>
+        <v>11.34156145225551</v>
       </c>
       <c r="D102">
-        <v>49.67785813796644</v>
+        <v>51.01288160391485</v>
       </c>
       <c r="E102">
-        <v>5.271437821998894</v>
+        <v>5.214406771434429</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3298,16 +3298,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>3.165710097510108</v>
+        <v>1.709942655760737</v>
       </c>
       <c r="C103">
-        <v>12.30149879902082</v>
+        <v>11.10511472800077</v>
       </c>
       <c r="D103">
-        <v>49.89554816171159</v>
+        <v>50.62747281448395</v>
       </c>
       <c r="E103">
-        <v>5.841316009469105</v>
+        <v>5.19719857827886</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3315,16 +3315,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>1.692539875464695</v>
+        <v>1.712264172807053</v>
       </c>
       <c r="C104">
-        <v>11.41856034755984</v>
+        <v>11.45167513060168</v>
       </c>
       <c r="D104">
-        <v>49.88070806255269</v>
+        <v>50.10213092644716</v>
       </c>
       <c r="E104">
-        <v>5.91188101860509</v>
+        <v>5.328911204498335</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3332,16 +3332,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>3.092867811581316</v>
+        <v>1.629234719392958</v>
       </c>
       <c r="C105">
-        <v>12.35578757162434</v>
+        <v>11.16334061455846</v>
       </c>
       <c r="D105">
-        <v>49.61477159862827</v>
+        <v>50.47804177049258</v>
       </c>
       <c r="E105">
-        <v>5.551749194556145</v>
+        <v>5.222359273386171</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3349,16 +3349,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>2.498144762707891</v>
+        <v>1.719821056795382</v>
       </c>
       <c r="C106">
-        <v>11.90574817937342</v>
+        <v>11.21502905462264</v>
       </c>
       <c r="D106">
-        <v>49.68902193393316</v>
+        <v>49.53544362268055</v>
       </c>
       <c r="E106">
-        <v>6.32818567284348</v>
+        <v>5.233005783897332</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3366,16 +3366,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>2.964250753103403</v>
+        <v>1.637831444847477</v>
       </c>
       <c r="C107">
-        <v>12.44408014527484</v>
+        <v>11.01788012555238</v>
       </c>
       <c r="D107">
-        <v>49.95457161703577</v>
+        <v>49.56512637028458</v>
       </c>
       <c r="E107">
-        <v>6.400659210688707</v>
+        <v>5.188058939214233</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3383,16 +3383,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>3.371389179967412</v>
+        <v>1.721340771751851</v>
       </c>
       <c r="C108">
-        <v>12.07629492899583</v>
+        <v>11.17287602015126</v>
       </c>
       <c r="D108">
-        <v>49.6706889156191</v>
+        <v>49.80399044460524</v>
       </c>
       <c r="E108">
-        <v>6.156575557604443</v>
+        <v>5.188240462499209</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3400,16 +3400,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>2.445141434079483</v>
+        <v>1.653866846582436</v>
       </c>
       <c r="C109">
-        <v>11.97662127431641</v>
+        <v>10.97598504264776</v>
       </c>
       <c r="D109">
-        <v>49.58252454108252</v>
+        <v>50.02404677518271</v>
       </c>
       <c r="E109">
-        <v>5.996949961108376</v>
+        <v>5.339501463467555</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3417,16 +3417,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>3.275057297773007</v>
+        <v>1.620811578491211</v>
       </c>
       <c r="C110">
-        <v>12.29226256500423</v>
+        <v>11.10680459320593</v>
       </c>
       <c r="D110">
-        <v>49.86172490786355</v>
+        <v>50.57366222630531</v>
       </c>
       <c r="E110">
-        <v>5.209333308021785</v>
+        <v>5.33778544971925</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3434,16 +3434,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>2.112999327699638</v>
+        <v>1.656375633917878</v>
       </c>
       <c r="C111">
-        <v>11.96983506408338</v>
+        <v>11.38725398159647</v>
       </c>
       <c r="D111">
-        <v>49.72766817934775</v>
+        <v>49.79748633860207</v>
       </c>
       <c r="E111">
-        <v>6.236607463342947</v>
+        <v>5.327182903841083</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3451,16 +3451,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>2.158562901464358</v>
+        <v>1.721846670084427</v>
       </c>
       <c r="C112">
-        <v>11.10891254138354</v>
+        <v>11.19261759518893</v>
       </c>
       <c r="D112">
-        <v>49.88488556223425</v>
+        <v>50.09587901078227</v>
       </c>
       <c r="E112">
-        <v>6.571553181985199</v>
+        <v>5.223552112833999</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3468,16 +3468,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>1.809885672479815</v>
+        <v>1.631857941577556</v>
       </c>
       <c r="C113">
-        <v>11.00774068051991</v>
+        <v>11.0102134633056</v>
       </c>
       <c r="D113">
-        <v>49.89355218007768</v>
+        <v>50.92526444395817</v>
       </c>
       <c r="E113">
-        <v>5.738609215334939</v>
+        <v>5.273051242638444</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3485,16 +3485,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>2.465515554779792</v>
+        <v>1.659682231791248</v>
       </c>
       <c r="C114">
-        <v>11.60825936616757</v>
+        <v>11.17063359917525</v>
       </c>
       <c r="D114">
-        <v>49.60596178123609</v>
+        <v>50.51566045914227</v>
       </c>
       <c r="E114">
-        <v>6.706065197608896</v>
+        <v>5.306863367459782</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3502,16 +3502,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>1.951048663837026</v>
+        <v>1.687066462282059</v>
       </c>
       <c r="C115">
-        <v>11.10223632562148</v>
+        <v>11.02564575631154</v>
       </c>
       <c r="D115">
-        <v>49.87306031187286</v>
+        <v>49.80529873865093</v>
       </c>
       <c r="E115">
-        <v>5.490878397203107</v>
+        <v>5.256056526428281</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -3519,16 +3519,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>2.969562549104762</v>
+        <v>1.715414992225503</v>
       </c>
       <c r="C116">
-        <v>12.19763779608417</v>
+        <v>11.03866210638552</v>
       </c>
       <c r="D116">
-        <v>49.6983399753385</v>
+        <v>51.03525819796121</v>
       </c>
       <c r="E116">
-        <v>5.28096458918067</v>
+        <v>5.302847904615478</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -3536,16 +3536,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>3.179836986956173</v>
+        <v>1.725536113679502</v>
       </c>
       <c r="C117">
-        <v>11.80986393601927</v>
+        <v>11.17113460282048</v>
       </c>
       <c r="D117">
-        <v>49.57259340150534</v>
+        <v>50.48094163030855</v>
       </c>
       <c r="E117">
-        <v>6.454176514648598</v>
+        <v>5.334232964534657</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -3553,16 +3553,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>2.870441555045302</v>
+        <v>1.644348465546529</v>
       </c>
       <c r="C118">
-        <v>11.12828039312921</v>
+        <v>11.14061290922414</v>
       </c>
       <c r="D118">
-        <v>49.57479950305677</v>
+        <v>50.18257211677658</v>
       </c>
       <c r="E118">
-        <v>5.339587776567892</v>
+        <v>5.203806985257263</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3570,16 +3570,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>3.328825190463501</v>
+        <v>1.672461397950789</v>
       </c>
       <c r="C119">
-        <v>12.50693102892161</v>
+        <v>11.02359557653869</v>
       </c>
       <c r="D119">
-        <v>49.9032094758757</v>
+        <v>50.70176210224014</v>
       </c>
       <c r="E119">
-        <v>6.163132305143383</v>
+        <v>5.310497322145445</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3587,16 +3587,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>2.308673386672441</v>
+        <v>1.622944308971662</v>
       </c>
       <c r="C120">
-        <v>11.8793634822026</v>
+        <v>11.3738595992402</v>
       </c>
       <c r="D120">
-        <v>49.64842836762317</v>
+        <v>49.83939241857624</v>
       </c>
       <c r="E120">
-        <v>6.227965714861548</v>
+        <v>5.321449467837049</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3604,16 +3604,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>2.299164139495777</v>
+        <v>1.628941255352299</v>
       </c>
       <c r="C121">
-        <v>11.13950684232008</v>
+        <v>11.3525647812835</v>
       </c>
       <c r="D121">
-        <v>49.53217307846888</v>
+        <v>50.48322629505576</v>
       </c>
       <c r="E121">
-        <v>6.038775571757308</v>
+        <v>5.25845280828314</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3621,16 +3621,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>1.906093022118147</v>
+        <v>1.661148270373505</v>
       </c>
       <c r="C122">
-        <v>11.67534730851279</v>
+        <v>10.95206281934065</v>
       </c>
       <c r="D122">
-        <v>49.91178899227103</v>
+        <v>49.63247754161289</v>
       </c>
       <c r="E122">
-        <v>5.83147351655313</v>
+        <v>5.190577661193061</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3638,16 +3638,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>2.970917543136018</v>
+        <v>1.639477177061199</v>
       </c>
       <c r="C123">
-        <v>12.18678969276513</v>
+        <v>11.21921623073224</v>
       </c>
       <c r="D123">
-        <v>49.70917944354626</v>
+        <v>50.87751293358818</v>
       </c>
       <c r="E123">
-        <v>5.48308716074204</v>
+        <v>5.308589720480879</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3655,16 +3655,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>3.217751854837742</v>
+        <v>1.620228329077512</v>
       </c>
       <c r="C124">
-        <v>12.34669618096538</v>
+        <v>11.43740726395595</v>
       </c>
       <c r="D124">
-        <v>49.88274069166953</v>
+        <v>50.9472195415457</v>
       </c>
       <c r="E124">
-        <v>5.564686791855624</v>
+        <v>5.23736572420432</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3672,16 +3672,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>2.492829581404647</v>
+        <v>1.632711125008605</v>
       </c>
       <c r="C125">
-        <v>11.87013890752023</v>
+        <v>11.45520121332199</v>
       </c>
       <c r="D125">
-        <v>49.52424017195132</v>
+        <v>50.0262223879142</v>
       </c>
       <c r="E125">
-        <v>5.89973776522416</v>
+        <v>5.252742725494107</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3689,16 +3689,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>2.731394362290692</v>
+        <v>1.627153862997027</v>
       </c>
       <c r="C126">
-        <v>11.74946256291022</v>
+        <v>11.34322515416937</v>
       </c>
       <c r="D126">
-        <v>49.77207368387959</v>
+        <v>50.06524340192361</v>
       </c>
       <c r="E126">
-        <v>5.879619467782203</v>
+        <v>5.266760596130386</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3706,16 +3706,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>2.734466776949702</v>
+        <v>1.66233868098784</v>
       </c>
       <c r="C127">
-        <v>11.14551964259243</v>
+        <v>11.43505157585653</v>
       </c>
       <c r="D127">
-        <v>49.74199874338084</v>
+        <v>49.93013097221167</v>
       </c>
       <c r="E127">
-        <v>6.079118293609106</v>
+        <v>5.262273906302348</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3723,16 +3723,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>2.841701535856843</v>
+        <v>1.665137801633186</v>
       </c>
       <c r="C128">
-        <v>12.09452213085121</v>
+        <v>11.44546856215241</v>
       </c>
       <c r="D128">
-        <v>49.78976559514398</v>
+        <v>50.25727110241532</v>
       </c>
       <c r="E128">
-        <v>5.709163923238599</v>
+        <v>5.333465943260181</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3740,16 +3740,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>1.645973477311834</v>
+        <v>1.633613664651661</v>
       </c>
       <c r="C129">
-        <v>11.57647864658438</v>
+        <v>11.33789191450175</v>
       </c>
       <c r="D129">
-        <v>49.86968614508576</v>
+        <v>50.61158901806982</v>
       </c>
       <c r="E129">
-        <v>6.753487658129677</v>
+        <v>5.185954490114963</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3757,16 +3757,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>3.16718983040511</v>
+        <v>1.646982595232446</v>
       </c>
       <c r="C130">
-        <v>12.04285732226536</v>
+        <v>11.44696140169737</v>
       </c>
       <c r="D130">
-        <v>49.77399221286657</v>
+        <v>50.70927194547807</v>
       </c>
       <c r="E130">
-        <v>5.492409364599826</v>
+        <v>5.220899671171907</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3774,16 +3774,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>2.92181829411818</v>
+        <v>1.688764282581221</v>
       </c>
       <c r="C131">
-        <v>12.0348004964192</v>
+        <v>11.34301842690773</v>
       </c>
       <c r="D131">
-        <v>49.86282062544395</v>
+        <v>50.752821578479</v>
       </c>
       <c r="E131">
-        <v>6.523090938265374</v>
+        <v>5.208197602562294</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3791,16 +3791,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>3.198300496875293</v>
+        <v>1.654894853102821</v>
       </c>
       <c r="C132">
-        <v>12.11675258397446</v>
+        <v>10.97344364234155</v>
       </c>
       <c r="D132">
-        <v>49.75300803160832</v>
+        <v>49.72627815922809</v>
       </c>
       <c r="E132">
-        <v>6.354975754647235</v>
+        <v>5.331696985605319</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3808,16 +3808,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>3.316447604892993</v>
+        <v>1.704286677865553</v>
       </c>
       <c r="C133">
-        <v>11.40846695456345</v>
+        <v>11.18567972235983</v>
       </c>
       <c r="D133">
-        <v>49.6340718845134</v>
+        <v>50.12226617207575</v>
       </c>
       <c r="E133">
-        <v>6.486445914081573</v>
+        <v>5.274602537496001</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3825,16 +3825,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>3.26980150056059</v>
+        <v>1.728655141647949</v>
       </c>
       <c r="C134">
-        <v>11.17844639042259</v>
+        <v>11.06854757602416</v>
       </c>
       <c r="D134">
-        <v>49.58242225451199</v>
+        <v>49.95435676108819</v>
       </c>
       <c r="E134">
-        <v>5.920265855870613</v>
+        <v>5.272680534183741</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3842,16 +3842,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>2.755742996679501</v>
+        <v>1.620444774410365</v>
       </c>
       <c r="C135">
-        <v>12.31902587186197</v>
+        <v>11.23514961734789</v>
       </c>
       <c r="D135">
-        <v>49.95659002801535</v>
+        <v>50.27365127314527</v>
       </c>
       <c r="E135">
-        <v>5.253165675809858</v>
+        <v>5.222228611602056</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3859,16 +3859,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>2.407357893391212</v>
+        <v>1.669712981989141</v>
       </c>
       <c r="C136">
-        <v>11.2045286448714</v>
+        <v>11.2845099557179</v>
       </c>
       <c r="D136">
-        <v>49.82088506737452</v>
+        <v>50.4062391637676</v>
       </c>
       <c r="E136">
-        <v>5.772343785470753</v>
+        <v>5.275860326362507</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3876,16 +3876,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>2.692025416348085</v>
+        <v>1.683111454389166</v>
       </c>
       <c r="C137">
-        <v>12.1973738759916</v>
+        <v>11.37966931204345</v>
       </c>
       <c r="D137">
-        <v>49.98380140742064</v>
+        <v>49.87158448211355</v>
       </c>
       <c r="E137">
-        <v>5.566949616096894</v>
+        <v>5.247178333706274</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3893,16 +3893,16 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>2.380479960460417</v>
+        <v>1.731341820401878</v>
       </c>
       <c r="C138">
-        <v>11.4543886421089</v>
+        <v>11.31090141025012</v>
       </c>
       <c r="D138">
-        <v>49.80246214926569</v>
+        <v>49.75519336876016</v>
       </c>
       <c r="E138">
-        <v>5.513401078371307</v>
+        <v>5.283384174600165</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3910,16 +3910,16 @@
         <v>142</v>
       </c>
       <c r="B139">
-        <v>2.496686447058165</v>
+        <v>1.68192307281615</v>
       </c>
       <c r="C139">
-        <v>12.47228322037424</v>
+        <v>11.13803140704981</v>
       </c>
       <c r="D139">
-        <v>49.61123298412058</v>
+        <v>50.93090241553443</v>
       </c>
       <c r="E139">
-        <v>5.258845490051332</v>
+        <v>5.339617725180085</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3927,16 +3927,16 @@
         <v>143</v>
       </c>
       <c r="B140">
-        <v>3.37460511336473</v>
+        <v>1.681909478278799</v>
       </c>
       <c r="C140">
-        <v>11.77652531970716</v>
+        <v>11.07935962916367</v>
       </c>
       <c r="D140">
-        <v>49.66845778724957</v>
+        <v>49.55544018569958</v>
       </c>
       <c r="E140">
-        <v>5.425567488117285</v>
+        <v>5.279733025300455</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3944,16 +3944,16 @@
         <v>144</v>
       </c>
       <c r="B141">
-        <v>4.196448877785261</v>
+        <v>2.969318742889948</v>
       </c>
       <c r="C141">
-        <v>18.08248713384027</v>
+        <v>17.21999539875375</v>
       </c>
       <c r="D141">
-        <v>23.75937449910269</v>
+        <v>24.61313766179342</v>
       </c>
       <c r="E141">
-        <v>6.534782281038478</v>
+        <v>6.406398457505291</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3961,16 +3961,16 @@
         <v>145</v>
       </c>
       <c r="B142">
-        <v>3.681013834007544</v>
+        <v>3.029507690812915</v>
       </c>
       <c r="C142">
-        <v>17.5877731484603</v>
+        <v>17.09750057680692</v>
       </c>
       <c r="D142">
-        <v>23.88603319664164</v>
+        <v>24.5522085828876</v>
       </c>
       <c r="E142">
-        <v>6.454616330778007</v>
+        <v>6.50026228852962</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3978,16 +3978,16 @@
         <v>146</v>
       </c>
       <c r="B143">
-        <v>3.035027464817137</v>
+        <v>3.004837484454126</v>
       </c>
       <c r="C143">
-        <v>17.0984240090871</v>
+        <v>17.35290951792079</v>
       </c>
       <c r="D143">
-        <v>23.8321491224078</v>
+        <v>23.86553203818193</v>
       </c>
       <c r="E143">
-        <v>7.953939660224417</v>
+        <v>6.471237114561625</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3995,16 +3995,16 @@
         <v>147</v>
       </c>
       <c r="B144">
-        <v>3.413190097990686</v>
+        <v>3.064094316382144</v>
       </c>
       <c r="C144">
-        <v>17.6550774244723</v>
+        <v>17.32314320871483</v>
       </c>
       <c r="D144">
-        <v>23.811376817187</v>
+        <v>24.42663225610034</v>
       </c>
       <c r="E144">
-        <v>7.831180099607001</v>
+        <v>6.534941921692848</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4012,16 +4012,16 @@
         <v>148</v>
       </c>
       <c r="B145">
-        <v>4.459869079261578</v>
+        <v>2.999730677645207</v>
       </c>
       <c r="C145">
-        <v>17.23342776917606</v>
+        <v>17.06141191171515</v>
       </c>
       <c r="D145">
-        <v>23.67503706413896</v>
+        <v>23.56226155350652</v>
       </c>
       <c r="E145">
-        <v>7.91636151047042</v>
+        <v>6.40433798793347</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4029,16 +4029,16 @@
         <v>149</v>
       </c>
       <c r="B146">
-        <v>4.107589640430134</v>
+        <v>3.009892559065998</v>
       </c>
       <c r="C146">
-        <v>18.22859778469376</v>
+        <v>17.16963968931066</v>
       </c>
       <c r="D146">
-        <v>23.63819005209044</v>
+        <v>23.95208536286753</v>
       </c>
       <c r="E146">
-        <v>6.473408403158841</v>
+        <v>6.427423160958728</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4046,16 +4046,16 @@
         <v>150</v>
       </c>
       <c r="B147">
-        <v>4.656883788879658</v>
+        <v>3.033487101010789</v>
       </c>
       <c r="C147">
-        <v>17.2477274335513</v>
+        <v>17.06480830779429</v>
       </c>
       <c r="D147">
-        <v>23.77090694673004</v>
+        <v>23.84717233565345</v>
       </c>
       <c r="E147">
-        <v>6.962962865256336</v>
+        <v>6.40404097909679</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4063,16 +4063,16 @@
         <v>151</v>
       </c>
       <c r="B148">
-        <v>3.502631609327193</v>
+        <v>3.03474477356814</v>
       </c>
       <c r="C148">
-        <v>17.1353988710672</v>
+        <v>16.95544661332742</v>
       </c>
       <c r="D148">
-        <v>23.81668197402255</v>
+        <v>24.14804266330585</v>
       </c>
       <c r="E148">
-        <v>6.764143004280208</v>
+        <v>6.48300943181657</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4080,16 +4080,16 @@
         <v>152</v>
       </c>
       <c r="B149">
-        <v>4.375409961841946</v>
+        <v>3.059468371318323</v>
       </c>
       <c r="C149">
-        <v>17.82431407715656</v>
+        <v>17.06042146099403</v>
       </c>
       <c r="D149">
-        <v>23.515992900615</v>
+        <v>24.85295960573846</v>
       </c>
       <c r="E149">
-        <v>7.99402216629491</v>
+        <v>6.461758107158549</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4097,16 +4097,16 @@
         <v>153</v>
       </c>
       <c r="B150">
-        <v>4.001393460658708</v>
+        <v>3.026045794320019</v>
       </c>
       <c r="C150">
-        <v>17.85982396522055</v>
+        <v>16.92192514111851</v>
       </c>
       <c r="D150">
-        <v>23.71216216508926</v>
+        <v>23.62828022567906</v>
       </c>
       <c r="E150">
-        <v>7.46631533600176</v>
+        <v>6.401221680893213</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4114,16 +4114,16 @@
         <v>154</v>
       </c>
       <c r="B151">
-        <v>3.579446851061465</v>
+        <v>2.975218780186474</v>
       </c>
       <c r="C151">
-        <v>17.66611598900338</v>
+        <v>17.23168923374735</v>
       </c>
       <c r="D151">
-        <v>23.84581983694318</v>
+        <v>24.65768151030152</v>
       </c>
       <c r="E151">
-        <v>7.852894516521912</v>
+        <v>6.409185489975127</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4131,16 +4131,16 @@
         <v>155</v>
       </c>
       <c r="B152">
-        <v>4.392356767081955</v>
+        <v>3.054620060465454</v>
       </c>
       <c r="C152">
-        <v>17.96838346773329</v>
+        <v>17.19524355917029</v>
       </c>
       <c r="D152">
-        <v>23.77490593002992</v>
+        <v>24.95211496058465</v>
       </c>
       <c r="E152">
-        <v>7.103013457393104</v>
+        <v>6.410243979103935</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4148,16 +4148,16 @@
         <v>156</v>
       </c>
       <c r="B153">
-        <v>4.659698005981737</v>
+        <v>3.048544029158092</v>
       </c>
       <c r="C153">
-        <v>17.56787294606571</v>
+        <v>16.96472024002098</v>
       </c>
       <c r="D153">
-        <v>23.46359371243408</v>
+        <v>24.79456595893003</v>
       </c>
       <c r="E153">
-        <v>7.488305680024089</v>
+        <v>6.5478743342419</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4165,16 +4165,16 @@
         <v>157</v>
       </c>
       <c r="B154">
-        <v>3.441900447606162</v>
+        <v>3.057798351627875</v>
       </c>
       <c r="C154">
-        <v>17.71582909450349</v>
+        <v>17.03638767903841</v>
       </c>
       <c r="D154">
-        <v>23.67630474926088</v>
+        <v>23.64723584983525</v>
       </c>
       <c r="E154">
-        <v>7.323874733996479</v>
+        <v>6.417368851760605</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4182,16 +4182,16 @@
         <v>158</v>
       </c>
       <c r="B155">
-        <v>4.122132455386428</v>
+        <v>3.013936775036889</v>
       </c>
       <c r="C155">
-        <v>17.93739271525715</v>
+        <v>17.27160431960695</v>
       </c>
       <c r="D155">
-        <v>23.91606183965653</v>
+        <v>24.76220908329775</v>
       </c>
       <c r="E155">
-        <v>7.24008198817878</v>
+        <v>6.419272006731866</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4199,16 +4199,16 @@
         <v>159</v>
       </c>
       <c r="B156">
-        <v>3.298525308144291</v>
+        <v>2.962453812628599</v>
       </c>
       <c r="C156">
-        <v>16.90196596649304</v>
+        <v>16.98998140926678</v>
       </c>
       <c r="D156">
-        <v>23.78276706504013</v>
+        <v>24.31242692946871</v>
       </c>
       <c r="E156">
-        <v>6.854263712769642</v>
+        <v>6.498993204907174</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4216,16 +4216,16 @@
         <v>160</v>
       </c>
       <c r="B157">
-        <v>4.534932071771039</v>
+        <v>2.989919202240251</v>
       </c>
       <c r="C157">
-        <v>17.04590155717228</v>
+        <v>17.03826003454061</v>
       </c>
       <c r="D157">
-        <v>23.53741226019574</v>
+        <v>23.89640079917873</v>
       </c>
       <c r="E157">
-        <v>7.260599639669572</v>
+        <v>6.415845772669144</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4233,16 +4233,16 @@
         <v>161</v>
       </c>
       <c r="B158">
-        <v>3.636026429988279</v>
+        <v>2.9811547263048</v>
       </c>
       <c r="C158">
-        <v>18.39042926726703</v>
+        <v>17.38961553389516</v>
       </c>
       <c r="D158">
-        <v>23.65604159179861</v>
+        <v>23.44187290976169</v>
       </c>
       <c r="E158">
-        <v>7.764895733771052</v>
+        <v>6.445804297263434</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4250,16 +4250,16 @@
         <v>162</v>
       </c>
       <c r="B159">
-        <v>3.161001793819688</v>
+        <v>2.971316398065574</v>
       </c>
       <c r="C159">
-        <v>17.2278281166157</v>
+        <v>17.24146607299127</v>
       </c>
       <c r="D159">
-        <v>23.9345254410016</v>
+        <v>24.6288995301651</v>
       </c>
       <c r="E159">
-        <v>6.798649988701484</v>
+        <v>6.5373298081975</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4267,16 +4267,16 @@
         <v>163</v>
       </c>
       <c r="B160">
-        <v>3.77711710097788</v>
+        <v>2.993444639443253</v>
       </c>
       <c r="C160">
-        <v>18.24135050540388</v>
+        <v>17.30288477361036</v>
       </c>
       <c r="D160">
-        <v>23.47626305137612</v>
+        <v>24.16387551285233</v>
       </c>
       <c r="E160">
-        <v>6.580182991390443</v>
+        <v>6.46691249374812</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4284,16 +4284,16 @@
         <v>164</v>
       </c>
       <c r="B161">
-        <v>4.381619339185611</v>
+        <v>3.060464188533868</v>
       </c>
       <c r="C161">
-        <v>17.05054648059055</v>
+        <v>17.39042768737756</v>
       </c>
       <c r="D161">
-        <v>23.90200429112734</v>
+        <v>24.75777214341312</v>
       </c>
       <c r="E161">
-        <v>7.593897293643177</v>
+        <v>6.408266250345001</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4301,16 +4301,16 @@
         <v>165</v>
       </c>
       <c r="B162">
-        <v>4.599468533005468</v>
+        <v>3.062568747653774</v>
       </c>
       <c r="C162">
-        <v>17.49838835968773</v>
+        <v>17.23317693025817</v>
       </c>
       <c r="D162">
-        <v>23.60271257067016</v>
+        <v>24.25334761025872</v>
       </c>
       <c r="E162">
-        <v>7.665292937446132</v>
+        <v>6.54317770431271</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4318,16 +4318,16 @@
         <v>166</v>
       </c>
       <c r="B163">
-        <v>3.100552723175753</v>
+        <v>3.003463478794702</v>
       </c>
       <c r="C163">
-        <v>17.45410794564849</v>
+        <v>16.98895656402389</v>
       </c>
       <c r="D163">
-        <v>23.70711736008942</v>
+        <v>24.62968301008281</v>
       </c>
       <c r="E163">
-        <v>7.138535706556908</v>
+        <v>6.49431847030189</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4335,16 +4335,16 @@
         <v>167</v>
       </c>
       <c r="B164">
-        <v>3.153434758022896</v>
+        <v>3.022222145419317</v>
       </c>
       <c r="C164">
-        <v>18.10091689871634</v>
+        <v>16.9979816519204</v>
       </c>
       <c r="D164">
-        <v>23.933776265994</v>
+        <v>24.59293661224026</v>
       </c>
       <c r="E164">
-        <v>7.224666379244471</v>
+        <v>6.408454786137706</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4352,16 +4352,16 @@
         <v>168</v>
       </c>
       <c r="B165">
-        <v>3.947844208893964</v>
+        <v>3.070652972778385</v>
       </c>
       <c r="C165">
-        <v>18.32295670604699</v>
+        <v>17.07239170192897</v>
       </c>
       <c r="D165">
-        <v>23.70873625248845</v>
+        <v>24.4782597864384</v>
       </c>
       <c r="E165">
-        <v>7.587485371894373</v>
+        <v>6.469125479388445</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4369,16 +4369,16 @@
         <v>169</v>
       </c>
       <c r="B166">
-        <v>4.470628077864255</v>
+        <v>3.005443080290354</v>
       </c>
       <c r="C166">
-        <v>18.15848434505649</v>
+        <v>17.39716380333432</v>
       </c>
       <c r="D166">
-        <v>23.89326559552585</v>
+        <v>23.6947241601093</v>
       </c>
       <c r="E166">
-        <v>6.471711749461018</v>
+        <v>6.451876768834932</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4386,16 +4386,16 @@
         <v>170</v>
       </c>
       <c r="B167">
-        <v>4.235879340883391</v>
+        <v>2.975117107377552</v>
       </c>
       <c r="C167">
-        <v>16.93952536447033</v>
+        <v>17.09119943854078</v>
       </c>
       <c r="D167">
-        <v>23.7653342280589</v>
+        <v>23.53555192229488</v>
       </c>
       <c r="E167">
-        <v>7.784885378448971</v>
+        <v>6.40736541390109</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4403,16 +4403,16 @@
         <v>171</v>
       </c>
       <c r="B168">
-        <v>3.958552195774206</v>
+        <v>3.06067640434323</v>
       </c>
       <c r="C168">
-        <v>17.64473654609817</v>
+        <v>17.2204222453796</v>
       </c>
       <c r="D168">
-        <v>23.82105739752085</v>
+        <v>23.87770990764134</v>
       </c>
       <c r="E168">
-        <v>6.886878004374304</v>
+        <v>6.403869434695541</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4420,16 +4420,16 @@
         <v>172</v>
       </c>
       <c r="B169">
-        <v>2.967204550343916</v>
+        <v>3.020000210895642</v>
       </c>
       <c r="C169">
-        <v>17.23329918794368</v>
+        <v>17.1160657557983</v>
       </c>
       <c r="D169">
-        <v>23.53879938709209</v>
+        <v>23.7104203659434</v>
       </c>
       <c r="E169">
-        <v>7.46353101314452</v>
+        <v>6.442367445914768</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4437,16 +4437,16 @@
         <v>173</v>
       </c>
       <c r="B170">
-        <v>3.982656855281842</v>
+        <v>2.965741392118328</v>
       </c>
       <c r="C170">
-        <v>17.30753644897969</v>
+        <v>17.26189974517719</v>
       </c>
       <c r="D170">
-        <v>23.72163693206098</v>
+        <v>24.09075093249223</v>
       </c>
       <c r="E170">
-        <v>6.682539829080565</v>
+        <v>6.530687824478271</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4454,16 +4454,16 @@
         <v>174</v>
       </c>
       <c r="B171">
-        <v>3.408787258090665</v>
+        <v>3.059720710700442</v>
       </c>
       <c r="C171">
-        <v>18.12009313182273</v>
+        <v>16.93053984909939</v>
       </c>
       <c r="D171">
-        <v>23.80848871917452</v>
+        <v>24.64537237561263</v>
       </c>
       <c r="E171">
-        <v>6.486636200578125</v>
+        <v>6.456611328082221</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4471,16 +4471,16 @@
         <v>175</v>
       </c>
       <c r="B172">
-        <v>3.950678242608555</v>
+        <v>3.012581175698648</v>
       </c>
       <c r="C172">
-        <v>17.46916177640074</v>
+        <v>17.33753113417875</v>
       </c>
       <c r="D172">
-        <v>23.7889923966025</v>
+        <v>23.98444835445198</v>
       </c>
       <c r="E172">
-        <v>7.074134868772754</v>
+        <v>6.451557868822734</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4488,16 +4488,16 @@
         <v>176</v>
       </c>
       <c r="B173">
-        <v>3.089034314779219</v>
+        <v>3.024442407215501</v>
       </c>
       <c r="C173">
-        <v>16.94426656130766</v>
+        <v>17.03435858536773</v>
       </c>
       <c r="D173">
-        <v>23.90553724636804</v>
+        <v>23.48003635183229</v>
       </c>
       <c r="E173">
-        <v>7.515602510374771</v>
+        <v>6.557926635285641</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4505,16 +4505,16 @@
         <v>177</v>
       </c>
       <c r="B174">
-        <v>3.429887585373742</v>
+        <v>3.045668653440195</v>
       </c>
       <c r="C174">
-        <v>18.37918616067902</v>
+        <v>17.32084981280553</v>
       </c>
       <c r="D174">
-        <v>23.82953875658128</v>
+        <v>24.75985817695795</v>
       </c>
       <c r="E174">
-        <v>7.47919423160384</v>
+        <v>6.407475427555223</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -4522,16 +4522,16 @@
         <v>178</v>
       </c>
       <c r="B175">
-        <v>3.855159583148806</v>
+        <v>2.971678285977214</v>
       </c>
       <c r="C175">
-        <v>17.24881375107583</v>
+        <v>17.01439059637713</v>
       </c>
       <c r="D175">
-        <v>23.74941455871054</v>
+        <v>24.28283617684298</v>
       </c>
       <c r="E175">
-        <v>6.666961657686651</v>
+        <v>6.510546150322371</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -4539,16 +4539,16 @@
         <v>179</v>
       </c>
       <c r="B176">
-        <v>4.334812931646108</v>
+        <v>3.062653495949525</v>
       </c>
       <c r="C176">
-        <v>17.89382887912809</v>
+        <v>16.96303834501854</v>
       </c>
       <c r="D176">
-        <v>23.54501815232187</v>
+        <v>23.88842387573854</v>
       </c>
       <c r="E176">
-        <v>7.066584836415462</v>
+        <v>6.479816285018645</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -4556,16 +4556,16 @@
         <v>180</v>
       </c>
       <c r="B177">
-        <v>4.743619715740889</v>
+        <v>2.977332879257064</v>
       </c>
       <c r="C177">
-        <v>18.25141720238327</v>
+        <v>16.92361092660328</v>
       </c>
       <c r="D177">
-        <v>23.79174942430758</v>
+        <v>24.72805314406384</v>
       </c>
       <c r="E177">
-        <v>7.494218373500918</v>
+        <v>6.559682569458708</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4573,16 +4573,16 @@
         <v>181</v>
       </c>
       <c r="B178">
-        <v>4.413916988099578</v>
+        <v>2.986926245713426</v>
       </c>
       <c r="C178">
-        <v>17.03567207753653</v>
+        <v>17.33267504732106</v>
       </c>
       <c r="D178">
-        <v>23.79183584097355</v>
+        <v>24.83175196239788</v>
       </c>
       <c r="E178">
-        <v>7.14258665651704</v>
+        <v>6.472618234235326</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4590,16 +4590,16 @@
         <v>182</v>
       </c>
       <c r="B179">
-        <v>4.263829683329838</v>
+        <v>2.97734753295072</v>
       </c>
       <c r="C179">
-        <v>18.47023581774042</v>
+        <v>17.06815334237629</v>
       </c>
       <c r="D179">
-        <v>23.71870539683456</v>
+        <v>24.67350022927044</v>
       </c>
       <c r="E179">
-        <v>7.02151903596766</v>
+        <v>6.502750813301769</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4607,16 +4607,16 @@
         <v>183</v>
       </c>
       <c r="B180">
-        <v>4.517439037118672</v>
+        <v>3.020199849210894</v>
       </c>
       <c r="C180">
-        <v>17.18329902366412</v>
+        <v>16.9149579755029</v>
       </c>
       <c r="D180">
-        <v>23.89210951349442</v>
+        <v>23.90699292249007</v>
       </c>
       <c r="E180">
-        <v>6.428654677410531</v>
+        <v>6.528258948653547</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4624,16 +4624,16 @@
         <v>184</v>
       </c>
       <c r="B181">
-        <v>3.083436552243605</v>
+        <v>3.03421375188227</v>
       </c>
       <c r="C181">
-        <v>17.42508504272335</v>
+        <v>16.95916166154171</v>
       </c>
       <c r="D181">
-        <v>23.6037116171378</v>
+        <v>24.85668860693186</v>
       </c>
       <c r="E181">
-        <v>6.410425864031783</v>
+        <v>6.566246769039462</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4641,16 +4641,16 @@
         <v>185</v>
       </c>
       <c r="B182">
-        <v>3.660863358880221</v>
+        <v>3.041018427985208</v>
       </c>
       <c r="C182">
-        <v>17.37692893268176</v>
+        <v>17.02662133303887</v>
       </c>
       <c r="D182">
-        <v>23.65378214912322</v>
+        <v>24.67231220829892</v>
       </c>
       <c r="E182">
-        <v>6.566540002688678</v>
+        <v>6.537077741860162</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4658,16 +4658,16 @@
         <v>186</v>
       </c>
       <c r="B183">
-        <v>4.281556867888659</v>
+        <v>3.016988071155402</v>
       </c>
       <c r="C183">
-        <v>17.50504665579077</v>
+        <v>17.22993124259489</v>
       </c>
       <c r="D183">
-        <v>23.83871978209769</v>
+        <v>23.95652660526311</v>
       </c>
       <c r="E183">
-        <v>7.406404669446228</v>
+        <v>6.455768312951154</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4675,16 +4675,16 @@
         <v>187</v>
       </c>
       <c r="B184">
-        <v>3.558747355031552</v>
+        <v>3.068821445734383</v>
       </c>
       <c r="C184">
-        <v>17.94985021956472</v>
+        <v>17.22335174182121</v>
       </c>
       <c r="D184">
-        <v>23.62538984737752</v>
+        <v>24.42523485778219</v>
       </c>
       <c r="E184">
-        <v>7.202791880496149</v>
+        <v>6.558568312500932</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4692,16 +4692,16 @@
         <v>188</v>
       </c>
       <c r="B185">
-        <v>3.216275133217127</v>
+        <v>3.046279421524583</v>
       </c>
       <c r="C185">
-        <v>17.55027279209382</v>
+        <v>16.93640675524769</v>
       </c>
       <c r="D185">
-        <v>23.88004616688881</v>
+        <v>23.86331629827463</v>
       </c>
       <c r="E185">
-        <v>6.903076378150798</v>
+        <v>6.449830433934652</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4709,16 +4709,16 @@
         <v>189</v>
       </c>
       <c r="B186">
-        <v>3.798573055709732</v>
+        <v>2.968586413157572</v>
       </c>
       <c r="C186">
-        <v>18.18400184681976</v>
+        <v>17.36628194228505</v>
       </c>
       <c r="D186">
-        <v>23.72208052782359</v>
+        <v>23.66734936755795</v>
       </c>
       <c r="E186">
-        <v>7.417965975175849</v>
+        <v>6.528437958642157</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4726,16 +4726,16 @@
         <v>190</v>
       </c>
       <c r="B187">
-        <v>4.599091295366566</v>
+        <v>2.969029382124804</v>
       </c>
       <c r="C187">
-        <v>17.88734918695186</v>
+        <v>16.98444623752688</v>
       </c>
       <c r="D187">
-        <v>23.53819182146288</v>
+        <v>24.20445816623192</v>
       </c>
       <c r="E187">
-        <v>6.989247129974102</v>
+        <v>6.424878754930933</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4743,16 +4743,16 @@
         <v>191</v>
       </c>
       <c r="B188">
-        <v>3.852308150814886</v>
+        <v>3.066425619553873</v>
       </c>
       <c r="C188">
-        <v>17.59935287858773</v>
+        <v>17.11281169038446</v>
       </c>
       <c r="D188">
-        <v>23.7707658774887</v>
+        <v>23.81232985740665</v>
       </c>
       <c r="E188">
-        <v>6.726779393661442</v>
+        <v>6.553264448128603</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4760,16 +4760,16 @@
         <v>192</v>
       </c>
       <c r="B189">
-        <v>4.096195527635102</v>
+        <v>3.033257307105147</v>
       </c>
       <c r="C189">
-        <v>17.58931933432976</v>
+        <v>17.16413631518491</v>
       </c>
       <c r="D189">
-        <v>23.68020892311249</v>
+        <v>23.84663280551539</v>
       </c>
       <c r="E189">
-        <v>7.609056696716916</v>
+        <v>6.41988095721019</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4777,16 +4777,16 @@
         <v>193</v>
       </c>
       <c r="B190">
-        <v>3.305987395202974</v>
+        <v>3.026061465997921</v>
       </c>
       <c r="C190">
-        <v>18.31582956762627</v>
+        <v>17.05890314132932</v>
       </c>
       <c r="D190">
-        <v>23.72624268855163</v>
+        <v>23.80753172415632</v>
       </c>
       <c r="E190">
-        <v>7.37346202652701</v>
+        <v>6.555234145304121</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4794,16 +4794,16 @@
         <v>194</v>
       </c>
       <c r="B191">
-        <v>3.27743908321283</v>
+        <v>2.999609188055783</v>
       </c>
       <c r="C191">
-        <v>17.44761441863773</v>
+        <v>17.2963682948394</v>
       </c>
       <c r="D191">
-        <v>23.48121198932288</v>
+        <v>23.65209313670215</v>
       </c>
       <c r="E191">
-        <v>6.425075199812945</v>
+        <v>6.467530540622458</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4811,16 +4811,16 @@
         <v>195</v>
       </c>
       <c r="B192">
-        <v>4.142899669443487</v>
+        <v>3.064740915294444</v>
       </c>
       <c r="C192">
-        <v>18.23563707769497</v>
+        <v>17.0632238130978</v>
       </c>
       <c r="D192">
-        <v>23.64708390714748</v>
+        <v>24.50696916484654</v>
       </c>
       <c r="E192">
-        <v>6.852579238567636</v>
+        <v>6.499406769809541</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4828,16 +4828,16 @@
         <v>196</v>
       </c>
       <c r="B193">
-        <v>4.426097309413751</v>
+        <v>3.000043009187091</v>
       </c>
       <c r="C193">
-        <v>17.868049782177</v>
+        <v>17.05988079438386</v>
       </c>
       <c r="D193">
-        <v>23.48136247937474</v>
+        <v>24.29331364797977</v>
       </c>
       <c r="E193">
-        <v>7.962847883715488</v>
+        <v>6.519123154736295</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4845,16 +4845,16 @@
         <v>197</v>
       </c>
       <c r="B194">
-        <v>3.804556058356902</v>
+        <v>2.970248585840695</v>
       </c>
       <c r="C194">
-        <v>17.62168372506041</v>
+        <v>17.15395672660586</v>
       </c>
       <c r="D194">
-        <v>23.53976548027436</v>
+        <v>24.49635830185945</v>
       </c>
       <c r="E194">
-        <v>6.934621433960982</v>
+        <v>6.450128498767337</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4862,16 +4862,16 @@
         <v>198</v>
       </c>
       <c r="B195">
-        <v>3.199282450273693</v>
+        <v>2.992399890177257</v>
       </c>
       <c r="C195">
-        <v>18.0554570348204</v>
+        <v>16.99660497315445</v>
       </c>
       <c r="D195">
-        <v>23.88105833831601</v>
+        <v>24.13656398282832</v>
       </c>
       <c r="E195">
-        <v>7.566769372019865</v>
+        <v>6.464094826688402</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4879,16 +4879,16 @@
         <v>199</v>
       </c>
       <c r="B196">
-        <v>4.631148187238857</v>
+        <v>3.02829316178232</v>
       </c>
       <c r="C196">
-        <v>18.47306788580882</v>
+        <v>16.99246992394637</v>
       </c>
       <c r="D196">
-        <v>23.78072113159539</v>
+        <v>23.64821431166001</v>
       </c>
       <c r="E196">
-        <v>7.938592697023285</v>
+        <v>6.53720196838585</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4896,16 +4896,16 @@
         <v>200</v>
       </c>
       <c r="B197">
-        <v>4.409447132992703</v>
+        <v>3.02409808951754</v>
       </c>
       <c r="C197">
-        <v>17.37081824479195</v>
+        <v>16.90511825650321</v>
       </c>
       <c r="D197">
-        <v>23.90033230194053</v>
+        <v>24.64488483154648</v>
       </c>
       <c r="E197">
-        <v>7.808957872753979</v>
+        <v>6.547458445632183</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4913,16 +4913,16 @@
         <v>201</v>
       </c>
       <c r="B198">
-        <v>3.113606039364987</v>
+        <v>2.982901752509223</v>
       </c>
       <c r="C198">
-        <v>18.01500802743731</v>
+        <v>17.375809995563</v>
       </c>
       <c r="D198">
-        <v>23.54963576867264</v>
+        <v>24.95912405038902</v>
       </c>
       <c r="E198">
-        <v>7.916973015012162</v>
+        <v>6.448051188976333</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4930,16 +4930,16 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>3.3609431795908</v>
+        <v>3.033524376636499</v>
       </c>
       <c r="C199">
-        <v>17.27511188147777</v>
+        <v>17.21325988100388</v>
       </c>
       <c r="D199">
-        <v>23.89499844068041</v>
+        <v>24.91849289998936</v>
       </c>
       <c r="E199">
-        <v>7.61685190767543</v>
+        <v>6.452849003990698</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4947,16 +4947,16 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>4.047040045073597</v>
+        <v>2.964343593187589</v>
       </c>
       <c r="C200">
-        <v>17.10740218396582</v>
+        <v>17.29232883285414</v>
       </c>
       <c r="D200">
-        <v>23.85038986818605</v>
+        <v>24.40861692043659</v>
       </c>
       <c r="E200">
-        <v>6.804213228750902</v>
+        <v>6.407547768506827</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4964,16 +4964,16 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>3.495917509978445</v>
+        <v>2.980982215298124</v>
       </c>
       <c r="C201">
-        <v>16.94744935388776</v>
+        <v>16.99068395662511</v>
       </c>
       <c r="D201">
-        <v>23.89717621962914</v>
+        <v>23.67906103139176</v>
       </c>
       <c r="E201">
-        <v>7.887669896337728</v>
+        <v>6.557109038244628</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4981,16 +4981,16 @@
         <v>205</v>
       </c>
       <c r="B202">
-        <v>4.092193931458784</v>
+        <v>3.002688268232417</v>
       </c>
       <c r="C202">
-        <v>17.86401813466475</v>
+        <v>17.2363001690191</v>
       </c>
       <c r="D202">
-        <v>23.87176761956986</v>
+        <v>23.44511264921624</v>
       </c>
       <c r="E202">
-        <v>7.851780904958281</v>
+        <v>6.500216850047972</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4998,16 +4998,16 @@
         <v>206</v>
       </c>
       <c r="B203">
-        <v>4.607834006754556</v>
+        <v>3.058778682531665</v>
       </c>
       <c r="C203">
-        <v>18.42597403249749</v>
+        <v>17.03479516588762</v>
       </c>
       <c r="D203">
-        <v>23.81565034561439</v>
+        <v>23.98197801589206</v>
       </c>
       <c r="E203">
-        <v>7.947768177482553</v>
+        <v>6.491290458190476</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -5015,16 +5015,16 @@
         <v>207</v>
       </c>
       <c r="B204">
-        <v>4.106719198114006</v>
+        <v>3.068663640955298</v>
       </c>
       <c r="C204">
-        <v>17.64818924918517</v>
+        <v>17.01624948428312</v>
       </c>
       <c r="D204">
-        <v>23.79358451643965</v>
+        <v>24.85535838606533</v>
       </c>
       <c r="E204">
-        <v>7.849943339586534</v>
+        <v>6.444898812057255</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -5032,16 +5032,16 @@
         <v>208</v>
       </c>
       <c r="B205">
-        <v>3.337688578579503</v>
+        <v>2.767920442146116</v>
       </c>
       <c r="C205">
-        <v>19.92928403845589</v>
+        <v>19.33471475851258</v>
       </c>
       <c r="D205">
-        <v>33.25880108209555</v>
+        <v>33.3485110634324</v>
       </c>
       <c r="E205">
-        <v>7.323285167709029</v>
+        <v>6.311935427850064</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -5049,16 +5049,16 @@
         <v>209</v>
       </c>
       <c r="B206">
-        <v>3.436154276366449</v>
+        <v>2.816751581689377</v>
       </c>
       <c r="C206">
-        <v>20.05349659689786</v>
+        <v>19.64732097836725</v>
       </c>
       <c r="D206">
-        <v>33.60705738270167</v>
+        <v>33.34987964618818</v>
       </c>
       <c r="E206">
-        <v>7.056849486389332</v>
+        <v>6.286098871329928</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -5066,16 +5066,16 @@
         <v>210</v>
       </c>
       <c r="B207">
-        <v>3.499634823797096</v>
+        <v>2.777936635750945</v>
       </c>
       <c r="C207">
-        <v>19.89521551596869</v>
+        <v>19.25882479276966</v>
       </c>
       <c r="D207">
-        <v>33.67066904419818</v>
+        <v>33.59195655209864</v>
       </c>
       <c r="E207">
-        <v>7.044151984126541</v>
+        <v>6.240363047899472</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -5083,16 +5083,16 @@
         <v>211</v>
       </c>
       <c r="B208">
-        <v>3.219057672536892</v>
+        <v>2.800320894752905</v>
       </c>
       <c r="C208">
-        <v>20.03740575893542</v>
+        <v>19.66407865385925</v>
       </c>
       <c r="D208">
-        <v>33.29935450539281</v>
+        <v>34.5871650630487</v>
       </c>
       <c r="E208">
-        <v>6.780523182935712</v>
+        <v>6.234269133046678</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -5100,16 +5100,16 @@
         <v>212</v>
       </c>
       <c r="B209">
-        <v>3.221268518877322</v>
+        <v>2.760535473890074</v>
       </c>
       <c r="C209">
-        <v>19.9419215830504</v>
+        <v>19.62967508901093</v>
       </c>
       <c r="D209">
-        <v>33.21584511169247</v>
+        <v>33.89589307492948</v>
       </c>
       <c r="E209">
-        <v>6.709210877567638</v>
+        <v>6.312153509356938</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -5117,16 +5117,16 @@
         <v>213</v>
       </c>
       <c r="B210">
-        <v>3.778784969866681</v>
+        <v>2.769189670847244</v>
       </c>
       <c r="C210">
-        <v>20.09740180332098</v>
+        <v>19.57865199515399</v>
       </c>
       <c r="D210">
-        <v>33.31282516576623</v>
+        <v>33.59828831666977</v>
       </c>
       <c r="E210">
-        <v>6.179258813174315</v>
+        <v>6.318075353695746</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5134,16 +5134,16 @@
         <v>214</v>
       </c>
       <c r="B211">
-        <v>3.180813094182523</v>
+        <v>2.80050644830767</v>
       </c>
       <c r="C211">
-        <v>19.78249240669672</v>
+        <v>19.59423260827415</v>
       </c>
       <c r="D211">
-        <v>33.64567710529575</v>
+        <v>33.83316761723937</v>
       </c>
       <c r="E211">
-        <v>6.289599444378529</v>
+        <v>6.244539637828492</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5151,16 +5151,16 @@
         <v>215</v>
       </c>
       <c r="B212">
-        <v>3.201660250035644</v>
+        <v>2.738754188397393</v>
       </c>
       <c r="C212">
-        <v>19.54700201941396</v>
+        <v>19.60279793176761</v>
       </c>
       <c r="D212">
-        <v>33.28003000783377</v>
+        <v>33.95588072286537</v>
       </c>
       <c r="E212">
-        <v>6.757909539671068</v>
+        <v>6.188351834369555</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5168,16 +5168,16 @@
         <v>216</v>
       </c>
       <c r="B213">
-        <v>4.424591897908156</v>
+        <v>2.791829546710472</v>
       </c>
       <c r="C213">
-        <v>19.41280665515262</v>
+        <v>19.32570335590207</v>
       </c>
       <c r="D213">
-        <v>33.69117588651034</v>
+        <v>34.45515665369667</v>
       </c>
       <c r="E213">
-        <v>7.084101024371912</v>
+        <v>6.181276996521009</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5185,16 +5185,16 @@
         <v>217</v>
       </c>
       <c r="B214">
-        <v>3.396087537422151</v>
+        <v>2.799065315130321</v>
       </c>
       <c r="C214">
-        <v>20.38247259597255</v>
+        <v>19.7236889799894</v>
       </c>
       <c r="D214">
-        <v>33.49494404893014</v>
+        <v>33.86952459972377</v>
       </c>
       <c r="E214">
-        <v>7.139311743218582</v>
+        <v>6.294711156298002</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5202,16 +5202,16 @@
         <v>218</v>
       </c>
       <c r="B215">
-        <v>2.887892397679679</v>
+        <v>2.826769465685688</v>
       </c>
       <c r="C215">
-        <v>19.63280824940757</v>
+        <v>19.34122808125799</v>
       </c>
       <c r="D215">
-        <v>33.27084481800247</v>
+        <v>33.39257749896834</v>
       </c>
       <c r="E215">
-        <v>6.607859102390024</v>
+        <v>6.306411512396325</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5219,16 +5219,16 @@
         <v>219</v>
       </c>
       <c r="B216">
-        <v>3.173895450805871</v>
+        <v>2.733789852796647</v>
       </c>
       <c r="C216">
-        <v>19.32290260625743</v>
+        <v>19.3132502278174</v>
       </c>
       <c r="D216">
-        <v>33.67495920070184</v>
+        <v>33.20827608800774</v>
       </c>
       <c r="E216">
-        <v>6.66660656038031</v>
+        <v>6.294284959552774</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5236,16 +5236,16 @@
         <v>220</v>
       </c>
       <c r="B217">
-        <v>4.246564646397712</v>
+        <v>2.806169766312221</v>
       </c>
       <c r="C217">
-        <v>19.7395539758359</v>
+        <v>19.52725741652105</v>
       </c>
       <c r="D217">
-        <v>33.33084574575149</v>
+        <v>33.7041161812825</v>
       </c>
       <c r="E217">
-        <v>7.565608851232746</v>
+        <v>6.313279666873364</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -5253,16 +5253,16 @@
         <v>221</v>
       </c>
       <c r="B218">
-        <v>4.173439787090679</v>
+        <v>2.734807742866113</v>
       </c>
       <c r="C218">
-        <v>19.25423293908741</v>
+        <v>19.22235465286732</v>
       </c>
       <c r="D218">
-        <v>33.66143816673923</v>
+        <v>34.13404918375792</v>
       </c>
       <c r="E218">
-        <v>7.16979911679373</v>
+        <v>6.290609743854274</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5270,16 +5270,16 @@
         <v>222</v>
       </c>
       <c r="B219">
-        <v>4.093435918980199</v>
+        <v>2.833264937691609</v>
       </c>
       <c r="C219">
-        <v>19.42813541509838</v>
+        <v>19.49073327621786</v>
       </c>
       <c r="D219">
-        <v>33.32191556337587</v>
+        <v>34.58248584066833</v>
       </c>
       <c r="E219">
-        <v>7.186690992093028</v>
+        <v>6.161247097137043</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -5287,16 +5287,16 @@
         <v>223</v>
       </c>
       <c r="B220">
-        <v>3.635938623098726</v>
+        <v>2.786166148168895</v>
       </c>
       <c r="C220">
-        <v>19.59277313271253</v>
+        <v>19.2851637557088</v>
       </c>
       <c r="D220">
-        <v>33.58174356846813</v>
+        <v>34.14105835770816</v>
       </c>
       <c r="E220">
-        <v>7.612100865210415</v>
+        <v>6.176002075399221</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5304,16 +5304,16 @@
         <v>224</v>
       </c>
       <c r="B221">
-        <v>3.906446960601051</v>
+        <v>2.735064044225255</v>
       </c>
       <c r="C221">
-        <v>20.19750754193428</v>
+        <v>19.28439116650615</v>
       </c>
       <c r="D221">
-        <v>33.36903985959599</v>
+        <v>34.6710374261913</v>
       </c>
       <c r="E221">
-        <v>6.628939990253649</v>
+        <v>6.23575545908397</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5321,16 +5321,16 @@
         <v>225</v>
       </c>
       <c r="B222">
-        <v>3.780495521386866</v>
+        <v>2.758086117831253</v>
       </c>
       <c r="C222">
-        <v>19.63849058988292</v>
+        <v>19.72929109185958</v>
       </c>
       <c r="D222">
-        <v>33.45228376346248</v>
+        <v>33.62503572983726</v>
       </c>
       <c r="E222">
-        <v>7.454932963209798</v>
+        <v>6.197094198410421</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5338,16 +5338,16 @@
         <v>226</v>
       </c>
       <c r="B223">
-        <v>3.512089368456476</v>
+        <v>2.764457662343163</v>
       </c>
       <c r="C223">
-        <v>20.77115155870317</v>
+        <v>19.29008627224808</v>
       </c>
       <c r="D223">
-        <v>33.43658445361741</v>
+        <v>34.74617695094108</v>
       </c>
       <c r="E223">
-        <v>7.404066797242993</v>
+        <v>6.240879932486541</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5355,16 +5355,16 @@
         <v>227</v>
       </c>
       <c r="B224">
-        <v>3.075617878410116</v>
+        <v>2.747057073728562</v>
       </c>
       <c r="C224">
-        <v>19.28236019436685</v>
+        <v>19.34120603307455</v>
       </c>
       <c r="D224">
-        <v>33.26883608025538</v>
+        <v>34.60303253455665</v>
       </c>
       <c r="E224">
-        <v>7.577676211040925</v>
+        <v>6.310149432560141</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5372,16 +5372,16 @@
         <v>228</v>
       </c>
       <c r="B225">
-        <v>4.11742453463553</v>
+        <v>2.764087004864137</v>
       </c>
       <c r="C225">
-        <v>19.60057238950103</v>
+        <v>19.66588277716463</v>
       </c>
       <c r="D225">
-        <v>33.46041465076914</v>
+        <v>33.61389855450005</v>
       </c>
       <c r="E225">
-        <v>7.033309987191201</v>
+        <v>6.258478055449643</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5389,16 +5389,16 @@
         <v>229</v>
       </c>
       <c r="B226">
-        <v>2.847732269498557</v>
+        <v>2.801050880968546</v>
       </c>
       <c r="C226">
-        <v>20.22433459543003</v>
+        <v>19.71153235630521</v>
       </c>
       <c r="D226">
-        <v>33.65528623278751</v>
+        <v>33.51516683999579</v>
       </c>
       <c r="E226">
-        <v>7.543127201961342</v>
+        <v>6.243071805815148</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5406,16 +5406,16 @@
         <v>230</v>
       </c>
       <c r="B227">
-        <v>3.900796608461039</v>
+        <v>2.783284398592375</v>
       </c>
       <c r="C227">
-        <v>20.60229557984994</v>
+        <v>19.35733949532871</v>
       </c>
       <c r="D227">
-        <v>33.34039357659276</v>
+        <v>34.1375996222481</v>
       </c>
       <c r="E227">
-        <v>7.526512879202732</v>
+        <v>6.191644211141653</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5423,16 +5423,16 @@
         <v>231</v>
       </c>
       <c r="B228">
-        <v>2.763546247806913</v>
+        <v>2.757448381001699</v>
       </c>
       <c r="C228">
-        <v>20.01525551394823</v>
+        <v>19.58697053851346</v>
       </c>
       <c r="D228">
-        <v>33.36222483876203</v>
+        <v>33.62467758580541</v>
       </c>
       <c r="E228">
-        <v>7.111985545831614</v>
+        <v>6.261344235960722</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5440,16 +5440,16 @@
         <v>232</v>
       </c>
       <c r="B229">
-        <v>4.170024634329817</v>
+        <v>2.76633842849896</v>
       </c>
       <c r="C229">
-        <v>20.33908165741813</v>
+        <v>19.54173247987051</v>
       </c>
       <c r="D229">
-        <v>33.42365831760505</v>
+        <v>33.33864776053109</v>
       </c>
       <c r="E229">
-        <v>6.661499781133415</v>
+        <v>6.308749185821439</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5457,16 +5457,16 @@
         <v>233</v>
       </c>
       <c r="B230">
-        <v>4.362934511568275</v>
+        <v>2.834903908578178</v>
       </c>
       <c r="C230">
-        <v>20.12528413546227</v>
+        <v>19.50443005345054</v>
       </c>
       <c r="D230">
-        <v>33.32762801856892</v>
+        <v>33.51136721903897</v>
       </c>
       <c r="E230">
-        <v>7.383946083050779</v>
+        <v>6.248846184306217</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5474,16 +5474,16 @@
         <v>234</v>
       </c>
       <c r="B231">
-        <v>3.422837456809703</v>
+        <v>2.768321159926842</v>
       </c>
       <c r="C231">
-        <v>19.25503593052468</v>
+        <v>19.47334656046119</v>
       </c>
       <c r="D231">
-        <v>33.31374767729914</v>
+        <v>34.25356489521786</v>
       </c>
       <c r="E231">
-        <v>6.298778049225688</v>
+        <v>6.150887946812739</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5491,16 +5491,16 @@
         <v>235</v>
       </c>
       <c r="B232">
-        <v>3.582004951010748</v>
+        <v>2.825871792386764</v>
       </c>
       <c r="C232">
-        <v>20.33351442808043</v>
+        <v>19.5218159611132</v>
       </c>
       <c r="D232">
-        <v>33.33608064870441</v>
+        <v>33.82491944561904</v>
       </c>
       <c r="E232">
-        <v>6.736319041332564</v>
+        <v>6.264031364389797</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5508,16 +5508,16 @@
         <v>236</v>
       </c>
       <c r="B233">
-        <v>3.042940179702065</v>
+        <v>2.83000011013717</v>
       </c>
       <c r="C233">
-        <v>20.49553589694575</v>
+        <v>19.2627065333196</v>
       </c>
       <c r="D233">
-        <v>33.51974150691186</v>
+        <v>34.15693371373519</v>
       </c>
       <c r="E233">
-        <v>6.351591599322208</v>
+        <v>6.207879718482465</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -5525,16 +5525,16 @@
         <v>237</v>
       </c>
       <c r="B234">
-        <v>4.270364227118048</v>
+        <v>2.74963935935017</v>
       </c>
       <c r="C234">
-        <v>19.94259414623797</v>
+        <v>19.37093143585544</v>
       </c>
       <c r="D234">
-        <v>33.49564237542841</v>
+        <v>33.39621262945062</v>
       </c>
       <c r="E234">
-        <v>6.164799117768528</v>
+        <v>6.304710476115082</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -5542,16 +5542,16 @@
         <v>238</v>
       </c>
       <c r="B235">
-        <v>2.876206083452212</v>
+        <v>2.829624761470713</v>
       </c>
       <c r="C235">
-        <v>19.91494955014065</v>
+        <v>19.3599523515763</v>
       </c>
       <c r="D235">
-        <v>33.25663132645017</v>
+        <v>33.55583045999574</v>
       </c>
       <c r="E235">
-        <v>6.348608171380407</v>
+        <v>6.168017601019143</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -5559,16 +5559,16 @@
         <v>239</v>
       </c>
       <c r="B236">
-        <v>3.316694656127055</v>
+        <v>2.818024601595765</v>
       </c>
       <c r="C236">
-        <v>20.32467693031093</v>
+        <v>19.67810631265868</v>
       </c>
       <c r="D236">
-        <v>33.42878709726868</v>
+        <v>34.44655138340332</v>
       </c>
       <c r="E236">
-        <v>7.095416714560822</v>
+        <v>6.19893565829564</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -5576,16 +5576,16 @@
         <v>240</v>
       </c>
       <c r="B237">
-        <v>4.451766727900886</v>
+        <v>2.814986365279445</v>
       </c>
       <c r="C237">
-        <v>20.45037360670728</v>
+        <v>19.70841280752802</v>
       </c>
       <c r="D237">
-        <v>33.22365246901393</v>
+        <v>33.71082852001118</v>
       </c>
       <c r="E237">
-        <v>7.246538503004209</v>
+        <v>6.244667350470576</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -5593,16 +5593,16 @@
         <v>241</v>
       </c>
       <c r="B238">
-        <v>3.289379402928978</v>
+        <v>2.832710741088532</v>
       </c>
       <c r="C238">
-        <v>19.893971689259</v>
+        <v>19.25008430899328</v>
       </c>
       <c r="D238">
-        <v>33.32353609161041</v>
+        <v>33.49090580571974</v>
       </c>
       <c r="E238">
-        <v>6.56904433863186</v>
+        <v>6.193790454360813</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -5610,16 +5610,16 @@
         <v>242</v>
       </c>
       <c r="B239">
-        <v>3.044825189304054</v>
+        <v>2.818896813755473</v>
       </c>
       <c r="C239">
-        <v>20.35287358888349</v>
+        <v>19.46103792499414</v>
       </c>
       <c r="D239">
-        <v>33.38342302005221</v>
+        <v>34.23841408175267</v>
       </c>
       <c r="E239">
-        <v>6.323897660593221</v>
+        <v>6.272909668591303</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -5627,16 +5627,16 @@
         <v>243</v>
       </c>
       <c r="B240">
-        <v>3.382362094502832</v>
+        <v>2.757059942428895</v>
       </c>
       <c r="C240">
-        <v>19.45294486557911</v>
+        <v>19.45132194230827</v>
       </c>
       <c r="D240">
-        <v>33.43375464326535</v>
+        <v>33.54042810989363</v>
       </c>
       <c r="E240">
-        <v>6.568248043197649</v>
+        <v>6.315313153748251</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -5644,16 +5644,16 @@
         <v>244</v>
       </c>
       <c r="B241">
-        <v>4.161824239485101</v>
+        <v>2.794327337576248</v>
       </c>
       <c r="C241">
-        <v>19.80946356189641</v>
+        <v>19.37605892126496</v>
       </c>
       <c r="D241">
-        <v>33.29322757383349</v>
+        <v>34.65371600817615</v>
       </c>
       <c r="E241">
-        <v>6.638359796395527</v>
+        <v>6.150922226009256</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -5661,16 +5661,16 @@
         <v>245</v>
       </c>
       <c r="B242">
-        <v>4.080502541754981</v>
+        <v>2.788491458411652</v>
       </c>
       <c r="C242">
-        <v>20.27012937697372</v>
+        <v>19.32941058939876</v>
       </c>
       <c r="D242">
-        <v>33.52317544845175</v>
+        <v>33.63589814316173</v>
       </c>
       <c r="E242">
-        <v>7.38282291985432</v>
+        <v>6.229929020188486</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -5678,16 +5678,16 @@
         <v>246</v>
       </c>
       <c r="B243">
-        <v>2.880578562661486</v>
+        <v>2.738586388979277</v>
       </c>
       <c r="C243">
-        <v>20.6929468141939</v>
+        <v>19.4913777797529</v>
       </c>
       <c r="D243">
-        <v>33.27186947620014</v>
+        <v>34.09601629381449</v>
       </c>
       <c r="E243">
-        <v>7.584290349883172</v>
+        <v>6.201874122403181</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -5695,16 +5695,16 @@
         <v>247</v>
       </c>
       <c r="B244">
-        <v>4.064136562594404</v>
+        <v>2.809226061355834</v>
       </c>
       <c r="C244">
-        <v>20.36160906894821</v>
+        <v>19.5541120908353</v>
       </c>
       <c r="D244">
-        <v>33.42580963573901</v>
+        <v>34.47168781849991</v>
       </c>
       <c r="E244">
-        <v>6.863033766677225</v>
+        <v>6.302286864091365</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -5712,16 +5712,16 @@
         <v>248</v>
       </c>
       <c r="B245">
-        <v>3.955614150317899</v>
+        <v>2.757395944595039</v>
       </c>
       <c r="C245">
-        <v>19.61061797146595</v>
+        <v>19.37375888737532</v>
       </c>
       <c r="D245">
-        <v>33.65751424433827</v>
+        <v>34.60386424892798</v>
       </c>
       <c r="E245">
-        <v>6.547986145796653</v>
+        <v>6.318175275280508</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -5729,16 +5729,16 @@
         <v>249</v>
       </c>
       <c r="B246">
-        <v>4.366175530969887</v>
+        <v>2.788143870490597</v>
       </c>
       <c r="C246">
-        <v>20.33375908900756</v>
+        <v>19.38818941916737</v>
       </c>
       <c r="D246">
-        <v>33.27025540012726</v>
+        <v>33.60519786820656</v>
       </c>
       <c r="E246">
-        <v>7.605162094209088</v>
+        <v>6.189920628643192</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -5746,16 +5746,16 @@
         <v>250</v>
       </c>
       <c r="B247">
-        <v>3.346600943401787</v>
+        <v>2.823525225432736</v>
       </c>
       <c r="C247">
-        <v>20.76708720789549</v>
+        <v>19.62542859423975</v>
       </c>
       <c r="D247">
-        <v>33.24993238767695</v>
+        <v>34.19845897371096</v>
       </c>
       <c r="E247">
-        <v>6.88565582741332</v>
+        <v>6.311058075877798</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5763,16 +5763,16 @@
         <v>251</v>
       </c>
       <c r="B248">
-        <v>4.108082247814642</v>
+        <v>2.797177142131294</v>
       </c>
       <c r="C248">
-        <v>19.4483543036773</v>
+        <v>19.24264786578927</v>
       </c>
       <c r="D248">
-        <v>33.60722564121792</v>
+        <v>33.24999593683555</v>
       </c>
       <c r="E248">
-        <v>7.194915099877006</v>
+        <v>6.270583084722502</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5780,16 +5780,16 @@
         <v>252</v>
       </c>
       <c r="B249">
-        <v>4.089861528086401</v>
+        <v>2.730524151466329</v>
       </c>
       <c r="C249">
-        <v>20.63642507117568</v>
+        <v>19.71242204997634</v>
       </c>
       <c r="D249">
-        <v>33.25658482038623</v>
+        <v>33.47296801845734</v>
       </c>
       <c r="E249">
-        <v>7.506183275738715</v>
+        <v>6.178169424696407</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5797,16 +5797,16 @@
         <v>253</v>
       </c>
       <c r="B250">
-        <v>2.959191513645527</v>
+        <v>2.743844888753971</v>
       </c>
       <c r="C250">
-        <v>19.30496340298251</v>
+        <v>19.31964046840986</v>
       </c>
       <c r="D250">
-        <v>33.61479132861515</v>
+        <v>34.57577723078891</v>
       </c>
       <c r="E250">
-        <v>6.373594256524355</v>
+        <v>6.182156771804292</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5814,16 +5814,16 @@
         <v>254</v>
       </c>
       <c r="B251">
-        <v>3.449729039648354</v>
+        <v>2.78868650984401</v>
       </c>
       <c r="C251">
-        <v>20.43375206780894</v>
+        <v>19.23158237961992</v>
       </c>
       <c r="D251">
-        <v>33.63974899474408</v>
+        <v>34.10431098839298</v>
       </c>
       <c r="E251">
-        <v>6.428458832872066</v>
+        <v>6.234130428058947</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5831,16 +5831,16 @@
         <v>255</v>
       </c>
       <c r="B252">
-        <v>4.50038698029272</v>
+        <v>2.802773160693895</v>
       </c>
       <c r="C252">
-        <v>19.68138847156246</v>
+        <v>19.59134632251802</v>
       </c>
       <c r="D252">
-        <v>33.27866697362224</v>
+        <v>34.35331443865523</v>
       </c>
       <c r="E252">
-        <v>7.250401048550675</v>
+        <v>6.187040379715157</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5848,16 +5848,16 @@
         <v>256</v>
       </c>
       <c r="B253">
-        <v>4.040765692165442</v>
+        <v>2.834010020263847</v>
       </c>
       <c r="C253">
-        <v>20.17015461303878</v>
+        <v>19.65869184373175</v>
       </c>
       <c r="D253">
-        <v>33.40949115530078</v>
+        <v>33.44745050842975</v>
       </c>
       <c r="E253">
-        <v>6.770890587904582</v>
+        <v>6.320148018498581</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5865,16 +5865,16 @@
         <v>257</v>
       </c>
       <c r="B254">
-        <v>2.848963919625826</v>
+        <v>2.771738011076077</v>
       </c>
       <c r="C254">
-        <v>20.51503823935471</v>
+        <v>19.68967626406468</v>
       </c>
       <c r="D254">
-        <v>33.28883456803461</v>
+        <v>33.62776332856292</v>
       </c>
       <c r="E254">
-        <v>6.703524808865564</v>
+        <v>6.242570340462174</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5882,16 +5882,16 @@
         <v>258</v>
       </c>
       <c r="B255">
-        <v>4.442749301315725</v>
+        <v>2.831034312142129</v>
       </c>
       <c r="C255">
-        <v>20.21988082833944</v>
+        <v>19.60424397745054</v>
       </c>
       <c r="D255">
-        <v>33.39903078913244</v>
+        <v>34.68559551194205</v>
       </c>
       <c r="E255">
-        <v>6.184203235535477</v>
+        <v>6.159761280884134</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5899,16 +5899,16 @@
         <v>259</v>
       </c>
       <c r="B256">
-        <v>4.280295238483175</v>
+        <v>2.807053098289017</v>
       </c>
       <c r="C256">
-        <v>20.75838260044094</v>
+        <v>19.62010073396468</v>
       </c>
       <c r="D256">
-        <v>33.69413728482201</v>
+        <v>34.59910440973064</v>
       </c>
       <c r="E256">
-        <v>7.469321780620732</v>
+        <v>6.31768680549168</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5916,16 +5916,16 @@
         <v>260</v>
       </c>
       <c r="B257">
-        <v>4.44157015052621</v>
+        <v>2.807155274678549</v>
       </c>
       <c r="C257">
-        <v>20.29785612357837</v>
+        <v>19.53683433216053</v>
       </c>
       <c r="D257">
-        <v>33.61133822320733</v>
+        <v>34.4294698576881</v>
       </c>
       <c r="E257">
-        <v>7.564685765251701</v>
+        <v>6.286095933790746</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5933,16 +5933,16 @@
         <v>261</v>
       </c>
       <c r="B258">
-        <v>3.244722256108877</v>
+        <v>2.798546759925081</v>
       </c>
       <c r="C258">
-        <v>19.90815572425388</v>
+        <v>19.695430341766</v>
       </c>
       <c r="D258">
-        <v>33.28209422499516</v>
+        <v>33.42209979631923</v>
       </c>
       <c r="E258">
-        <v>6.813174625524106</v>
+        <v>6.177378005744695</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5950,16 +5950,16 @@
         <v>262</v>
       </c>
       <c r="B259">
-        <v>3.478131434975172</v>
+        <v>2.825715161416488</v>
       </c>
       <c r="C259">
-        <v>19.62016423836017</v>
+        <v>19.57175856166548</v>
       </c>
       <c r="D259">
-        <v>33.21628664076419</v>
+        <v>34.29273130291747</v>
       </c>
       <c r="E259">
-        <v>6.765134777004892</v>
+        <v>6.193016399758267</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5967,16 +5967,16 @@
         <v>263</v>
       </c>
       <c r="B260">
-        <v>4.282480749646044</v>
+        <v>2.767702413861174</v>
       </c>
       <c r="C260">
-        <v>19.31450539721516</v>
+        <v>19.42807577192249</v>
       </c>
       <c r="D260">
-        <v>33.69612170543856</v>
+        <v>34.48808383749364</v>
       </c>
       <c r="E260">
-        <v>6.601756148113176</v>
+        <v>6.261549386575347</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5984,16 +5984,16 @@
         <v>264</v>
       </c>
       <c r="B261">
-        <v>4.393033159635934</v>
+        <v>2.721644146169699</v>
       </c>
       <c r="C261">
-        <v>20.54252581401158</v>
+        <v>19.43884715628514</v>
       </c>
       <c r="D261">
-        <v>33.3084667660281</v>
+        <v>34.66969894073537</v>
       </c>
       <c r="E261">
-        <v>7.524899295856067</v>
+        <v>6.238539000996599</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -6001,16 +6001,16 @@
         <v>265</v>
       </c>
       <c r="B262">
-        <v>3.476183542946905</v>
+        <v>2.741056584887917</v>
       </c>
       <c r="C262">
-        <v>19.91500576050328</v>
+        <v>19.24891399241169</v>
       </c>
       <c r="D262">
-        <v>33.45404840004295</v>
+        <v>33.74483377232512</v>
       </c>
       <c r="E262">
-        <v>6.464149929001907</v>
+        <v>6.26704086218385</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -6018,16 +6018,16 @@
         <v>266</v>
       </c>
       <c r="B263">
-        <v>3.517305372522672</v>
+        <v>2.784772483210059</v>
       </c>
       <c r="C263">
-        <v>20.4714065665953</v>
+        <v>19.25630712360181</v>
       </c>
       <c r="D263">
-        <v>33.37196769670171</v>
+        <v>34.17103188258132</v>
       </c>
       <c r="E263">
-        <v>6.699539981950738</v>
+        <v>6.212202787541154</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -6035,16 +6035,16 @@
         <v>267</v>
       </c>
       <c r="B264">
-        <v>3.758228298756349</v>
+        <v>2.805858165950183</v>
       </c>
       <c r="C264">
-        <v>19.63082024765015</v>
+        <v>19.64185074726021</v>
       </c>
       <c r="D264">
-        <v>33.3067574012292</v>
+        <v>33.75226839521888</v>
       </c>
       <c r="E264">
-        <v>7.195491020670101</v>
+        <v>6.216780170902701</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -6052,16 +6052,16 @@
         <v>268</v>
       </c>
       <c r="B265">
-        <v>4.204285147047536</v>
+        <v>2.776154327955486</v>
       </c>
       <c r="C265">
-        <v>19.51906895463944</v>
+        <v>19.55313116495659</v>
       </c>
       <c r="D265">
-        <v>33.35799509997452</v>
+        <v>34.45878535959046</v>
       </c>
       <c r="E265">
-        <v>6.607074723710265</v>
+        <v>6.207941809019366</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -6069,16 +6069,16 @@
         <v>269</v>
       </c>
       <c r="B266">
-        <v>3.70932084302511</v>
+        <v>2.767545172637568</v>
       </c>
       <c r="C266">
-        <v>19.38425144376097</v>
+        <v>19.62200093584725</v>
       </c>
       <c r="D266">
-        <v>33.26399213865013</v>
+        <v>33.87957823474081</v>
       </c>
       <c r="E266">
-        <v>6.5409413884406</v>
+        <v>6.206509568898454</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -6086,16 +6086,16 @@
         <v>270</v>
       </c>
       <c r="B267">
-        <v>3.060184903923155</v>
+        <v>2.743889264864783</v>
       </c>
       <c r="C267">
-        <v>19.79633386681543</v>
+        <v>19.46339439852136</v>
       </c>
       <c r="D267">
-        <v>33.44002304235682</v>
+        <v>34.49895391708201</v>
       </c>
       <c r="E267">
-        <v>7.64804832056056</v>
+        <v>6.182888800808732</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -6103,16 +6103,16 @@
         <v>271</v>
       </c>
       <c r="B268">
-        <v>5.542733626737111</v>
+        <v>5.118097183184503</v>
       </c>
       <c r="C268">
-        <v>18.6969773478773</v>
+        <v>18.5240439591785</v>
       </c>
       <c r="D268">
-        <v>28.25299802560883</v>
+        <v>28.35385544841649</v>
       </c>
       <c r="E268">
-        <v>6.600047451939351</v>
+        <v>6.545635395003085</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -6120,16 +6120,16 @@
         <v>272</v>
       </c>
       <c r="B269">
-        <v>5.506215423821371</v>
+        <v>5.175466669928032</v>
       </c>
       <c r="C269">
-        <v>19.11453372807458</v>
+        <v>18.14689953637615</v>
       </c>
       <c r="D269">
-        <v>28.21176780722006</v>
+        <v>28.50363916950436</v>
       </c>
       <c r="E269">
-        <v>7.711359034986856</v>
+        <v>6.615471277484571</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -6137,16 +6137,16 @@
         <v>273</v>
       </c>
       <c r="B270">
-        <v>5.168802306023256</v>
+        <v>5.159958922288216</v>
       </c>
       <c r="C270">
-        <v>19.38308648286001</v>
+        <v>18.39059328819787</v>
       </c>
       <c r="D270">
-        <v>28.38299011938273</v>
+        <v>29.37817196636019</v>
       </c>
       <c r="E270">
-        <v>6.975115472138492</v>
+        <v>6.692256173598595</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -6154,16 +6154,16 @@
         <v>274</v>
       </c>
       <c r="B271">
-        <v>6.495808609785612</v>
+        <v>5.125938420763119</v>
       </c>
       <c r="C271">
-        <v>18.23869155028161</v>
+        <v>18.56386718679302</v>
       </c>
       <c r="D271">
-        <v>28.3380045466093</v>
+        <v>28.66255239685458</v>
       </c>
       <c r="E271">
-        <v>7.856079746725657</v>
+        <v>6.655217838197498</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -6171,16 +6171,16 @@
         <v>275</v>
       </c>
       <c r="B272">
-        <v>6.88292547465858</v>
+        <v>5.197946177828509</v>
       </c>
       <c r="C272">
-        <v>19.49346682560889</v>
+        <v>18.33489820149924</v>
       </c>
       <c r="D272">
-        <v>28.29186828851993</v>
+        <v>28.38446316487142</v>
       </c>
       <c r="E272">
-        <v>6.622768253151981</v>
+        <v>6.62044784745034</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -6188,16 +6188,16 @@
         <v>276</v>
       </c>
       <c r="B273">
-        <v>6.095871239329411</v>
+        <v>5.111767925817123</v>
       </c>
       <c r="C273">
-        <v>18.96003154895832</v>
+        <v>18.24585479646271</v>
       </c>
       <c r="D273">
-        <v>28.18540463104845</v>
+        <v>28.32192819181295</v>
       </c>
       <c r="E273">
-        <v>7.040603375261656</v>
+        <v>6.657660928526893</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -6205,16 +6205,16 @@
         <v>277</v>
       </c>
       <c r="B274">
-        <v>6.221443656747103</v>
+        <v>5.105494307073592</v>
       </c>
       <c r="C274">
-        <v>19.10781220995311</v>
+        <v>18.35029443643448</v>
       </c>
       <c r="D274">
-        <v>28.28390702596926</v>
+        <v>28.98407636222577</v>
       </c>
       <c r="E274">
-        <v>7.632509264893393</v>
+        <v>6.652847157430522</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -6222,16 +6222,16 @@
         <v>278</v>
       </c>
       <c r="B275">
-        <v>6.279828285198037</v>
+        <v>5.173930026895889</v>
       </c>
       <c r="C275">
-        <v>18.40058378070379</v>
+        <v>18.17438631969649</v>
       </c>
       <c r="D275">
-        <v>28.53653613493674</v>
+        <v>29.50819559641369</v>
       </c>
       <c r="E275">
-        <v>7.94025394701193</v>
+        <v>6.699263715852717</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -6239,16 +6239,16 @@
         <v>279</v>
       </c>
       <c r="B276">
-        <v>6.161043347384921</v>
+        <v>5.125833235644863</v>
       </c>
       <c r="C276">
-        <v>19.47270183767468</v>
+        <v>18.11659249276796</v>
       </c>
       <c r="D276">
-        <v>28.31753917283623</v>
+        <v>28.23699119243307</v>
       </c>
       <c r="E276">
-        <v>7.846682729282234</v>
+        <v>6.670837996728535</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -6256,16 +6256,16 @@
         <v>280</v>
       </c>
       <c r="B277">
-        <v>5.578676763752158</v>
+        <v>5.172873190678119</v>
       </c>
       <c r="C277">
-        <v>19.46496781806241</v>
+        <v>18.17280772677843</v>
       </c>
       <c r="D277">
-        <v>28.3267724621984</v>
+        <v>29.35137029165429</v>
       </c>
       <c r="E277">
-        <v>7.409134439556762</v>
+        <v>6.673516307651981</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -6273,16 +6273,16 @@
         <v>281</v>
       </c>
       <c r="B278">
-        <v>5.83376598933293</v>
+        <v>5.137831160383762</v>
       </c>
       <c r="C278">
-        <v>18.2478095178372</v>
+        <v>18.15194439187254</v>
       </c>
       <c r="D278">
-        <v>28.38145930151274</v>
+        <v>29.35490084183427</v>
       </c>
       <c r="E278">
-        <v>7.496577867181589</v>
+        <v>6.605628198761737</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -6290,16 +6290,16 @@
         <v>282</v>
       </c>
       <c r="B279">
-        <v>6.578102804122016</v>
+        <v>5.200331151557211</v>
       </c>
       <c r="C279">
-        <v>18.57275867793783</v>
+        <v>18.18506321266295</v>
       </c>
       <c r="D279">
-        <v>28.6056040481377</v>
+        <v>29.53616863280163</v>
       </c>
       <c r="E279">
-        <v>8.073274782977776</v>
+        <v>6.69800518374339</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6307,16 +6307,16 @@
         <v>283</v>
       </c>
       <c r="B280">
-        <v>6.231106856678532</v>
+        <v>5.137028410447801</v>
       </c>
       <c r="C280">
-        <v>19.68656560922348</v>
+        <v>18.14730968249964</v>
       </c>
       <c r="D280">
-        <v>28.38193156236217</v>
+        <v>28.94511923510504</v>
       </c>
       <c r="E280">
-        <v>7.959126916253993</v>
+        <v>6.625497831454464</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -6324,16 +6324,16 @@
         <v>284</v>
       </c>
       <c r="B281">
-        <v>6.825575083098437</v>
+        <v>5.205255022536814</v>
       </c>
       <c r="C281">
-        <v>18.75886426317039</v>
+        <v>18.12733575232416</v>
       </c>
       <c r="D281">
-        <v>28.29548796716182</v>
+        <v>29.27113057512107</v>
       </c>
       <c r="E281">
-        <v>7.073514142754292</v>
+        <v>6.544941423384996</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -6341,16 +6341,16 @@
         <v>285</v>
       </c>
       <c r="B282">
-        <v>5.132671324690843</v>
+        <v>5.118377080047813</v>
       </c>
       <c r="C282">
-        <v>18.10440229310876</v>
+        <v>18.10108500427147</v>
       </c>
       <c r="D282">
-        <v>28.34179103742969</v>
+        <v>28.60928548691305</v>
       </c>
       <c r="E282">
-        <v>6.680755297325326</v>
+        <v>6.58332220426845</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -6358,16 +6358,16 @@
         <v>286</v>
       </c>
       <c r="B283">
-        <v>5.159228426349548</v>
+        <v>5.176085222317451</v>
       </c>
       <c r="C283">
-        <v>18.75655635451303</v>
+        <v>18.17332449016209</v>
       </c>
       <c r="D283">
-        <v>28.36298248235084</v>
+        <v>28.76319076215717</v>
       </c>
       <c r="E283">
-        <v>7.860856884156362</v>
+        <v>6.686450517638166</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -6375,16 +6375,16 @@
         <v>287</v>
       </c>
       <c r="B284">
-        <v>5.516410409665103</v>
+        <v>5.176485863670067</v>
       </c>
       <c r="C284">
-        <v>19.02531559963077</v>
+        <v>18.2923251109939</v>
       </c>
       <c r="D284">
-        <v>28.49167090587873</v>
+        <v>28.23165573991877</v>
       </c>
       <c r="E284">
-        <v>6.996490692719737</v>
+        <v>6.608709095528394</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -6392,16 +6392,16 @@
         <v>288</v>
       </c>
       <c r="B285">
-        <v>6.385803709790486</v>
+        <v>5.119830869819822</v>
       </c>
       <c r="C285">
-        <v>19.62651558961253</v>
+        <v>18.15738558406368</v>
       </c>
       <c r="D285">
-        <v>28.57620540800451</v>
+        <v>28.4183689303754</v>
       </c>
       <c r="E285">
-        <v>7.253308730196943</v>
+        <v>6.625800163009423</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -6409,16 +6409,16 @@
         <v>289</v>
       </c>
       <c r="B286">
-        <v>6.239845472019704</v>
+        <v>5.1833660968916</v>
       </c>
       <c r="C286">
-        <v>18.3063436228856</v>
+        <v>18.34807206695228</v>
       </c>
       <c r="D286">
-        <v>28.43130216311092</v>
+        <v>29.63977356189682</v>
       </c>
       <c r="E286">
-        <v>6.666730492010361</v>
+        <v>6.64716565616118</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6426,16 +6426,16 @@
         <v>290</v>
       </c>
       <c r="B287">
-        <v>6.886642741482447</v>
+        <v>5.177313159877318</v>
       </c>
       <c r="C287">
-        <v>19.16150522895978</v>
+        <v>18.29333703360503</v>
       </c>
       <c r="D287">
-        <v>28.48882624082365</v>
+        <v>29.70402428714718</v>
       </c>
       <c r="E287">
-        <v>6.720953846319277</v>
+        <v>6.680879816478243</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -6443,16 +6443,16 @@
         <v>291</v>
       </c>
       <c r="B288">
-        <v>5.246097677759913</v>
+        <v>5.153006098527451</v>
       </c>
       <c r="C288">
-        <v>19.0836599099468</v>
+        <v>18.10329705217716</v>
       </c>
       <c r="D288">
-        <v>28.27932072859683</v>
+        <v>28.58632127006301</v>
       </c>
       <c r="E288">
-        <v>6.954790830488675</v>
+        <v>6.576925954076552</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -6460,16 +6460,16 @@
         <v>292</v>
       </c>
       <c r="B289">
-        <v>5.286295519097306</v>
+        <v>5.103654713774273</v>
       </c>
       <c r="C289">
-        <v>18.39926571971086</v>
+        <v>18.57016582936687</v>
       </c>
       <c r="D289">
-        <v>28.53637355434516</v>
+        <v>28.73939677468788</v>
       </c>
       <c r="E289">
-        <v>6.921137566433955</v>
+        <v>6.561257020270658</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -6477,16 +6477,16 @@
         <v>293</v>
       </c>
       <c r="B290">
-        <v>6.185805451046434</v>
+        <v>5.185524235628272</v>
       </c>
       <c r="C290">
-        <v>18.85888006759876</v>
+        <v>18.17961643923255</v>
       </c>
       <c r="D290">
-        <v>28.45986186808448</v>
+        <v>28.88077019099327</v>
       </c>
       <c r="E290">
-        <v>7.557110459589552</v>
+        <v>6.564292834788704</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -6494,16 +6494,16 @@
         <v>294</v>
       </c>
       <c r="B291">
-        <v>6.037526682332536</v>
+        <v>5.211052750354943</v>
       </c>
       <c r="C291">
-        <v>18.45650368826678</v>
+        <v>18.14962567582519</v>
       </c>
       <c r="D291">
-        <v>28.64096571639549</v>
+        <v>29.23210777037161</v>
       </c>
       <c r="E291">
-        <v>7.044907211711759</v>
+        <v>6.688687353546891</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -6511,16 +6511,16 @@
         <v>295</v>
       </c>
       <c r="B292">
-        <v>6.316784140600359</v>
+        <v>5.177118392560573</v>
       </c>
       <c r="C292">
-        <v>18.92666046577046</v>
+        <v>18.4432380124965</v>
       </c>
       <c r="D292">
-        <v>28.50194942847865</v>
+        <v>28.54913291125878</v>
       </c>
       <c r="E292">
-        <v>7.017465277117717</v>
+        <v>6.547194927415091</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -6528,16 +6528,16 @@
         <v>296</v>
       </c>
       <c r="B293">
-        <v>5.337859966582632</v>
+        <v>5.113231248524944</v>
       </c>
       <c r="C293">
-        <v>19.33963342209665</v>
+        <v>18.45843947858837</v>
       </c>
       <c r="D293">
-        <v>28.22836181500502</v>
+        <v>29.6090667303876</v>
       </c>
       <c r="E293">
-        <v>7.470394925343584</v>
+        <v>6.541489532925798</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -6545,16 +6545,16 @@
         <v>297</v>
       </c>
       <c r="B294">
-        <v>5.683321196556666</v>
+        <v>5.119054273851331</v>
       </c>
       <c r="C294">
-        <v>18.520552458625</v>
+        <v>18.10993587345384</v>
       </c>
       <c r="D294">
-        <v>28.3784794842277</v>
+        <v>28.65752536452252</v>
       </c>
       <c r="E294">
-        <v>6.656452660564672</v>
+        <v>6.601082085934888</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -6562,16 +6562,16 @@
         <v>298</v>
       </c>
       <c r="B295">
-        <v>6.296387772101221</v>
+        <v>5.212639787044225</v>
       </c>
       <c r="C295">
-        <v>18.35139325206421</v>
+        <v>18.12083890203879</v>
       </c>
       <c r="D295">
-        <v>28.37048238307101</v>
+        <v>28.68689167218865</v>
       </c>
       <c r="E295">
-        <v>7.0002322906592</v>
+        <v>6.689305589340414</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -6579,16 +6579,16 @@
         <v>299</v>
       </c>
       <c r="B296">
-        <v>6.054924781806807</v>
+        <v>5.132564769592836</v>
       </c>
       <c r="C296">
-        <v>19.3249708113727</v>
+        <v>18.5461515019404</v>
       </c>
       <c r="D296">
-        <v>28.56448064550423</v>
+        <v>28.89136522555918</v>
       </c>
       <c r="E296">
-        <v>7.611408069108784</v>
+        <v>6.591370177434941</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -6596,16 +6596,16 @@
         <v>300</v>
       </c>
       <c r="B297">
-        <v>6.609625932508848</v>
+        <v>5.199666318491683</v>
       </c>
       <c r="C297">
-        <v>18.49850864530034</v>
+        <v>18.11308688217159</v>
       </c>
       <c r="D297">
-        <v>28.61130988514159</v>
+        <v>28.40507876257242</v>
       </c>
       <c r="E297">
-        <v>8.092043162412915</v>
+        <v>6.61077538112747</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -6613,16 +6613,16 @@
         <v>301</v>
       </c>
       <c r="B298">
-        <v>5.583264248234356</v>
+        <v>5.122556007352618</v>
       </c>
       <c r="C298">
-        <v>19.10598598248799</v>
+        <v>18.5464561822676</v>
       </c>
       <c r="D298">
-        <v>28.56150653534035</v>
+        <v>29.22115076883523</v>
       </c>
       <c r="E298">
-        <v>7.584935650455321</v>
+        <v>6.573650344532309</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -6630,16 +6630,16 @@
         <v>302</v>
       </c>
       <c r="B299">
-        <v>6.787811373079495</v>
+        <v>5.194297226367679</v>
       </c>
       <c r="C299">
-        <v>19.23489190083724</v>
+        <v>18.5403259098033</v>
       </c>
       <c r="D299">
-        <v>28.64859285682265</v>
+        <v>29.15768035597664</v>
       </c>
       <c r="E299">
-        <v>7.628532513404781</v>
+        <v>6.610122113178114</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -6647,16 +6647,16 @@
         <v>303</v>
       </c>
       <c r="B300">
-        <v>5.960914231674408</v>
+        <v>5.108408434837764</v>
       </c>
       <c r="C300">
-        <v>19.18619777120673</v>
+        <v>18.42488830612726</v>
       </c>
       <c r="D300">
-        <v>28.63289269997727</v>
+        <v>29.07956535525142</v>
       </c>
       <c r="E300">
-        <v>6.673517139827679</v>
+        <v>6.648731707360384</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -6664,16 +6664,16 @@
         <v>304</v>
       </c>
       <c r="B301">
-        <v>5.369386154782705</v>
+        <v>5.189775216298778</v>
       </c>
       <c r="C301">
-        <v>19.14945844242789</v>
+        <v>18.52844740149814</v>
       </c>
       <c r="D301">
-        <v>28.3177590234648</v>
+        <v>29.05693913488363</v>
       </c>
       <c r="E301">
-        <v>7.752362264280141</v>
+        <v>6.5714535301372</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -6681,16 +6681,16 @@
         <v>305</v>
       </c>
       <c r="B302">
-        <v>5.262084846577031</v>
+        <v>5.20305054372416</v>
       </c>
       <c r="C302">
-        <v>18.67192712399134</v>
+        <v>18.48596862256886</v>
       </c>
       <c r="D302">
-        <v>28.42105623052227</v>
+        <v>28.9330025195977</v>
       </c>
       <c r="E302">
-        <v>7.361823027152166</v>
+        <v>6.66189030975135</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -6698,16 +6698,16 @@
         <v>306</v>
       </c>
       <c r="B303">
-        <v>5.253048923402311</v>
+        <v>5.174055460866834</v>
       </c>
       <c r="C303">
-        <v>18.11272286345916</v>
+        <v>18.18546438249386</v>
       </c>
       <c r="D303">
-        <v>28.63894329169189</v>
+        <v>29.71325134536338</v>
       </c>
       <c r="E303">
-        <v>6.566744907435417</v>
+        <v>6.59584182905583</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -6715,16 +6715,16 @@
         <v>307</v>
       </c>
       <c r="B304">
-        <v>6.016337620687828</v>
+        <v>5.122240365325113</v>
       </c>
       <c r="C304">
-        <v>18.60576022649295</v>
+        <v>18.36605909738805</v>
       </c>
       <c r="D304">
-        <v>28.24626508724235</v>
+        <v>28.6528551624258</v>
       </c>
       <c r="E304">
-        <v>7.777028672242245</v>
+        <v>6.639979760717684</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -6732,16 +6732,16 @@
         <v>308</v>
       </c>
       <c r="B305">
-        <v>6.486340756946477</v>
+        <v>5.105756753071621</v>
       </c>
       <c r="C305">
-        <v>19.46548654226419</v>
+        <v>18.38982682077983</v>
       </c>
       <c r="D305">
-        <v>28.38283580405391</v>
+        <v>29.18223733115641</v>
       </c>
       <c r="E305">
-        <v>6.618238365873006</v>
+        <v>6.698042379661258</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -6749,16 +6749,16 @@
         <v>309</v>
       </c>
       <c r="B306">
-        <v>5.842402373108475</v>
+        <v>5.203284635999976</v>
       </c>
       <c r="C306">
-        <v>18.46924026170744</v>
+        <v>18.22243028485471</v>
       </c>
       <c r="D306">
-        <v>28.48884561736527</v>
+        <v>29.28861640022281</v>
       </c>
       <c r="E306">
-        <v>7.321072544351201</v>
+        <v>6.562398451566471</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -6766,16 +6766,16 @@
         <v>310</v>
       </c>
       <c r="B307">
-        <v>6.75276432862411</v>
+        <v>5.168101999811433</v>
       </c>
       <c r="C307">
-        <v>18.44740724764925</v>
+        <v>18.36518376238944</v>
       </c>
       <c r="D307">
-        <v>28.39289330532046</v>
+        <v>29.02589685258586</v>
       </c>
       <c r="E307">
-        <v>7.481615039308116</v>
+        <v>6.639197251959644</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -6783,16 +6783,16 @@
         <v>311</v>
       </c>
       <c r="B308">
-        <v>6.883827077306542</v>
+        <v>5.177907136600778</v>
       </c>
       <c r="C308">
-        <v>19.11555710802022</v>
+        <v>18.25180442586453</v>
       </c>
       <c r="D308">
-        <v>28.18049374912476</v>
+        <v>28.44361781553925</v>
       </c>
       <c r="E308">
-        <v>6.652330560653048</v>
+        <v>6.702560910599508</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -6800,16 +6800,16 @@
         <v>312</v>
       </c>
       <c r="B309">
-        <v>5.15801100768448</v>
+        <v>5.107032270859462</v>
       </c>
       <c r="C309">
-        <v>18.51230673919949</v>
+        <v>18.11812311970199</v>
       </c>
       <c r="D309">
-        <v>28.5682577426327</v>
+        <v>29.43426866948401</v>
       </c>
       <c r="E309">
-        <v>7.427433577570913</v>
+        <v>6.631324139795555</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -6817,16 +6817,16 @@
         <v>313</v>
       </c>
       <c r="B310">
-        <v>6.216634846505078</v>
+        <v>5.171343751150038</v>
       </c>
       <c r="C310">
-        <v>18.74063879814315</v>
+        <v>18.20434131471147</v>
       </c>
       <c r="D310">
-        <v>28.57318243223585</v>
+        <v>28.48065817551941</v>
       </c>
       <c r="E310">
-        <v>7.213940938115249</v>
+        <v>6.551862882537288</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -6834,16 +6834,16 @@
         <v>314</v>
       </c>
       <c r="B311">
-        <v>5.561216665219147</v>
+        <v>5.101878363960235</v>
       </c>
       <c r="C311">
-        <v>19.34842654663246</v>
+        <v>18.28792407041773</v>
       </c>
       <c r="D311">
-        <v>28.41723438482775</v>
+        <v>28.93955480254031</v>
       </c>
       <c r="E311">
-        <v>7.803425919960302</v>
+        <v>6.569974213777121</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -6851,16 +6851,16 @@
         <v>315</v>
       </c>
       <c r="B312">
-        <v>5.269481381994282</v>
+        <v>5.143795744471636</v>
       </c>
       <c r="C312">
-        <v>18.47760114724568</v>
+        <v>18.25727286359549</v>
       </c>
       <c r="D312">
-        <v>28.38345734663984</v>
+        <v>29.24937125995497</v>
       </c>
       <c r="E312">
-        <v>6.636473207333238</v>
+        <v>6.653668288066489</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -6868,16 +6868,16 @@
         <v>316</v>
       </c>
       <c r="B313">
-        <v>6.446363565616045</v>
+        <v>5.158551774534602</v>
       </c>
       <c r="C313">
-        <v>18.92171679294643</v>
+        <v>18.34028985359944</v>
       </c>
       <c r="D313">
-        <v>28.44685479561498</v>
+        <v>29.06884671644088</v>
       </c>
       <c r="E313">
-        <v>7.758859831954037</v>
+        <v>6.592383904785637</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -6885,16 +6885,16 @@
         <v>317</v>
       </c>
       <c r="B314">
-        <v>6.834693293563322</v>
+        <v>5.182116639311975</v>
       </c>
       <c r="C314">
-        <v>18.41176215017631</v>
+        <v>18.51231352357679</v>
       </c>
       <c r="D314">
-        <v>28.56371688137525</v>
+        <v>28.23706304160211</v>
       </c>
       <c r="E314">
-        <v>7.588907340732635</v>
+        <v>6.589672131107831</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -6902,16 +6902,16 @@
         <v>318</v>
       </c>
       <c r="B315">
-        <v>5.934874385895887</v>
+        <v>5.164839800965545</v>
       </c>
       <c r="C315">
-        <v>19.45917305588965</v>
+        <v>18.12416769696525</v>
       </c>
       <c r="D315">
-        <v>28.33535599038608</v>
+        <v>29.44463603345875</v>
       </c>
       <c r="E315">
-        <v>6.849177302410776</v>
+        <v>6.683870272225954</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6919,16 +6919,16 @@
         <v>319</v>
       </c>
       <c r="B316">
-        <v>6.671471891441284</v>
+        <v>5.17812366574523</v>
       </c>
       <c r="C316">
-        <v>18.77872773168262</v>
+        <v>18.29972222716542</v>
       </c>
       <c r="D316">
-        <v>28.44830357848051</v>
+        <v>29.45552195350911</v>
       </c>
       <c r="E316">
-        <v>7.989294308776024</v>
+        <v>6.626977136763391</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -6936,16 +6936,16 @@
         <v>320</v>
       </c>
       <c r="B317">
-        <v>5.889547450485222</v>
+        <v>5.167247890506973</v>
       </c>
       <c r="C317">
-        <v>19.64306303144643</v>
+        <v>18.31029333706621</v>
       </c>
       <c r="D317">
-        <v>28.55603983141656</v>
+        <v>28.92646760243812</v>
       </c>
       <c r="E317">
-        <v>7.195064424985899</v>
+        <v>6.5485993612742</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -6953,16 +6953,16 @@
         <v>321</v>
       </c>
       <c r="B318">
-        <v>5.885548264453496</v>
+        <v>5.18432119357105</v>
       </c>
       <c r="C318">
-        <v>19.49340390744296</v>
+        <v>18.52644592403619</v>
       </c>
       <c r="D318">
-        <v>28.53327510941455</v>
+        <v>29.54341305704479</v>
       </c>
       <c r="E318">
-        <v>8.126832299801004</v>
+        <v>6.549005757903528</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -6970,16 +6970,16 @@
         <v>322</v>
       </c>
       <c r="B319">
-        <v>5.737166491174807</v>
+        <v>5.172775703176159</v>
       </c>
       <c r="C319">
-        <v>18.27897121724055</v>
+        <v>18.20815258824518</v>
       </c>
       <c r="D319">
-        <v>28.22627233621961</v>
+        <v>28.29065892647439</v>
       </c>
       <c r="E319">
-        <v>7.823284454076495</v>
+        <v>6.556974865523107</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6987,16 +6987,16 @@
         <v>323</v>
       </c>
       <c r="B320">
-        <v>6.519242847785632</v>
+        <v>5.172504564939295</v>
       </c>
       <c r="C320">
-        <v>18.38037034311565</v>
+        <v>18.14604641556968</v>
       </c>
       <c r="D320">
-        <v>28.6237068789556</v>
+        <v>28.20986557118487</v>
       </c>
       <c r="E320">
-        <v>8.110263582615735</v>
+        <v>6.655766839335993</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -7004,16 +7004,16 @@
         <v>324</v>
       </c>
       <c r="B321">
-        <v>5.402922555191099</v>
+        <v>5.128834784668427</v>
       </c>
       <c r="C321">
-        <v>19.2445677955615</v>
+        <v>18.23775346622794</v>
       </c>
       <c r="D321">
-        <v>28.57514062294054</v>
+        <v>28.40943629662033</v>
       </c>
       <c r="E321">
-        <v>7.572500152692552</v>
+        <v>6.588292237308197</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -7021,16 +7021,16 @@
         <v>325</v>
       </c>
       <c r="B322">
-        <v>6.592423893350261</v>
+        <v>5.164525522094131</v>
       </c>
       <c r="C322">
-        <v>18.18987323525844</v>
+        <v>18.32424002265872</v>
       </c>
       <c r="D322">
-        <v>28.63466592963875</v>
+        <v>28.33092054175607</v>
       </c>
       <c r="E322">
-        <v>8.075720485671644</v>
+        <v>6.639549968804555</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -7038,16 +7038,16 @@
         <v>326</v>
       </c>
       <c r="B323">
-        <v>6.256500548891822</v>
+        <v>5.18950347883422</v>
       </c>
       <c r="C323">
-        <v>18.17501376560747</v>
+        <v>18.31287564773697</v>
       </c>
       <c r="D323">
-        <v>28.1938423185012</v>
+        <v>28.75298138867924</v>
       </c>
       <c r="E323">
-        <v>7.940316639791622</v>
+        <v>6.695591004468948</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -7055,16 +7055,16 @@
         <v>327</v>
       </c>
       <c r="B324">
-        <v>6.446727965181978</v>
+        <v>5.158392389700854</v>
       </c>
       <c r="C324">
-        <v>18.12498598550416</v>
+        <v>18.35759764156177</v>
       </c>
       <c r="D324">
-        <v>28.31219684632033</v>
+        <v>29.09802921873472</v>
       </c>
       <c r="E324">
-        <v>7.029520136171021</v>
+        <v>6.695063778284311</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -7072,16 +7072,16 @@
         <v>328</v>
       </c>
       <c r="B325">
-        <v>5.67410479921272</v>
+        <v>5.150492181453155</v>
       </c>
       <c r="C325">
-        <v>19.64233150496812</v>
+        <v>18.23785745501856</v>
       </c>
       <c r="D325">
-        <v>28.35368000375519</v>
+        <v>28.32997425433991</v>
       </c>
       <c r="E325">
-        <v>7.251498990423834</v>
+        <v>6.605376585694218</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -7089,16 +7089,16 @@
         <v>329</v>
       </c>
       <c r="B326">
-        <v>5.879128210620213</v>
+        <v>5.177700953820264</v>
       </c>
       <c r="C326">
-        <v>19.4448983854217</v>
+        <v>18.21519102665088</v>
       </c>
       <c r="D326">
-        <v>28.48413796498826</v>
+        <v>29.20049013322594</v>
       </c>
       <c r="E326">
-        <v>8.050163402890364</v>
+        <v>6.631145929375907</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -7106,16 +7106,16 @@
         <v>330</v>
       </c>
       <c r="B327">
-        <v>6.542505498995856</v>
+        <v>5.127405869881053</v>
       </c>
       <c r="C327">
-        <v>19.69013216848086</v>
+        <v>18.28682651045697</v>
       </c>
       <c r="D327">
-        <v>28.61247269978954</v>
+        <v>29.42301072229004</v>
       </c>
       <c r="E327">
-        <v>6.599910052222246</v>
+        <v>6.593842386720895</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -7123,16 +7123,16 @@
         <v>331</v>
       </c>
       <c r="B328">
-        <v>6.307992740118235</v>
+        <v>5.158396165898249</v>
       </c>
       <c r="C328">
-        <v>19.48082279864087</v>
+        <v>18.36671123114304</v>
       </c>
       <c r="D328">
-        <v>28.40784417917718</v>
+        <v>29.27245956544868</v>
       </c>
       <c r="E328">
-        <v>7.520279321199107</v>
+        <v>6.647065454397302</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -7140,16 +7140,16 @@
         <v>332</v>
       </c>
       <c r="B329">
-        <v>6.50547059841349</v>
+        <v>5.156116555747137</v>
       </c>
       <c r="C329">
-        <v>18.7485651548139</v>
+        <v>18.34289376544723</v>
       </c>
       <c r="D329">
-        <v>28.53990154954938</v>
+        <v>28.71250805671581</v>
       </c>
       <c r="E329">
-        <v>8.083366629799945</v>
+        <v>6.616187729641797</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -7157,16 +7157,16 @@
         <v>333</v>
       </c>
       <c r="B330">
-        <v>2.343325322243685</v>
+        <v>1.873684239314836</v>
       </c>
       <c r="C330">
-        <v>6.96881465699109</v>
+        <v>5.946791977021442</v>
       </c>
       <c r="D330">
-        <v>58.13718672357489</v>
+        <v>58.14649845331883</v>
       </c>
       <c r="E330">
-        <v>2.071010844904865</v>
+        <v>1.267762986733639</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -7174,16 +7174,16 @@
         <v>334</v>
       </c>
       <c r="B331">
-        <v>3.470305399962826</v>
+        <v>1.894193805086764</v>
       </c>
       <c r="C331">
-        <v>5.954909987064802</v>
+        <v>6.072390154580368</v>
       </c>
       <c r="D331">
-        <v>58.19114517031176</v>
+        <v>58.04297622622881</v>
       </c>
       <c r="E331">
-        <v>2.408553026347066</v>
+        <v>1.249795971613139</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -7191,16 +7191,16 @@
         <v>335</v>
       </c>
       <c r="B332">
-        <v>1.850060104043005</v>
+        <v>1.876675319518512</v>
       </c>
       <c r="C332">
-        <v>6.10687993946776</v>
+        <v>6.290564766012124</v>
       </c>
       <c r="D332">
-        <v>58.24637701398861</v>
+        <v>58.94747168951636</v>
       </c>
       <c r="E332">
-        <v>2.532309605524716</v>
+        <v>1.338150506659048</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -7208,16 +7208,16 @@
         <v>336</v>
       </c>
       <c r="B333">
-        <v>2.202996433026629</v>
+        <v>1.794757932815675</v>
       </c>
       <c r="C333">
-        <v>6.377011110566653</v>
+        <v>6.311597705696991</v>
       </c>
       <c r="D333">
-        <v>58.12050116445409</v>
+        <v>58.49679342429682</v>
       </c>
       <c r="E333">
-        <v>2.304905037993365</v>
+        <v>1.366860645055909</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -7225,16 +7225,16 @@
         <v>337</v>
       </c>
       <c r="B334">
-        <v>2.220588858592683</v>
+        <v>1.813448862890296</v>
       </c>
       <c r="C334">
-        <v>6.660237253103874</v>
+        <v>5.97777630108</v>
       </c>
       <c r="D334">
-        <v>57.90223097555567</v>
+        <v>57.8374398984903</v>
       </c>
       <c r="E334">
-        <v>2.737742904373149</v>
+        <v>1.381317805057503</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -7242,16 +7242,16 @@
         <v>338</v>
       </c>
       <c r="B335">
-        <v>3.388038483295766</v>
+        <v>1.80127953655974</v>
       </c>
       <c r="C335">
-        <v>6.09657921085509</v>
+        <v>5.990311292515143</v>
       </c>
       <c r="D335">
-        <v>58.10947691948299</v>
+        <v>58.11699357359273</v>
       </c>
       <c r="E335">
-        <v>2.75759967381064</v>
+        <v>1.361894074599714</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -7259,16 +7259,16 @@
         <v>339</v>
       </c>
       <c r="B336">
-        <v>2.002357541680854</v>
+        <v>1.850087113517741</v>
       </c>
       <c r="C336">
-        <v>6.698200904080614</v>
+        <v>5.957282950795319</v>
       </c>
       <c r="D336">
-        <v>57.79557147761256</v>
+        <v>58.39090092872346</v>
       </c>
       <c r="E336">
-        <v>2.1119131777268</v>
+        <v>1.353157739406062</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -7276,16 +7276,16 @@
         <v>340</v>
       </c>
       <c r="B337">
-        <v>2.686225396648948</v>
+        <v>1.808190271613153</v>
       </c>
       <c r="C337">
-        <v>7.296316360430994</v>
+        <v>6.245852138962563</v>
       </c>
       <c r="D337">
-        <v>57.96084203505233</v>
+        <v>58.62721280790446</v>
       </c>
       <c r="E337">
-        <v>2.216102648580483</v>
+        <v>1.373360847211267</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -7293,16 +7293,16 @@
         <v>341</v>
       </c>
       <c r="B338">
-        <v>3.127784911635852</v>
+        <v>1.880205365927537</v>
       </c>
       <c r="C338">
-        <v>7.339301218091759</v>
+        <v>5.929047684853517</v>
       </c>
       <c r="D338">
-        <v>58.18640128816071</v>
+        <v>58.35526537160698</v>
       </c>
       <c r="E338">
-        <v>2.152448921410712</v>
+        <v>1.343228889123252</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -7310,16 +7310,16 @@
         <v>342</v>
       </c>
       <c r="B339">
-        <v>2.674522819573613</v>
+        <v>1.78886394538791</v>
       </c>
       <c r="C339">
-        <v>7.128943370068285</v>
+        <v>6.290522630137434</v>
       </c>
       <c r="D339">
-        <v>57.9001423553509</v>
+        <v>58.55810186157657</v>
       </c>
       <c r="E339">
-        <v>2.027611390262563</v>
+        <v>1.344084784716904</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -7327,16 +7327,16 @@
         <v>343</v>
       </c>
       <c r="B340">
-        <v>1.810098645518141</v>
+        <v>1.837501820967345</v>
       </c>
       <c r="C340">
-        <v>6.699796892977931</v>
+        <v>6.367633821640619</v>
       </c>
       <c r="D340">
-        <v>58.1831055579171</v>
+        <v>58.80585592254948</v>
       </c>
       <c r="E340">
-        <v>2.720653445328441</v>
+        <v>1.390297216651198</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -7344,16 +7344,16 @@
         <v>344</v>
       </c>
       <c r="B341">
-        <v>3.48027992158928</v>
+        <v>1.782429085963204</v>
       </c>
       <c r="C341">
-        <v>5.988591689308641</v>
+        <v>6.073269363321738</v>
       </c>
       <c r="D341">
-        <v>58.23655736616602</v>
+        <v>58.96930706537145</v>
       </c>
       <c r="E341">
-        <v>1.2739340302571</v>
+        <v>1.385931394830968</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -7361,16 +7361,16 @@
         <v>345</v>
       </c>
       <c r="B342">
-        <v>3.288718798974151</v>
+        <v>1.887970965978392</v>
       </c>
       <c r="C342">
-        <v>5.997328897412688</v>
+        <v>6.341411792680834</v>
       </c>
       <c r="D342">
-        <v>58.1949988343023</v>
+        <v>58.32866933773923</v>
       </c>
       <c r="E342">
-        <v>2.237321078172034</v>
+        <v>1.36881214684288</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -7378,16 +7378,16 @@
         <v>346</v>
       </c>
       <c r="B343">
-        <v>2.770279066588513</v>
+        <v>1.826485179308106</v>
       </c>
       <c r="C343">
-        <v>7.254135158157158</v>
+        <v>5.964366465293652</v>
       </c>
       <c r="D343">
-        <v>58.03811734371667</v>
+        <v>58.59799740886942</v>
       </c>
       <c r="E343">
-        <v>1.858546236038383</v>
+        <v>1.350380035695901</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -7395,16 +7395,16 @@
         <v>347</v>
       </c>
       <c r="B344">
-        <v>3.396810645040886</v>
+        <v>1.882937968244212</v>
       </c>
       <c r="C344">
-        <v>6.595390731949374</v>
+        <v>6.055029636295737</v>
       </c>
       <c r="D344">
-        <v>57.90085690509354</v>
+        <v>58.92931675296057</v>
       </c>
       <c r="E344">
-        <v>2.197265517842157</v>
+        <v>1.263957889619467</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -7412,16 +7412,16 @@
         <v>348</v>
       </c>
       <c r="B345">
-        <v>1.901696898428362</v>
+        <v>1.780525949391578</v>
       </c>
       <c r="C345">
-        <v>6.544494982979786</v>
+        <v>5.964232956376563</v>
       </c>
       <c r="D345">
-        <v>57.93099446407611</v>
+        <v>59.00042025216339</v>
       </c>
       <c r="E345">
-        <v>1.911956734931438</v>
+        <v>1.390306740197608</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -7429,16 +7429,16 @@
         <v>349</v>
       </c>
       <c r="B346">
-        <v>3.390228396845751</v>
+        <v>1.886617745721373</v>
       </c>
       <c r="C346">
-        <v>7.129809196533892</v>
+        <v>6.099635607825003</v>
       </c>
       <c r="D346">
-        <v>57.903271408651</v>
+        <v>58.45376014958777</v>
       </c>
       <c r="E346">
-        <v>1.394461641545885</v>
+        <v>1.325576820634784</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -7446,16 +7446,16 @@
         <v>350</v>
       </c>
       <c r="B347">
-        <v>2.341669845148152</v>
+        <v>1.891515591935628</v>
       </c>
       <c r="C347">
-        <v>6.095188992336217</v>
+        <v>6.096355353819244</v>
       </c>
       <c r="D347">
-        <v>58.21460540899444</v>
+        <v>57.85260106120966</v>
       </c>
       <c r="E347">
-        <v>2.761997865342707</v>
+        <v>1.305918140269496</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -7463,16 +7463,16 @@
         <v>351</v>
       </c>
       <c r="B348">
-        <v>2.9929120016221</v>
+        <v>1.820737717831599</v>
       </c>
       <c r="C348">
-        <v>6.108149521671093</v>
+        <v>5.917821552641217</v>
       </c>
       <c r="D348">
-        <v>58.0102881740326</v>
+        <v>58.12178823726906</v>
       </c>
       <c r="E348">
-        <v>2.300446993109568</v>
+        <v>1.297221260982983</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -7480,16 +7480,16 @@
         <v>352</v>
       </c>
       <c r="B349">
-        <v>2.476096930337412</v>
+        <v>1.831287839147036</v>
       </c>
       <c r="C349">
-        <v>7.068456776355251</v>
+        <v>6.103351683489452</v>
       </c>
       <c r="D349">
-        <v>58.07733859008275</v>
+        <v>58.31042396293955</v>
       </c>
       <c r="E349">
-        <v>1.526404931179601</v>
+        <v>1.395077430606836</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -7497,16 +7497,16 @@
         <v>353</v>
       </c>
       <c r="B350">
-        <v>3.543073627144441</v>
+        <v>1.836583857539779</v>
       </c>
       <c r="C350">
-        <v>6.492610414006073</v>
+        <v>6.238024575259836</v>
       </c>
       <c r="D350">
-        <v>57.84396330306958</v>
+        <v>58.29401789229166</v>
       </c>
       <c r="E350">
-        <v>1.49996107303451</v>
+        <v>1.378688162292646</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -7514,16 +7514,16 @@
         <v>354</v>
       </c>
       <c r="B351">
-        <v>1.983174296600106</v>
+        <v>1.792075024854968</v>
       </c>
       <c r="C351">
-        <v>6.70497107844289</v>
+        <v>5.967207747686882</v>
       </c>
       <c r="D351">
-        <v>58.10946555049797</v>
+        <v>59.00973478959307</v>
       </c>
       <c r="E351">
-        <v>1.64038150732678</v>
+        <v>1.248657883254071</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -7531,16 +7531,16 @@
         <v>355</v>
       </c>
       <c r="B352">
-        <v>2.737465107020927</v>
+        <v>1.789862593069817</v>
       </c>
       <c r="C352">
-        <v>5.939681651826493</v>
+        <v>6.182900855856729</v>
       </c>
       <c r="D352">
-        <v>57.83879002828157</v>
+        <v>58.31462037787947</v>
       </c>
       <c r="E352">
-        <v>2.617214379136229</v>
+        <v>1.293705238241675</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -7548,16 +7548,16 @@
         <v>356</v>
       </c>
       <c r="B353">
-        <v>2.128691713653114</v>
+        <v>1.892827837685525</v>
       </c>
       <c r="C353">
-        <v>6.040700262090636</v>
+        <v>5.935752464610302</v>
       </c>
       <c r="D353">
-        <v>57.81331972643605</v>
+        <v>57.82987347779945</v>
       </c>
       <c r="E353">
-        <v>2.786005251912078</v>
+        <v>1.351575634188062</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -7565,16 +7565,16 @@
         <v>357</v>
       </c>
       <c r="B354">
-        <v>1.987261758491428</v>
+        <v>1.895636335547505</v>
       </c>
       <c r="C354">
-        <v>6.356462274784429</v>
+        <v>6.044269749113233</v>
       </c>
       <c r="D354">
-        <v>58.26119307162146</v>
+        <v>58.66467040019703</v>
       </c>
       <c r="E354">
-        <v>2.739928230122291</v>
+        <v>1.407475999811044</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -7582,16 +7582,16 @@
         <v>358</v>
       </c>
       <c r="B355">
-        <v>2.238947788414885</v>
+        <v>1.800260081726477</v>
       </c>
       <c r="C355">
-        <v>6.412705351738104</v>
+        <v>6.399534712334114</v>
       </c>
       <c r="D355">
-        <v>58.01498061861685</v>
+        <v>58.03267285953624</v>
       </c>
       <c r="E355">
-        <v>1.403910915694736</v>
+        <v>1.364860632956251</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -7599,16 +7599,16 @@
         <v>359</v>
       </c>
       <c r="B356">
-        <v>2.068140647776926</v>
+        <v>1.885379285798903</v>
       </c>
       <c r="C356">
-        <v>7.031950665161464</v>
+        <v>6.001092329185375</v>
       </c>
       <c r="D356">
-        <v>58.0038167544206</v>
+        <v>58.06404252438561</v>
       </c>
       <c r="E356">
-        <v>1.741067759573201</v>
+        <v>1.390488955506793</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -7616,16 +7616,16 @@
         <v>360</v>
       </c>
       <c r="B357">
-        <v>2.389639205437371</v>
+        <v>1.877142635677094</v>
       </c>
       <c r="C357">
-        <v>6.428187933886387</v>
+        <v>6.061658262274609</v>
       </c>
       <c r="D357">
-        <v>58.17424176372633</v>
+        <v>59.02584236785765</v>
       </c>
       <c r="E357">
-        <v>2.609509257068564</v>
+        <v>1.34139064328488</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -7633,16 +7633,16 @@
         <v>361</v>
       </c>
       <c r="B358">
-        <v>2.407408728093169</v>
+        <v>1.858087901658586</v>
       </c>
       <c r="C358">
-        <v>7.076690505582791</v>
+        <v>5.94037785355108</v>
       </c>
       <c r="D358">
-        <v>58.0863655341683</v>
+        <v>58.67275182074624</v>
       </c>
       <c r="E358">
-        <v>1.6098825298359</v>
+        <v>1.305179668872761</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -7650,16 +7650,16 @@
         <v>362</v>
       </c>
       <c r="B359">
-        <v>2.011224599391169</v>
+        <v>1.893959104819187</v>
       </c>
       <c r="C359">
-        <v>6.066653451885794</v>
+        <v>6.315414975777583</v>
       </c>
       <c r="D359">
-        <v>57.83287790674516</v>
+        <v>58.33364406456923</v>
       </c>
       <c r="E359">
-        <v>2.672587076121449</v>
+        <v>1.365212118974665</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -7667,16 +7667,16 @@
         <v>363</v>
       </c>
       <c r="B360">
-        <v>3.102776577712884</v>
+        <v>1.829974314157162</v>
       </c>
       <c r="C360">
-        <v>7.018841209446395</v>
+        <v>5.934566876310406</v>
       </c>
       <c r="D360">
-        <v>57.94033205398348</v>
+        <v>57.84702179497978</v>
       </c>
       <c r="E360">
-        <v>1.6189531471843</v>
+        <v>1.35220435298299</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -7684,16 +7684,16 @@
         <v>364</v>
       </c>
       <c r="B361">
-        <v>1.98956356896746</v>
+        <v>1.80671311944785</v>
       </c>
       <c r="C361">
-        <v>6.984442132826088</v>
+        <v>6.194725596420136</v>
       </c>
       <c r="D361">
-        <v>58.07491261957747</v>
+        <v>58.10837772445532</v>
       </c>
       <c r="E361">
-        <v>1.910613856934994</v>
+        <v>1.384467566088038</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -7701,16 +7701,16 @@
         <v>365</v>
       </c>
       <c r="B362">
-        <v>3.465481825210373</v>
+        <v>1.859294082780296</v>
       </c>
       <c r="C362">
-        <v>6.864518494696225</v>
+        <v>6.209347709612583</v>
       </c>
       <c r="D362">
-        <v>57.96811036555017</v>
+        <v>58.72435130134029</v>
       </c>
       <c r="E362">
-        <v>2.319742591335978</v>
+        <v>1.34999070354824</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -7718,16 +7718,16 @@
         <v>366</v>
       </c>
       <c r="B363">
-        <v>1.955813486597399</v>
+        <v>1.84685412381223</v>
       </c>
       <c r="C363">
-        <v>5.952177333312663</v>
+        <v>6.070488955101887</v>
       </c>
       <c r="D363">
-        <v>58.05896011610051</v>
+        <v>59.17907611988748</v>
       </c>
       <c r="E363">
-        <v>2.728496510475883</v>
+        <v>1.304105060183072</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -7735,16 +7735,16 @@
         <v>367</v>
       </c>
       <c r="B364">
-        <v>3.168502130672663</v>
+        <v>1.890562846132147</v>
       </c>
       <c r="C364">
-        <v>6.078266083049139</v>
+        <v>6.003457796824387</v>
       </c>
       <c r="D364">
-        <v>57.92727365475018</v>
+        <v>59.1595429761372</v>
       </c>
       <c r="E364">
-        <v>2.396733675217214</v>
+        <v>1.368958507774662</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -7752,16 +7752,16 @@
         <v>368</v>
       </c>
       <c r="B365">
-        <v>2.166049287576784</v>
+        <v>1.7944671023502</v>
       </c>
       <c r="C365">
-        <v>7.350674375856366</v>
+        <v>6.213801855354308</v>
       </c>
       <c r="D365">
-        <v>58.27297056404498</v>
+        <v>58.92369008030018</v>
       </c>
       <c r="E365">
-        <v>1.894805097831195</v>
+        <v>1.402662576744999</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -7769,16 +7769,16 @@
         <v>369</v>
       </c>
       <c r="B366">
-        <v>3.259843946006528</v>
+        <v>1.813066747909119</v>
       </c>
       <c r="C366">
-        <v>7.354348035681607</v>
+        <v>6.399333718716045</v>
       </c>
       <c r="D366">
-        <v>58.08441718625371</v>
+        <v>58.54747578413158</v>
       </c>
       <c r="E366">
-        <v>2.243650406639776</v>
+        <v>1.362684348490704</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -7786,16 +7786,16 @@
         <v>370</v>
       </c>
       <c r="B367">
-        <v>3.343542272300159</v>
+        <v>1.780598002835418</v>
       </c>
       <c r="C367">
-        <v>6.978967678445544</v>
+        <v>5.917565107782246</v>
       </c>
       <c r="D367">
-        <v>58.01370294992238</v>
+        <v>58.73896373822502</v>
       </c>
       <c r="E367">
-        <v>1.761022869198678</v>
+        <v>1.279102175767843</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -7803,16 +7803,16 @@
         <v>371</v>
       </c>
       <c r="B368">
-        <v>3.178628625605569</v>
+        <v>1.816771423733054</v>
       </c>
       <c r="C368">
-        <v>6.951104099244311</v>
+        <v>6.341823399312251</v>
       </c>
       <c r="D368">
-        <v>57.99481448826121</v>
+        <v>58.58207391375422</v>
       </c>
       <c r="E368">
-        <v>1.246762083263791</v>
+        <v>1.361406662930178</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -7820,16 +7820,16 @@
         <v>372</v>
       </c>
       <c r="B369">
-        <v>3.109789158130881</v>
+        <v>1.837406048180495</v>
       </c>
       <c r="C369">
-        <v>6.367772712396107</v>
+        <v>6.133443400508877</v>
       </c>
       <c r="D369">
-        <v>58.19688557777448</v>
+        <v>59.22657578894962</v>
       </c>
       <c r="E369">
-        <v>1.672636540424344</v>
+        <v>1.299573202273698</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -7837,16 +7837,16 @@
         <v>373</v>
       </c>
       <c r="B370">
-        <v>2.536698549437127</v>
+        <v>1.802493392704799</v>
       </c>
       <c r="C370">
-        <v>7.095452298852829</v>
+        <v>6.15797658054184</v>
       </c>
       <c r="D370">
-        <v>58.24328098578555</v>
+        <v>58.88735602360892</v>
       </c>
       <c r="E370">
-        <v>2.10896278408769</v>
+        <v>1.341073148000594</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -7854,16 +7854,16 @@
         <v>374</v>
       </c>
       <c r="B371">
-        <v>2.505342590243917</v>
+        <v>1.791034086963369</v>
       </c>
       <c r="C371">
-        <v>6.473997206779689</v>
+        <v>6.377968157294824</v>
       </c>
       <c r="D371">
-        <v>58.27009708303456</v>
+        <v>59.11846740286381</v>
       </c>
       <c r="E371">
-        <v>2.217356694291221</v>
+        <v>1.322635812199009</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -7871,16 +7871,16 @@
         <v>375</v>
       </c>
       <c r="B372">
-        <v>3.563232963183729</v>
+        <v>1.837329564186873</v>
       </c>
       <c r="C372">
-        <v>6.600276915970052</v>
+        <v>6.188956753413865</v>
       </c>
       <c r="D372">
-        <v>57.98013778599235</v>
+        <v>58.6491394036586</v>
       </c>
       <c r="E372">
-        <v>1.452520808610792</v>
+        <v>1.34218399250147</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -7888,16 +7888,16 @@
         <v>376</v>
       </c>
       <c r="B373">
-        <v>2.036698736466347</v>
+        <v>1.784790780982919</v>
       </c>
       <c r="C373">
-        <v>6.870287691308622</v>
+        <v>6.054733859089953</v>
       </c>
       <c r="D373">
-        <v>58.00167395642011</v>
+        <v>58.19923443507233</v>
       </c>
       <c r="E373">
-        <v>1.467703914274658</v>
+        <v>1.390523268866315</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -7905,16 +7905,16 @@
         <v>377</v>
       </c>
       <c r="B374">
-        <v>2.397237165621834</v>
+        <v>1.824148657921396</v>
       </c>
       <c r="C374">
-        <v>5.982444953636688</v>
+        <v>6.273992058665488</v>
       </c>
       <c r="D374">
-        <v>58.12547932735964</v>
+        <v>58.81468647445517</v>
       </c>
       <c r="E374">
-        <v>2.150505145142154</v>
+        <v>1.351959497772427</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -7922,16 +7922,16 @@
         <v>378</v>
       </c>
       <c r="B375">
-        <v>2.649421614340422</v>
+        <v>1.862430083289287</v>
       </c>
       <c r="C375">
-        <v>6.588021859987575</v>
+        <v>6.048214236731114</v>
       </c>
       <c r="D375">
-        <v>58.07858061879863</v>
+        <v>58.05920705275674</v>
       </c>
       <c r="E375">
-        <v>2.496145253219095</v>
+        <v>1.338765112766238</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7939,16 +7939,16 @@
         <v>379</v>
       </c>
       <c r="B376">
-        <v>3.53575158456356</v>
+        <v>1.782446895566974</v>
       </c>
       <c r="C376">
-        <v>6.113351028208506</v>
+        <v>6.099808646412241</v>
       </c>
       <c r="D376">
-        <v>58.11867759615075</v>
+        <v>58.54857182239959</v>
       </c>
       <c r="E376">
-        <v>2.605053824434794</v>
+        <v>1.325780259357367</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -7956,16 +7956,16 @@
         <v>380</v>
       </c>
       <c r="B377">
-        <v>3.482590964295596</v>
+        <v>1.895535381812438</v>
       </c>
       <c r="C377">
-        <v>6.517627999254693</v>
+        <v>6.304391635008217</v>
       </c>
       <c r="D377">
-        <v>58.19725859636795</v>
+        <v>59.19075115907152</v>
       </c>
       <c r="E377">
-        <v>1.643491697078324</v>
+        <v>1.322093533733318</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -7973,16 +7973,16 @@
         <v>381</v>
       </c>
       <c r="B378">
-        <v>3.482797085802679</v>
+        <v>1.860382051054341</v>
       </c>
       <c r="C378">
-        <v>6.159915094637825</v>
+        <v>6.067676694388363</v>
       </c>
       <c r="D378">
-        <v>58.25817957931489</v>
+        <v>58.39950172704068</v>
       </c>
       <c r="E378">
-        <v>1.263120555864907</v>
+        <v>1.333729582232921</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7990,16 +7990,16 @@
         <v>382</v>
       </c>
       <c r="B379">
-        <v>2.184088110025487</v>
+        <v>1.824317405106731</v>
       </c>
       <c r="C379">
-        <v>7.15480187641616</v>
+        <v>6.24262200119124</v>
       </c>
       <c r="D379">
-        <v>58.11082170286671</v>
+        <v>57.96111372831519</v>
       </c>
       <c r="E379">
-        <v>1.339218550329786</v>
+        <v>1.374426694636579</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -8007,16 +8007,16 @@
         <v>383</v>
       </c>
       <c r="B380">
-        <v>2.603487623161131</v>
+        <v>1.81091467725855</v>
       </c>
       <c r="C380">
-        <v>7.13955288088765</v>
+        <v>6.117405745594813</v>
       </c>
       <c r="D380">
-        <v>58.19713612354678</v>
+        <v>58.63971580944815</v>
       </c>
       <c r="E380">
-        <v>1.418163223490505</v>
+        <v>1.387635682822441</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -8024,16 +8024,16 @@
         <v>384</v>
       </c>
       <c r="B381">
-        <v>2.387423928107646</v>
+        <v>1.871024361584816</v>
       </c>
       <c r="C381">
-        <v>6.118487767614454</v>
+        <v>5.93787815361776</v>
       </c>
       <c r="D381">
-        <v>57.90579332347016</v>
+        <v>58.00552527987873</v>
       </c>
       <c r="E381">
-        <v>2.819634264160586</v>
+        <v>1.366493218974072</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -8041,16 +8041,16 @@
         <v>385</v>
       </c>
       <c r="B382">
-        <v>1.967258698598893</v>
+        <v>1.794703220296439</v>
       </c>
       <c r="C382">
-        <v>6.977333331736995</v>
+        <v>6.045274453107285</v>
       </c>
       <c r="D382">
-        <v>58.19152205810811</v>
+        <v>58.78408257819493</v>
       </c>
       <c r="E382">
-        <v>2.8164791838967</v>
+        <v>1.248539322857868</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -8058,16 +8058,16 @@
         <v>386</v>
       </c>
       <c r="B383">
-        <v>1.959111612852306</v>
+        <v>1.85548997484713</v>
       </c>
       <c r="C383">
-        <v>6.574814135362229</v>
+        <v>6.171338785306985</v>
       </c>
       <c r="D383">
-        <v>57.96011691359259</v>
+        <v>57.91504971955055</v>
       </c>
       <c r="E383">
-        <v>2.178185673320046</v>
+        <v>1.341764349308128</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -8075,16 +8075,16 @@
         <v>387</v>
       </c>
       <c r="B384">
-        <v>2.313387276342652</v>
+        <v>1.824493242553559</v>
       </c>
       <c r="C384">
-        <v>6.100648026435664</v>
+        <v>6.019788040016071</v>
       </c>
       <c r="D384">
-        <v>58.08932612099753</v>
+        <v>57.83173814892816</v>
       </c>
       <c r="E384">
-        <v>2.460918583706643</v>
+        <v>1.318354071462292</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -8092,16 +8092,16 @@
         <v>388</v>
       </c>
       <c r="B385">
-        <v>2.31342799942759</v>
+        <v>1.884938058512209</v>
       </c>
       <c r="C385">
-        <v>6.238173780437291</v>
+        <v>6.167672625749404</v>
       </c>
       <c r="D385">
-        <v>58.12671013076669</v>
+        <v>59.01659564497129</v>
       </c>
       <c r="E385">
-        <v>1.305946785316249</v>
+        <v>1.267621842776552</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -8109,16 +8109,16 @@
         <v>389</v>
       </c>
       <c r="B386">
-        <v>1.828391522406631</v>
+        <v>1.803180209729278</v>
       </c>
       <c r="C386">
-        <v>6.698236379311282</v>
+        <v>5.943239409274571</v>
       </c>
       <c r="D386">
-        <v>58.20852617525416</v>
+        <v>59.06496397210545</v>
       </c>
       <c r="E386">
-        <v>1.6962249397543</v>
+        <v>1.3294886476757</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -8126,16 +8126,16 @@
         <v>390</v>
       </c>
       <c r="B387">
-        <v>3.500197525411643</v>
+        <v>1.852368462856438</v>
       </c>
       <c r="C387">
-        <v>6.684917218249571</v>
+        <v>6.018675576572133</v>
       </c>
       <c r="D387">
-        <v>57.85564305398159</v>
+        <v>58.01670610546379</v>
       </c>
       <c r="E387">
-        <v>1.833810084369308</v>
+        <v>1.346629393554032</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -8143,16 +8143,16 @@
         <v>391</v>
       </c>
       <c r="B388">
-        <v>2.120329528679945</v>
+        <v>1.785059522756365</v>
       </c>
       <c r="C388">
-        <v>5.953919181823043</v>
+        <v>5.918742939205385</v>
       </c>
       <c r="D388">
-        <v>58.26722110249236</v>
+        <v>58.95345931929595</v>
       </c>
       <c r="E388">
-        <v>1.779773782849449</v>
+        <v>1.289768421036863</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -8160,16 +8160,16 @@
         <v>392</v>
       </c>
       <c r="B389">
-        <v>2.030106194429405</v>
+        <v>1.894811304387962</v>
       </c>
       <c r="C389">
-        <v>6.826772518899678</v>
+        <v>6.240626682393854</v>
       </c>
       <c r="D389">
-        <v>58.2190454816331</v>
+        <v>59.09200542523632</v>
       </c>
       <c r="E389">
-        <v>2.553725193716797</v>
+        <v>1.363354824624887</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -8177,16 +8177,16 @@
         <v>393</v>
       </c>
       <c r="B390">
-        <v>3.37804573283643</v>
+        <v>1.842435398408413</v>
       </c>
       <c r="C390">
-        <v>6.28031555551028</v>
+        <v>6.078824928285822</v>
       </c>
       <c r="D390">
-        <v>57.99810121862598</v>
+        <v>58.17836793654708</v>
       </c>
       <c r="E390">
-        <v>2.442782393995746</v>
+        <v>1.264772777736116</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -8194,16 +8194,16 @@
         <v>394</v>
       </c>
       <c r="B391">
-        <v>2.693658710938186</v>
+        <v>1.826164563905156</v>
       </c>
       <c r="C391">
-        <v>7.281803434613223</v>
+        <v>6.228010764077686</v>
       </c>
       <c r="D391">
-        <v>58.21770938492449</v>
+        <v>58.93609504547705</v>
       </c>
       <c r="E391">
-        <v>2.60817118868443</v>
+        <v>1.364030826528665</v>
       </c>
     </row>
   </sheetData>
